--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE869809-1E14-4F87-A1D4-5481D7E654EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69AD922-5F2F-4434-8574-E7A4E650C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,7 +809,7 @@
     <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="9.5" customWidth="1"/>
     <col min="8" max="8" width="23.375" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="17.625" customWidth="1"/>
     <col min="10" max="10" width="28.625" customWidth="1"/>
     <col min="11" max="11" width="20.625" customWidth="1"/>
     <col min="12" max="12" width="19.75" customWidth="1"/>
@@ -1127,7 +1127,7 @@
         <v>100101</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69AD922-5F2F-4434-8574-E7A4E650C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45280811-98B7-4ED1-9B98-4DC7DB55E390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -280,115 +280,129 @@
     <t>gameType</t>
   </si>
   <si>
+    <t>modelId</t>
+  </si>
+  <si>
+    <t>spinType</t>
+  </si>
+  <si>
+    <t>extraBet</t>
+  </si>
+  <si>
+    <t>spinStatus</t>
+  </si>
+  <si>
+    <t>element</t>
+  </si>
+  <si>
+    <t>notReplaceEle</t>
+  </si>
+  <si>
+    <t>bigBlockSize</t>
+  </si>
+  <si>
+    <t>randCount</t>
+  </si>
+  <si>
+    <t>afterUpdateValid</t>
+  </si>
+  <si>
+    <t>girdSizeLimit</t>
+  </si>
+  <si>
+    <t>notExistValid</t>
+  </si>
+  <si>
+    <t>extra</t>
+  </si>
+  <si>
+    <t>syncGird</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
+  </si>
+  <si>
+    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
+  </si>
+  <si>
+    <t>选择拉火车，转出触发局</t>
+  </si>
+  <si>
+    <t>18,1;15,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>19,1;20,1;21,1;22,1;16,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,1-2-3-4,1;15,5,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1;17,1,1;18,1,1;19,1,1;20,1,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;list&lt;string&gt;{,}&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map&lt;int{,}int&gt;{;}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>affectGird</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1;2,1;3,1;4,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递"/utf8修改出美元图标收集&gt;&gt;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>girdUpdateType</t>
-  </si>
-  <si>
-    <t>modelId</t>
-  </si>
-  <si>
-    <t>spinType</t>
-  </si>
-  <si>
-    <t>extraBet</t>
-  </si>
-  <si>
-    <t>spinStatus</t>
-  </si>
-  <si>
-    <t>element</t>
-  </si>
-  <si>
-    <t>notReplaceEle</t>
-  </si>
-  <si>
-    <t>bigBlockSize</t>
-  </si>
-  <si>
-    <t>randCount</t>
-  </si>
-  <si>
-    <t>afterUpdateValid</t>
-  </si>
-  <si>
-    <t>girdSizeLimit</t>
-  </si>
-  <si>
-    <t>notExistValid</t>
-  </si>
-  <si>
-    <t>extra</t>
-  </si>
-  <si>
-    <t>syncGird</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
-  </si>
-  <si>
-    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
-  </si>
-  <si>
-    <t>选择拉火车，转出触发局</t>
-  </si>
-  <si>
-    <t>18,1;15,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>19,1;20,1;21,1;22,1;16,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,1-2-3-4,1;15,5,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1;17,1,1;18,1,1;19,1,1;20,1,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;list&lt;string&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>affectGird</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>[12,13,14,15,16,17,18,19,20,21,22]</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1;4,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8修改出美元图标收集&gt;&gt;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,13,14,15,16,17,18,19,20,21,22</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{,}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递"/utf8修改出黄金列车&gt;&gt;</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -901,17 +915,19 @@
         <v>19</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="J2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>20</v>
@@ -933,49 +949,49 @@
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -1024,40 +1040,38 @@
         <v>3</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
@@ -1083,40 +1097,38 @@
         <v>3</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="M6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="S6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
@@ -1124,7 +1136,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1">
-        <v>100101</v>
+        <v>100100</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -1142,39 +1154,96 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>45</v>
+      <c r="L7" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="R7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S7" s="1"/>
+    </row>
+    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="1"/>
+      <c r="M8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45280811-98B7-4ED1-9B98-4DC7DB55E390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B219617-DA09-49B3-9CC9-F6BF028A5528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,10 +378,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>0,1;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;&lt;"美元快递"/utf8修改出美元图标收集&gt;&gt;</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -403,6 +399,10 @@
   </si>
   <si>
     <t>&lt;&lt;"美元快递"/utf8修改出黄金列车&gt;&gt;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,20;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +918,7 @@
         <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>46</v>
@@ -949,7 +949,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>22</v>
@@ -1157,16 +1157,16 @@
         <v>49</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S7" s="1"/>
     </row>
@@ -1214,16 +1214,16 @@
         <v>49</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>1</v>
@@ -1241,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S8" s="1"/>
     </row>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B219617-DA09-49B3-9CC9-F6BF028A5528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AC6A1A-636C-417E-904D-ACDABD16DA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1100,7 +1100,7 @@
         <v>41</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K6" s="1" t="s">

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AC6A1A-636C-417E-904D-ACDABD16DA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BAE9A7-C2F2-4202-A610-3BFA03E10917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -403,6 +403,10 @@
   </si>
   <si>
     <t>0,20;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递1"/utf8&gt;&gt;</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1068,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>38</v>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BAE9A7-C2F2-4202-A610-3BFA03E10917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B30724-355B-4627-9B46-43F390038A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,8 @@
             <charset val="134"/>
           </rPr>
           <t>0. 随机多种组合元素不同位置
-1  指定元素替换随机元素位置</t>
+1  指定元素替换随机元素位置
+2  指定元素替换随机元素位置1</t>
         </r>
       </text>
     </comment>
@@ -212,7 +213,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -398,15 +399,23 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;&lt;"美元快递"/utf8修改出黄金列车&gt;&gt;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>0,20;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>&lt;&lt;"美元快递1"/utf8&gt;&gt;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1;4,1;5,1;6,1;7,1;8,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递"/utf8重转修改出黄金列车触发局&gt;&gt;</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;&lt;"美元快递"/utf8普通修改出黄金列车&gt;&gt;</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -819,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -1072,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>38</v>
@@ -1167,7 +1176,7 @@
         <v>50</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>53</v>
@@ -1224,7 +1233,7 @@
         <v>50</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>53</v>
@@ -1245,9 +1254,66 @@
         <v>1</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B30724-355B-4627-9B46-43F390038A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
+    <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
@@ -29,42 +37,38 @@
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0. 随机多种组合元素不同位置
-1  指定元素替换随机元素位置
-2  指定元素替换随机元素位置1</t>
+1  指定元素替换随机元素位置</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0默认包含所有模式</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -117,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -125,7 +129,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">pgos:
@@ -136,7 +139,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1.普通
@@ -146,14 +148,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="3">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po8zhaojinglei:</t>
@@ -162,7 +163,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -170,14 +170,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="4">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -186,7 +185,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -194,13 +192,38 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">次数:权重;次数:权重;
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">格子ID,权重,次数;格子ID,权重,次数;
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
           <t>是，为前端不需要展示变化过程；
@@ -213,7 +236,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="120">
   <si>
     <t>id</t>
   </si>
@@ -278,9 +301,24 @@
     <t>bool</t>
   </si>
   <si>
+    <t>Map&lt;int{,}int&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{,}</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;string&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
+  </si>
+  <si>
     <t>gameType</t>
   </si>
   <si>
+    <t>girdUpdateType</t>
+  </si>
+  <si>
     <t>modelId</t>
   </si>
   <si>
@@ -305,6 +343,9 @@
     <t>randCount</t>
   </si>
   <si>
+    <t>affectGird</t>
+  </si>
+  <si>
     <t>afterUpdateValid</t>
   </si>
   <si>
@@ -320,110 +361,254 @@
     <t>syncGird</t>
   </si>
   <si>
+    <t>18,1;15,1</t>
+  </si>
+  <si>
+    <t>18,1-2-3-4,1;15,5,1</t>
+  </si>
+  <si>
+    <t>2,1;3,18;4,15;5,6;6,1</t>
+  </si>
+  <si>
+    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1;17,1,1;18,1,1;19,1,1;20,1,1</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
-  </si>
-  <si>
     <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
   </si>
   <si>
     <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
   </si>
   <si>
+    <t>19,1;20,1;21,1;22,1;16,1</t>
+  </si>
+  <si>
+    <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
+  </si>
+  <si>
     <t>选择拉火车，转出触发局</t>
   </si>
   <si>
-    <t>18,1;15,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>19,1;20,1;21,1;22,1;16,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,1-2-3-4,1;15,5,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1;17,1,1;18,1,1;19,1,1;20,1,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;list&lt;string&gt;{,}&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>affectGird</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>18,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,13,14,15,16,17,18,19,20,21,22</t>
   </si>
   <si>
     <t>1,1;2,1;3,1;4,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8修改出美元图标收集&gt;&gt;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>girdUpdateType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,110;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
   </si>
   <si>
     <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>12,13,14,15,16,17,18,19,20,21,22</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;int&gt;{,}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,20;1,1;2,2;3,1;4,1;5,1;6,1;7,1;8,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递1"/utf8&gt;&gt;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1;4,1;5,1;6,1;7,1;8,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8重转修改出黄金列车触发局&gt;&gt;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8普通修改出黄金列车&gt;&gt;</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改出美元图标收集</t>
+  </si>
+  <si>
+    <t>普通修改出黄金列车</t>
+  </si>
+  <si>
+    <t>4,1;5,1;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>重转修改出黄金列车触发局</t>
+  </si>
+  <si>
+    <t>0,120;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>0,150;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>0,200;1,1;2,10;3,10;4,3;5,1;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>0,350;1,1;2,10;3,10;4,5;5,1;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>0,450;1,1;2,10;3,10;4,5;5,1;6,1;7,1;8,1</t>
+  </si>
+  <si>
+    <t>格子修改</t>
+  </si>
+  <si>
+    <t>typeID</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>随机多种组合元素不同位置</t>
+  </si>
+  <si>
+    <t>美元快递拉火车</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>指定元素替换随机元素位置</t>
+  </si>
+  <si>
+    <t>美元快递改出美元钞票、重转改出黄金列车触发局</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>指定元素替换随机元素位置1</t>
+  </si>
+  <si>
+    <t>美元快递改出美元钞票、普通改出黄金列车触发局</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
+    <t>重转</t>
+  </si>
+  <si>
+    <t>选择标识</t>
+  </si>
+  <si>
+    <t>扩展旋转</t>
+  </si>
+  <si>
+    <t>通用免费1</t>
+  </si>
+  <si>
+    <t>通用免费2</t>
+  </si>
+  <si>
+    <t>通用免费3</t>
+  </si>
+  <si>
+    <t>通用免费4</t>
+  </si>
+  <si>
+    <t>通用免费5</t>
+  </si>
+  <si>
+    <t>通用免费6</t>
+  </si>
+  <si>
+    <t>通用免费7</t>
+  </si>
+  <si>
+    <t>通用免费8</t>
+  </si>
+  <si>
+    <t>通用免费9</t>
+  </si>
+  <si>
+    <t>通用免费10</t>
+  </si>
+  <si>
+    <t>通用免费11</t>
+  </si>
+  <si>
+    <t>通用免费12</t>
+  </si>
+  <si>
+    <t>通用免费13</t>
+  </si>
+  <si>
+    <t>通用免费14</t>
+  </si>
+  <si>
+    <t>通用免费15</t>
+  </si>
+  <si>
+    <t>通用免费16</t>
+  </si>
+  <si>
+    <t>免费1</t>
+  </si>
+  <si>
+    <t>通用重转1</t>
+  </si>
+  <si>
+    <t>通用重转2</t>
+  </si>
+  <si>
+    <t>通用重转3</t>
+  </si>
+  <si>
+    <t>通用重转4</t>
+  </si>
+  <si>
+    <t>通用重转5</t>
+  </si>
+  <si>
+    <t>通用重转6</t>
+  </si>
+  <si>
+    <t>通用重转7</t>
+  </si>
+  <si>
+    <t>通用重转8</t>
+  </si>
+  <si>
+    <t>通用重转9</t>
+  </si>
+  <si>
+    <t>通用重转10</t>
+  </si>
+  <si>
+    <t>通用重转11</t>
+  </si>
+  <si>
+    <t>通用重转12</t>
+  </si>
+  <si>
+    <t>通用普通1</t>
+  </si>
+  <si>
+    <t>通用普通2</t>
+  </si>
+  <si>
+    <t>通用普通3</t>
+  </si>
+  <si>
+    <t>通用普通4</t>
+  </si>
+  <si>
+    <t>通用普通5</t>
+  </si>
+  <si>
+    <t>通用普通6</t>
+  </si>
+  <si>
+    <t>通用普通7</t>
+  </si>
+  <si>
+    <t>通用普通8</t>
+  </si>
+  <si>
+    <t>通用普通9</t>
+  </si>
+  <si>
+    <t>通用普通10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,34 +620,166 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -470,40 +787,210 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -511,42 +998,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 12 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 80" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 12 10" xfId="49"/>
+    <cellStyle name="常规 73" xfId="50"/>
+    <cellStyle name="常规 80" xfId="51"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -556,18 +1330,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -822,14 +1586,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -846,7 +1610,7 @@
     <col min="17" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -905,7 +1669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -927,20 +1691,20 @@
       <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>47</v>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>20</v>
@@ -954,62 +1718,62 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" hidden="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" hidden="1" spans="1:19">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1030,7 +1794,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="16.5" spans="1:19">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1052,42 +1816,42 @@
       <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>40</v>
+      <c r="H5" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="M5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:19">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1109,42 +1873,42 @@
       <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>41</v>
+      <c r="H6" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="1" t="s">
         <v>44</v>
       </c>
       <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:19">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1155,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1167,41 +1931,43 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" ht="16.5" spans="1:19">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1224,41 +1990,43 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:19">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1266,7 +2034,7 @@
         <v>100100</v>
       </c>
       <c r="C9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1278,56 +2046,844 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:19">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="s">
+      <c r="K10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:19">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="S9" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:19">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:19">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:19">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:19">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G1 G4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4">
       <formula1>"普通,免费,重转,全部"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="5" max="5" width="23.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -1,34 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81231D9-282C-4318-94E2-CCE51942EB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
@@ -37,13 +30,14 @@
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0. 随机多种组合元素不同位置
@@ -51,24 +45,26 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0默认包含所有模式</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -121,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="2">
+    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -129,6 +125,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">pgos:
@@ -139,6 +136,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1.普通
@@ -148,13 +146,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="3">
+    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po8zhaojinglei:</t>
@@ -163,6 +162,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -170,13 +170,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="4">
+    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -185,6 +186,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -192,12 +194,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">次数:权重;次数:权重;
@@ -205,12 +208,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">格子ID,权重,次数;格子ID,权重,次数;
@@ -218,12 +222,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>是，为前端不需要展示变化过程；
@@ -236,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="121">
   <si>
     <t>id</t>
   </si>
@@ -596,19 +601,17 @@
   </si>
   <si>
     <t>通用普通10</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,166 +623,26 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -787,210 +650,41 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -998,329 +692,39 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 12 10" xfId="49"/>
-    <cellStyle name="常规 73" xfId="50"/>
-    <cellStyle name="常规 80" xfId="51"/>
+    <cellStyle name="常规 12 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 80" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1329,6 +733,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1586,14 +993,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -1610,7 +1017,7 @@
     <col min="17" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:19">
+    <row r="1" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1669,7 +1076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:19">
+    <row r="2" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1718,7 +1125,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:19">
+    <row r="3" spans="1:19" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1773,7 +1180,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:19">
+    <row r="4" spans="1:19" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1794,7 +1201,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:19">
+    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1851,7 +1258,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:19">
+    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1908,7 +1315,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:19">
+    <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1940,7 +1347,7 @@
         <v>53</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>55</v>
@@ -1967,7 +1374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:19">
+    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1975,7 +1382,7 @@
         <v>100100</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -1987,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>51</v>
@@ -1999,7 +1406,7 @@
         <v>53</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>55</v>
@@ -2026,7 +1433,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:19">
+    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -2046,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>51</v>
@@ -2085,7 +1492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:19">
+    <row r="10" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -2144,7 +1551,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:19">
+    <row r="11" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -2203,7 +1610,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:19">
+    <row r="12" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -2262,7 +1669,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:19">
+    <row r="13" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -2321,7 +1728,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:19">
+    <row r="14" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>10</v>
       </c>
@@ -2380,7 +1787,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:19">
+    <row r="15" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>11</v>
       </c>
@@ -2440,32 +1847,31 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G1 G4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"普通,免费,重转,全部"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -2473,7 +1879,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -2487,7 +1893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -2504,7 +1910,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2521,7 +1927,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2538,7 +1944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2546,7 +1952,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
@@ -2554,7 +1960,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2562,7 +1968,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2570,7 +1976,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2578,7 +1984,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
@@ -2586,7 +1992,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2594,7 +2000,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
@@ -2602,7 +2008,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
@@ -2610,7 +2016,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
@@ -2618,7 +2024,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
@@ -2626,7 +2032,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
@@ -2634,7 +2040,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
@@ -2642,7 +2048,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
@@ -2650,7 +2056,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
@@ -2658,7 +2064,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
@@ -2666,7 +2072,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
@@ -2674,7 +2080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
@@ -2682,7 +2088,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>21</v>
       </c>
@@ -2690,7 +2096,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
@@ -2698,7 +2104,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
@@ -2706,7 +2112,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
@@ -2714,7 +2120,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
@@ -2722,7 +2128,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
@@ -2730,7 +2136,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
@@ -2738,7 +2144,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
@@ -2746,7 +2152,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
@@ -2754,7 +2160,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
@@ -2762,7 +2168,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
@@ -2770,7 +2176,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>32</v>
       </c>
@@ -2778,7 +2184,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>33</v>
       </c>
@@ -2786,7 +2192,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>34</v>
       </c>
@@ -2794,7 +2200,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>35</v>
       </c>
@@ -2802,7 +2208,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>36</v>
       </c>
@@ -2810,7 +2216,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>37</v>
       </c>
@@ -2818,7 +2224,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>38</v>
       </c>
@@ -2826,7 +2232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>39</v>
       </c>
@@ -2834,7 +2240,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2842,7 +2248,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41</v>
       </c>
@@ -2850,7 +2256,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>42</v>
       </c>
@@ -2858,7 +2264,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
@@ -2866,7 +2272,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>44</v>
       </c>
@@ -2874,7 +2280,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>45</v>
       </c>
@@ -2883,7 +2289,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -1,27 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81231D9-282C-4318-94E2-CCE51942EB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
@@ -30,14 +37,13 @@
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0. 随机多种组合元素不同位置
@@ -45,26 +51,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0默认包含所有模式</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -117,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -125,7 +129,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">pgos:
@@ -136,7 +139,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1.普通
@@ -146,14 +148,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="3">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po8zhaojinglei:</t>
@@ -162,7 +163,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -170,14 +170,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="4">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -186,7 +185,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -194,13 +192,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">次数:权重;次数:权重;
@@ -208,13 +205,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">格子ID,权重,次数;格子ID,权重,次数;
@@ -222,13 +218,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>是，为前端不需要展示变化过程；
@@ -241,7 +236,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="117">
   <si>
     <t>id</t>
   </si>
@@ -393,6 +388,9 @@
     <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
   </si>
   <si>
+    <t>2,1;3,18;4,10</t>
+  </si>
+  <si>
     <t>选择拉火车，转出触发局</t>
   </si>
   <si>
@@ -423,19 +421,7 @@
     <t>重转修改出黄金列车触发局</t>
   </si>
   <si>
-    <t>0,120;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>0,150;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>0,200;1,1;2,10;3,10;4,3;5,1;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>0,350;1,1;2,10;3,10;4,5;5,1;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>0,450;1,1;2,10;3,10;4,5;5,1;6,1;7,1;8,1</t>
+    <t>2,1;3,18;4,8</t>
   </si>
   <si>
     <t>格子修改</t>
@@ -601,17 +587,19 @@
   </si>
   <si>
     <t>通用普通10</t>
-  </si>
-  <si>
-    <t>0,1;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,26 +611,166 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -650,41 +778,210 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -692,39 +989,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 12 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 73" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 80" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 12 10" xfId="49"/>
+    <cellStyle name="常规 73" xfId="50"/>
+    <cellStyle name="常规 80" xfId="51"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -733,9 +1320,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -993,14 +1577,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -1017,7 +1601,7 @@
     <col min="17" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="16.5" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" ht="16.5" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1125,7 +1709,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" hidden="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1180,7 +1764,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" hidden="1" spans="1:19">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1201,7 +1785,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="16.5" spans="1:19">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1258,7 +1842,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" ht="16.5" spans="1:19">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1288,7 +1872,7 @@
         <v>49</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>44</v>
@@ -1312,10 +1896,10 @@
         <v>46</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:19">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1338,19 +1922,19 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>1</v>
@@ -1371,10 +1955,10 @@
         <v>46</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:19">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1382,7 +1966,7 @@
         <v>100100</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -1394,22 +1978,22 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>1</v>
@@ -1430,10 +2014,10 @@
         <v>46</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:19">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1453,22 +2037,22 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M9" s="1" t="b">
         <v>1</v>
@@ -1489,10 +2073,10 @@
         <v>46</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:19">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1515,19 +2099,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M10" s="1" t="b">
         <v>1</v>
@@ -1548,10 +2132,10 @@
         <v>46</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:19">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1574,19 +2158,19 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M11" s="1" t="b">
         <v>1</v>
@@ -1607,10 +2191,10 @@
         <v>46</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:19">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -1633,19 +2217,19 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="1" t="b">
         <v>1</v>
@@ -1666,10 +2250,10 @@
         <v>46</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:19">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -1692,19 +2276,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M13" s="1" t="b">
         <v>1</v>
@@ -1725,10 +2309,10 @@
         <v>46</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:19">
       <c r="A14" s="3">
         <v>10</v>
       </c>
@@ -1751,19 +2335,19 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M14" s="1" t="b">
         <v>1</v>
@@ -1784,10 +2368,10 @@
         <v>46</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:19">
       <c r="A15" s="3">
         <v>11</v>
       </c>
@@ -1810,19 +2394,19 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M15" s="1" t="b">
         <v>1</v>
@@ -1843,453 +2427,454 @@
         <v>46</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G1 G4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4">
       <formula1>"普通,免费,重转,全部"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -30,125 +30,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>po8zhaojinglei</author>
     <author>Administrator</author>
-    <author>chuge</author>
-    <author/>
-    <author>po8zhaojinglei</author>
-    <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0. 随机多种组合元素不同位置
-1  指定元素替换随机元素位置</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0默认包含所有模式</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">0 全部 
-1 无
-2 普通
-3 免费
-4 重转
-5 选择标识
-6 扩展旋转
-7 通用免费1
-8 通用免费2
-9 通用免费3
-10 通用免费4
-11 通用免费5
-12 通用免费6
-13 通用免费7
-14 通用免费8
-15 通用免费9
-16 通用免费10
-17 通用免费11
-18 通用免费12
-19 通用免费13
-20 通用免费14
-21 通用免费15
-22 通用免费16
-23 免费1
-24 通用重转1
-25 通用重转2
-26 通用重转3
-27 通用重转4
-28 通用重转5
-29 通用重转6
-30 通用重转7
-31 通用重转8
-32 通用重转9
-33 通用重转10
-34 通用重转11
-35 通用重转12
-36 通用普通1
-37 通用普通2
-38 通用普通3
-39 通用普通4
-40 通用普通5
-41 通用普通6
-42 通用普通7
-43 通用普通8
-44 通用普通9
-45 通用普通10
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="2">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">pgos:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1.普通
-2.免费
-3.重转
-4.全部</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="3">
       <text>
         <r>
           <rPr>
@@ -166,33 +52,26 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+需要出现的元素
 格式：[元素ID,权重]</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="4">
+    <comment ref="G1" authorId="1">
       <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>po5lichaoqun:</t>
-        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-格式:[巨型块列数,巨型块行数]</t>
+          <t>格子ID，根据游戏的行列进行排列，先按列排序，再按从左至右
+格子权重，当前权重再所有列表格子权重总和的占比为实际概率
+格子次数：每次随机出一个结构后，此格子次数-1，表示此格子不能再被选中修改</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -205,29 +84,51 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="J1" authorId="1">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">格子ID,权重,次数;格子ID,权重,次数;
-</t>
+          <t>倍率_权重|……倍率_权重|</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="K1" authorId="1">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>是，为前端不需要展示变化过程；
-否，为前端需要展示前后格子变化</t>
+          <t>倍率类型：
+1 单线押分_0
+2 总押分_0
+3 
+4 平均押分_被动游戏ID</t>
         </r>
       </text>
     </comment>
@@ -236,192 +137,279 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="146">
+  <si>
+    <t>小游戏ID</t>
+  </si>
+  <si>
+    <t>游戏ID</t>
+  </si>
+  <si>
+    <t>需要出现的元素图案：权重</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>格子ID_格子权重_格子次数</t>
+  </si>
+  <si>
+    <t>不可替换元素列表</t>
+  </si>
+  <si>
+    <t>随机次数</t>
+  </si>
+  <si>
+    <t>每次修改成功后赋予值</t>
+  </si>
+  <si>
+    <t>每次修改成功后赋予值类型</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Map&lt;int{_}int&gt;{|}</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>游戏ID</t>
-  </si>
-  <si>
-    <t>格式修改算法</t>
-  </si>
-  <si>
-    <t>模式ID</t>
+    <t>gameType</t>
+  </si>
+  <si>
+    <t>element</t>
+  </si>
+  <si>
+    <t>affectGird</t>
+  </si>
+  <si>
+    <t>notReplaceEle</t>
+  </si>
+  <si>
+    <t>randCount</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>valueType</t>
+  </si>
+  <si>
+    <t>常规模式</t>
+  </si>
+  <si>
+    <t>概率出现美元图案18</t>
+  </si>
+  <si>
+    <t>18_1</t>
+  </si>
+  <si>
+    <t>概率出美元图标收集</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1</t>
+  </si>
+  <si>
+    <t>12_13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
+    <t>0_110|2_10|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>5_500|10_2500|15_2000|20_1000|25_800|30_400|50_200|80_50|100_10|150_5|200_0</t>
+  </si>
+  <si>
+    <t>1_0</t>
+  </si>
+  <si>
+    <t>概率出现3个以下免费图案</t>
+  </si>
+  <si>
+    <t>17_1</t>
+  </si>
+  <si>
+    <t>概率出all aboard</t>
+  </si>
+  <si>
+    <t>0_70|1_20|2_10</t>
+  </si>
+  <si>
+    <t>拉火车模式</t>
+  </si>
+  <si>
+    <t>免费-最后一列出现保险箱</t>
+  </si>
+  <si>
+    <t>16_1</t>
+  </si>
+  <si>
+    <t>必然出现保险箱</t>
+  </si>
+  <si>
+    <t>17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>免费-概率出现绿火车</t>
+  </si>
+  <si>
+    <t>19_1</t>
+  </si>
+  <si>
+    <t>必然出现绿火车</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1</t>
+  </si>
+  <si>
+    <t>1_98|2_2</t>
+  </si>
+  <si>
+    <t>免费-概率出现蓝火车</t>
+  </si>
+  <si>
+    <t>20_1</t>
+  </si>
+  <si>
+    <t>概率出现蓝火车</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>0_20|1_78|2_2</t>
+  </si>
+  <si>
+    <t>免费-概率出现紫火车</t>
+  </si>
+  <si>
+    <t>21_1</t>
+  </si>
+  <si>
+    <t>概率出现紫火车</t>
+  </si>
+  <si>
+    <t>9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>0_40|1_58|2_2</t>
+  </si>
+  <si>
+    <t>免费-概率出现红火车</t>
+  </si>
+  <si>
+    <t>22_1</t>
+  </si>
+  <si>
+    <t>概率出现红火车</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1|15_1_1|16_1_1</t>
+  </si>
+  <si>
+    <t>0_60|1_38|2_2</t>
+  </si>
+  <si>
+    <t>必然出现特殊美元图案28（不计入投资）</t>
+  </si>
+  <si>
+    <t>28_1</t>
+  </si>
+  <si>
+    <t>黄金列车模式</t>
+  </si>
+  <si>
+    <t>必然出美元图标收集</t>
+  </si>
+  <si>
+    <t>2_10|3_20|4_10|5_2</t>
+  </si>
+  <si>
+    <t>4_5001003</t>
+  </si>
+  <si>
+    <t>最后一列必出金火车</t>
+  </si>
+  <si>
+    <t>15_1</t>
+  </si>
+  <si>
+    <t>all board(二选一触发局)</t>
+  </si>
+  <si>
+    <t>后四列必然出3个以上免费图案</t>
+  </si>
+  <si>
+    <t>必出3个以上all aboard</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>3_75|4_20|5_5</t>
+  </si>
+  <si>
+    <t>保险箱</t>
+  </si>
+  <si>
+    <t>3_20|4_10|5_2</t>
+  </si>
+  <si>
+    <t>免费模式-触发局|结果库用，实际不会出现</t>
+  </si>
+  <si>
+    <t>出现隐藏图案30（不计入投资）</t>
+  </si>
+  <si>
+    <t>30_1</t>
+  </si>
+  <si>
+    <t>出现隐藏图案</t>
+  </si>
+  <si>
+    <t>必然出现蓝火车</t>
+  </si>
+  <si>
+    <t>必然出现紫火车</t>
+  </si>
+  <si>
+    <t>免费模式-1倍百搭</t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>出现1倍百搭</t>
+  </si>
+  <si>
+    <t>1_30</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1</t>
+  </si>
+  <si>
+    <t>0_15|1_3|2_2</t>
+  </si>
+  <si>
+    <t>必然出3个以上免费图案</t>
+  </si>
+  <si>
+    <t>3_2|4_1</t>
   </si>
   <si>
     <t>旋转标识</t>
-  </si>
-  <si>
-    <t>是否额外投注</t>
-  </si>
-  <si>
-    <t>旋转状态</t>
-  </si>
-  <si>
-    <t>元素</t>
-  </si>
-  <si>
-    <t>不替换元素列表</t>
-  </si>
-  <si>
-    <t>巨型块大小</t>
-  </si>
-  <si>
-    <t>随机次数</t>
-  </si>
-  <si>
-    <t>影响格子</t>
-  </si>
-  <si>
-    <t>是否在别的格子修改后才生效</t>
-  </si>
-  <si>
-    <t>格子大小限制</t>
-  </si>
-  <si>
-    <t>不存在这些元素时才生效</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>是否同步格子</t>
-  </si>
-  <si>
-    <t>游戏名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Map&lt;int{,}int&gt;{;}</t>
-  </si>
-  <si>
-    <t>list&lt;int&gt;{,}</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;string&gt;{,}&gt;{;}</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{,}&gt;{;}</t>
-  </si>
-  <si>
-    <t>gameType</t>
-  </si>
-  <si>
-    <t>girdUpdateType</t>
-  </si>
-  <si>
-    <t>modelId</t>
-  </si>
-  <si>
-    <t>spinType</t>
-  </si>
-  <si>
-    <t>extraBet</t>
-  </si>
-  <si>
-    <t>spinStatus</t>
-  </si>
-  <si>
-    <t>element</t>
-  </si>
-  <si>
-    <t>notReplaceEle</t>
-  </si>
-  <si>
-    <t>bigBlockSize</t>
-  </si>
-  <si>
-    <t>randCount</t>
-  </si>
-  <si>
-    <t>affectGird</t>
-  </si>
-  <si>
-    <t>afterUpdateValid</t>
-  </si>
-  <si>
-    <t>girdSizeLimit</t>
-  </si>
-  <si>
-    <t>notExistValid</t>
-  </si>
-  <si>
-    <t>extra</t>
-  </si>
-  <si>
-    <t>syncGird</t>
-  </si>
-  <si>
-    <t>18,1;15,1</t>
-  </si>
-  <si>
-    <t>18,1-2-3-4,1;15,5,1</t>
-  </si>
-  <si>
-    <t>2,1;3,18;4,15;5,6;6,1</t>
-  </si>
-  <si>
-    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1;17,1,1;18,1,1;19,1,1;20,1,1</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
-  </si>
-  <si>
-    <t>地图全解锁送黄金列车/4个分散，转出触发局</t>
-  </si>
-  <si>
-    <t>19,1;20,1;21,1;22,1;16,1</t>
-  </si>
-  <si>
-    <t>19,1-2-3-4,1;20,1-2-3-4,1;21,1-2-3-4,1;22,1-2-3-4,1;16,5,1</t>
-  </si>
-  <si>
-    <t>2,1;3,18;4,10</t>
-  </si>
-  <si>
-    <t>选择拉火车，转出触发局</t>
-  </si>
-  <si>
-    <t>18,1</t>
-  </si>
-  <si>
-    <t>12,13,14,15,16,17,18,19,20,21,22</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1;4,1</t>
-  </si>
-  <si>
-    <t>0,110;1,1;2,10;3,10;4,5;5,2;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>1,1,1;2,1,1;3,1,1;4,1,1;5,1,1;6,1,1;7,1,1;8,1,1;9,1,1;10,1,1;11,1,1;12,1,1;13,1,1;14,1,1;15,1,1;16,1,1</t>
-  </si>
-  <si>
-    <t>修改出美元图标收集</t>
-  </si>
-  <si>
-    <t>普通修改出黄金列车</t>
-  </si>
-  <si>
-    <t>4,1;5,1;6,1;7,1;8,1</t>
-  </si>
-  <si>
-    <t>重转修改出黄金列车触发局</t>
-  </si>
-  <si>
-    <t>2,1;3,18;4,8</t>
   </si>
   <si>
     <t>格子修改</t>
@@ -599,7 +587,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,9 +602,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
+      <b/>
+      <sz val="11"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -763,12 +761,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -776,23 +768,76 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1105,100 +1150,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1207,10 +1222,10 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1219,10 +1234,10 @@
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1231,27 +1246,171 @@
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1307,15 +1466,6 @@
     <cellStyle name="常规 73" xfId="50"/>
     <cellStyle name="常规 80" xfId="51"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1583,864 +1733,816 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="10.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="9.5" customWidth="1"/>
-    <col min="8" max="8" width="23.375" customWidth="1"/>
-    <col min="9" max="9" width="17.625" customWidth="1"/>
-    <col min="10" max="10" width="28.625" customWidth="1"/>
-    <col min="11" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="19.75" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="17" max="17" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="27.7833333333333" customWidth="1"/>
+    <col min="8" max="8" width="27.625" customWidth="1"/>
+    <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.6166666666667" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:19">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.5" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:11">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:11">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="I3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:19">
-      <c r="A2" s="1" t="s">
+      <c r="J3" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="K3" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="4" ht="16.5" spans="1:11">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="34"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A5" s="1">
+        <v>10010011</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="E5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A6" s="1">
+        <v>10010012</v>
+      </c>
+      <c r="B6" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="D6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="39"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A7" s="1">
+        <v>10010021</v>
+      </c>
+      <c r="B7" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="40"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A8" s="1">
+        <v>10010022</v>
+      </c>
+      <c r="B8" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A9" s="1">
+        <v>10010023</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="41"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A10" s="1">
+        <v>10010024</v>
+      </c>
+      <c r="B10" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A11" s="1">
+        <v>10010025</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="41"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A12" s="1">
+        <v>10010026</v>
+      </c>
+      <c r="B12" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:19">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="G12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="H12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="I12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="J12" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="K12" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A13" s="1">
+        <v>10010031</v>
+      </c>
+      <c r="B13" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A14" s="1">
+        <v>10010032</v>
+      </c>
+      <c r="B14" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A15" s="1">
+        <v>10010041</v>
+      </c>
+      <c r="B15" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="43"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A16" s="1">
+        <v>10010051</v>
+      </c>
+      <c r="B16" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="18"/>
+      <c r="K16" s="44"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A17" s="1">
+        <v>10010052</v>
+      </c>
+      <c r="B17" s="4">
+        <v>100100</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A18" s="21">
+        <v>10010061</v>
+      </c>
+      <c r="B18" s="22">
+        <v>100100</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="21"/>
+      <c r="K18" s="45"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A19" s="2">
+        <v>10010071</v>
+      </c>
+      <c r="B19" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="25"/>
+      <c r="I19" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="46"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A20" s="2">
+        <v>10010072</v>
+      </c>
+      <c r="B20" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="25"/>
+      <c r="I20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="25"/>
+      <c r="K20" s="47"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A21" s="2">
+        <v>10010073</v>
+      </c>
+      <c r="B21" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="25"/>
+      <c r="I21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="25"/>
+      <c r="K21" s="47"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A22" s="2">
+        <v>10010074</v>
+      </c>
+      <c r="B22" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="25"/>
+      <c r="I22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="47"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A23" s="2">
+        <v>10010075</v>
+      </c>
+      <c r="B23" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="25"/>
+      <c r="I23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="47"/>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A24" s="2">
+        <v>10010076</v>
+      </c>
+      <c r="B24" s="25">
+        <v>100100</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A25" s="27">
+        <v>10010091</v>
+      </c>
+      <c r="B25" s="28">
+        <v>100100</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="28"/>
+      <c r="K25" s="48"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A26" s="29">
+        <v>10070011</v>
+      </c>
+      <c r="B26" s="30">
+        <v>100700</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:19">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:19">
-      <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:19">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>25</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:19">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:19">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:19">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:19">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:19">
-      <c r="A11" s="3">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:19">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:19">
-      <c r="A13" s="3">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:19">
-      <c r="A14" s="3">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-      <c r="F14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:19">
-      <c r="A15" s="3">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="E26" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="30"/>
+      <c r="I26" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="J26" s="29"/>
+      <c r="K26" s="49"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A27" s="31">
+        <v>10070021</v>
+      </c>
+      <c r="B27" s="32">
+        <v>100700</v>
+      </c>
+      <c r="C27" s="32"/>
+      <c r="D27" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="32"/>
+      <c r="I27" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" s="31"/>
+      <c r="K27" s="50"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G1 G4">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1 G4">
-      <formula1>"普通,免费,重转,全部"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
@@ -2453,29 +2555,29 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="5" max="5" width="23.75" customWidth="1"/>
+    <col min="5" max="5" width="31.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2483,16 +2585,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2500,16 +2602,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2517,16 +2619,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2534,7 +2636,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2542,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2550,7 +2652,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2558,7 +2660,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2566,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2574,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2582,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2590,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2598,7 +2700,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2606,7 +2708,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2614,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2622,7 +2724,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2630,7 +2732,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2638,7 +2740,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2646,7 +2748,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2654,7 +2756,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2662,7 +2764,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2670,7 +2772,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2678,7 +2780,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2686,7 +2788,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2694,7 +2796,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2702,7 +2804,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2710,7 +2812,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2718,7 +2820,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2726,7 +2828,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2734,7 +2836,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2742,7 +2844,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2750,7 +2852,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2758,7 +2860,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2766,7 +2868,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2774,7 +2876,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2782,7 +2884,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2790,7 +2892,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2798,7 +2900,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2806,7 +2908,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2814,7 +2916,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2822,7 +2924,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2830,7 +2932,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2838,7 +2940,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2846,7 +2948,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2854,7 +2956,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2862,7 +2964,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2870,7 +2972,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="150">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -376,10 +376,22 @@
     <t>出现隐藏图案</t>
   </si>
   <si>
+    <t>1_65|2_35</t>
+  </si>
+  <si>
     <t>必然出现蓝火车</t>
   </si>
   <si>
+    <t>1_75|2_25</t>
+  </si>
+  <si>
     <t>必然出现紫火车</t>
+  </si>
+  <si>
+    <t>1_85|2_15</t>
+  </si>
+  <si>
+    <t>0_40|1_50|2_10</t>
   </si>
   <si>
     <t>免费模式-1倍百搭</t>
@@ -2332,7 +2344,7 @@
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="2" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="J20" s="25"/>
       <c r="K20" s="47"/>
@@ -2354,14 +2366,14 @@
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="J21" s="25"/>
       <c r="K21" s="47"/>
@@ -2383,14 +2395,14 @@
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J22" s="25"/>
       <c r="K22" s="47"/>
@@ -2419,7 +2431,7 @@
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="8" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="J23" s="25"/>
       <c r="K23" s="47"/>
@@ -2468,13 +2480,13 @@
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G25" s="27" t="s">
         <v>71</v>
@@ -2483,7 +2495,7 @@
         <v>26</v>
       </c>
       <c r="I25" s="27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J25" s="28"/>
       <c r="K25" s="48"/>
@@ -2500,17 +2512,17 @@
         <v>30</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F26" s="29" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H26" s="30"/>
       <c r="I26" s="29" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J26" s="29"/>
       <c r="K26" s="49"/>
@@ -2524,20 +2536,20 @@
       </c>
       <c r="C27" s="32"/>
       <c r="D27" s="31" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G27" s="31" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J27" s="31"/>
       <c r="K27" s="50"/>
@@ -2560,24 +2572,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2585,16 +2597,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2602,16 +2614,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2619,16 +2631,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2636,7 +2648,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2644,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2652,7 +2664,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2660,7 +2672,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2668,7 +2680,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2676,7 +2688,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2684,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2692,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2700,7 +2712,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2708,7 +2720,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2716,7 +2728,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2724,7 +2736,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2732,7 +2744,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2740,7 +2752,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2748,7 +2760,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2756,7 +2768,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2764,7 +2776,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2772,7 +2784,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2780,7 +2792,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2788,7 +2800,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2796,7 +2808,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2804,7 +2816,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2812,7 +2824,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2820,7 +2832,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2828,7 +2840,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2836,7 +2848,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2844,7 +2856,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2852,7 +2864,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2860,7 +2872,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2868,7 +2880,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2876,7 +2888,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2884,7 +2896,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2892,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2900,7 +2912,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2908,7 +2920,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2916,7 +2928,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2924,7 +2936,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2932,7 +2944,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2940,7 +2952,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2948,7 +2960,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2956,7 +2968,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2964,7 +2976,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2972,7 +2984,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -127,7 +127,7 @@
           <t>倍率类型：
 1 单线押分_0
 2 总押分_0
-3 
+3 倍率，直接显示，不需要计算
 4 平均押分_被动游戏ID</t>
         </r>
       </text>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="223">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -406,6 +406,57 @@
     <t>1_30</t>
   </si>
   <si>
+    <t>樱桃出现</t>
+  </si>
+  <si>
+    <t>必出出樱桃中奖</t>
+  </si>
+  <si>
+    <t>6_1</t>
+  </si>
+  <si>
+    <t>樱桃中奖</t>
+  </si>
+  <si>
+    <t>2_1_1|5_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>7_8_9_10_99</t>
+  </si>
+  <si>
+    <t>1_10|2_5|3_2</t>
+  </si>
+  <si>
+    <t>樱桃出现_不中奖</t>
+  </si>
+  <si>
+    <t>必出出樱桃_不在中奖线上</t>
+  </si>
+  <si>
+    <t>樱桃</t>
+  </si>
+  <si>
+    <t>1_1_1|3_1_1|4_1_1|6_1_1|7_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>1_10|2_10|3_10|4_10</t>
+  </si>
+  <si>
+    <t>倍数&amp;jackpot百搭出现</t>
+  </si>
+  <si>
+    <t>必出出Wild-倍率-jackpot</t>
+  </si>
+  <si>
+    <t>7_1|8_1|9_1|10_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</t>
+  </si>
+  <si>
+    <t>倍率图标集合&amp;jackpot</t>
+  </si>
+  <si>
+    <t>8_1_1</t>
+  </si>
+  <si>
     <t>10_1</t>
   </si>
   <si>
@@ -419,6 +470,174 @@
   </si>
   <si>
     <t>3_2|4_1</t>
+  </si>
+  <si>
+    <t>随机出大财神-不足5个</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>概率出现5个以下大财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>0_100|1_25|2_20|3_5|4_1</t>
+  </si>
+  <si>
+    <t>必出大财神-5个</t>
+  </si>
+  <si>
+    <t>5_1</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>第1行改为横财神</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>必然出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>4_1_1|7_1_1|10_1_1</t>
+  </si>
+  <si>
+    <t>第2行改为横财神</t>
+  </si>
+  <si>
+    <t>5_1_1|8_1_1|11_1_1</t>
+  </si>
+  <si>
+    <t>第3行改为横财神</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>6_1_1|9_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>正财神</t>
+  </si>
+  <si>
+    <t>第2列改为正财神</t>
+  </si>
+  <si>
+    <t>14_1</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1</t>
+  </si>
+  <si>
+    <t>第3列改为正财神</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第4列改为正财神</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>中央第1行改为wild</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>中央第2行改为wild</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>中央第3行改为wild</t>
+  </si>
+  <si>
+    <t>正财神第2列</t>
+  </si>
+  <si>
+    <t>中央第2列改为wild</t>
+  </si>
+  <si>
+    <t>中央第3列改为wild</t>
+  </si>
+  <si>
+    <t>中央第4列改为wild</t>
+  </si>
+  <si>
+    <t>横财神2次出现</t>
+  </si>
+  <si>
+    <t>概率出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26</t>
+  </si>
+  <si>
+    <t>0_60|1_40</t>
+  </si>
+  <si>
+    <t>23_1</t>
+  </si>
+  <si>
+    <t>正财神2次出现</t>
+  </si>
+  <si>
+    <t>24_1</t>
+  </si>
+  <si>
+    <t>25_1</t>
+  </si>
+  <si>
+    <t>26_1</t>
+  </si>
+  <si>
+    <t>横财神3次出现</t>
+  </si>
+  <si>
+    <t>31_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
+  </si>
+  <si>
+    <t>0_80|1_20</t>
+  </si>
+  <si>
+    <t>32_1</t>
+  </si>
+  <si>
+    <t>33_1</t>
+  </si>
+  <si>
+    <t>正财神3次出现</t>
+  </si>
+  <si>
+    <t>34_1</t>
+  </si>
+  <si>
+    <t>35_1</t>
+  </si>
+  <si>
+    <t>36_1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -773,18 +992,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -805,6 +1024,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -848,6 +1085,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1168,7 +1411,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1192,16 +1435,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1210,25 +1453,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1289,111 +1520,118 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1401,28 +1639,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1745,7 +2000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -1753,148 +2008,148 @@
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="22.125" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="25.1416666666667" customWidth="1"/>
     <col min="7" max="7" width="27.7833333333333" customWidth="1"/>
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="11.6166666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="38" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="41" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="34"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="39"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="7">
         <v>100100</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="43" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1902,210 +2157,210 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="7">
         <v>100100</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="39"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="7">
         <v>100100</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="51" t="s">
+      <c r="H7" s="12"/>
+      <c r="I7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="40"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="7">
         <v>100100</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="12"/>
+      <c r="I8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="41"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="46"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>100100</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="12"/>
+      <c r="I9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="41"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="46"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>100100</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="8" t="s">
+      <c r="H10" s="12"/>
+      <c r="I10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="41"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="46"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="7">
         <v>100100</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="12"/>
+      <c r="I11" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="41"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="46"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="7">
         <v>100100</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="46" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2113,32 +2368,32 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="7">
         <v>100100</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="42" t="s">
+      <c r="K13" s="47" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2146,165 +2401,165 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="7">
         <v>100100</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="52" t="s">
+      <c r="H14" s="15"/>
+      <c r="I14" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="42"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="47"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="7">
         <v>100100</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="15" t="s">
+      <c r="H15" s="19"/>
+      <c r="I15" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="43"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="48"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="7">
         <v>100100</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="53" t="s">
+      <c r="H16" s="22"/>
+      <c r="I16" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="44"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="49"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="7">
         <v>100100</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="18" t="s">
+      <c r="H17" s="22"/>
+      <c r="I17" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="37" t="s">
+      <c r="J17" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A18" s="21">
+      <c r="A18" s="24">
         <v>10010061</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="25">
         <v>100100</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="21" t="s">
+      <c r="H18" s="25"/>
+      <c r="I18" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="45"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="50"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="28">
         <v>100100</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="28" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2313,27 +2568,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="25"/>
-      <c r="I19" s="54" t="s">
+      <c r="H19" s="28"/>
+      <c r="I19" s="60" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="46"/>
+      <c r="K19" s="51"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="28">
         <v>100100</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="28" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2342,27 +2597,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="47"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="52"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="28">
         <v>100100</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="28" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2371,27 +2626,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="25"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="25"/>
-      <c r="K21" s="47"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="52"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="28">
         <v>100100</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="28" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2400,27 +2655,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="25"/>
-      <c r="K22" s="47"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="52"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="28">
         <v>100100</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="28" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2429,27 +2684,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="28"/>
+      <c r="I23" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="47"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="52"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="28">
         <v>100100</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="28" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2458,101 +2713,990 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="25" t="s">
+      <c r="H24" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="47" t="s">
+      <c r="K24" s="52" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="27">
+      <c r="A25" s="30">
         <v>10010091</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="31">
         <v>100100</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="27" t="s">
+      <c r="C25" s="31"/>
+      <c r="D25" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="27" t="s">
+      <c r="G25" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="48"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="53"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A26" s="29">
+      <c r="A26" s="1">
+        <v>10030021</v>
+      </c>
+      <c r="B26" s="7">
+        <v>100300</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="42"/>
+      <c r="K26" s="43"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A27" s="1">
+        <v>10030022</v>
+      </c>
+      <c r="B27" s="7">
+        <v>100300</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A28" s="1">
+        <v>10030031</v>
+      </c>
+      <c r="B28" s="7">
+        <v>100300</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="52"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A29" s="32">
         <v>10070011</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B29" s="33">
         <v>100700</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="29" t="s">
+      <c r="C29" s="33"/>
+      <c r="D29" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="29" t="s">
+      <c r="E29" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="J26" s="29"/>
-      <c r="K26" s="49"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A27" s="31">
+      <c r="G29" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="32"/>
+      <c r="K29" s="54"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A30" s="34">
         <v>10070021</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B30" s="35">
         <v>100700</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="31"/>
-      <c r="K27" s="50"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="35"/>
+      <c r="I30" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="34"/>
+      <c r="K30" s="55"/>
+    </row>
+    <row r="31" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A31" s="9">
+        <v>10120011</v>
+      </c>
+      <c r="B31" s="8">
+        <v>101200</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J31" s="9"/>
+      <c r="K31" s="44"/>
+    </row>
+    <row r="32" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A32" s="9">
+        <v>10120021</v>
+      </c>
+      <c r="B32" s="8">
+        <v>101200</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" s="8"/>
+      <c r="I32" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="44"/>
+    </row>
+    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A33" s="9">
+        <v>10120031</v>
+      </c>
+      <c r="B33" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="9"/>
+      <c r="K33" s="44"/>
+    </row>
+    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A34" s="9">
+        <v>10120032</v>
+      </c>
+      <c r="B34" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="9"/>
+      <c r="K34" s="44"/>
+    </row>
+    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A35" s="9">
+        <v>10120033</v>
+      </c>
+      <c r="B35" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I35" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="9"/>
+      <c r="K35" s="44"/>
+    </row>
+    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A36" s="9">
+        <v>10120034</v>
+      </c>
+      <c r="B36" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="9"/>
+      <c r="K36" s="44"/>
+    </row>
+    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A37" s="9">
+        <v>10120035</v>
+      </c>
+      <c r="B37" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="9"/>
+      <c r="K37" s="44"/>
+    </row>
+    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A38" s="9">
+        <v>10120036</v>
+      </c>
+      <c r="B38" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="9"/>
+      <c r="K38" s="44"/>
+    </row>
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A39" s="37">
+        <v>10120041</v>
+      </c>
+      <c r="B39" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="36">
+        <v>10</v>
+      </c>
+      <c r="I39" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J39" s="37"/>
+      <c r="K39" s="56"/>
+    </row>
+    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A40" s="37">
+        <v>10120042</v>
+      </c>
+      <c r="B40" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" s="36">
+        <v>10</v>
+      </c>
+      <c r="I40" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J40" s="37"/>
+      <c r="K40" s="56"/>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A41" s="37">
+        <v>10120043</v>
+      </c>
+      <c r="B41" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41" s="36">
+        <v>10</v>
+      </c>
+      <c r="I41" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="37"/>
+      <c r="K41" s="56"/>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A42" s="37">
+        <v>10120044</v>
+      </c>
+      <c r="B42" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="36">
+        <v>10</v>
+      </c>
+      <c r="I42" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J42" s="37"/>
+      <c r="K42" s="56"/>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A43" s="37">
+        <v>10120045</v>
+      </c>
+      <c r="B43" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="G43" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43" s="36">
+        <v>10</v>
+      </c>
+      <c r="I43" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J43" s="37"/>
+      <c r="K43" s="56"/>
+    </row>
+    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A44" s="37">
+        <v>10120046</v>
+      </c>
+      <c r="B44" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" s="36">
+        <v>10</v>
+      </c>
+      <c r="I44" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="J44" s="37"/>
+      <c r="K44" s="56"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="9">
+        <v>10120051</v>
+      </c>
+      <c r="B45" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J45" s="9"/>
+      <c r="K45" s="44"/>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="9">
+        <v>10120052</v>
+      </c>
+      <c r="B46" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J46" s="9"/>
+      <c r="K46" s="44"/>
+    </row>
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="9">
+        <v>10120053</v>
+      </c>
+      <c r="B47" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I47" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J47" s="9"/>
+      <c r="K47" s="44"/>
+    </row>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="9">
+        <v>10120054</v>
+      </c>
+      <c r="B48" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J48" s="9"/>
+      <c r="K48" s="44"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="9">
+        <v>10120055</v>
+      </c>
+      <c r="B49" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I49" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="44"/>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="9">
+        <v>10120056</v>
+      </c>
+      <c r="B50" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I50" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="J50" s="9"/>
+      <c r="K50" s="44"/>
+    </row>
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="16">
+        <v>10120061</v>
+      </c>
+      <c r="B51" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I51" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J51" s="16"/>
+      <c r="K51" s="47"/>
+    </row>
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="16">
+        <v>10120062</v>
+      </c>
+      <c r="B52" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I52" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J52" s="16"/>
+      <c r="K52" s="47"/>
+    </row>
+    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="16">
+        <v>10120063</v>
+      </c>
+      <c r="B53" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I53" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J53" s="16"/>
+      <c r="K53" s="47"/>
+    </row>
+    <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="16">
+        <v>10120064</v>
+      </c>
+      <c r="B54" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I54" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J54" s="16"/>
+      <c r="K54" s="47"/>
+    </row>
+    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="16">
+        <v>10120065</v>
+      </c>
+      <c r="B55" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I55" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J55" s="16"/>
+      <c r="K55" s="47"/>
+    </row>
+    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="16">
+        <v>10120066</v>
+      </c>
+      <c r="B56" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="J56" s="16"/>
+      <c r="K56" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2572,24 +3716,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2597,16 +3741,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2614,16 +3758,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2631,16 +3775,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2648,7 +3792,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2656,7 +3800,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2664,7 +3808,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2672,7 +3816,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2680,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2688,7 +3832,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2696,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2704,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2712,7 +3856,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2720,7 +3864,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2728,7 +3872,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2736,7 +3880,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2744,7 +3888,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2752,7 +3896,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2760,7 +3904,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2768,7 +3912,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2776,7 +3920,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2784,7 +3928,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2792,7 +3936,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2800,7 +3944,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2808,7 +3952,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2816,7 +3960,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2824,7 +3968,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2832,7 +3976,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2840,7 +3984,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2848,7 +3992,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2856,7 +4000,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2864,7 +4008,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2872,7 +4016,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2880,7 +4024,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2888,7 +4032,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2896,7 +4040,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2904,7 +4048,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2912,7 +4056,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2920,7 +4064,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2928,7 +4072,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2936,7 +4080,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2944,7 +4088,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2952,7 +4096,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2960,7 +4104,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2968,7 +4112,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2976,7 +4120,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2984,7 +4128,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -1003,7 +1003,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1036,19 +1036,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1085,12 +1073,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1411,7 +1393,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1435,16 +1417,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1453,92 +1435,92 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1551,133 +1533,130 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2040,10 +2019,10 @@
       <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="35" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2069,10 +2048,10 @@
       <c r="I2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="36" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2098,10 +2077,10 @@
       <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2116,7 +2095,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="39"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
@@ -2128,28 +2107,28 @@
       <c r="C5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="40" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2163,26 +2142,26 @@
       <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="44"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="41"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
@@ -2191,27 +2170,27 @@
       <c r="B7" s="7">
         <v>100100</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="57" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="45"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="42"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
@@ -2220,27 +2199,27 @@
       <c r="B8" s="7">
         <v>100100</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11" t="s">
+      <c r="H8" s="11"/>
+      <c r="I8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="46"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="43"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
@@ -2249,27 +2228,27 @@
       <c r="B9" s="7">
         <v>100100</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11" t="s">
+      <c r="H9" s="11"/>
+      <c r="I9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="46"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="43"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
@@ -2278,27 +2257,27 @@
       <c r="B10" s="7">
         <v>100100</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="46"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="43"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
@@ -2307,27 +2286,27 @@
       <c r="B11" s="7">
         <v>100100</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11" t="s">
+      <c r="H11" s="11"/>
+      <c r="I11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="46"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="43"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
@@ -2336,31 +2315,31 @@
       <c r="B12" s="7">
         <v>100100</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="42" t="s">
+      <c r="J12" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="43" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2371,29 +2350,29 @@
       <c r="B13" s="7">
         <v>100100</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="16" t="s">
+      <c r="H13" s="14"/>
+      <c r="I13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="44" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2404,27 +2383,27 @@
       <c r="B14" s="7">
         <v>100100</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="58" t="s">
+      <c r="H14" s="14"/>
+      <c r="I14" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="47"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="44"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
@@ -2433,27 +2412,27 @@
       <c r="B15" s="7">
         <v>100100</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="18" t="s">
+      <c r="H15" s="17"/>
+      <c r="I15" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="48"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
@@ -2462,27 +2441,27 @@
       <c r="B16" s="7">
         <v>100100</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="59" t="s">
+      <c r="H16" s="20"/>
+      <c r="I16" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="49"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="46"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17" s="1">
@@ -2491,75 +2470,75 @@
       <c r="B17" s="7">
         <v>100100</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="21" t="s">
+      <c r="H17" s="20"/>
+      <c r="I17" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="42" t="s">
+      <c r="J17" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="49" t="s">
+      <c r="K17" s="46" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A18" s="24">
+      <c r="A18" s="22">
         <v>10010061</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="23">
         <v>100100</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="25"/>
-      <c r="I18" s="24" t="s">
+      <c r="H18" s="23"/>
+      <c r="I18" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="50"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="47"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="26">
         <v>100100</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="26" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2568,27 +2547,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="28"/>
-      <c r="I19" s="60" t="s">
+      <c r="H19" s="26"/>
+      <c r="I19" s="57" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="51"/>
+      <c r="K19" s="48"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="26">
         <v>100100</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="26" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2597,27 +2576,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="52"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="49"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="26">
         <v>100100</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="26" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2626,27 +2605,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="28"/>
+      <c r="H21" s="26"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="52"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="26">
         <v>100100</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="26" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2655,27 +2634,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="26"/>
       <c r="I22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="52"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="49"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="26">
         <v>100100</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="26" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2684,27 +2663,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="11" t="s">
+      <c r="H23" s="26"/>
+      <c r="I23" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="52"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="49"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="26">
         <v>100100</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2713,47 +2692,47 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="26" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="42" t="s">
+      <c r="J24" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="52" t="s">
+      <c r="K24" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="30">
+      <c r="A25" s="28">
         <v>10010091</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="29">
         <v>100100</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30" t="s">
+      <c r="C25" s="29"/>
+      <c r="D25" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="G25" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="30" t="s">
+      <c r="I25" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="J25" s="31"/>
-      <c r="K25" s="53"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="50"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A26" s="1">
@@ -2765,26 +2744,26 @@
       <c r="C26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="3" t="s">
         <v>90</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J26" s="42"/>
-      <c r="K26" s="43"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="40"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A27" s="1">
@@ -2796,26 +2775,26 @@
       <c r="C27" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="3" t="s">
         <v>97</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="3" t="s">
         <v>99</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="43"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="40"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A28" s="1">
@@ -2827,876 +2806,876 @@
       <c r="C28" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="3" t="s">
         <v>105</v>
       </c>
       <c r="H28" s="8"/>
-      <c r="I28" s="61" t="s">
+      <c r="I28" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="52"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="49"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="32">
+      <c r="A29" s="30">
         <v>10070011</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="31">
         <v>100700</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="31"/>
+      <c r="D29" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="32" t="s">
+      <c r="H29" s="31"/>
+      <c r="I29" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="J29" s="32"/>
-      <c r="K29" s="54"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="51"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="34">
+      <c r="A30" s="32">
         <v>10070021</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="33">
         <v>100700</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="34" t="s">
+      <c r="C30" s="33"/>
+      <c r="D30" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F30" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="H30" s="35"/>
-      <c r="I30" s="34" t="s">
+      <c r="H30" s="33"/>
+      <c r="I30" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="34"/>
-      <c r="K30" s="55"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="52"/>
     </row>
     <row r="31" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A31" s="9">
+      <c r="A31" s="3">
         <v>10120011</v>
       </c>
       <c r="B31" s="8">
         <v>101200</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="3" t="s">
         <v>111</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="3" t="s">
         <v>114</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="44"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="41"/>
     </row>
     <row r="32" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A32" s="9">
+      <c r="A32" s="3">
         <v>10120021</v>
       </c>
       <c r="B32" s="8">
         <v>101200</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="3" t="s">
         <v>107</v>
       </c>
       <c r="H32" s="8"/>
-      <c r="I32" s="61" t="s">
+      <c r="I32" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="44"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="41"/>
     </row>
     <row r="33" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A33" s="9">
+      <c r="A33" s="3">
         <v>10120031</v>
       </c>
       <c r="B33" s="8">
         <v>101200</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I33" s="61" t="s">
+      <c r="I33" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="44"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="41"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A34" s="9">
+      <c r="A34" s="3">
         <v>10120032</v>
       </c>
       <c r="B34" s="8">
         <v>101200</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="3" t="s">
         <v>124</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G34" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I34" s="61" t="s">
+      <c r="I34" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="44"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="41"/>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A35" s="9">
+      <c r="A35" s="3">
         <v>10120033</v>
       </c>
       <c r="B35" s="8">
         <v>101200</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="37" t="s">
+      <c r="G35" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I35" s="61" t="s">
+      <c r="I35" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="9"/>
-      <c r="K35" s="44"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="41"/>
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A36" s="9">
+      <c r="A36" s="3">
         <v>10120034</v>
       </c>
       <c r="B36" s="8">
         <v>101200</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="3" t="s">
         <v>130</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="37" t="s">
+      <c r="G36" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I36" s="61" t="s">
+      <c r="I36" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="44"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="41"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A37" s="9">
+      <c r="A37" s="3">
         <v>10120035</v>
       </c>
       <c r="B37" s="8">
         <v>101200</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G37" s="37" t="s">
+      <c r="G37" s="4" t="s">
         <v>134</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I37" s="61" t="s">
+      <c r="I37" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="44"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="41"/>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A38" s="9">
+      <c r="A38" s="3">
         <v>10120036</v>
       </c>
       <c r="B38" s="8">
         <v>101200</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="3" t="s">
         <v>135</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G38" s="4" t="s">
         <v>136</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I38" s="61" t="s">
+      <c r="I38" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="44"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="41"/>
     </row>
     <row r="39" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A39" s="37">
+      <c r="A39" s="4">
         <v>10120041</v>
       </c>
-      <c r="B39" s="36">
+      <c r="B39" s="34">
         <v>101200</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H39" s="36">
+      <c r="H39" s="34">
         <v>10</v>
       </c>
-      <c r="I39" s="62" t="s">
+      <c r="I39" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J39" s="37"/>
-      <c r="K39" s="56"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="53"/>
     </row>
     <row r="40" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A40" s="37">
+      <c r="A40" s="4">
         <v>10120042</v>
       </c>
-      <c r="B40" s="36">
+      <c r="B40" s="34">
         <v>101200</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="36" t="s">
+      <c r="E40" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G40" s="37" t="s">
+      <c r="G40" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H40" s="36">
+      <c r="H40" s="34">
         <v>10</v>
       </c>
-      <c r="I40" s="62" t="s">
+      <c r="I40" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J40" s="37"/>
-      <c r="K40" s="56"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="53"/>
     </row>
     <row r="41" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A41" s="37">
+      <c r="A41" s="4">
         <v>10120043</v>
       </c>
-      <c r="B41" s="36">
+      <c r="B41" s="34">
         <v>101200</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="36" t="s">
+      <c r="E41" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G41" s="37" t="s">
+      <c r="G41" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="36">
+      <c r="H41" s="34">
         <v>10</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J41" s="37"/>
-      <c r="K41" s="56"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="53"/>
     </row>
     <row r="42" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A42" s="37">
+      <c r="A42" s="4">
         <v>10120044</v>
       </c>
-      <c r="B42" s="36">
+      <c r="B42" s="34">
         <v>101200</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="D42" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="E42" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="G42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H42" s="36">
+      <c r="H42" s="34">
         <v>10</v>
       </c>
-      <c r="I42" s="62" t="s">
+      <c r="I42" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J42" s="37"/>
-      <c r="K42" s="56"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="53"/>
     </row>
     <row r="43" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A43" s="37">
+      <c r="A43" s="4">
         <v>10120045</v>
       </c>
-      <c r="B43" s="36">
+      <c r="B43" s="34">
         <v>101200</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="G43" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H43" s="36">
+      <c r="H43" s="34">
         <v>10</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J43" s="37"/>
-      <c r="K43" s="56"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="53"/>
     </row>
     <row r="44" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A44" s="37">
+      <c r="A44" s="4">
         <v>10120046</v>
       </c>
-      <c r="B44" s="36">
+      <c r="B44" s="34">
         <v>101200</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="37" t="s">
+      <c r="D44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E44" s="36" t="s">
+      <c r="E44" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G44" s="37" t="s">
+      <c r="G44" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H44" s="36">
+      <c r="H44" s="34">
         <v>10</v>
       </c>
-      <c r="I44" s="62" t="s">
+      <c r="I44" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="J44" s="37"/>
-      <c r="K44" s="56"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="53"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="9">
+      <c r="A45" s="3">
         <v>10120051</v>
       </c>
       <c r="B45" s="8">
         <v>101200</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G45" s="37" t="s">
+      <c r="G45" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I45" s="61" t="s">
+      <c r="I45" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J45" s="9"/>
-      <c r="K45" s="44"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="41"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A46" s="9">
+      <c r="A46" s="3">
         <v>10120052</v>
       </c>
       <c r="B46" s="8">
         <v>101200</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="3" t="s">
         <v>124</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="4" t="s">
         <v>125</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I46" s="61" t="s">
+      <c r="I46" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J46" s="9"/>
-      <c r="K46" s="44"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="41"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A47" s="9">
+      <c r="A47" s="3">
         <v>10120053</v>
       </c>
       <c r="B47" s="8">
         <v>101200</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C47" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G47" s="37" t="s">
+      <c r="G47" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I47" s="61" t="s">
+      <c r="I47" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J47" s="9"/>
-      <c r="K47" s="44"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="41"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A48" s="9">
+      <c r="A48" s="3">
         <v>10120054</v>
       </c>
       <c r="B48" s="8">
         <v>101200</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="3" t="s">
         <v>130</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="37" t="s">
+      <c r="G48" s="4" t="s">
         <v>132</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I48" s="61" t="s">
+      <c r="I48" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J48" s="9"/>
-      <c r="K48" s="44"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="41"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="9">
+      <c r="A49" s="3">
         <v>10120055</v>
       </c>
       <c r="B49" s="8">
         <v>101200</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="G49" s="4" t="s">
         <v>134</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I49" s="61" t="s">
+      <c r="I49" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J49" s="9"/>
-      <c r="K49" s="44"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="41"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="9">
+      <c r="A50" s="3">
         <v>10120056</v>
       </c>
       <c r="B50" s="8">
         <v>101200</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="3" t="s">
         <v>135</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G50" s="37" t="s">
+      <c r="G50" s="4" t="s">
         <v>136</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I50" s="61" t="s">
+      <c r="I50" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="J50" s="9"/>
-      <c r="K50" s="44"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="41"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A51" s="16">
+      <c r="A51" s="5">
         <v>10120061</v>
       </c>
       <c r="B51" s="8">
         <v>101200</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="H51" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I51" s="58" t="s">
+      <c r="I51" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J51" s="16"/>
-      <c r="K51" s="47"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="44"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A52" s="16">
+      <c r="A52" s="5">
         <v>10120062</v>
       </c>
       <c r="B52" s="8">
         <v>101200</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="H52" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I52" s="58" t="s">
+      <c r="I52" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J52" s="16"/>
-      <c r="K52" s="47"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="44"/>
     </row>
     <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A53" s="16">
+      <c r="A53" s="5">
         <v>10120063</v>
       </c>
       <c r="B53" s="8">
         <v>101200</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H53" s="15" t="s">
+      <c r="H53" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I53" s="58" t="s">
+      <c r="I53" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J53" s="16"/>
-      <c r="K53" s="47"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="44"/>
     </row>
     <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A54" s="16">
+      <c r="A54" s="5">
         <v>10120064</v>
       </c>
       <c r="B54" s="8">
         <v>101200</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D54" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H54" s="15" t="s">
+      <c r="H54" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I54" s="58" t="s">
+      <c r="I54" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J54" s="16"/>
-      <c r="K54" s="47"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="44"/>
     </row>
     <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="16">
+      <c r="A55" s="5">
         <v>10120065</v>
       </c>
       <c r="B55" s="8">
         <v>101200</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G55" s="16" t="s">
+      <c r="G55" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H55" s="15" t="s">
+      <c r="H55" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I55" s="58" t="s">
+      <c r="I55" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J55" s="16"/>
-      <c r="K55" s="47"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="44"/>
     </row>
     <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="16">
+      <c r="A56" s="5">
         <v>10120066</v>
       </c>
       <c r="B56" s="8">
         <v>101200</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="H56" s="15" t="s">
+      <c r="H56" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I56" s="58" t="s">
+      <c r="I56" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="J56" s="16"/>
-      <c r="K56" s="47"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="225">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -223,7 +223,7 @@
     <t>0_110|2_10|3_10|4_5|5_1</t>
   </si>
   <si>
-    <t>5_500|10_2500|15_2000|20_1000|25_800|30_400|50_200|80_50|100_10|150_5|200_0</t>
+    <t>20_500|30_2500|40_2000|50_1000|60_800|80_400|100_200|120_50|150_10|200_5|250_0</t>
   </si>
   <si>
     <t>1_0</t>
@@ -397,121 +397,127 @@
     <t>免费模式-1倍百搭</t>
   </si>
   <si>
+    <t>12_4|13_2|14_1</t>
+  </si>
+  <si>
+    <t>出现1/2/5倍百搭</t>
+  </si>
+  <si>
+    <t>1_40|2_30|3_20|4_10</t>
+  </si>
+  <si>
+    <t>樱桃出现</t>
+  </si>
+  <si>
+    <t>必出出樱桃中奖</t>
+  </si>
+  <si>
+    <t>6_1</t>
+  </si>
+  <si>
+    <t>樱桃中奖</t>
+  </si>
+  <si>
+    <t>2_1_1|5_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>7_8_9_10_99</t>
+  </si>
+  <si>
+    <t>1_10|2_5|3_2</t>
+  </si>
+  <si>
+    <t>樱桃出现_不中奖</t>
+  </si>
+  <si>
+    <t>必出出樱桃_不在中奖线上</t>
+  </si>
+  <si>
+    <t>樱桃</t>
+  </si>
+  <si>
+    <t>1_1_1|3_1_1|4_1_1|6_1_1|7_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>1_10|2_10|3_10|4_10</t>
+  </si>
+  <si>
+    <t>倍数&amp;jackpot百搭出现</t>
+  </si>
+  <si>
+    <t>必出出Wild-倍率-jackpot</t>
+  </si>
+  <si>
+    <t>7_1|8_1|9_1|10_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</t>
+  </si>
+  <si>
+    <t>倍率图标集合&amp;jackpot</t>
+  </si>
+  <si>
+    <t>8_1_1</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1</t>
+  </si>
+  <si>
+    <t>0_15|1_3|2_2</t>
+  </si>
+  <si>
+    <t>必然出3个以上免费图案</t>
+  </si>
+  <si>
+    <t>3_2|4_1</t>
+  </si>
+  <si>
+    <t>随机出大财神-不足5个</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>概率出现5个以下大财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>0_100|1_25|2_20|3_5|4_1</t>
+  </si>
+  <si>
+    <t>必出大财神-5个</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>5_1</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>第1行改为横财神</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>必然出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>4_1_1|7_1_1|10_1_1</t>
+  </si>
+  <si>
+    <t>第2行改为横财神</t>
+  </si>
+  <si>
     <t>12_1</t>
-  </si>
-  <si>
-    <t>出现1倍百搭</t>
-  </si>
-  <si>
-    <t>1_30</t>
-  </si>
-  <si>
-    <t>樱桃出现</t>
-  </si>
-  <si>
-    <t>必出出樱桃中奖</t>
-  </si>
-  <si>
-    <t>6_1</t>
-  </si>
-  <si>
-    <t>樱桃中奖</t>
-  </si>
-  <si>
-    <t>2_1_1|5_1_1|8_1_1</t>
-  </si>
-  <si>
-    <t>7_8_9_10_99</t>
-  </si>
-  <si>
-    <t>1_10|2_5|3_2</t>
-  </si>
-  <si>
-    <t>樱桃出现_不中奖</t>
-  </si>
-  <si>
-    <t>必出出樱桃_不在中奖线上</t>
-  </si>
-  <si>
-    <t>樱桃</t>
-  </si>
-  <si>
-    <t>1_1_1|3_1_1|4_1_1|6_1_1|7_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>1_10|2_10|3_10|4_10</t>
-  </si>
-  <si>
-    <t>倍数&amp;jackpot百搭出现</t>
-  </si>
-  <si>
-    <t>必出出Wild-倍率-jackpot</t>
-  </si>
-  <si>
-    <t>7_1|8_1|9_1|10_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</t>
-  </si>
-  <si>
-    <t>倍率图标集合&amp;jackpot</t>
-  </si>
-  <si>
-    <t>8_1_1</t>
-  </si>
-  <si>
-    <t>10_1</t>
-  </si>
-  <si>
-    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1</t>
-  </si>
-  <si>
-    <t>0_15|1_3|2_2</t>
-  </si>
-  <si>
-    <t>必然出3个以上免费图案</t>
-  </si>
-  <si>
-    <t>3_2|4_1</t>
-  </si>
-  <si>
-    <t>随机出大财神-不足5个</t>
-  </si>
-  <si>
-    <t>9_1</t>
-  </si>
-  <si>
-    <t>概率出现5个以下大财神</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>0_100|1_25|2_20|3_5|4_1</t>
-  </si>
-  <si>
-    <t>必出大财神-5个</t>
-  </si>
-  <si>
-    <t>5_1</t>
-  </si>
-  <si>
-    <t>横财神</t>
-  </si>
-  <si>
-    <t>第1行改为横财神</t>
-  </si>
-  <si>
-    <t>11_1</t>
-  </si>
-  <si>
-    <t>必然出1个正&amp;横财神</t>
-  </si>
-  <si>
-    <t>4_1_1|7_1_1|10_1_1</t>
-  </si>
-  <si>
-    <t>第2行改为横财神</t>
   </si>
   <si>
     <t>5_1_1|8_1_1|11_1_1</t>
@@ -2924,11 +2930,11 @@
         <v>117</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="41"/>
@@ -2941,19 +2947,19 @@
         <v>101200</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>115</v>
@@ -2972,19 +2978,19 @@
         <v>101200</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>115</v>
@@ -3003,19 +3009,19 @@
         <v>101200</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>115</v>
@@ -3034,19 +3040,19 @@
         <v>101200</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>115</v>
@@ -3065,19 +3071,19 @@
         <v>101200</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>67</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>115</v>
@@ -3096,19 +3102,19 @@
         <v>101200</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>115</v>
@@ -3127,25 +3133,25 @@
         <v>101200</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E39" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H39" s="34">
         <v>10</v>
       </c>
       <c r="I39" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="53"/>
@@ -3158,25 +3164,25 @@
         <v>101200</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E40" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H40" s="34">
         <v>10</v>
       </c>
       <c r="I40" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="53"/>
@@ -3189,25 +3195,25 @@
         <v>101200</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H41" s="34">
         <v>10</v>
       </c>
       <c r="I41" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="53"/>
@@ -3220,25 +3226,25 @@
         <v>101200</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E42" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H42" s="34">
         <v>10</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="53"/>
@@ -3251,25 +3257,25 @@
         <v>101200</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E43" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H43" s="34">
         <v>10</v>
       </c>
       <c r="I43" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="53"/>
@@ -3282,25 +3288,25 @@
         <v>101200</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E44" s="34" t="s">
         <v>106</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H44" s="34">
         <v>10</v>
       </c>
       <c r="I44" s="59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="53"/>
@@ -3313,25 +3319,25 @@
         <v>101200</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I45" s="58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="41"/>
@@ -3344,25 +3350,25 @@
         <v>101200</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>56</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I46" s="58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="41"/>
@@ -3375,25 +3381,25 @@
         <v>101200</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E47" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="I47" s="58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="41"/>
@@ -3406,25 +3412,25 @@
         <v>101200</v>
       </c>
       <c r="C48" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I48" s="58" t="s">
         <v>153</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I48" s="58" t="s">
-        <v>151</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="41"/>
@@ -3437,25 +3443,25 @@
         <v>101200</v>
       </c>
       <c r="C49" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I49" s="58" t="s">
         <v>153</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I49" s="58" t="s">
-        <v>151</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="41"/>
@@ -3468,25 +3474,25 @@
         <v>101200</v>
       </c>
       <c r="C50" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="I50" s="58" t="s">
         <v>153</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I50" s="58" t="s">
-        <v>151</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="41"/>
@@ -3499,25 +3505,25 @@
         <v>101200</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I51" s="55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="44"/>
@@ -3530,25 +3536,25 @@
         <v>101200</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E52" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H52" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>159</v>
-      </c>
       <c r="I52" s="55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="44"/>
@@ -3561,25 +3567,25 @@
         <v>101200</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E53" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I53" s="55" t="s">
         <v>162</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I53" s="55" t="s">
-        <v>160</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="44"/>
@@ -3592,25 +3598,25 @@
         <v>101200</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I54" s="55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="44"/>
@@ -3623,25 +3629,25 @@
         <v>101200</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H55" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I55" s="55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="44"/>
@@ -3654,25 +3660,25 @@
         <v>101200</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I56" s="55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="44"/>
@@ -3695,24 +3701,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3720,16 +3726,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3737,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3754,16 +3760,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3771,7 +3777,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3779,7 +3785,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3787,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3795,7 +3801,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3803,7 +3809,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3811,7 +3817,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3819,7 +3825,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3827,7 +3833,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3835,7 +3841,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3843,7 +3849,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3851,7 +3857,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3859,7 +3865,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3867,7 +3873,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3875,7 +3881,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3883,7 +3889,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3891,7 +3897,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3899,7 +3905,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3907,7 +3913,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3915,7 +3921,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3923,7 +3929,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3931,7 +3937,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3939,7 +3945,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3947,7 +3953,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3955,7 +3961,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3963,7 +3969,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3971,7 +3977,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3979,7 +3985,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3987,7 +3993,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3995,7 +4001,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4003,7 +4009,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4011,7 +4017,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4019,7 +4025,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4027,7 +4033,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4035,7 +4041,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4043,7 +4049,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4051,7 +4057,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4059,7 +4065,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4067,7 +4073,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4075,7 +4081,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4083,7 +4089,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4091,7 +4097,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4099,7 +4105,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4107,7 +4113,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="223">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -223,7 +223,7 @@
     <t>0_110|2_10|3_10|4_5|5_1</t>
   </si>
   <si>
-    <t>20_500|30_2500|40_2000|50_1000|60_800|80_400|100_200|120_50|150_10|200_5|250_0</t>
+    <t>80_500|90_2500|100_2000|110_1000|120_800|130_400|140_200|150_50|180_10|200_5|220_0</t>
   </si>
   <si>
     <t>1_0</t>
@@ -331,7 +331,7 @@
     <t>必然出美元图标收集</t>
   </si>
   <si>
-    <t>2_10|3_20|4_10|5_2</t>
+    <t>2_0|3_20|4_10|5_2</t>
   </si>
   <si>
     <t>4_5001003</t>
@@ -376,22 +376,16 @@
     <t>出现隐藏图案</t>
   </si>
   <si>
-    <t>1_65|2_35</t>
+    <t>1_90|2_10</t>
   </si>
   <si>
     <t>必然出现蓝火车</t>
   </si>
   <si>
-    <t>1_75|2_25</t>
+    <t>0_37|1_60|2_3</t>
   </si>
   <si>
     <t>必然出现紫火车</t>
-  </si>
-  <si>
-    <t>1_85|2_15</t>
-  </si>
-  <si>
-    <t>0_40|1_50|2_10</t>
   </si>
   <si>
     <t>免费模式-1倍百搭</t>
@@ -2642,7 +2636,7 @@
       </c>
       <c r="H22" s="26"/>
       <c r="I22" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J22" s="26"/>
       <c r="K22" s="49"/>
@@ -2671,7 +2665,7 @@
       </c>
       <c r="H23" s="26"/>
       <c r="I23" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J23" s="26"/>
       <c r="K23" s="49"/>
@@ -2720,13 +2714,13 @@
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="28" t="s">
         <v>85</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>87</v>
       </c>
       <c r="G25" s="28" t="s">
         <v>71</v>
@@ -2735,7 +2729,7 @@
         <v>26</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J25" s="29"/>
       <c r="K25" s="50"/>
@@ -2748,25 +2742,25 @@
         <v>100300</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="G26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="J26" s="39"/>
       <c r="K26" s="40"/>
@@ -2779,25 +2773,25 @@
         <v>100300</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="J27" s="39"/>
       <c r="K27" s="40"/>
@@ -2810,19 +2804,19 @@
         <v>100300</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="G28" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="58" t="s">
@@ -2843,17 +2837,17 @@
         <v>30</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F29" s="30" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H29" s="31"/>
       <c r="I29" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J29" s="30"/>
       <c r="K29" s="51"/>
@@ -2867,20 +2861,20 @@
       </c>
       <c r="C30" s="33"/>
       <c r="D30" s="32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G30" s="32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H30" s="33"/>
       <c r="I30" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="52"/>
@@ -2893,22 +2887,22 @@
         <v>101200</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="G31" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="H31" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="I31" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="41"/>
@@ -2921,20 +2915,20 @@
         <v>101200</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="41"/>
@@ -2947,22 +2941,22 @@
         <v>101200</v>
       </c>
       <c r="C33" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="G33" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="H33" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I33" s="58" t="s">
         <v>39</v>
@@ -2978,22 +2972,22 @@
         <v>101200</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="H34" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I34" s="58" t="s">
         <v>39</v>
@@ -3009,22 +3003,22 @@
         <v>101200</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="H35" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I35" s="58" t="s">
         <v>39</v>
@@ -3040,22 +3034,22 @@
         <v>101200</v>
       </c>
       <c r="C36" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="F36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="H36" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I36" s="58" t="s">
         <v>39</v>
@@ -3071,22 +3065,22 @@
         <v>101200</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>67</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I37" s="58" t="s">
         <v>39</v>
@@ -3102,22 +3096,22 @@
         <v>101200</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I38" s="58" t="s">
         <v>39</v>
@@ -3133,25 +3127,25 @@
         <v>101200</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H39" s="34">
         <v>10</v>
       </c>
       <c r="I39" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="53"/>
@@ -3164,25 +3158,25 @@
         <v>101200</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H40" s="34">
         <v>10</v>
       </c>
       <c r="I40" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="53"/>
@@ -3195,25 +3189,25 @@
         <v>101200</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E41" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H41" s="34">
         <v>10</v>
       </c>
       <c r="I41" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="53"/>
@@ -3226,25 +3220,25 @@
         <v>101200</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H42" s="34">
         <v>10</v>
       </c>
       <c r="I42" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="53"/>
@@ -3257,25 +3251,25 @@
         <v>101200</v>
       </c>
       <c r="C43" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="E43" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H43" s="34">
         <v>10</v>
       </c>
       <c r="I43" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="53"/>
@@ -3288,25 +3282,25 @@
         <v>101200</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H44" s="34">
         <v>10</v>
       </c>
       <c r="I44" s="59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="53"/>
@@ -3319,25 +3313,25 @@
         <v>101200</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I45" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I45" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="41"/>
@@ -3350,25 +3344,25 @@
         <v>101200</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>56</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I46" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="41"/>
@@ -3381,25 +3375,25 @@
         <v>101200</v>
       </c>
       <c r="C47" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="I47" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I47" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="41"/>
@@ -3412,25 +3406,25 @@
         <v>101200</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="H48" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I48" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I48" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="41"/>
@@ -3443,25 +3437,25 @@
         <v>101200</v>
       </c>
       <c r="C49" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>157</v>
-      </c>
       <c r="F49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I49" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I49" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="41"/>
@@ -3474,25 +3468,25 @@
         <v>101200</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F50" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I50" s="58" t="s">
         <v>151</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I50" s="58" t="s">
-        <v>153</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="41"/>
@@ -3505,25 +3499,25 @@
         <v>101200</v>
       </c>
       <c r="C51" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E51" s="14" t="s">
+      <c r="I51" s="55" t="s">
         <v>160</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="I51" s="55" t="s">
-        <v>162</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="44"/>
@@ -3536,25 +3530,25 @@
         <v>101200</v>
       </c>
       <c r="C52" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H52" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>161</v>
-      </c>
       <c r="I52" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="44"/>
@@ -3567,25 +3561,25 @@
         <v>101200</v>
       </c>
       <c r="C53" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>161</v>
-      </c>
       <c r="I53" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="44"/>
@@ -3598,25 +3592,25 @@
         <v>101200</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="H54" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I54" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="44"/>
@@ -3629,25 +3623,25 @@
         <v>101200</v>
       </c>
       <c r="C55" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>167</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H55" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I55" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="44"/>
@@ -3660,25 +3654,25 @@
         <v>101200</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I56" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="44"/>
@@ -3701,24 +3695,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3726,16 +3720,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3743,16 +3737,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3760,16 +3754,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3777,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3785,7 +3779,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3793,7 +3787,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3801,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3809,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3817,7 +3811,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3825,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3833,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3841,7 +3835,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3849,7 +3843,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3857,7 +3851,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3865,7 +3859,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3873,7 +3867,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3881,7 +3875,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3889,7 +3883,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3897,7 +3891,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3905,7 +3899,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3913,7 +3907,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3921,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3929,7 +3923,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3937,7 +3931,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3945,7 +3939,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3953,7 +3947,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3961,7 +3955,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3969,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3977,7 +3971,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3985,7 +3979,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3993,7 +3987,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4001,7 +3995,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4009,7 +4003,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4017,7 +4011,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4025,7 +4019,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4033,7 +4027,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4041,7 +4035,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4049,7 +4043,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4057,7 +4051,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4065,7 +4059,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4073,7 +4067,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4081,7 +4075,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4089,7 +4083,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4097,7 +4091,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4105,7 +4099,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4113,7 +4107,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -127,8 +127,7 @@
           <t>倍率类型：
 1 单线押分_0
 2 总押分_0
-3 倍率，直接显示，不需要计算
-4 平均押分_被动游戏ID</t>
+4 平均单线押分_0</t>
         </r>
       </text>
     </comment>
@@ -238,7 +237,7 @@
     <t>概率出all aboard</t>
   </si>
   <si>
-    <t>0_70|1_20|2_10</t>
+    <t>0_70|1_25|2_5</t>
   </si>
   <si>
     <t>拉火车模式</t>
@@ -334,7 +333,7 @@
     <t>2_0|3_20|4_10|5_2</t>
   </si>
   <si>
-    <t>4_5001003</t>
+    <t>4_0</t>
   </si>
   <si>
     <t>最后一列必出金火车</t>
@@ -361,7 +360,7 @@
     <t>保险箱</t>
   </si>
   <si>
-    <t>3_20|4_10|5_2</t>
+    <t>3_25|4_15|5_10</t>
   </si>
   <si>
     <t>免费模式-触发局|结果库用，实际不会出现</t>
@@ -391,13 +390,13 @@
     <t>免费模式-1倍百搭</t>
   </si>
   <si>
-    <t>12_4|13_2|14_1</t>
+    <t>12_2|13_2|14_2</t>
   </si>
   <si>
     <t>出现1/2/5倍百搭</t>
   </si>
   <si>
-    <t>1_40|2_30|3_20|4_10</t>
+    <t>1_30|2_40|3_20|4_10</t>
   </si>
   <si>
     <t>樱桃出现</t>
@@ -1991,7 +1990,7 @@
     <col min="7" max="7" width="27.7833333333333" customWidth="1"/>
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="11.6166666666667" customWidth="1"/>
+    <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
     <col min="11" max="11" width="11.6166666666667" style="6" customWidth="1"/>
   </cols>
   <sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="245">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -459,12 +459,93 @@
     <t>0_15|1_3|2_2</t>
   </si>
   <si>
+    <t>免费中获得额外免费次数</t>
+  </si>
+  <si>
+    <t>0_95|1_5</t>
+  </si>
+  <si>
     <t>必然出3个以上免费图案</t>
   </si>
   <si>
     <t>3_2|4_1</t>
   </si>
   <si>
+    <t>概率出现金色图标</t>
+  </si>
+  <si>
+    <t>11_1|12_1|13_1|14_1|15_1|16_1|17_1|18_1</t>
+  </si>
+  <si>
+    <t>修改对应图标</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_20|3_10|</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-2条</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_80|1_20</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-2筒</t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5条</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5筒</t>
+  </si>
+  <si>
+    <t>14_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-八万</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-白板</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-红中</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-发财</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
     <t>随机出大财神-不足5个</t>
   </si>
   <si>
@@ -498,9 +579,6 @@
     <t>第1行改为横财神</t>
   </si>
   <si>
-    <t>11_1</t>
-  </si>
-  <si>
     <t>必然出1个正&amp;横财神</t>
   </si>
   <si>
@@ -510,18 +588,12 @@
     <t>第2行改为横财神</t>
   </si>
   <si>
-    <t>12_1</t>
-  </si>
-  <si>
     <t>5_1_1|8_1_1|11_1_1</t>
   </si>
   <si>
     <t>第3行改为横财神</t>
   </si>
   <si>
-    <t>13_1</t>
-  </si>
-  <si>
     <t>6_1_1|9_1_1|12_1_1</t>
   </si>
   <si>
@@ -531,9 +603,6 @@
     <t>第2列改为正财神</t>
   </si>
   <si>
-    <t>14_1</t>
-  </si>
-  <si>
     <t>4_1_1|5_1_1|6_1_1</t>
   </si>
   <si>
@@ -616,9 +685,6 @@
   </si>
   <si>
     <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
-  </si>
-  <si>
-    <t>0_80|1_20</t>
   </si>
   <si>
     <t>32_1</t>
@@ -1002,7 +1068,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,6 +1078,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1392,7 +1464,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1416,16 +1488,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1434,128 +1506,122 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -1563,25 +1629,28 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1590,72 +1659,83 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1978,156 +2058,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="10.125" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="32.2" customWidth="1"/>
     <col min="6" max="6" width="25.1416666666667" customWidth="1"/>
     <col min="7" max="7" width="27.7833333333333" customWidth="1"/>
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="6" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="38" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="40" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="38"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>100100</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="42" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2135,210 +2215,210 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>100100</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="41"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="43"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>100100</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="54" t="s">
+      <c r="H7" s="12"/>
+      <c r="I7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="42"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="44"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>100100</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10" t="s">
+      <c r="H8" s="12"/>
+      <c r="I8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <v>100100</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10" t="s">
+      <c r="H9" s="12"/>
+      <c r="I9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="43"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <v>100100</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="10" t="s">
+      <c r="H10" s="12"/>
+      <c r="I10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="43"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="45"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>100100</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="10" t="s">
+      <c r="H11" s="12"/>
+      <c r="I11" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="43"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="45"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>100100</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="43" t="s">
+      <c r="K12" s="45" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2346,32 +2426,32 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <v>100100</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="5" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="46" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2379,165 +2459,165 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>100100</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="55" t="s">
+      <c r="H14" s="15"/>
+      <c r="I14" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="44"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="46"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>100100</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="16" t="s">
+      <c r="H15" s="18"/>
+      <c r="I15" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="45"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="47"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>100100</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="56" t="s">
+      <c r="H16" s="21"/>
+      <c r="I16" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="46"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="48"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>100100</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="19" t="s">
+      <c r="H17" s="21"/>
+      <c r="I17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="46" t="s">
+      <c r="K17" s="48" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A18" s="22">
+      <c r="A18" s="23">
         <v>10010061</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="24">
         <v>100100</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="23"/>
-      <c r="I18" s="22" t="s">
+      <c r="H18" s="24"/>
+      <c r="I18" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="47"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="49"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <v>100100</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="27" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2546,27 +2626,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="57" t="s">
+      <c r="H19" s="27"/>
+      <c r="I19" s="60" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="48"/>
+      <c r="K19" s="50"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <v>100100</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="27" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2575,27 +2655,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="49"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="51"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <v>100100</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="27" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2604,27 +2684,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="26"/>
+      <c r="H21" s="27"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="49"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="51"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <v>100100</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="27" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2633,27 +2713,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="26"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="49"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="51"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <v>100100</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="27" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2662,27 +2742,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="10" t="s">
+      <c r="H23" s="27"/>
+      <c r="I23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="49"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="51"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <v>100100</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="27" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2691,990 +2771,1276 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="26" t="s">
+      <c r="H24" s="27" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="49" t="s">
+      <c r="K24" s="51" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="28">
+      <c r="A25" s="29">
         <v>10010091</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <v>100100</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="28" t="s">
+      <c r="C25" s="30"/>
+      <c r="D25" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="28" t="s">
+      <c r="G25" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="29" t="s">
+      <c r="H25" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="29"/>
-      <c r="K25" s="50"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="52"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>100300</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="39"/>
-      <c r="K26" s="40"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="42"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>100300</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="39"/>
-      <c r="K27" s="40"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="42"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>100300</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="58" t="s">
+      <c r="H28" s="9"/>
+      <c r="I28" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="49"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="51"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="30">
+      <c r="A29" s="31">
         <v>10070011</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <v>100700</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30" t="s">
+      <c r="C29" s="32"/>
+      <c r="D29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="30" t="s">
+      <c r="G29" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="31"/>
-      <c r="I29" s="30" t="s">
+      <c r="H29" s="32"/>
+      <c r="I29" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="30"/>
-      <c r="K29" s="51"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="53"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="32">
+      <c r="A30" s="31">
+        <v>10070012</v>
+      </c>
+      <c r="B30" s="32">
+        <v>100700</v>
+      </c>
+      <c r="C30" s="32"/>
+      <c r="D30" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="32"/>
+      <c r="I30" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="J30" s="31"/>
+      <c r="K30" s="53"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A31" s="33">
         <v>10070021</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B31" s="34">
         <v>100700</v>
       </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="C31" s="34"/>
+      <c r="D31" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="32" t="s">
+      <c r="F31" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="52"/>
-    </row>
-    <row r="31" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A31" s="3">
-        <v>10120011</v>
-      </c>
-      <c r="B31" s="8">
-        <v>101200</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="H31" s="34"/>
+      <c r="I31" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="33"/>
+      <c r="K31" s="54"/>
+    </row>
+    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A32" s="3">
+        <v>10070030</v>
+      </c>
+      <c r="B32" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="E32" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="F32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" s="35"/>
+      <c r="I32" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="41"/>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A32" s="3">
-        <v>10120021</v>
-      </c>
-      <c r="B32" s="8">
-        <v>101200</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="58" t="s">
-        <v>117</v>
-      </c>
       <c r="J32" s="3"/>
-      <c r="K32" s="41"/>
+      <c r="K32" s="55"/>
     </row>
     <row r="33" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A33" s="3">
-        <v>10120031</v>
-      </c>
-      <c r="B33" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C33" s="34" t="s">
+        <v>10070031</v>
+      </c>
+      <c r="B33" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C33" s="35"/>
+      <c r="D33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I33" s="58" t="s">
-        <v>39</v>
-      </c>
       <c r="J33" s="3"/>
-      <c r="K33" s="41"/>
+      <c r="K33" s="55"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A34" s="3">
-        <v>10120032</v>
-      </c>
-      <c r="B34" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>118</v>
-      </c>
+        <v>10070032</v>
+      </c>
+      <c r="B34" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C34" s="35"/>
       <c r="D34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>120</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I34" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="41"/>
+      <c r="I34" s="62" t="str">
+        <f>I33</f>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K34" s="55"/>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35" s="3">
-        <v>10120033</v>
-      </c>
-      <c r="B35" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>118</v>
-      </c>
+        <v>10070033</v>
+      </c>
+      <c r="B35" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C35" s="35"/>
       <c r="D35" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>123</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="I35" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="41"/>
+      <c r="G35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="I35" s="62" t="str">
+        <f t="shared" ref="I35:I40" si="0">I34</f>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K35" s="55"/>
     </row>
     <row r="36" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A36" s="3">
-        <v>10120034</v>
-      </c>
-      <c r="B36" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>129</v>
-      </c>
+        <v>10070034</v>
+      </c>
+      <c r="B36" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C36" s="35"/>
       <c r="D36" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>131</v>
+        <v>125</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>126</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H36" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="I36" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="41"/>
+      <c r="G36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="I36" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K36" s="55"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A37" s="3">
-        <v>10120035</v>
-      </c>
-      <c r="B37" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C37" s="34" t="s">
+        <v>10070035</v>
+      </c>
+      <c r="B37" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C37" s="35"/>
+      <c r="D37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I37" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="41"/>
+      <c r="I37" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K37" s="55"/>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A38" s="3">
-        <v>10120036</v>
-      </c>
-      <c r="B38" s="8">
+        <v>10070036</v>
+      </c>
+      <c r="B38" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C38" s="35"/>
+      <c r="D38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I38" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K38" s="55"/>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A39" s="3">
+        <v>10070037</v>
+      </c>
+      <c r="B39" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C39" s="35"/>
+      <c r="D39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K39" s="55"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A40" s="3">
+        <v>10070038</v>
+      </c>
+      <c r="B40" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C40" s="35"/>
+      <c r="D40" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="I40" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_80|1_20</v>
+      </c>
+      <c r="K40" s="55"/>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A41" s="4">
+        <v>10120011</v>
+      </c>
+      <c r="B41" s="9">
         <v>101200</v>
       </c>
-      <c r="C38" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I38" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="41"/>
-    </row>
-    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A39" s="4">
-        <v>10120041</v>
-      </c>
-      <c r="B39" s="34">
+      <c r="E41" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A42" s="4">
+        <v>10120021</v>
+      </c>
+      <c r="B42" s="9">
         <v>101200</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="D42" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E39" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H39" s="34">
-        <v>10</v>
-      </c>
-      <c r="I39" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="53"/>
-    </row>
-    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A40" s="4">
-        <v>10120042</v>
-      </c>
-      <c r="B40" s="34">
-        <v>101200</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H40" s="34">
-        <v>10</v>
-      </c>
-      <c r="I40" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="53"/>
-    </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A41" s="4">
-        <v>10120043</v>
-      </c>
-      <c r="B41" s="34">
-        <v>101200</v>
-      </c>
-      <c r="C41" s="34" t="s">
+      <c r="F42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H41" s="34">
-        <v>10</v>
-      </c>
-      <c r="I41" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="53"/>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A42" s="4">
-        <v>10120044</v>
-      </c>
-      <c r="B42" s="34">
-        <v>101200</v>
-      </c>
-      <c r="C42" s="34" t="s">
+      <c r="H42" s="9"/>
+      <c r="I42" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H42" s="34">
-        <v>10</v>
-      </c>
-      <c r="I42" s="59" t="s">
-        <v>139</v>
-      </c>
       <c r="J42" s="4"/>
-      <c r="K42" s="53"/>
+      <c r="K42" s="43"/>
     </row>
     <row r="43" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A43" s="4">
-        <v>10120045</v>
-      </c>
-      <c r="B43" s="34">
+        <v>10120031</v>
+      </c>
+      <c r="B43" s="9">
         <v>101200</v>
       </c>
-      <c r="C43" s="34" t="s">
-        <v>144</v>
+      <c r="C43" s="36" t="s">
+        <v>145</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E43" s="34" t="s">
-        <v>104</v>
+      <c r="E43" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H43" s="34">
-        <v>10</v>
-      </c>
-      <c r="I43" s="59" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I43" s="61" t="s">
+        <v>39</v>
       </c>
       <c r="J43" s="4"/>
-      <c r="K43" s="53"/>
+      <c r="K43" s="43"/>
     </row>
     <row r="44" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A44" s="4">
-        <v>10120046</v>
-      </c>
-      <c r="B44" s="34">
+        <v>10120032</v>
+      </c>
+      <c r="B44" s="9">
         <v>101200</v>
       </c>
-      <c r="C44" s="34" t="s">
-        <v>144</v>
+      <c r="C44" s="36" t="s">
+        <v>145</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" s="34" t="s">
-        <v>104</v>
+        <v>149</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H44" s="34">
+      <c r="G44" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="43"/>
+    </row>
+    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="4">
+        <v>10120033</v>
+      </c>
+      <c r="B45" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J45" s="4"/>
+      <c r="K45" s="43"/>
+    </row>
+    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="4">
+        <v>10120034</v>
+      </c>
+      <c r="B46" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="43"/>
+    </row>
+    <row r="47" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="4">
+        <v>10120035</v>
+      </c>
+      <c r="B47" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="43"/>
+    </row>
+    <row r="48" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="4">
+        <v>10120036</v>
+      </c>
+      <c r="B48" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J48" s="4"/>
+      <c r="K48" s="43"/>
+    </row>
+    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="5">
+        <v>10120041</v>
+      </c>
+      <c r="B49" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H49" s="36">
         <v>10</v>
       </c>
-      <c r="I44" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="53"/>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="3">
-        <v>10120051</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="I49" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="J49" s="5"/>
+      <c r="K49" s="56"/>
+    </row>
+    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="5">
+        <v>10120042</v>
+      </c>
+      <c r="B50" s="36">
         <v>101200</v>
       </c>
-      <c r="C45" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H45" s="8" t="s">
+      <c r="C50" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I45" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="41"/>
-    </row>
-    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A46" s="3">
-        <v>10120052</v>
-      </c>
-      <c r="B46" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C46" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I46" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="41"/>
-    </row>
-    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A47" s="3">
-        <v>10120053</v>
-      </c>
-      <c r="B47" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I47" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="41"/>
-    </row>
-    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A48" s="3">
-        <v>10120054</v>
-      </c>
-      <c r="B48" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I48" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="41"/>
-    </row>
-    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="3">
-        <v>10120055</v>
-      </c>
-      <c r="B49" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I49" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="41"/>
-    </row>
-    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="3">
-        <v>10120056</v>
-      </c>
-      <c r="B50" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I50" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="41"/>
+      <c r="H50" s="36">
+        <v>10</v>
+      </c>
+      <c r="I50" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="J50" s="5"/>
+      <c r="K50" s="56"/>
     </row>
     <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A51" s="5">
-        <v>10120061</v>
-      </c>
-      <c r="B51" s="8">
+        <v>10120043</v>
+      </c>
+      <c r="B51" s="36">
         <v>101200</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>157</v>
+      <c r="C51" s="36" t="s">
+        <v>165</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>149</v>
+        <v>166</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I51" s="55" t="s">
-        <v>160</v>
+        <v>152</v>
+      </c>
+      <c r="H51" s="36">
+        <v>10</v>
+      </c>
+      <c r="I51" s="63" t="s">
+        <v>162</v>
       </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="44"/>
+      <c r="K51" s="56"/>
     </row>
     <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A52" s="5">
-        <v>10120062</v>
-      </c>
-      <c r="B52" s="8">
+        <v>10120044</v>
+      </c>
+      <c r="B52" s="36">
         <v>101200</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>157</v>
+      <c r="C52" s="36" t="s">
+        <v>167</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>149</v>
+        <v>168</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I52" s="55" t="s">
-        <v>160</v>
+        <v>155</v>
+      </c>
+      <c r="H52" s="36">
+        <v>10</v>
+      </c>
+      <c r="I52" s="63" t="s">
+        <v>162</v>
       </c>
       <c r="J52" s="5"/>
-      <c r="K52" s="44"/>
+      <c r="K52" s="56"/>
     </row>
     <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="5">
-        <v>10120063</v>
-      </c>
-      <c r="B53" s="8">
+        <v>10120045</v>
+      </c>
+      <c r="B53" s="36">
         <v>101200</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="14" t="s">
+      <c r="H53" s="36">
+        <v>10</v>
+      </c>
+      <c r="I53" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I53" s="55" t="s">
-        <v>160</v>
-      </c>
       <c r="J53" s="5"/>
-      <c r="K53" s="44"/>
+      <c r="K53" s="56"/>
     </row>
     <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="5">
+        <v>10120046</v>
+      </c>
+      <c r="B54" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H54" s="36">
+        <v>10</v>
+      </c>
+      <c r="I54" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="J54" s="5"/>
+      <c r="K54" s="56"/>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="4">
+        <v>10120051</v>
+      </c>
+      <c r="B55" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I55" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="4">
+        <v>10120052</v>
+      </c>
+      <c r="B56" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I56" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="4">
+        <v>10120053</v>
+      </c>
+      <c r="B57" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C57" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I57" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="43"/>
+    </row>
+    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="4">
+        <v>10120054</v>
+      </c>
+      <c r="B58" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I58" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A59" s="4">
+        <v>10120055</v>
+      </c>
+      <c r="B59" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I59" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="43"/>
+    </row>
+    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A60" s="4">
+        <v>10120056</v>
+      </c>
+      <c r="B60" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I60" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="J60" s="4"/>
+      <c r="K60" s="43"/>
+    </row>
+    <row r="61" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="6">
+        <v>10120061</v>
+      </c>
+      <c r="B61" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I61" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J61" s="6"/>
+      <c r="K61" s="46"/>
+    </row>
+    <row r="62" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="6">
+        <v>10120062</v>
+      </c>
+      <c r="B62" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I62" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" s="6"/>
+      <c r="K62" s="46"/>
+    </row>
+    <row r="63" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="6">
+        <v>10120063</v>
+      </c>
+      <c r="B63" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I63" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="46"/>
+    </row>
+    <row r="64" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="6">
         <v>10120064</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B64" s="9">
         <v>101200</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H54" s="14" t="s">
+      <c r="C64" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I64" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" s="6"/>
+      <c r="K64" s="46"/>
+    </row>
+    <row r="65" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A65" s="6">
+        <v>10120065</v>
+      </c>
+      <c r="B65" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="46"/>
+    </row>
+    <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A66" s="6">
+        <v>10120066</v>
+      </c>
+      <c r="B66" s="9">
+        <v>101200</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="I54" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="44"/>
-    </row>
-    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="5">
-        <v>10120065</v>
-      </c>
-      <c r="B55" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I55" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="J55" s="5"/>
-      <c r="K55" s="44"/>
-    </row>
-    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="5">
-        <v>10120066</v>
-      </c>
-      <c r="B56" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="I56" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="44"/>
+      <c r="H66" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J66" s="6"/>
+      <c r="K66" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3694,24 +4060,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3719,16 +4085,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3736,16 +4102,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="F4" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3753,16 +4119,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3770,7 +4136,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3778,7 +4144,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3786,7 +4152,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3794,7 +4160,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3802,7 +4168,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3810,7 +4176,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3818,7 +4184,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3826,7 +4192,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3834,7 +4200,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3842,7 +4208,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3850,7 +4216,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3858,7 +4224,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3866,7 +4232,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3874,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3882,7 +4248,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3890,7 +4256,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3898,7 +4264,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3906,7 +4272,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3914,7 +4280,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3922,7 +4288,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3930,7 +4296,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3938,7 +4304,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3946,7 +4312,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3954,7 +4320,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3962,7 +4328,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3970,7 +4336,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3978,7 +4344,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3986,7 +4352,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3994,7 +4360,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4002,7 +4368,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4010,7 +4376,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4018,7 +4384,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4026,7 +4392,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4034,7 +4400,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4042,7 +4408,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4050,7 +4416,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4058,7 +4424,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4066,7 +4432,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4074,7 +4440,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4082,7 +4448,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4090,7 +4456,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4098,7 +4464,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4106,7 +4472,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -68,6 +68,28 @@
           <t>格子ID，根据游戏的行列进行排列，先按列排序，再按从左至右
 格子权重，当前权重再所有列表格子权重总和的占比为实际概率
 格子次数：每次随机出一个结构后，此格子次数-1，表示此格子不能再被选中修改</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+服务器修改时，会先排除不可修改的区域和图案，再在剩下的图案中找一个替换修改</t>
         </r>
       </text>
     </comment>
@@ -136,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="252">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -703,6 +725,27 @@
   </si>
   <si>
     <t>36_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭图案</t>
+  </si>
+  <si>
+    <t>概率出现百搭</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_13</t>
+  </si>
+  <si>
+    <t>0_60|1_20|2_10|3_4</t>
+  </si>
+  <si>
+    <t>0_20|1_40|2_30|3_10</t>
+  </si>
+  <si>
+    <t>概率出现jackpot</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1599,6 +1642,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1611,7 +1655,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2058,7 +2101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2071,31 +2114,31 @@
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="7" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="24" t="s">
@@ -2106,25 +2149,25 @@
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="24" t="s">
@@ -2135,25 +2178,25 @@
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="39" t="s">
@@ -2164,32 +2207,32 @@
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
       <c r="K4" s="38"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>100100</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2198,7 +2241,7 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -2215,16 +2258,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>100100</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2233,7 +2276,7 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -2246,55 +2289,55 @@
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="9">
         <v>100100</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="44"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="9">
         <v>100100</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
       <c r="H8" s="12"/>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="J8" s="12"/>
@@ -2304,26 +2347,26 @@
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <v>100100</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H9" s="12"/>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
       <c r="J9" s="12"/>
@@ -2333,26 +2376,26 @@
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <v>100100</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="12"/>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
       <c r="J10" s="12"/>
@@ -2362,26 +2405,26 @@
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="9">
         <v>100100</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
       <c r="H11" s="12"/>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
       <c r="J11" s="12"/>
@@ -2391,28 +2434,28 @@
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <v>100100</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J12" s="41" t="s">
@@ -2426,7 +2469,7 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <v>100100</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -2459,7 +2502,7 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <v>100100</v>
       </c>
       <c r="C14" s="13" t="s">
@@ -2488,7 +2531,7 @@
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>100100</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -2517,7 +2560,7 @@
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="9">
         <v>100100</v>
       </c>
       <c r="C16" s="19" t="s">
@@ -2546,7 +2589,7 @@
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <v>100100</v>
       </c>
       <c r="C17" s="19" t="s">
@@ -2743,7 +2786,7 @@
         <v>58</v>
       </c>
       <c r="H23" s="27"/>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
       <c r="J23" s="27"/>
@@ -2817,16 +2860,16 @@
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="9">
         <v>100300</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -2835,7 +2878,7 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -2848,16 +2891,16 @@
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="9">
         <v>100300</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -2866,7 +2909,7 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="10" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
@@ -2879,16 +2922,16 @@
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="9">
         <v>100300</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -2897,7 +2940,7 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="61" t="s">
         <v>39</v>
       </c>
@@ -3248,13 +3291,13 @@
       <c r="A41" s="4">
         <v>10120011</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>101200</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="10" t="s">
         <v>137</v>
       </c>
       <c r="F41" s="4" t="s">
@@ -3263,7 +3306,7 @@
       <c r="G41" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -3276,13 +3319,13 @@
       <c r="A42" s="4">
         <v>10120021</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>101200</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="10" t="s">
         <v>137</v>
       </c>
       <c r="F42" s="4" t="s">
@@ -3291,7 +3334,7 @@
       <c r="G42" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H42" s="9"/>
+      <c r="H42" s="10"/>
       <c r="I42" s="61" t="s">
         <v>144</v>
       </c>
@@ -3302,7 +3345,7 @@
       <c r="A43" s="4">
         <v>10120031</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>101200</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3311,7 +3354,7 @@
       <c r="D43" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="10" t="s">
         <v>116</v>
       </c>
       <c r="F43" s="4" t="s">
@@ -3320,7 +3363,7 @@
       <c r="G43" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I43" s="61" t="s">
@@ -3333,7 +3376,7 @@
       <c r="A44" s="4">
         <v>10120032</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="10">
         <v>101200</v>
       </c>
       <c r="C44" s="36" t="s">
@@ -3342,7 +3385,7 @@
       <c r="D44" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="10" t="s">
         <v>120</v>
       </c>
       <c r="F44" s="4" t="s">
@@ -3351,7 +3394,7 @@
       <c r="G44" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I44" s="61" t="s">
@@ -3364,7 +3407,7 @@
       <c r="A45" s="4">
         <v>10120033</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>101200</v>
       </c>
       <c r="C45" s="36" t="s">
@@ -3373,7 +3416,7 @@
       <c r="D45" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="10" t="s">
         <v>123</v>
       </c>
       <c r="F45" s="4" t="s">
@@ -3382,7 +3425,7 @@
       <c r="G45" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I45" s="61" t="s">
@@ -3395,7 +3438,7 @@
       <c r="A46" s="4">
         <v>10120034</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>101200</v>
       </c>
       <c r="C46" s="36" t="s">
@@ -3404,7 +3447,7 @@
       <c r="D46" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="10" t="s">
         <v>126</v>
       </c>
       <c r="F46" s="4" t="s">
@@ -3413,7 +3456,7 @@
       <c r="G46" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I46" s="61" t="s">
@@ -3426,7 +3469,7 @@
       <c r="A47" s="4">
         <v>10120035</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="10">
         <v>101200</v>
       </c>
       <c r="C47" s="36" t="s">
@@ -3435,7 +3478,7 @@
       <c r="D47" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="10" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="4" t="s">
@@ -3444,7 +3487,7 @@
       <c r="G47" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I47" s="61" t="s">
@@ -3457,7 +3500,7 @@
       <c r="A48" s="4">
         <v>10120036</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="10">
         <v>101200</v>
       </c>
       <c r="C48" s="36" t="s">
@@ -3466,7 +3509,7 @@
       <c r="D48" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="10" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="4" t="s">
@@ -3475,7 +3518,7 @@
       <c r="G48" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="10" t="s">
         <v>140</v>
       </c>
       <c r="I48" s="61" t="s">
@@ -3674,7 +3717,7 @@
       <c r="A55" s="4">
         <v>10120051</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="10">
         <v>101200</v>
       </c>
       <c r="C55" s="36" t="s">
@@ -3683,7 +3726,7 @@
       <c r="D55" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="10" t="s">
         <v>51</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -3692,7 +3735,7 @@
       <c r="G55" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I55" s="61" t="s">
@@ -3705,7 +3748,7 @@
       <c r="A56" s="4">
         <v>10120052</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="10">
         <v>101200</v>
       </c>
       <c r="C56" s="36" t="s">
@@ -3714,7 +3757,7 @@
       <c r="D56" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="10" t="s">
         <v>56</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -3723,7 +3766,7 @@
       <c r="G56" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I56" s="61" t="s">
@@ -3736,7 +3779,7 @@
       <c r="A57" s="4">
         <v>10120053</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="10">
         <v>101200</v>
       </c>
       <c r="C57" s="36" t="s">
@@ -3745,7 +3788,7 @@
       <c r="D57" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="10" t="s">
         <v>175</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -3754,7 +3797,7 @@
       <c r="G57" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I57" s="61" t="s">
@@ -3767,7 +3810,7 @@
       <c r="A58" s="4">
         <v>10120054</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="10">
         <v>101200</v>
       </c>
       <c r="C58" s="36" t="s">
@@ -3776,7 +3819,7 @@
       <c r="D58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="10" t="s">
         <v>177</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -3785,7 +3828,7 @@
       <c r="G58" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="H58" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I58" s="61" t="s">
@@ -3798,7 +3841,7 @@
       <c r="A59" s="4">
         <v>10120055</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="10">
         <v>101200</v>
       </c>
       <c r="C59" s="36" t="s">
@@ -3807,7 +3850,7 @@
       <c r="D59" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="10" t="s">
         <v>178</v>
       </c>
       <c r="F59" s="4" t="s">
@@ -3816,7 +3859,7 @@
       <c r="G59" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H59" s="9" t="s">
+      <c r="H59" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I59" s="61" t="s">
@@ -3829,7 +3872,7 @@
       <c r="A60" s="4">
         <v>10120056</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="10">
         <v>101200</v>
       </c>
       <c r="C60" s="36" t="s">
@@ -3838,7 +3881,7 @@
       <c r="D60" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" s="10" t="s">
         <v>179</v>
       </c>
       <c r="F60" s="4" t="s">
@@ -3847,7 +3890,7 @@
       <c r="G60" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H60" s="10" t="s">
         <v>173</v>
       </c>
       <c r="I60" s="61" t="s">
@@ -3860,7 +3903,7 @@
       <c r="A61" s="6">
         <v>10120061</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="10">
         <v>101200</v>
       </c>
       <c r="C61" s="15" t="s">
@@ -3891,7 +3934,7 @@
       <c r="A62" s="6">
         <v>10120062</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="10">
         <v>101200</v>
       </c>
       <c r="C62" s="15" t="s">
@@ -3922,7 +3965,7 @@
       <c r="A63" s="6">
         <v>10120063</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="10">
         <v>101200</v>
       </c>
       <c r="C63" s="15" t="s">
@@ -3953,7 +3996,7 @@
       <c r="A64" s="6">
         <v>10120064</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="10">
         <v>101200</v>
       </c>
       <c r="C64" s="15" t="s">
@@ -3984,7 +4027,7 @@
       <c r="A65" s="6">
         <v>10120065</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="10">
         <v>101200</v>
       </c>
       <c r="C65" s="15" t="s">
@@ -4015,7 +4058,7 @@
       <c r="A66" s="6">
         <v>10120066</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="10">
         <v>101200</v>
       </c>
       <c r="C66" s="15" t="s">
@@ -4041,6 +4084,96 @@
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="46"/>
+    </row>
+    <row r="67" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="3">
+        <v>10140001</v>
+      </c>
+      <c r="B67" s="35">
+        <v>101400</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I67" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="K67" s="55"/>
+    </row>
+    <row r="68" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="3">
+        <v>10140011</v>
+      </c>
+      <c r="B68" s="35">
+        <v>101400</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="I68" s="62" t="s">
+        <v>194</v>
+      </c>
+      <c r="K68" s="55"/>
+    </row>
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="7">
+        <v>10140021</v>
+      </c>
+      <c r="B69" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H69" s="12">
+        <v>13</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K69" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4060,24 +4193,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4085,16 +4218,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4102,16 +4235,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4119,16 +4252,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4136,7 +4269,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4144,7 +4277,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4152,7 +4285,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4160,7 +4293,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4168,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4176,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4184,7 +4317,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4192,7 +4325,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4200,7 +4333,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4208,7 +4341,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4216,7 +4349,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4224,7 +4357,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4232,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4240,7 +4373,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4248,7 +4381,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4256,7 +4389,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4264,7 +4397,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4272,7 +4405,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4280,7 +4413,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4288,7 +4421,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4296,7 +4429,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4304,7 +4437,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4312,7 +4445,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4320,7 +4453,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4328,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4336,7 +4469,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4344,7 +4477,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4352,7 +4485,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4360,7 +4493,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4368,7 +4501,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4376,7 +4509,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4384,7 +4517,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4392,7 +4525,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4400,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4408,7 +4541,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4416,7 +4549,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4424,7 +4557,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4432,7 +4565,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4440,7 +4573,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4448,7 +4581,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4456,7 +4589,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4464,7 +4597,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4472,7 +4605,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="257">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -463,7 +463,7 @@
     <t>必出出Wild-倍率-jackpot</t>
   </si>
   <si>
-    <t>7_1|8_1|9_1|10_1|21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</t>
+    <t>7_1|8_1|9_1|10_1|21_2357|22_1571|23_1178|24_943|25_673|26_589|27_442|28_372|29_289|30_244|31_208|32_179|33_166|34_147|35_135|36_129|37_113|38_102|39_94|40_67</t>
   </si>
   <si>
     <t>倍率图标集合&amp;jackpot</t>
@@ -472,6 +472,24 @@
     <t>8_1_1</t>
   </si>
   <si>
+    <t>必中奖</t>
+  </si>
+  <si>
+    <t>2_1_1|5_1_1</t>
+  </si>
+  <si>
+    <t>2_1</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>4_1</t>
+  </si>
+  <si>
+    <t>5_1</t>
+  </si>
+  <si>
     <t>10_1</t>
   </si>
   <si>
@@ -484,13 +502,13 @@
     <t>免费中获得额外免费次数</t>
   </si>
   <si>
-    <t>0_95|1_5</t>
+    <t>0_98|1_2</t>
   </si>
   <si>
     <t>必然出3个以上免费图案</t>
   </si>
   <si>
-    <t>3_2|4_1</t>
+    <t>3_10|4_1</t>
   </si>
   <si>
     <t>概率出现金色图标</t>
@@ -502,7 +520,7 @@
     <t>修改对应图标</t>
   </si>
   <si>
-    <t>0_40|1_30|2_20|3_10|</t>
+    <t>0_80|1_15|2_10|3_2</t>
   </si>
   <si>
     <t>概率出现金色图标-2条</t>
@@ -514,201 +532,198 @@
     <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
   </si>
   <si>
+    <t>0_90|1_10</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-2筒</t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5条</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-5筒</t>
+  </si>
+  <si>
+    <t>14_1</t>
+  </si>
+  <si>
+    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-八万</t>
+  </si>
+  <si>
+    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-白板</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-红中</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-发财</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>随机出大财神-不足5个</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>概率出现5个以下大财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16</t>
+  </si>
+  <si>
+    <t>0_100|1_25|2_20|3_5|4_1</t>
+  </si>
+  <si>
+    <t>必出大财神-5个</t>
+  </si>
+  <si>
+    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>第1行改为横财神</t>
+  </si>
+  <si>
+    <t>必然出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>4_1_1|7_1_1|10_1_1</t>
+  </si>
+  <si>
+    <t>第2行改为横财神</t>
+  </si>
+  <si>
+    <t>5_1_1|8_1_1|11_1_1</t>
+  </si>
+  <si>
+    <t>第3行改为横财神</t>
+  </si>
+  <si>
+    <t>6_1_1|9_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>正财神</t>
+  </si>
+  <si>
+    <t>第2列改为正财神</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1</t>
+  </si>
+  <si>
+    <t>第3列改为正财神</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>第4列改为正财神</t>
+  </si>
+  <si>
+    <t>10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>中央第1行改为wild</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>中央第2行改为wild</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>中央第3行改为wild</t>
+  </si>
+  <si>
+    <t>正财神第2列</t>
+  </si>
+  <si>
+    <t>中央第2列改为wild</t>
+  </si>
+  <si>
+    <t>中央第3列改为wild</t>
+  </si>
+  <si>
+    <t>中央第4列改为wild</t>
+  </si>
+  <si>
+    <t>横财神2次出现</t>
+  </si>
+  <si>
+    <t>概率出1个正&amp;横财神</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26</t>
+  </si>
+  <si>
+    <t>0_60|1_40</t>
+  </si>
+  <si>
+    <t>23_1</t>
+  </si>
+  <si>
+    <t>正财神2次出现</t>
+  </si>
+  <si>
+    <t>24_1</t>
+  </si>
+  <si>
+    <t>25_1</t>
+  </si>
+  <si>
+    <t>26_1</t>
+  </si>
+  <si>
+    <t>横财神3次出现</t>
+  </si>
+  <si>
+    <t>31_1</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
+  </si>
+  <si>
     <t>0_80|1_20</t>
   </si>
   <si>
-    <t>概率出现金色图标-2筒</t>
-  </si>
-  <si>
-    <t>12_1</t>
-  </si>
-  <si>
-    <t>1_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-5条</t>
-  </si>
-  <si>
-    <t>13_1</t>
-  </si>
-  <si>
-    <t>1_2_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-5筒</t>
-  </si>
-  <si>
-    <t>14_1</t>
-  </si>
-  <si>
-    <t>1_2_3_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-八万</t>
-  </si>
-  <si>
-    <t>1_2_3_4_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-白板</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_7_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-红中</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_8_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>概率出现金色图标-发财</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_9_10_11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>随机出大财神-不足5个</t>
-  </si>
-  <si>
-    <t>9_1</t>
-  </si>
-  <si>
-    <t>概率出现5个以下大财神</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16</t>
-  </si>
-  <si>
-    <t>0_100|1_25|2_20|3_5|4_1</t>
-  </si>
-  <si>
-    <t>必出大财神-5个</t>
-  </si>
-  <si>
-    <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>5_1</t>
-  </si>
-  <si>
-    <t>横财神</t>
-  </si>
-  <si>
-    <t>第1行改为横财神</t>
-  </si>
-  <si>
-    <t>必然出1个正&amp;横财神</t>
-  </si>
-  <si>
-    <t>4_1_1|7_1_1|10_1_1</t>
-  </si>
-  <si>
-    <t>第2行改为横财神</t>
-  </si>
-  <si>
-    <t>5_1_1|8_1_1|11_1_1</t>
-  </si>
-  <si>
-    <t>第3行改为横财神</t>
-  </si>
-  <si>
-    <t>6_1_1|9_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>正财神</t>
-  </si>
-  <si>
-    <t>第2列改为正财神</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1</t>
-  </si>
-  <si>
-    <t>第3列改为正财神</t>
-  </si>
-  <si>
-    <t>7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>第4列改为正财神</t>
-  </si>
-  <si>
-    <t>10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>横财神第1行</t>
-  </si>
-  <si>
-    <t>中央第1行改为wild</t>
-  </si>
-  <si>
-    <t>3_1</t>
-  </si>
-  <si>
-    <t>横财神第2行</t>
-  </si>
-  <si>
-    <t>中央第2行改为wild</t>
-  </si>
-  <si>
-    <t>横财神第3行</t>
-  </si>
-  <si>
-    <t>中央第3行改为wild</t>
-  </si>
-  <si>
-    <t>正财神第2列</t>
-  </si>
-  <si>
-    <t>中央第2列改为wild</t>
-  </si>
-  <si>
-    <t>中央第3列改为wild</t>
-  </si>
-  <si>
-    <t>中央第4列改为wild</t>
-  </si>
-  <si>
-    <t>横财神2次出现</t>
-  </si>
-  <si>
-    <t>概率出1个正&amp;横财神</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16_21_22_23_24_25_26</t>
-  </si>
-  <si>
-    <t>0_60|1_40</t>
-  </si>
-  <si>
-    <t>23_1</t>
-  </si>
-  <si>
-    <t>正财神2次出现</t>
-  </si>
-  <si>
-    <t>24_1</t>
-  </si>
-  <si>
-    <t>25_1</t>
-  </si>
-  <si>
-    <t>26_1</t>
-  </si>
-  <si>
-    <t>横财神3次出现</t>
-  </si>
-  <si>
-    <t>31_1</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15_16_21_22_23_24_25_26_31_32_33_34_35_36</t>
-  </si>
-  <si>
     <t>32_1</t>
   </si>
   <si>
@@ -739,10 +754,10 @@
     <t>12_13</t>
   </si>
   <si>
-    <t>0_60|1_20|2_10|3_4</t>
-  </si>
-  <si>
-    <t>0_20|1_40|2_30|3_10</t>
+    <t>0_80|1_12|2_6|3_2</t>
+  </si>
+  <si>
+    <t>0_50|1_25|2_15|3_10</t>
   </si>
   <si>
     <t>概率出现jackpot</t>
@@ -1100,12 +1115,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2101,7 +2116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2918,7 +2933,7 @@
       <c r="J27" s="41"/>
       <c r="K27" s="42"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:11">
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
@@ -2946,580 +2961,586 @@
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="51"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A29" s="31">
+      <c r="L28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A29" s="1">
+        <v>10030041</v>
+      </c>
+      <c r="B29" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="51"/>
+      <c r="L29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A30" s="1">
+        <v>10030042</v>
+      </c>
+      <c r="B30" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="51"/>
+      <c r="L30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A31" s="1">
+        <v>10030043</v>
+      </c>
+      <c r="B31" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="K31" s="51"/>
+      <c r="L31"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A32" s="1">
+        <v>10030044</v>
+      </c>
+      <c r="B32" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="51"/>
+      <c r="L32"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A33" s="1">
+        <v>10030045</v>
+      </c>
+      <c r="B33" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="51"/>
+      <c r="L33"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A34" s="31">
         <v>10070011</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B34" s="32">
         <v>100700</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="31" t="s">
+      <c r="C34" s="32"/>
+      <c r="D34" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" s="31" t="s">
+      <c r="E34" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" s="32"/>
-      <c r="I29" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="J29" s="31"/>
-      <c r="K29" s="53"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A30" s="31">
+      <c r="G34" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="H34" s="32"/>
+      <c r="I34" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="J34" s="31"/>
+      <c r="K34" s="53"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A35" s="31">
         <v>10070012</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B35" s="32">
         <v>100700</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="31" t="s">
+      <c r="C35" s="32"/>
+      <c r="D35" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="J30" s="31"/>
-      <c r="K30" s="53"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A31" s="33">
+      <c r="E35" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" s="32"/>
+      <c r="I35" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="J35" s="31"/>
+      <c r="K35" s="53"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A36" s="33">
         <v>10070021</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B36" s="34">
         <v>100700</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="G31" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="33" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="33"/>
-      <c r="K31" s="54"/>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A32" s="3">
-        <v>10070030</v>
-      </c>
-      <c r="B32" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="3" t="s">
+      <c r="F36" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H32" s="35"/>
-      <c r="I32" s="62" t="s">
-        <v>114</v>
-      </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="55"/>
-    </row>
-    <row r="33" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A33" s="3">
-        <v>10070031</v>
-      </c>
-      <c r="B33" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="35" t="s">
+      <c r="H36" s="34"/>
+      <c r="I36" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H33" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="I33" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="55"/>
-    </row>
-    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A34" s="3">
-        <v>10070032</v>
-      </c>
-      <c r="B34" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H34" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="I34" s="62" t="str">
-        <f>I33</f>
-        <v>0_80|1_20</v>
-      </c>
-      <c r="K34" s="55"/>
-    </row>
-    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A35" s="3">
-        <v>10070033</v>
-      </c>
-      <c r="B35" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="I35" s="62" t="str">
-        <f t="shared" ref="I35:I40" si="0">I34</f>
-        <v>0_80|1_20</v>
-      </c>
-      <c r="K35" s="55"/>
-    </row>
-    <row r="36" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A36" s="3">
-        <v>10070034</v>
-      </c>
-      <c r="B36" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="I36" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_80|1_20</v>
-      </c>
-      <c r="K36" s="55"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="54"/>
     </row>
     <row r="37" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A37" s="3">
-        <v>10070035</v>
+        <v>10070030</v>
       </c>
       <c r="B37" s="35">
         <v>100700</v>
       </c>
       <c r="C37" s="35"/>
       <c r="D37" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H37" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_80|1_20</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H37" s="35"/>
+      <c r="I37" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="J37" s="3"/>
       <c r="K37" s="55"/>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A38" s="3">
-        <v>10070036</v>
+        <v>10070031</v>
       </c>
       <c r="B38" s="35">
         <v>100700</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="I38" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_80|1_20</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="I38" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="J38" s="3"/>
       <c r="K38" s="55"/>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A39" s="3">
-        <v>10070037</v>
+        <v>10070032</v>
       </c>
       <c r="B39" s="35">
         <v>100700</v>
       </c>
       <c r="C39" s="35"/>
       <c r="D39" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I39" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_80|1_20</v>
+        <f>I38</f>
+        <v>0_90|1_10</v>
       </c>
       <c r="K39" s="55"/>
     </row>
     <row r="40" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A40" s="3">
-        <v>10070038</v>
+        <v>10070033</v>
       </c>
       <c r="B40" s="35">
         <v>100700</v>
       </c>
       <c r="C40" s="35"/>
       <c r="D40" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="I40" s="62" t="str">
+        <f t="shared" ref="I40:I45" si="0">I39</f>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K40" s="55"/>
+    </row>
+    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A41" s="3">
+        <v>10070034</v>
+      </c>
+      <c r="B41" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C41" s="35"/>
+      <c r="D41" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K41" s="55"/>
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A42" s="3">
+        <v>10070035</v>
+      </c>
+      <c r="B42" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C42" s="35"/>
+      <c r="D42" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E42" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="I42" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K42" s="55"/>
+    </row>
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A43" s="3">
+        <v>10070036</v>
+      </c>
+      <c r="B43" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C43" s="35"/>
+      <c r="D43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="I43" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K43" s="55"/>
+    </row>
+    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A44" s="3">
+        <v>10070037</v>
+      </c>
+      <c r="B44" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C44" s="35"/>
+      <c r="D44" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H44" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I44" s="62" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K44" s="55"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="3">
+        <v>10070038</v>
+      </c>
+      <c r="B45" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C45" s="35"/>
+      <c r="D45" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="I40" s="62" t="str">
+      <c r="F45" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" s="62" t="str">
         <f t="shared" si="0"/>
-        <v>0_80|1_20</v>
-      </c>
-      <c r="K40" s="55"/>
-    </row>
-    <row r="41" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A41" s="4">
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K45" s="55"/>
+    </row>
+    <row r="46" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A46" s="4">
         <v>10120011</v>
-      </c>
-      <c r="B41" s="10">
-        <v>101200</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="43"/>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A42" s="4">
-        <v>10120021</v>
-      </c>
-      <c r="B42" s="10">
-        <v>101200</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H42" s="10"/>
-      <c r="I42" s="61" t="s">
-        <v>144</v>
-      </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="43"/>
-    </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A43" s="4">
-        <v>10120031</v>
-      </c>
-      <c r="B43" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I43" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="43"/>
-    </row>
-    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A44" s="4">
-        <v>10120032</v>
-      </c>
-      <c r="B44" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="43"/>
-    </row>
-    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="4">
-        <v>10120033</v>
-      </c>
-      <c r="B45" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I45" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J45" s="4"/>
-      <c r="K45" s="43"/>
-    </row>
-    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A46" s="4">
-        <v>10120034</v>
       </c>
       <c r="B46" s="10">
         <v>101200</v>
       </c>
-      <c r="C46" s="36" t="s">
-        <v>153</v>
-      </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I46" s="61" t="s">
-        <v>39</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="43"/>
     </row>
-    <row r="47" s="4" customFormat="1" ht="16.5" spans="1:11">
+    <row r="47" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A47" s="4">
-        <v>10120035</v>
+        <v>10120021</v>
       </c>
       <c r="B47" s="10">
         <v>101200</v>
       </c>
-      <c r="C47" s="36" t="s">
-        <v>153</v>
-      </c>
       <c r="D47" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>140</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" s="10"/>
       <c r="I47" s="61" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="43"/>
     </row>
     <row r="48" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A48" s="4">
-        <v>10120036</v>
+        <v>10120031</v>
       </c>
       <c r="B48" s="10">
         <v>101200</v>
       </c>
       <c r="C48" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="H48" s="10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I48" s="61" t="s">
         <v>39</v>
@@ -3527,653 +3548,808 @@
       <c r="J48" s="4"/>
       <c r="K48" s="43"/>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="5">
-        <v>10120041</v>
-      </c>
-      <c r="B49" s="36">
+    <row r="49" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="4">
+        <v>10120032</v>
+      </c>
+      <c r="B49" s="10">
         <v>101200</v>
       </c>
       <c r="C49" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I49" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="43"/>
+    </row>
+    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="4">
+        <v>10120033</v>
+      </c>
+      <c r="B50" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I50" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="43"/>
+    </row>
+    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="4">
+        <v>10120034</v>
+      </c>
+      <c r="B51" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C51" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="H51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I51" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="43"/>
+    </row>
+    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="4">
+        <v>10120035</v>
+      </c>
+      <c r="B52" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E49" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H49" s="36">
-        <v>10</v>
-      </c>
-      <c r="I49" s="63" t="s">
+      <c r="E52" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="56"/>
-    </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="5">
-        <v>10120042</v>
-      </c>
-      <c r="B50" s="36">
+      <c r="H52" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I52" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="43"/>
+    </row>
+    <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="4">
+        <v>10120036</v>
+      </c>
+      <c r="B53" s="10">
         <v>101200</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C53" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E53" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E50" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H50" s="36">
-        <v>10</v>
-      </c>
-      <c r="I50" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="56"/>
-    </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A51" s="5">
-        <v>10120043</v>
-      </c>
-      <c r="B51" s="36">
-        <v>101200</v>
-      </c>
-      <c r="C51" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H51" s="36">
-        <v>10</v>
-      </c>
-      <c r="I51" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="56"/>
-    </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A52" s="5">
-        <v>10120044</v>
-      </c>
-      <c r="B52" s="36">
-        <v>101200</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H52" s="36">
-        <v>10</v>
-      </c>
-      <c r="I52" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="56"/>
-    </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A53" s="5">
-        <v>10120045</v>
-      </c>
-      <c r="B53" s="36">
-        <v>101200</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H53" s="36">
-        <v>10</v>
-      </c>
-      <c r="I53" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="J53" s="5"/>
-      <c r="K53" s="56"/>
+      <c r="H53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I53" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="43"/>
     </row>
     <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="5">
-        <v>10120046</v>
+        <v>10120041</v>
       </c>
       <c r="B54" s="36">
         <v>101200</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H54" s="36">
         <v>10</v>
       </c>
       <c r="I54" s="63" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="56"/>
     </row>
-    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="4">
-        <v>10120051</v>
-      </c>
-      <c r="B55" s="10">
+    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="5">
+        <v>10120042</v>
+      </c>
+      <c r="B55" s="36">
         <v>101200</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I55" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="J55" s="4"/>
-      <c r="K55" s="43"/>
-    </row>
-    <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="4">
-        <v>10120052</v>
-      </c>
-      <c r="B56" s="10">
+        <v>155</v>
+      </c>
+      <c r="H55" s="36">
+        <v>10</v>
+      </c>
+      <c r="I55" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J55" s="5"/>
+      <c r="K55" s="56"/>
+    </row>
+    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="5">
+        <v>10120043</v>
+      </c>
+      <c r="B56" s="36">
         <v>101200</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I56" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="J56" s="4"/>
-      <c r="K56" s="43"/>
-    </row>
-    <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A57" s="4">
-        <v>10120053</v>
-      </c>
-      <c r="B57" s="10">
+        <v>157</v>
+      </c>
+      <c r="H56" s="36">
+        <v>10</v>
+      </c>
+      <c r="I56" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J56" s="5"/>
+      <c r="K56" s="56"/>
+    </row>
+    <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="5">
+        <v>10120044</v>
+      </c>
+      <c r="B57" s="36">
         <v>101200</v>
       </c>
       <c r="C57" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F57" s="4" t="s">
+      <c r="D57" s="5" t="s">
         <v>172</v>
       </c>
+      <c r="E57" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G57" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="H57" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="36">
+        <v>10</v>
+      </c>
+      <c r="I57" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J57" s="5"/>
+      <c r="K57" s="56"/>
+    </row>
+    <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="5">
+        <v>10120045</v>
+      </c>
+      <c r="B58" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="I57" s="61" t="s">
+      <c r="E58" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H58" s="36">
+        <v>10</v>
+      </c>
+      <c r="I58" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J58" s="5"/>
+      <c r="K58" s="56"/>
+    </row>
+    <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A59" s="5">
+        <v>10120046</v>
+      </c>
+      <c r="B59" s="36">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J57" s="4"/>
-      <c r="K57" s="43"/>
-    </row>
-    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A58" s="4">
-        <v>10120054</v>
-      </c>
-      <c r="B58" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I58" s="61" t="s">
+      <c r="E59" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="J58" s="4"/>
-      <c r="K58" s="43"/>
-    </row>
-    <row r="59" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A59" s="4">
-        <v>10120055</v>
-      </c>
-      <c r="B59" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C59" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G59" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I59" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="J59" s="4"/>
-      <c r="K59" s="43"/>
+        <v>164</v>
+      </c>
+      <c r="H59" s="36">
+        <v>10</v>
+      </c>
+      <c r="I59" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="J59" s="5"/>
+      <c r="K59" s="56"/>
     </row>
     <row r="60" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="4">
-        <v>10120056</v>
+        <v>10120051</v>
       </c>
       <c r="B60" s="10">
         <v>101200</v>
       </c>
       <c r="C60" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G60" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I60" s="61" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="43"/>
     </row>
-    <row r="61" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A61" s="6">
-        <v>10120061</v>
+    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="4">
+        <v>10120052</v>
       </c>
       <c r="B61" s="10">
         <v>101200</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>181</v>
+      <c r="C61" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I61" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="J61" s="6"/>
-      <c r="K61" s="46"/>
-    </row>
-    <row r="62" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A62" s="6">
-        <v>10120062</v>
+        <v>176</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I61" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J61" s="4"/>
+      <c r="K61" s="43"/>
+    </row>
+    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="4">
+        <v>10120053</v>
       </c>
       <c r="B62" s="10">
         <v>101200</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>183</v>
+      <c r="C62" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H62" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I62" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="J62" s="6"/>
-      <c r="K62" s="46"/>
-    </row>
-    <row r="63" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A63" s="6">
-        <v>10120063</v>
+        <v>176</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I62" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J62" s="4"/>
+      <c r="K62" s="43"/>
+    </row>
+    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="4">
+        <v>10120054</v>
       </c>
       <c r="B63" s="10">
         <v>101200</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>184</v>
+      <c r="D63" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="H63" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I63" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="J63" s="6"/>
-      <c r="K63" s="46"/>
-    </row>
-    <row r="64" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A64" s="6">
-        <v>10120064</v>
+        <v>176</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="43"/>
+    </row>
+    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="4">
+        <v>10120055</v>
       </c>
       <c r="B64" s="10">
         <v>101200</v>
       </c>
-      <c r="C64" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>186</v>
+      <c r="C64" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>182</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I64" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="46"/>
-    </row>
-    <row r="65" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A65" s="6">
-        <v>10120065</v>
+        <v>176</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I64" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="43"/>
+    </row>
+    <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A65" s="4">
+        <v>10120056</v>
       </c>
       <c r="B65" s="10">
         <v>101200</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>187</v>
+      <c r="C65" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="I65" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="J65" s="6"/>
-      <c r="K65" s="46"/>
+        <v>176</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I65" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="J65" s="4"/>
+      <c r="K65" s="43"/>
     </row>
     <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="6">
-        <v>10120066</v>
+        <v>10120061</v>
       </c>
       <c r="B66" s="10">
         <v>101200</v>
       </c>
       <c r="C66" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>188</v>
-      </c>
       <c r="F66" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I66" s="58" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="46"/>
     </row>
-    <row r="67" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A67" s="3">
+    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="6">
+        <v>10120062</v>
+      </c>
+      <c r="B67" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="46"/>
+    </row>
+    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="6">
+        <v>10120063</v>
+      </c>
+      <c r="B68" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I68" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="J68" s="6"/>
+      <c r="K68" s="46"/>
+    </row>
+    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="6">
+        <v>10120064</v>
+      </c>
+      <c r="B69" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="J69" s="6"/>
+      <c r="K69" s="46"/>
+    </row>
+    <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A70" s="6">
+        <v>10120065</v>
+      </c>
+      <c r="B70" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I70" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="J70" s="6"/>
+      <c r="K70" s="46"/>
+    </row>
+    <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A71" s="6">
+        <v>10120066</v>
+      </c>
+      <c r="B71" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I71" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="J71" s="6"/>
+      <c r="K71" s="46"/>
+    </row>
+    <row r="72" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A72" s="3">
         <v>10140001</v>
       </c>
-      <c r="B67" s="35">
+      <c r="B72" s="35">
         <v>101400</v>
       </c>
-      <c r="C67" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E67" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="I67" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="K67" s="55"/>
-    </row>
-    <row r="68" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A68" s="3">
+      <c r="C72" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="I72" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="K72" s="55"/>
+    </row>
+    <row r="73" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A73" s="3">
         <v>10140011</v>
       </c>
-      <c r="B68" s="35">
+      <c r="B73" s="35">
         <v>101400</v>
       </c>
-      <c r="C68" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E68" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H68" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="I68" s="62" t="s">
+      <c r="C73" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="K68" s="55"/>
-    </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A69" s="7">
+      <c r="D73" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E73" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="I73" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="K73" s="55"/>
+    </row>
+    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A74" s="7">
         <v>10140021</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B74" s="12">
         <v>101400</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H69" s="12">
+      <c r="C74" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H74" s="12">
         <v>13</v>
       </c>
-      <c r="I69" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="K69" s="44"/>
+      <c r="I74" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K74" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4193,24 +4369,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4218,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4235,16 +4411,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4252,16 +4428,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4269,7 +4445,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4277,7 +4453,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4285,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4293,7 +4469,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4301,7 +4477,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4309,7 +4485,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4317,7 +4493,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4325,7 +4501,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4333,7 +4509,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4341,7 +4517,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4349,7 +4525,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4357,7 +4533,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4365,7 +4541,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4373,7 +4549,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4381,7 +4557,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4389,7 +4565,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4397,7 +4573,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4405,7 +4581,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4413,7 +4589,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4421,7 +4597,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4429,7 +4605,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4437,7 +4613,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4445,7 +4621,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4453,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4461,7 +4637,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4469,7 +4645,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4477,7 +4653,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4485,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4493,7 +4669,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4501,7 +4677,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4509,7 +4685,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4517,7 +4693,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4525,7 +4701,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4533,7 +4709,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4541,7 +4717,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4549,7 +4725,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4557,7 +4733,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4565,7 +4741,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4573,7 +4749,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4581,7 +4757,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4589,7 +4765,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4597,7 +4773,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4605,7 +4781,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="258">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -601,7 +601,7 @@
     <t>10_11_12_13_14_15_16</t>
   </si>
   <si>
-    <t>0_100|1_25|2_20|3_5|4_1</t>
+    <t>0_200|1_15|2_10|3_5|4_1</t>
   </si>
   <si>
     <t>必出大财神-5个</t>
@@ -754,10 +754,13 @@
     <t>12_13</t>
   </si>
   <si>
-    <t>0_80|1_12|2_6|3_2</t>
-  </si>
-  <si>
-    <t>0_50|1_25|2_15|3_10</t>
+    <t>0_70|1_30</t>
+  </si>
+  <si>
+    <t>1_100</t>
+  </si>
+  <si>
+    <t>概率出现jackpot图案</t>
   </si>
   <si>
     <t>概率出现jackpot</t>
@@ -4316,7 +4319,7 @@
       <c r="H73" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I73" s="62" t="s">
+      <c r="I73" s="3" t="s">
         <v>199</v>
       </c>
       <c r="K73" s="55"/>
@@ -4329,10 +4332,10 @@
         <v>101400</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>129</v>
@@ -4369,24 +4372,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" t="s">
-        <v>203</v>
-      </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4394,16 +4397,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4411,16 +4414,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4428,16 +4431,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4445,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4453,7 +4456,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4461,7 +4464,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4469,7 +4472,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4477,7 +4480,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4485,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4493,7 +4496,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4501,7 +4504,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4509,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4517,7 +4520,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4525,7 +4528,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4533,7 +4536,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4541,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4549,7 +4552,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4557,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4565,7 +4568,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4573,7 +4576,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4581,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4589,7 +4592,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4597,7 +4600,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4605,7 +4608,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4613,7 +4616,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4621,7 +4624,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4629,7 +4632,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4637,7 +4640,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4645,7 +4648,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4653,7 +4656,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4661,7 +4664,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4669,7 +4672,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4677,7 +4680,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4685,7 +4688,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4693,7 +4696,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4701,7 +4704,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4709,7 +4712,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4717,7 +4720,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4725,7 +4728,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4733,7 +4736,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4741,7 +4744,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4749,7 +4752,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4757,7 +4760,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4765,7 +4768,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4773,7 +4776,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4781,7 +4784,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="260">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -751,19 +751,25 @@
     <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
   </si>
   <si>
-    <t>12_13</t>
-  </si>
-  <si>
-    <t>0_70|1_30</t>
-  </si>
-  <si>
-    <t>1_100</t>
-  </si>
-  <si>
-    <t>概率出现jackpot图案</t>
+    <t>12_13_1</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_30</t>
+  </si>
+  <si>
+    <t>1_70|2_20|3_10</t>
+  </si>
+  <si>
+    <t>必出出现jackpot图案</t>
   </si>
   <si>
     <t>概率出现jackpot</t>
+  </si>
+  <si>
+    <t>概率出现jackpot图案，最多2个</t>
+  </si>
+  <si>
+    <t>0_80|1_10|2_5</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1118,12 +1124,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2119,7 +2125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -4346,13 +4352,43 @@
       <c r="G74" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="H74" s="12">
-        <v>13</v>
+      <c r="H74" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>109</v>
       </c>
       <c r="K74" s="44"/>
+    </row>
+    <row r="75" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A75" s="7">
+        <v>10140022</v>
+      </c>
+      <c r="B75" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="I75" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="K75" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4372,24 +4408,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4397,16 +4433,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4414,16 +4450,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4431,16 +4467,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4448,7 +4484,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4456,7 +4492,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4464,7 +4500,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4472,7 +4508,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4480,7 +4516,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4488,7 +4524,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4496,7 +4532,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4504,7 +4540,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4512,7 +4548,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4520,7 +4556,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4528,7 +4564,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4536,7 +4572,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4544,7 +4580,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4552,7 +4588,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4560,7 +4596,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4568,7 +4604,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4576,7 +4612,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4584,7 +4620,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4592,7 +4628,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4600,7 +4636,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4608,7 +4644,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4616,7 +4652,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4624,7 +4660,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4632,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4640,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4648,7 +4684,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4656,7 +4692,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4664,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4672,7 +4708,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4680,7 +4716,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4688,7 +4724,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4696,7 +4732,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4704,7 +4740,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4712,7 +4748,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4720,7 +4756,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4728,7 +4764,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4736,7 +4772,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4744,7 +4780,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4752,7 +4788,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4760,7 +4796,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4768,7 +4804,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4776,7 +4812,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4784,7 +4820,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="261">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -754,10 +754,10 @@
     <t>12_13_1</t>
   </si>
   <si>
-    <t>0_40|1_30|2_30</t>
-  </si>
-  <si>
-    <t>1_70|2_20|3_10</t>
+    <t>0_50|1_30|2_20</t>
+  </si>
+  <si>
+    <t>1_60|2_25|3_15</t>
   </si>
   <si>
     <t>必出出现jackpot图案</t>
@@ -766,10 +766,13 @@
     <t>概率出现jackpot</t>
   </si>
   <si>
-    <t>概率出现jackpot图案，最多2个</t>
-  </si>
-  <si>
-    <t>0_80|1_10|2_5</t>
+    <t>第2列概率出现jackpot图案，最多1个</t>
+  </si>
+  <si>
+    <t>0_95|1_5</t>
+  </si>
+  <si>
+    <t>第3列概率出现jackpot图案，最多1个</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2125,12 +2128,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="10.125" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="28.625" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="32.2" customWidth="1"/>
     <col min="6" max="6" width="25.1416666666667" customWidth="1"/>
@@ -4380,7 +4383,7 @@
         <v>119</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>129</v>
@@ -4389,6 +4392,36 @@
         <v>203</v>
       </c>
       <c r="K75" s="44"/>
+    </row>
+    <row r="76" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A76" s="7">
+        <v>10140023</v>
+      </c>
+      <c r="B76" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="I76" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="K76" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4408,24 +4441,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" t="s">
         <v>207</v>
       </c>
-      <c r="D2" t="s">
-        <v>206</v>
-      </c>
       <c r="E2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4433,16 +4466,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4450,16 +4483,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4467,16 +4500,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4484,7 +4517,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4492,7 +4525,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4500,7 +4533,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4508,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4516,7 +4549,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4524,7 +4557,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4532,7 +4565,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4540,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4548,7 +4581,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4556,7 +4589,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4564,7 +4597,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4572,7 +4605,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4580,7 +4613,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4588,7 +4621,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4596,7 +4629,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4604,7 +4637,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4612,7 +4645,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4620,7 +4653,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4628,7 +4661,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4636,7 +4669,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4644,7 +4677,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4652,7 +4685,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4660,7 +4693,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4668,7 +4701,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4676,7 +4709,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4684,7 +4717,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4692,7 +4725,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4700,7 +4733,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4708,7 +4741,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4716,7 +4749,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4724,7 +4757,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4732,7 +4765,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4740,7 +4773,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4748,7 +4781,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4756,7 +4789,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4764,7 +4797,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4772,7 +4805,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4780,7 +4813,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4788,7 +4821,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4796,7 +4829,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4804,7 +4837,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4812,7 +4845,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4820,7 +4853,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="271">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -493,22 +493,52 @@
     <t>10_1</t>
   </si>
   <si>
+    <t>免费中获得额外免费次数</t>
+  </si>
+  <si>
     <t>5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1</t>
   </si>
   <si>
-    <t>0_15|1_3|2_2</t>
-  </si>
-  <si>
-    <t>免费中获得额外免费次数</t>
-  </si>
-  <si>
     <t>0_98|1_2</t>
   </si>
   <si>
-    <t>必然出3个以上免费图案</t>
-  </si>
-  <si>
-    <t>3_10|4_1</t>
+    <t>2列概率出现3个以下免费图案</t>
+  </si>
+  <si>
+    <t>概率出现1个免费图案</t>
+  </si>
+  <si>
+    <t>0_85|1_15</t>
+  </si>
+  <si>
+    <t>3列概率出现3个以下免费图案</t>
+  </si>
+  <si>
+    <t>2列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>12次&amp;14次免费</t>
+  </si>
+  <si>
+    <t>3列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>4列必然出1个免费图案</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1</t>
+  </si>
+  <si>
+    <t>4列必然额外出1个免费图案</t>
+  </si>
+  <si>
+    <t>14次免费</t>
+  </si>
+  <si>
+    <t>16_1_1</t>
+  </si>
+  <si>
+    <t>0_10|1_1</t>
   </si>
   <si>
     <t>概率出现金色图标</t>
@@ -947,11 +977,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1661,7 +1692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1787,6 +1818,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2128,7 +2160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2142,6 +2174,10 @@
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
     <col min="11" max="11" width="11.6166666666667" style="8" customWidth="1"/>
+    <col min="12" max="12" width="9.375"/>
+    <col min="13" max="13" width="12.5"/>
+    <col min="14" max="14" width="9.375"/>
+    <col min="17" max="17" width="9.375"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
@@ -2335,7 +2371,7 @@
         <v>38</v>
       </c>
       <c r="H7" s="12"/>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="58" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
@@ -2548,7 +2584,7 @@
         <v>38</v>
       </c>
       <c r="H14" s="15"/>
-      <c r="I14" s="58" t="s">
+      <c r="I14" s="59" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
@@ -2606,7 +2642,7 @@
         <v>38</v>
       </c>
       <c r="H16" s="21"/>
-      <c r="I16" s="59" t="s">
+      <c r="I16" s="60" t="s">
         <v>39</v>
       </c>
       <c r="J16" s="20"/>
@@ -2697,7 +2733,7 @@
         <v>38</v>
       </c>
       <c r="H19" s="27"/>
-      <c r="I19" s="60" t="s">
+      <c r="I19" s="61" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
@@ -2968,7 +3004,7 @@
         <v>103</v>
       </c>
       <c r="H28" s="10"/>
-      <c r="I28" s="61" t="s">
+      <c r="I28" s="62" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
@@ -3000,7 +3036,7 @@
       <c r="H29" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I29" s="61" t="s">
+      <c r="I29" s="62" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
@@ -3032,7 +3068,7 @@
       <c r="H30" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="61" t="s">
+      <c r="I30" s="62" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
@@ -3064,7 +3100,7 @@
       <c r="H31" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="61" t="s">
+      <c r="I31" s="62" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
@@ -3096,14 +3132,14 @@
       <c r="H32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="61" t="s">
+      <c r="I32" s="62" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="51"/>
       <c r="L32"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:12">
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
@@ -3128,16 +3164,18 @@
       <c r="H33" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="61" t="s">
+      <c r="I33" s="62" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="51"/>
-      <c r="L33"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A34" s="31">
-        <v>10070011</v>
+        <v>10070010</v>
       </c>
       <c r="B34" s="32">
         <v>100700</v>
@@ -3150,276 +3188,268 @@
         <v>110</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H34" s="32"/>
       <c r="I34" s="31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J34" s="31"/>
-      <c r="K34" s="53"/>
+      <c r="K34" s="54"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35" s="31">
-        <v>10070012</v>
+        <v>10070011</v>
       </c>
       <c r="B35" s="32">
         <v>100700</v>
       </c>
       <c r="C35" s="32"/>
       <c r="D35" s="31" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="E35" s="32" t="s">
         <v>110</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="H35" s="32"/>
       <c r="I35" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J35" s="31"/>
-      <c r="K35" s="53"/>
+      <c r="K35" s="54"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A36" s="33">
+      <c r="A36" s="31">
+        <v>10070012</v>
+      </c>
+      <c r="B36" s="32">
+        <v>100700</v>
+      </c>
+      <c r="C36" s="32"/>
+      <c r="D36" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" s="32"/>
+      <c r="I36" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="J36" s="31"/>
+      <c r="K36" s="54"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A37" s="33">
         <v>10070021</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B37" s="34">
         <v>100700</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" s="34" t="s">
+      <c r="C37" s="34"/>
+      <c r="D37" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="F36" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="G36" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="J36" s="33"/>
-      <c r="K36" s="54"/>
-    </row>
-    <row r="37" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A37" s="3">
-        <v>10070030</v>
-      </c>
-      <c r="B37" s="35">
+      <c r="F37" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="34"/>
+      <c r="I37" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="33"/>
+      <c r="K37" s="55"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A38" s="33">
+        <v>10070022</v>
+      </c>
+      <c r="B38" s="34">
         <v>100700</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="C38" s="34"/>
+      <c r="D38" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="55"/>
-    </row>
-    <row r="38" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A38" s="3">
-        <v>10070031</v>
-      </c>
-      <c r="B38" s="35">
+      <c r="G38" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38" s="34"/>
+      <c r="I38" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="33"/>
+      <c r="K38" s="55"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A39" s="33">
+        <v>10070023</v>
+      </c>
+      <c r="B39" s="34">
         <v>100700</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="3" t="s">
+      <c r="C39" s="34"/>
+      <c r="D39" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="35" t="s">
+      <c r="E39" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G39" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="35" t="s">
+      <c r="H39" s="34"/>
+      <c r="I39" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="33"/>
+      <c r="K39" s="55"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A40" s="33">
+        <v>10070024</v>
+      </c>
+      <c r="B40" s="34">
+        <v>100700</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="I38" s="62" t="s">
+      <c r="E40" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="55"/>
-    </row>
-    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A39" s="3">
-        <v>10070032</v>
-      </c>
-      <c r="B39" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="3" t="s">
+      <c r="G40" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="35" t="s">
+      <c r="H40" s="34"/>
+      <c r="I40" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="I39" s="62" t="str">
-        <f>I38</f>
-        <v>0_90|1_10</v>
-      </c>
-      <c r="K39" s="55"/>
-    </row>
-    <row r="40" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A40" s="3">
-        <v>10070033</v>
-      </c>
-      <c r="B40" s="35">
-        <v>100700</v>
-      </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="I40" s="62" t="str">
-        <f t="shared" ref="I40:I45" si="0">I39</f>
-        <v>0_90|1_10</v>
-      </c>
+      <c r="J40" s="33"/>
       <c r="K40" s="55"/>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A41" s="3">
-        <v>10070034</v>
+        <v>10070030</v>
       </c>
       <c r="B41" s="35">
         <v>100700</v>
       </c>
       <c r="C41" s="35"/>
       <c r="D41" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E41" s="35" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="I41" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
-      </c>
-      <c r="K41" s="55"/>
+        <v>112</v>
+      </c>
+      <c r="H41" s="35"/>
+      <c r="I41" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="56"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A42" s="3">
-        <v>10070035</v>
+        <v>10070031</v>
       </c>
       <c r="B42" s="35">
         <v>100700</v>
       </c>
       <c r="C42" s="35"/>
       <c r="D42" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="I42" s="62" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
-      </c>
-      <c r="K42" s="55"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="56"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A43" s="3">
-        <v>10070036</v>
+        <v>10070032</v>
       </c>
       <c r="B43" s="35">
         <v>100700</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="35" t="s">
-        <v>36</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H43" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="62" t="str">
-        <f t="shared" si="0"/>
+      <c r="I43" s="63" t="str">
+        <f>I42</f>
         <v>0_90|1_10</v>
       </c>
-      <c r="K43" s="55"/>
+      <c r="K43" s="56"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A44" s="3">
-        <v>10070037</v>
+        <v>10070033</v>
       </c>
       <c r="B44" s="35">
         <v>100700</v>
@@ -3429,256 +3459,248 @@
         <v>138</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="I44" s="62" t="str">
+        <v>140</v>
+      </c>
+      <c r="I44" s="63" t="str">
+        <f t="shared" ref="I44:I49" si="0">I43</f>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K44" s="56"/>
+    </row>
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A45" s="3">
+        <v>10070034</v>
+      </c>
+      <c r="B45" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C45" s="35"/>
+      <c r="D45" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I45" s="63" t="str">
         <f t="shared" si="0"/>
         <v>0_90|1_10</v>
       </c>
-      <c r="K44" s="55"/>
-    </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A45" s="3">
-        <v>10070038</v>
-      </c>
-      <c r="B45" s="35">
+      <c r="K45" s="56"/>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A46" s="3">
+        <v>10070035</v>
+      </c>
+      <c r="B46" s="35">
         <v>100700</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E45" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H45" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="I45" s="62" t="str">
+      <c r="C46" s="35"/>
+      <c r="D46" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H46" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="I46" s="63" t="str">
         <f t="shared" si="0"/>
         <v>0_90|1_10</v>
       </c>
-      <c r="K45" s="55"/>
-    </row>
-    <row r="46" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A46" s="4">
+      <c r="K46" s="56"/>
+    </row>
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A47" s="3">
+        <v>10070036</v>
+      </c>
+      <c r="B47" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C47" s="35"/>
+      <c r="D47" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="I47" s="63" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K47" s="56"/>
+    </row>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="3">
+        <v>10070037</v>
+      </c>
+      <c r="B48" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C48" s="35"/>
+      <c r="D48" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H48" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I48" s="63" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K48" s="56"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="3">
+        <v>10070038</v>
+      </c>
+      <c r="B49" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C49" s="35"/>
+      <c r="D49" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49" s="63" t="str">
+        <f t="shared" si="0"/>
+        <v>0_90|1_10</v>
+      </c>
+      <c r="K49" s="56"/>
+    </row>
+    <row r="50" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
+      <c r="A50" s="4">
         <v>10120011</v>
-      </c>
-      <c r="B46" s="10">
-        <v>101200</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="J46" s="4"/>
-      <c r="K46" s="43"/>
-    </row>
-    <row r="47" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A47" s="4">
-        <v>10120021</v>
-      </c>
-      <c r="B47" s="10">
-        <v>101200</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="43"/>
-    </row>
-    <row r="48" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A48" s="4">
-        <v>10120031</v>
-      </c>
-      <c r="B48" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I48" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J48" s="4"/>
-      <c r="K48" s="43"/>
-    </row>
-    <row r="49" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A49" s="4">
-        <v>10120032</v>
-      </c>
-      <c r="B49" s="10">
-        <v>101200</v>
-      </c>
-      <c r="C49" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I49" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J49" s="4"/>
-      <c r="K49" s="43"/>
-    </row>
-    <row r="50" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A50" s="4">
-        <v>10120033</v>
       </c>
       <c r="B50" s="10">
         <v>101200</v>
       </c>
-      <c r="C50" s="36" t="s">
-        <v>150</v>
-      </c>
       <c r="D50" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="I50" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I50" s="61" t="s">
-        <v>39</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="43"/>
     </row>
-    <row r="51" s="4" customFormat="1" ht="16.5" spans="1:11">
+    <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
-        <v>10120034</v>
+        <v>10120021</v>
       </c>
       <c r="B51" s="10">
         <v>101200</v>
       </c>
-      <c r="C51" s="36" t="s">
+      <c r="D51" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I51" s="61" t="s">
-        <v>39</v>
+      <c r="H51" s="10"/>
+      <c r="I51" s="62" t="s">
+        <v>109</v>
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="43"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A52" s="4">
-        <v>10120035</v>
+        <v>10120031</v>
       </c>
       <c r="B52" s="10">
         <v>101200</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I52" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="I52" s="62" t="s">
         <v>39</v>
       </c>
       <c r="J52" s="4"/>
@@ -3686,742 +3708,866 @@
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
-        <v>10120036</v>
+        <v>10120032</v>
       </c>
       <c r="B53" s="10">
         <v>101200</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="I53" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="I53" s="62" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="43"/>
     </row>
-    <row r="54" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A54" s="5">
-        <v>10120041</v>
-      </c>
-      <c r="B54" s="36">
+    <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="4">
+        <v>10120033</v>
+      </c>
+      <c r="B54" s="10">
         <v>101200</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="D54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E54" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>166</v>
+      <c r="E54" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H54" s="36">
-        <v>10</v>
-      </c>
-      <c r="I54" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="56"/>
-    </row>
-    <row r="55" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A55" s="5">
-        <v>10120042</v>
-      </c>
-      <c r="B55" s="36">
+        <v>167</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" s="4"/>
+      <c r="K54" s="43"/>
+    </row>
+    <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="4">
+        <v>10120034</v>
+      </c>
+      <c r="B55" s="10">
         <v>101200</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E55" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F55" s="5" t="s">
+      <c r="D55" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="4">
+        <v>10120035</v>
+      </c>
+      <c r="B56" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C56" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55" s="36">
-        <v>10</v>
-      </c>
-      <c r="I55" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="J55" s="5"/>
-      <c r="K55" s="56"/>
-    </row>
-    <row r="56" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A56" s="5">
-        <v>10120043</v>
-      </c>
-      <c r="B56" s="36">
+      <c r="D56" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I56" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="43"/>
+    </row>
+    <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="4">
+        <v>10120036</v>
+      </c>
+      <c r="B57" s="10">
         <v>101200</v>
       </c>
-      <c r="C56" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="36">
-        <v>10</v>
-      </c>
-      <c r="I56" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="56"/>
-    </row>
-    <row r="57" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A57" s="5">
-        <v>10120044</v>
-      </c>
-      <c r="B57" s="36">
-        <v>101200</v>
-      </c>
       <c r="C57" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H57" s="36">
-        <v>10</v>
-      </c>
-      <c r="I57" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="56"/>
+        <v>174</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="43"/>
     </row>
     <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="5">
-        <v>10120045</v>
+        <v>10120041</v>
       </c>
       <c r="B58" s="36">
         <v>101200</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E58" s="36" t="s">
         <v>110</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H58" s="36">
         <v>10</v>
       </c>
-      <c r="I58" s="63" t="s">
+      <c r="I58" s="64" t="s">
         <v>107</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="56"/>
+      <c r="K58" s="57"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
-        <v>10120046</v>
+        <v>10120042</v>
       </c>
       <c r="B59" s="36">
         <v>101200</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E59" s="36" t="s">
         <v>110</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H59" s="36">
         <v>10</v>
       </c>
-      <c r="I59" s="63" t="s">
+      <c r="I59" s="64" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="56"/>
-    </row>
-    <row r="60" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A60" s="4">
-        <v>10120051</v>
-      </c>
-      <c r="B60" s="10">
+      <c r="K59" s="57"/>
+    </row>
+    <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A60" s="5">
+        <v>10120043</v>
+      </c>
+      <c r="B60" s="36">
         <v>101200</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I60" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="J60" s="4"/>
-      <c r="K60" s="43"/>
-    </row>
-    <row r="61" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A61" s="4">
-        <v>10120052</v>
-      </c>
-      <c r="B61" s="10">
+        <v>167</v>
+      </c>
+      <c r="H60" s="36">
+        <v>10</v>
+      </c>
+      <c r="I60" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J60" s="5"/>
+      <c r="K60" s="57"/>
+    </row>
+    <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A61" s="5">
+        <v>10120044</v>
+      </c>
+      <c r="B61" s="36">
         <v>101200</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I61" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="J61" s="4"/>
-      <c r="K61" s="43"/>
-    </row>
-    <row r="62" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A62" s="4">
-        <v>10120053</v>
-      </c>
-      <c r="B62" s="10">
+        <v>170</v>
+      </c>
+      <c r="H61" s="36">
+        <v>10</v>
+      </c>
+      <c r="I61" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J61" s="5"/>
+      <c r="K61" s="57"/>
+    </row>
+    <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A62" s="5">
+        <v>10120045</v>
+      </c>
+      <c r="B62" s="36">
         <v>101200</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I62" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="J62" s="4"/>
-      <c r="K62" s="43"/>
-    </row>
-    <row r="63" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A63" s="4">
-        <v>10120054</v>
-      </c>
-      <c r="B63" s="10">
+        <v>172</v>
+      </c>
+      <c r="H62" s="36">
+        <v>10</v>
+      </c>
+      <c r="I62" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J62" s="5"/>
+      <c r="K62" s="57"/>
+    </row>
+    <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A63" s="5">
+        <v>10120046</v>
+      </c>
+      <c r="B63" s="36">
         <v>101200</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E63" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>176</v>
+      <c r="D63" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I63" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="J63" s="4"/>
-      <c r="K63" s="43"/>
+        <v>174</v>
+      </c>
+      <c r="H63" s="36">
+        <v>10</v>
+      </c>
+      <c r="I63" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J63" s="5"/>
+      <c r="K63" s="57"/>
     </row>
     <row r="64" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="4">
-        <v>10120055</v>
+        <v>10120051</v>
       </c>
       <c r="B64" s="10">
         <v>101200</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>182</v>
+        <v>51</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I64" s="61" t="s">
-        <v>178</v>
+        <v>187</v>
+      </c>
+      <c r="I64" s="62" t="s">
+        <v>188</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="43"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
-        <v>10120056</v>
+        <v>10120052</v>
       </c>
       <c r="B65" s="10">
         <v>101200</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I65" s="61" t="s">
-        <v>178</v>
+        <v>187</v>
+      </c>
+      <c r="I65" s="62" t="s">
+        <v>188</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="43"/>
     </row>
-    <row r="66" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A66" s="6">
-        <v>10120061</v>
+    <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A66" s="4">
+        <v>10120053</v>
       </c>
       <c r="B66" s="10">
         <v>101200</v>
       </c>
-      <c r="C66" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E66" s="15" t="s">
+      <c r="C66" s="36" t="s">
         <v>185</v>
       </c>
+      <c r="D66" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="F66" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H66" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I66" s="58" t="s">
+      <c r="G66" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H66" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="J66" s="6"/>
-      <c r="K66" s="46"/>
-    </row>
-    <row r="67" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A67" s="6">
-        <v>10120062</v>
+      <c r="I66" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="J66" s="4"/>
+      <c r="K66" s="43"/>
+    </row>
+    <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A67" s="4">
+        <v>10120054</v>
       </c>
       <c r="B67" s="10">
         <v>101200</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E67" s="15" t="s">
+      <c r="C67" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I67" s="62" t="s">
         <v>188</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I67" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="J67" s="6"/>
-      <c r="K67" s="46"/>
-    </row>
-    <row r="68" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A68" s="6">
-        <v>10120063</v>
+      <c r="J67" s="4"/>
+      <c r="K67" s="43"/>
+    </row>
+    <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A68" s="4">
+        <v>10120055</v>
       </c>
       <c r="B68" s="10">
         <v>101200</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>189</v>
+      <c r="C68" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H68" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I68" s="58" t="s">
+      <c r="G68" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="J68" s="6"/>
-      <c r="K68" s="46"/>
-    </row>
-    <row r="69" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A69" s="6">
-        <v>10120064</v>
+      <c r="I68" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="J68" s="4"/>
+      <c r="K68" s="43"/>
+    </row>
+    <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A69" s="4">
+        <v>10120056</v>
       </c>
       <c r="B69" s="10">
         <v>101200</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>191</v>
+      <c r="D69" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>193</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="H69" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I69" s="58" t="s">
+      <c r="G69" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="J69" s="6"/>
-      <c r="K69" s="46"/>
+      <c r="I69" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="J69" s="4"/>
+      <c r="K69" s="43"/>
     </row>
     <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="6">
-        <v>10120065</v>
+        <v>10120061</v>
       </c>
       <c r="B70" s="10">
         <v>101200</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>161</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I70" s="58" t="s">
-        <v>187</v>
+        <v>196</v>
+      </c>
+      <c r="I70" s="59" t="s">
+        <v>197</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="46"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
-        <v>10120066</v>
+        <v>10120062</v>
       </c>
       <c r="B71" s="10">
         <v>101200</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="I71" s="58" t="s">
-        <v>187</v>
+        <v>196</v>
+      </c>
+      <c r="I71" s="59" t="s">
+        <v>197</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="46"/>
     </row>
-    <row r="72" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A72" s="3">
+    <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A72" s="6">
+        <v>10120063</v>
+      </c>
+      <c r="B72" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="I72" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="J72" s="6"/>
+      <c r="K72" s="46"/>
+    </row>
+    <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A73" s="6">
+        <v>10120064</v>
+      </c>
+      <c r="B73" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="I73" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="J73" s="6"/>
+      <c r="K73" s="46"/>
+    </row>
+    <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A74" s="6">
+        <v>10120065</v>
+      </c>
+      <c r="B74" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="I74" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="J74" s="6"/>
+      <c r="K74" s="46"/>
+    </row>
+    <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A75" s="6">
+        <v>10120066</v>
+      </c>
+      <c r="B75" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="I75" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="J75" s="6"/>
+      <c r="K75" s="46"/>
+    </row>
+    <row r="76" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A76" s="3">
         <v>10140001</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B76" s="35">
         <v>101400</v>
       </c>
-      <c r="C72" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E72" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H72" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I72" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="K72" s="55"/>
-    </row>
-    <row r="73" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A73" s="3">
+      <c r="C76" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I76" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="K76" s="56"/>
+    </row>
+    <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A77" s="3">
         <v>10140011</v>
       </c>
-      <c r="B73" s="35">
+      <c r="B77" s="35">
         <v>101400</v>
       </c>
-      <c r="C73" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E73" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K73" s="55"/>
-    </row>
-    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A74" s="7">
+      <c r="C77" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K77" s="56"/>
+    </row>
+    <row r="78" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A78" s="7">
         <v>10140021</v>
       </c>
-      <c r="B74" s="12">
+      <c r="B78" s="12">
         <v>101400</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E74" s="12" t="s">
+      <c r="C78" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="H74" s="12" t="s">
+      <c r="G78" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K78" s="44"/>
+    </row>
+    <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A79" s="7">
+        <v>10140022</v>
+      </c>
+      <c r="B79" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I74" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K74" s="44"/>
-    </row>
-    <row r="75" s="7" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A75" s="7">
-        <v>10140022</v>
-      </c>
-      <c r="B75" s="12">
+      <c r="G79" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="I79" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="K79" s="44"/>
+    </row>
+    <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A80" s="7">
+        <v>10140023</v>
+      </c>
+      <c r="B80" s="12">
         <v>101400</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" s="12" t="s">
+      <c r="C80" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F80" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="I75" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="K75" s="44"/>
-    </row>
-    <row r="76" s="7" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A76" s="7">
-        <v>10140023</v>
-      </c>
-      <c r="B76" s="12">
-        <v>101400</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="G76" s="7" t="s">
+      <c r="G80" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H76" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="I76" s="62" t="s">
-        <v>114</v>
-      </c>
-      <c r="K76" s="44"/>
+      <c r="H80" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="I80" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="K80" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4441,24 +4587,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="D1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4466,16 +4612,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4483,16 +4629,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F4" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4500,16 +4646,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4517,7 +4663,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4525,7 +4671,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4533,7 +4679,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4541,7 +4687,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4549,7 +4695,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4557,7 +4703,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4565,7 +4711,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4573,7 +4719,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4581,7 +4727,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4589,7 +4735,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4597,7 +4743,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4605,7 +4751,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4613,7 +4759,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4621,7 +4767,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4629,7 +4775,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4637,7 +4783,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4645,7 +4791,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4653,7 +4799,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4661,7 +4807,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4669,7 +4815,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4677,7 +4823,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4685,7 +4831,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4693,7 +4839,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4701,7 +4847,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4709,7 +4855,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4717,7 +4863,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4725,7 +4871,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4733,7 +4879,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4741,7 +4887,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4749,7 +4895,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4757,7 +4903,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4765,7 +4911,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4773,7 +4919,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4781,7 +4927,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4789,7 +4935,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4797,7 +4943,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4805,7 +4951,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4813,7 +4959,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4821,7 +4967,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4829,7 +4975,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4837,7 +4983,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4845,7 +4991,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4853,7 +4999,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="274">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -490,6 +490,18 @@
     <t>5_1</t>
   </si>
   <si>
+    <t>上下两行都为空格</t>
+  </si>
+  <si>
+    <t>搭配41-45必中奖使用</t>
+  </si>
+  <si>
+    <t>99_1</t>
+  </si>
+  <si>
+    <t>1_1_1|3_1_1|4_1_1|6_1_1</t>
+  </si>
+  <si>
     <t>10_1</t>
   </si>
   <si>
@@ -562,7 +574,7 @@
     <t>2_3_4_5_6_7_8_9_10_11_12_13_14_15_16_17_18</t>
   </si>
   <si>
-    <t>0_90|1_10</t>
+    <t>0_95|1_5</t>
   </si>
   <si>
     <t>概率出现金色图标-2筒</t>
@@ -797,9 +809,6 @@
   </si>
   <si>
     <t>第2列概率出现jackpot图案，最多1个</t>
-  </si>
-  <si>
-    <t>0_95|1_5</t>
   </si>
   <si>
     <t>第3列概率出现jackpot图案，最多1个</t>
@@ -2160,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -3033,9 +3042,7 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>92</v>
-      </c>
+      <c r="H29" s="10"/>
       <c r="I29" s="62" t="s">
         <v>106</v>
       </c>
@@ -3065,9 +3072,7 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>92</v>
-      </c>
+      <c r="H30" s="10"/>
       <c r="I30" s="62" t="s">
         <v>106</v>
       </c>
@@ -3097,9 +3102,7 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="10" t="s">
-        <v>92</v>
-      </c>
+      <c r="H31" s="10"/>
       <c r="I31" s="62" t="s">
         <v>106</v>
       </c>
@@ -3129,9 +3132,7 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>92</v>
-      </c>
+      <c r="H32" s="10"/>
       <c r="I32" s="62" t="s">
         <v>106</v>
       </c>
@@ -3161,9 +3162,7 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>92</v>
-      </c>
+      <c r="H33" s="10"/>
       <c r="I33" s="62" t="s">
         <v>106</v>
       </c>
@@ -3173,133 +3172,138 @@
       <c r="M33" s="53"/>
       <c r="N33" s="53"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A34" s="31">
-        <v>10070010</v>
-      </c>
-      <c r="B34" s="32">
-        <v>100700</v>
-      </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="32" t="s">
+    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A34" s="1">
+        <v>10030050</v>
+      </c>
+      <c r="B34" s="9">
+        <v>100300</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="E34" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="31" t="s">
+      <c r="F34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="54"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A35" s="31">
-        <v>10070011</v>
+        <v>10070010</v>
       </c>
       <c r="B35" s="32">
         <v>100700</v>
       </c>
       <c r="C35" s="32"/>
       <c r="D35" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="32" t="s">
         <v>114</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>110</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>115</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="H35" s="32"/>
       <c r="I35" s="31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J35" s="31"/>
       <c r="K35" s="54"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A36" s="31">
-        <v>10070012</v>
+        <v>10070011</v>
       </c>
       <c r="B36" s="32">
         <v>100700</v>
       </c>
       <c r="C36" s="32"/>
       <c r="D36" s="31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G36" s="31" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H36" s="32"/>
       <c r="I36" s="31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J36" s="31"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A37" s="33">
-        <v>10070021</v>
-      </c>
-      <c r="B37" s="34">
+      <c r="A37" s="31">
+        <v>10070012</v>
+      </c>
+      <c r="B37" s="32">
         <v>100700</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" s="33" t="s">
+      <c r="C37" s="32"/>
+      <c r="D37" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37" s="33"/>
-      <c r="K37" s="55"/>
+      <c r="G37" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" s="32"/>
+      <c r="I37" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="J37" s="31"/>
+      <c r="K37" s="54"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A38" s="33">
-        <v>10070022</v>
+        <v>10070021</v>
       </c>
       <c r="B38" s="34">
         <v>100700</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G38" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H38" s="34"/>
       <c r="I38" s="33" t="s">
@@ -3310,23 +3314,23 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A39" s="33">
-        <v>10070023</v>
+        <v>10070022</v>
       </c>
       <c r="B39" s="34">
         <v>100700</v>
       </c>
       <c r="C39" s="34"/>
       <c r="D39" s="33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="H39" s="34"/>
       <c r="I39" s="33" t="s">
@@ -3337,61 +3341,61 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A40" s="33">
-        <v>10070024</v>
+        <v>10070023</v>
       </c>
       <c r="B40" s="34">
         <v>100700</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="E40" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>124</v>
-      </c>
       <c r="G40" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H40" s="34"/>
       <c r="I40" s="33" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="J40" s="33"/>
       <c r="K40" s="55"/>
     </row>
-    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A41" s="3">
-        <v>10070030</v>
-      </c>
-      <c r="B41" s="35">
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A41" s="33">
+        <v>10070024</v>
+      </c>
+      <c r="B41" s="34">
         <v>100700</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="3" t="s">
+      <c r="C41" s="34"/>
+      <c r="D41" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="E41" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="63" t="s">
+      <c r="H41" s="34"/>
+      <c r="I41" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="56"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="55"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A42" s="3">
-        <v>10070031</v>
+        <v>10070030</v>
       </c>
       <c r="B42" s="35">
         <v>100700</v>
@@ -3404,14 +3408,12 @@
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>133</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="H42" s="35"/>
       <c r="I42" s="63" t="s">
         <v>134</v>
       </c>
@@ -3420,7 +3422,7 @@
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A43" s="3">
-        <v>10070032</v>
+        <v>10070031</v>
       </c>
       <c r="B43" s="35">
         <v>100700</v>
@@ -3433,234 +3435,228 @@
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H43" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="63" t="str">
-        <f>I42</f>
-        <v>0_90|1_10</v>
-      </c>
+      <c r="I43" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="J43" s="3"/>
       <c r="K43" s="56"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A44" s="3">
-        <v>10070033</v>
+        <v>10070032</v>
       </c>
       <c r="B44" s="35">
         <v>100700</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="I44" s="63" t="s">
         <v>138</v>
-      </c>
-      <c r="E44" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="63" t="str">
-        <f t="shared" ref="I44:I49" si="0">I43</f>
-        <v>0_90|1_10</v>
       </c>
       <c r="K44" s="56"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A45" s="3">
-        <v>10070034</v>
+        <v>10070033</v>
       </c>
       <c r="B45" s="35">
         <v>100700</v>
       </c>
       <c r="C45" s="35"/>
       <c r="D45" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
+        <v>144</v>
+      </c>
+      <c r="I45" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="K45" s="56"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A46" s="3">
-        <v>10070035</v>
+        <v>10070034</v>
       </c>
       <c r="B46" s="35">
         <v>100700</v>
       </c>
       <c r="C46" s="35"/>
       <c r="D46" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H46" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="I46" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
+        <v>147</v>
+      </c>
+      <c r="I46" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="K46" s="56"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A47" s="3">
-        <v>10070036</v>
+        <v>10070035</v>
       </c>
       <c r="B47" s="35">
         <v>100700</v>
       </c>
       <c r="C47" s="35"/>
       <c r="D47" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H47" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="I47" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
+        <v>149</v>
+      </c>
+      <c r="I47" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="K47" s="56"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A48" s="3">
-        <v>10070037</v>
+        <v>10070036</v>
       </c>
       <c r="B48" s="35">
         <v>100700</v>
       </c>
       <c r="C48" s="35"/>
       <c r="D48" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E48" s="35" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H48" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="I48" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
+        <v>151</v>
+      </c>
+      <c r="I48" s="63" t="s">
+        <v>138</v>
       </c>
       <c r="K48" s="56"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A49" s="3">
-        <v>10070038</v>
+        <v>10070037</v>
       </c>
       <c r="B49" s="35">
         <v>100700</v>
       </c>
       <c r="C49" s="35"/>
       <c r="D49" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E49" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H49" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I49" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="K49" s="56"/>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="3">
+        <v>10070038</v>
+      </c>
+      <c r="B50" s="35">
+        <v>100700</v>
+      </c>
+      <c r="C50" s="35"/>
+      <c r="D50" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="I49" s="63" t="str">
-        <f t="shared" si="0"/>
-        <v>0_90|1_10</v>
-      </c>
-      <c r="K49" s="56"/>
-    </row>
-    <row r="50" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
-      <c r="A50" s="4">
-        <v>10120011</v>
-      </c>
-      <c r="B50" s="10">
-        <v>101200</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="F50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="H50" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="43"/>
+      <c r="I50" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="K50" s="56"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
-        <v>10120021</v>
+        <v>10120011</v>
       </c>
       <c r="B51" s="10">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>158</v>
@@ -3668,68 +3664,65 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="62" t="s">
-        <v>109</v>
+      <c r="H51" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="43"/>
     </row>
-    <row r="52" s="4" customFormat="1" ht="16.5" spans="1:11">
+    <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
-        <v>10120031</v>
+        <v>10120021</v>
       </c>
       <c r="B52" s="10">
         <v>101200</v>
       </c>
-      <c r="C52" s="36" t="s">
-        <v>160</v>
-      </c>
       <c r="D52" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="10" t="s">
-        <v>156</v>
-      </c>
+      <c r="H52" s="10"/>
       <c r="I52" s="62" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="43"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
-        <v>10120032</v>
+        <v>10120031</v>
       </c>
       <c r="B53" s="10">
         <v>101200</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I53" s="62" t="s">
         <v>39</v>
@@ -3739,28 +3732,28 @@
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
-        <v>10120033</v>
+        <v>10120032</v>
       </c>
       <c r="B54" s="10">
         <v>101200</v>
       </c>
       <c r="C54" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="I54" s="62" t="s">
         <v>39</v>
@@ -3770,28 +3763,28 @@
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
-        <v>10120034</v>
+        <v>10120033</v>
       </c>
       <c r="B55" s="10">
         <v>101200</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I55" s="62" t="s">
         <v>39</v>
@@ -3801,28 +3794,28 @@
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
-        <v>10120035</v>
+        <v>10120034</v>
       </c>
       <c r="B56" s="10">
         <v>101200</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I56" s="62" t="s">
         <v>39</v>
@@ -3832,28 +3825,28 @@
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
-        <v>10120036</v>
+        <v>10120035</v>
       </c>
       <c r="B57" s="10">
         <v>101200</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I57" s="62" t="s">
         <v>39</v>
@@ -3861,58 +3854,58 @@
       <c r="J57" s="4"/>
       <c r="K57" s="43"/>
     </row>
-    <row r="58" s="5" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A58" s="5">
-        <v>10120041</v>
-      </c>
-      <c r="B58" s="36">
+    <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="4">
+        <v>10120036</v>
+      </c>
+      <c r="B58" s="10">
         <v>101200</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="H58" s="36">
-        <v>10</v>
-      </c>
-      <c r="I58" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="57"/>
+        <v>178</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I58" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="43"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
-        <v>10120042</v>
+        <v>10120041</v>
       </c>
       <c r="B59" s="36">
         <v>101200</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H59" s="36">
         <v>10</v>
@@ -3925,25 +3918,25 @@
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
-        <v>10120043</v>
+        <v>10120042</v>
       </c>
       <c r="B60" s="36">
         <v>101200</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H60" s="36">
         <v>10</v>
@@ -3956,25 +3949,25 @@
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
-        <v>10120044</v>
+        <v>10120043</v>
       </c>
       <c r="B61" s="36">
         <v>101200</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E61" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H61" s="36">
         <v>10</v>
@@ -3987,25 +3980,25 @@
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
-        <v>10120045</v>
+        <v>10120044</v>
       </c>
       <c r="B62" s="36">
         <v>101200</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E62" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H62" s="36">
         <v>10</v>
@@ -4018,25 +4011,25 @@
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
-        <v>10120046</v>
+        <v>10120045</v>
       </c>
       <c r="B63" s="36">
         <v>101200</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E63" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H63" s="36">
         <v>10</v>
@@ -4047,527 +4040,558 @@
       <c r="J63" s="5"/>
       <c r="K63" s="57"/>
     </row>
-    <row r="64" s="4" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A64" s="4">
-        <v>10120051</v>
-      </c>
-      <c r="B64" s="10">
+    <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A64" s="5">
+        <v>10120046</v>
+      </c>
+      <c r="B64" s="36">
         <v>101200</v>
       </c>
       <c r="C64" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>186</v>
+      <c r="D64" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I64" s="62" t="s">
-        <v>188</v>
-      </c>
-      <c r="J64" s="4"/>
-      <c r="K64" s="43"/>
+        <v>178</v>
+      </c>
+      <c r="H64" s="36">
+        <v>10</v>
+      </c>
+      <c r="I64" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="J64" s="5"/>
+      <c r="K64" s="57"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
-        <v>10120052</v>
+        <v>10120051</v>
       </c>
       <c r="B65" s="10">
         <v>101200</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I65" s="62" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="43"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
-        <v>10120053</v>
+        <v>10120052</v>
       </c>
       <c r="B66" s="10">
         <v>101200</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I66" s="62" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J66" s="4"/>
       <c r="K66" s="43"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
-        <v>10120054</v>
+        <v>10120053</v>
       </c>
       <c r="B67" s="10">
         <v>101200</v>
       </c>
       <c r="C67" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E67" s="10" t="s">
+      <c r="G67" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="I67" s="62" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="43"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
-        <v>10120055</v>
+        <v>10120054</v>
       </c>
       <c r="B68" s="10">
         <v>101200</v>
       </c>
       <c r="C68" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" s="10" t="s">
+      <c r="G68" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="I68" s="62" t="s">
         <v>192</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I68" s="62" t="s">
-        <v>188</v>
       </c>
       <c r="J68" s="4"/>
       <c r="K68" s="43"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
-        <v>10120056</v>
+        <v>10120055</v>
       </c>
       <c r="B69" s="10">
         <v>101200</v>
       </c>
       <c r="C69" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="G69" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I69" s="62" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="43"/>
     </row>
-    <row r="70" s="6" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A70" s="6">
-        <v>10120061</v>
+    <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A70" s="4">
+        <v>10120056</v>
       </c>
       <c r="B70" s="10">
         <v>101200</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>195</v>
+      <c r="D70" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="I70" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="J70" s="6"/>
-      <c r="K70" s="46"/>
+        <v>190</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="62" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="4"/>
+      <c r="K70" s="43"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
-        <v>10120062</v>
+        <v>10120061</v>
       </c>
       <c r="B71" s="10">
         <v>101200</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I71" s="59" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="46"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
-        <v>10120063</v>
+        <v>10120062</v>
       </c>
       <c r="B72" s="10">
         <v>101200</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I72" s="59" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="46"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
-        <v>10120064</v>
+        <v>10120063</v>
       </c>
       <c r="B73" s="10">
         <v>101200</v>
       </c>
       <c r="C73" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E73" s="15" t="s">
+      <c r="I73" s="59" t="s">
         <v>201</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="I73" s="59" t="s">
-        <v>197</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="46"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
-        <v>10120065</v>
+        <v>10120064</v>
       </c>
       <c r="B74" s="10">
         <v>101200</v>
       </c>
       <c r="C74" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>196</v>
-      </c>
       <c r="I74" s="59" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="46"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
-        <v>10120066</v>
+        <v>10120065</v>
       </c>
       <c r="B75" s="10">
         <v>101200</v>
       </c>
       <c r="C75" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H75" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H75" s="15" t="s">
-        <v>196</v>
-      </c>
       <c r="I75" s="59" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="46"/>
     </row>
-    <row r="76" s="3" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A76" s="3">
-        <v>10140001</v>
-      </c>
-      <c r="B76" s="35">
-        <v>101400</v>
-      </c>
-      <c r="C76" s="35" t="s">
+    <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A76" s="6">
+        <v>10120066</v>
+      </c>
+      <c r="B76" s="10">
+        <v>101200</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E76" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H76" s="12" t="s">
+      <c r="D76" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="I76" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="K76" s="56"/>
+      <c r="F76" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I76" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="J76" s="6"/>
+      <c r="K76" s="46"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
-        <v>10140011</v>
+        <v>10140001</v>
       </c>
       <c r="B77" s="35">
         <v>101400</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="I77" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I77" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="K77" s="56"/>
+    </row>
+    <row r="78" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A78" s="3">
+        <v>10140011</v>
+      </c>
+      <c r="B78" s="35">
+        <v>101400</v>
+      </c>
+      <c r="C78" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K77" s="56"/>
-    </row>
-    <row r="78" s="7" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A78" s="7">
-        <v>10140021</v>
-      </c>
-      <c r="B78" s="12">
-        <v>101400</v>
-      </c>
-      <c r="C78" s="12" t="s">
+      <c r="E78" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="H78" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K78" s="44"/>
+      <c r="I78" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K78" s="56"/>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="7">
-        <v>10140022</v>
+        <v>10140021</v>
       </c>
       <c r="B79" s="12">
         <v>101400</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="I79" s="63" t="s">
-        <v>213</v>
+        <v>143</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="K79" s="44"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
-        <v>10140023</v>
+        <v>10140022</v>
       </c>
       <c r="B80" s="12">
         <v>101400</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G80" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="I80" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="K80" s="44"/>
+    </row>
+    <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A81" s="7">
+        <v>10140023</v>
+      </c>
+      <c r="B81" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="I80" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="K80" s="44"/>
+      <c r="H81" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="I81" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="K81" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4587,24 +4611,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4612,16 +4636,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4629,16 +4653,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4646,16 +4670,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4663,7 +4687,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4671,7 +4695,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4679,7 +4703,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4687,7 +4711,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4695,7 +4719,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4703,7 +4727,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4711,7 +4735,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4719,7 +4743,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4727,7 +4751,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4735,7 +4759,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4743,7 +4767,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4751,7 +4775,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4759,7 +4783,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4767,7 +4791,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4775,7 +4799,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4783,7 +4807,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4791,7 +4815,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4799,7 +4823,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4807,7 +4831,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4815,7 +4839,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4823,7 +4847,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4831,7 +4855,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4839,7 +4863,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4847,7 +4871,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4855,7 +4879,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4863,7 +4887,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4871,7 +4895,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4879,7 +4903,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4887,7 +4911,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4895,7 +4919,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4903,7 +4927,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4911,7 +4935,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4919,7 +4943,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4927,7 +4951,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4935,7 +4959,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4943,7 +4967,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -4951,7 +4975,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -4959,7 +4983,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -4967,7 +4991,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -4975,7 +4999,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -4983,7 +5007,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -4991,7 +5015,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -4999,7 +5023,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="274">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -2169,7 +2169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -4593,6 +4593,642 @@
       </c>
       <c r="K81" s="44"/>
     </row>
+    <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A82" s="1">
+        <v>10240011</v>
+      </c>
+      <c r="B82" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K82" s="42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A83" s="1">
+        <v>10240012</v>
+      </c>
+      <c r="B83" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J83" s="4"/>
+      <c r="K83" s="43"/>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A84" s="1">
+        <v>10240021</v>
+      </c>
+      <c r="B84" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H84" s="12"/>
+      <c r="I84" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J84" s="7"/>
+      <c r="K84" s="44"/>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A85" s="1">
+        <v>10240022</v>
+      </c>
+      <c r="B85" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="12"/>
+      <c r="I85" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J85" s="12"/>
+      <c r="K85" s="45"/>
+    </row>
+    <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A86" s="1">
+        <v>10240023</v>
+      </c>
+      <c r="B86" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H86" s="12"/>
+      <c r="I86" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J86" s="12"/>
+      <c r="K86" s="45"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A87" s="1">
+        <v>10240024</v>
+      </c>
+      <c r="B87" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="12"/>
+      <c r="I87" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J87" s="12"/>
+      <c r="K87" s="45"/>
+    </row>
+    <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A88" s="1">
+        <v>10240025</v>
+      </c>
+      <c r="B88" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H88" s="12"/>
+      <c r="I88" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J88" s="12"/>
+      <c r="K88" s="45"/>
+    </row>
+    <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A89" s="1">
+        <v>10240026</v>
+      </c>
+      <c r="B89" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J89" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K89" s="45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A90" s="1">
+        <v>10240031</v>
+      </c>
+      <c r="B90" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J90" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K90" s="46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A91" s="1">
+        <v>10240032</v>
+      </c>
+      <c r="B91" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H91" s="15"/>
+      <c r="I91" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="J91" s="6"/>
+      <c r="K91" s="46"/>
+    </row>
+    <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A92" s="1">
+        <v>10240041</v>
+      </c>
+      <c r="B92" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H92" s="18"/>
+      <c r="I92" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J92" s="17"/>
+      <c r="K92" s="47"/>
+    </row>
+    <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A93" s="1">
+        <v>10240051</v>
+      </c>
+      <c r="B93" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H93" s="21"/>
+      <c r="I93" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J93" s="20"/>
+      <c r="K93" s="48"/>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A94" s="1">
+        <v>10240052</v>
+      </c>
+      <c r="B94" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H94" s="21"/>
+      <c r="I94" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="J94" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K94" s="48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
+      <c r="A95" s="23">
+        <v>10240061</v>
+      </c>
+      <c r="B95" s="24">
+        <v>102400</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E95" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" s="24"/>
+      <c r="I95" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="J95" s="23"/>
+      <c r="K95" s="49"/>
+    </row>
+    <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A96" s="2">
+        <v>10240071</v>
+      </c>
+      <c r="B96" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H96" s="27"/>
+      <c r="I96" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="K96" s="50"/>
+    </row>
+    <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A97" s="2">
+        <v>10240072</v>
+      </c>
+      <c r="B97" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="27"/>
+      <c r="I97" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J97" s="27"/>
+      <c r="K97" s="51"/>
+    </row>
+    <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A98" s="2">
+        <v>10240073</v>
+      </c>
+      <c r="B98" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C98" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H98" s="27"/>
+      <c r="I98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J98" s="27"/>
+      <c r="K98" s="51"/>
+    </row>
+    <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A99" s="2">
+        <v>10240074</v>
+      </c>
+      <c r="B99" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E99" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H99" s="27"/>
+      <c r="I99" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" s="27"/>
+      <c r="K99" s="51"/>
+    </row>
+    <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A100" s="2">
+        <v>10240075</v>
+      </c>
+      <c r="B100" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H100" s="27"/>
+      <c r="I100" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J100" s="27"/>
+      <c r="K100" s="51"/>
+    </row>
+    <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A101" s="2">
+        <v>10240076</v>
+      </c>
+      <c r="B101" s="27">
+        <v>102400</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J101" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101" s="51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A102" s="29">
+        <v>10240091</v>
+      </c>
+      <c r="B102" s="30">
+        <v>102400</v>
+      </c>
+      <c r="C102" s="30"/>
+      <c r="D102" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E102" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="F102" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G102" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H102" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I102" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J102" s="30"/>
+      <c r="K102" s="52"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="305">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -812,6 +812,99 @@
   </si>
   <si>
     <t>第3列概率出现jackpot图案，最多1个</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-铃铛</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-鞋子</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-杯子</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-饮品</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕1</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕2</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕3</t>
+  </si>
+  <si>
+    <t>概率出现金色图标-蛋糕4</t>
+  </si>
+  <si>
+    <t>改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>9_10_11_12_13_14_15_16_17_18_19_20_21_22</t>
+  </si>
+  <si>
+    <t>改出1个奖池符号</t>
+  </si>
+  <si>
+    <t>19_10|20_5|21_2|22_1</t>
+  </si>
+  <si>
+    <t>冰冻玩法改出百搭</t>
+  </si>
+  <si>
+    <t>改出百搭</t>
+  </si>
+  <si>
+    <t>百搭出现</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_14</t>
+  </si>
+  <si>
+    <t>火焰玩法改出百搭</t>
+  </si>
+  <si>
+    <t>13_14</t>
+  </si>
+  <si>
+    <t>中央两个海姆</t>
+  </si>
+  <si>
+    <t>结束特殊玩法</t>
+  </si>
+  <si>
+    <t>6_1_1|7_1_1</t>
+  </si>
+  <si>
+    <t>11_14</t>
+  </si>
+  <si>
+    <t>改出1个大奖</t>
+  </si>
+  <si>
+    <t>改出奖池符号</t>
+  </si>
+  <si>
+    <t>15_10|16_5|17_2|18_1</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>99999_1</t>
+  </si>
+  <si>
+    <t>3_1_1|9_1_1|15_1_1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1223,6 +1316,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1230,12 +1329,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1701,7 +1794,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1710,20 +1803,51 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1732,12 +1856,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -1746,107 +1866,85 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2169,7 +2267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2182,7 +2280,7 @@
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="8" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="9" customWidth="1"/>
     <col min="12" max="12" width="9.375"/>
     <col min="13" max="13" width="12.5"/>
     <col min="14" max="14" width="9.375"/>
@@ -2190,121 +2288,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="38"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="16" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2313,16 +2411,16 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="16" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="18" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2330,16 +2428,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="16" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2348,29 +2446,29 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="16" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="43"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="21" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -2379,27 +2477,27 @@
       <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="58" t="s">
+      <c r="H7" s="21"/>
+      <c r="I7" s="60" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="44"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>100100</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="21" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2408,27 +2506,27 @@
       <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="45"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>100100</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="21" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2437,27 +2535,27 @@
       <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="45"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>100100</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="21" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2466,27 +2564,27 @@
       <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="45"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>100100</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="21" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2495,27 +2593,27 @@
       <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="21"/>
       <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="45"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>100100</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="21" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2524,16 +2622,16 @@
       <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2541,16 +2639,16 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>100100</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -2559,14 +2657,14 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="15"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="27" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2574,16 +2672,16 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>100100</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="24" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="26" t="s">
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -2592,147 +2690,147 @@
       <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="59" t="s">
+      <c r="H14" s="26"/>
+      <c r="I14" s="61" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="46"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="10">
         <v>100100</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="17" t="s">
+      <c r="H15" s="30"/>
+      <c r="I15" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="47"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="31"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>100100</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="60" t="s">
+      <c r="H16" s="34"/>
+      <c r="I16" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="20"/>
-      <c r="K16" s="48"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J16" s="33"/>
+      <c r="K16" s="35"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>100100</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="20" t="s">
+      <c r="H17" s="34"/>
+      <c r="I17" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="35" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A18" s="23">
+    <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A18" s="37">
         <v>10010061</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="11">
         <v>100100</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="23" t="s">
+      <c r="H18" s="11"/>
+      <c r="I18" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="49"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J18" s="37"/>
+      <c r="K18" s="40"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="41">
         <v>100100</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="41" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2741,27 +2839,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="27"/>
-      <c r="I19" s="61" t="s">
+      <c r="H19" s="41"/>
+      <c r="I19" s="63" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="50"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K19" s="43"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="41">
         <v>100100</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="41" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2770,27 +2868,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="51"/>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J20" s="41"/>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="41">
         <v>100100</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="41" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2799,27 +2897,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="27"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="51"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J21" s="41"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="41">
         <v>100100</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="41" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2828,27 +2926,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="27"/>
-      <c r="K22" s="51"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J22" s="41"/>
+      <c r="K22" s="44"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="41">
         <v>100100</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="41" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2857,27 +2955,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="27"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="51"/>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J23" s="41"/>
+      <c r="K23" s="44"/>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="41">
         <v>100100</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="41" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2886,62 +2984,62 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="27" t="s">
+      <c r="H24" s="41" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="J24" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="51" t="s">
+      <c r="K24" s="44" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A25" s="29">
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A25" s="45">
         <v>10010091</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="46">
         <v>100100</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="29" t="s">
+      <c r="C25" s="46"/>
+      <c r="D25" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="29" t="s">
+      <c r="I25" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="30"/>
-      <c r="K25" s="52"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J25" s="46"/>
+      <c r="K25" s="47"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="10">
         <v>100300</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="16" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="16" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -2950,29 +3048,29 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="16" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="41"/>
-      <c r="K26" s="42"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J26" s="17"/>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <v>100300</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="16" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -2981,29 +3079,29 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="16" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="41"/>
-      <c r="K27" s="42"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="18"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>100300</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="16" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3012,28 +3110,28 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="10"/>
-      <c r="I28" s="62" t="s">
+      <c r="H28" s="16"/>
+      <c r="I28" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
-      <c r="K28" s="51"/>
+      <c r="K28" s="44"/>
       <c r="L28"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A29" s="1">
         <v>10030041</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>100300</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="16" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3042,28 +3140,28 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="62" t="s">
+      <c r="H29" s="16"/>
+      <c r="I29" s="64" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="51"/>
+      <c r="K29" s="44"/>
       <c r="L29"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A30" s="1">
         <v>10030042</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>100300</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="16" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3072,28 +3170,28 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="62" t="s">
+      <c r="H30" s="16"/>
+      <c r="I30" s="64" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="51"/>
+      <c r="K30" s="44"/>
       <c r="L30"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A31" s="1">
         <v>10030043</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>100300</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3102,28 +3200,28 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="62" t="s">
+      <c r="H31" s="16"/>
+      <c r="I31" s="64" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="51"/>
+      <c r="K31" s="44"/>
       <c r="L31"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <v>10030044</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>100300</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="16" t="s">
         <v>108</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -3132,28 +3230,28 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="10"/>
-      <c r="I32" s="62" t="s">
+      <c r="H32" s="16"/>
+      <c r="I32" s="64" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
-      <c r="K32" s="51"/>
+      <c r="K32" s="44"/>
       <c r="L32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="10">
         <v>100300</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="16" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -3162,30 +3260,30 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="10"/>
-      <c r="I33" s="62" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="64" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>10030050</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="10">
         <v>100300</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="16" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="16" t="s">
         <v>112</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -3194,217 +3292,217 @@
       <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="10"/>
-      <c r="I34" s="62" t="s">
+      <c r="H34" s="16"/>
+      <c r="I34" s="64" t="s">
         <v>108</v>
       </c>
       <c r="J34" s="4"/>
-      <c r="K34" s="51"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A35" s="31">
+      <c r="K34" s="44"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A35" s="49">
         <v>10070010</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="50">
         <v>100700</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="31" t="s">
+      <c r="C35" s="50"/>
+      <c r="D35" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F35" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="31" t="s">
+      <c r="H35" s="50"/>
+      <c r="I35" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="31"/>
-      <c r="K35" s="54"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A36" s="31">
+      <c r="J35" s="49"/>
+      <c r="K35" s="51"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A36" s="49">
         <v>10070011</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="50">
         <v>100700</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="31" t="s">
+      <c r="C36" s="50"/>
+      <c r="D36" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="31" t="s">
+      <c r="H36" s="50"/>
+      <c r="I36" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="31"/>
-      <c r="K36" s="54"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A37" s="31">
+      <c r="J36" s="49"/>
+      <c r="K36" s="51"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A37" s="49">
         <v>10070012</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="50">
         <v>100700</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="31" t="s">
+      <c r="C37" s="50"/>
+      <c r="D37" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="31" t="s">
+      <c r="H37" s="50"/>
+      <c r="I37" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="31"/>
-      <c r="K37" s="54"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A38" s="33">
+      <c r="J37" s="49"/>
+      <c r="K37" s="51"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A38" s="52">
         <v>10070021</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="53">
         <v>100700</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="33" t="s">
+      <c r="C38" s="53"/>
+      <c r="D38" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="33" t="s">
+      <c r="F38" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="33" t="s">
+      <c r="G38" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="33" t="s">
+      <c r="H38" s="53"/>
+      <c r="I38" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="33"/>
-      <c r="K38" s="55"/>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A39" s="33">
+      <c r="J38" s="52"/>
+      <c r="K38" s="54"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A39" s="52">
         <v>10070022</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="53">
         <v>100700</v>
       </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="33" t="s">
+      <c r="C39" s="53"/>
+      <c r="D39" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33" t="s">
+      <c r="H39" s="53"/>
+      <c r="I39" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="33"/>
-      <c r="K39" s="55"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A40" s="33">
+      <c r="J39" s="52"/>
+      <c r="K39" s="54"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A40" s="52">
         <v>10070023</v>
       </c>
-      <c r="B40" s="34">
+      <c r="B40" s="53">
         <v>100700</v>
       </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="33" t="s">
+      <c r="C40" s="53"/>
+      <c r="D40" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="33" t="s">
+      <c r="H40" s="53"/>
+      <c r="I40" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="33"/>
-      <c r="K40" s="55"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A41" s="33">
+      <c r="J40" s="52"/>
+      <c r="K40" s="54"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A41" s="52">
         <v>10070024</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="53">
         <v>100700</v>
       </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="33" t="s">
+      <c r="C41" s="53"/>
+      <c r="D41" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="34" t="s">
+      <c r="E41" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="33" t="s">
+      <c r="H41" s="53"/>
+      <c r="I41" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="33"/>
-      <c r="K41" s="55"/>
-    </row>
-    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:11">
+      <c r="J41" s="52"/>
+      <c r="K41" s="54"/>
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="3">
         <v>10070030</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="55">
         <v>100700</v>
       </c>
-      <c r="C42" s="35"/>
+      <c r="C42" s="55"/>
       <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="55" t="s">
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -3413,25 +3511,25 @@
       <c r="G42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="63" t="s">
+      <c r="H42" s="55"/>
+      <c r="I42" s="65" t="s">
         <v>134</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="56"/>
     </row>
-    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="3">
         <v>10070031</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="55">
         <v>100700</v>
       </c>
-      <c r="C43" s="35"/>
+      <c r="C43" s="55"/>
       <c r="D43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E43" s="35" t="s">
+      <c r="E43" s="55" t="s">
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -3440,27 +3538,27 @@
       <c r="G43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="35" t="s">
+      <c r="H43" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="63" t="s">
+      <c r="I43" s="65" t="s">
         <v>138</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="56"/>
     </row>
-    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="44" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="3">
         <v>10070032</v>
       </c>
-      <c r="B44" s="35">
+      <c r="B44" s="55">
         <v>100700</v>
       </c>
-      <c r="C44" s="35"/>
+      <c r="C44" s="55"/>
       <c r="D44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="35" t="s">
+      <c r="E44" s="55" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -3469,26 +3567,26 @@
       <c r="G44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="35" t="s">
+      <c r="H44" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="63" t="s">
+      <c r="I44" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K44" s="56"/>
     </row>
-    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="45" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="3">
         <v>10070033</v>
       </c>
-      <c r="B45" s="35">
+      <c r="B45" s="55">
         <v>100700</v>
       </c>
-      <c r="C45" s="35"/>
+      <c r="C45" s="55"/>
       <c r="D45" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="35" t="s">
+      <c r="E45" s="55" t="s">
         <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -3497,26 +3595,26 @@
       <c r="G45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H45" s="35" t="s">
+      <c r="H45" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="63" t="s">
+      <c r="I45" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K45" s="56"/>
     </row>
-    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="3">
         <v>10070034</v>
       </c>
-      <c r="B46" s="35">
+      <c r="B46" s="55">
         <v>100700</v>
       </c>
-      <c r="C46" s="35"/>
+      <c r="C46" s="55"/>
       <c r="D46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="35" t="s">
+      <c r="E46" s="55" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -3525,26 +3623,26 @@
       <c r="G46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="I46" s="63" t="s">
+      <c r="I46" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K46" s="56"/>
     </row>
-    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="3">
         <v>10070035</v>
       </c>
-      <c r="B47" s="35">
+      <c r="B47" s="55">
         <v>100700</v>
       </c>
-      <c r="C47" s="35"/>
+      <c r="C47" s="55"/>
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="E47" s="55" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -3553,26 +3651,26 @@
       <c r="G47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="63" t="s">
+      <c r="I47" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K47" s="56"/>
     </row>
-    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:11">
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="3">
         <v>10070036</v>
       </c>
-      <c r="B48" s="35">
+      <c r="B48" s="55">
         <v>100700</v>
       </c>
-      <c r="C48" s="35"/>
+      <c r="C48" s="55"/>
       <c r="D48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="35" t="s">
+      <c r="E48" s="55" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -3581,10 +3679,10 @@
       <c r="G48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="35" t="s">
+      <c r="H48" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="63" t="s">
+      <c r="I48" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K48" s="56"/>
@@ -3593,14 +3691,14 @@
       <c r="A49" s="3">
         <v>10070037</v>
       </c>
-      <c r="B49" s="35">
+      <c r="B49" s="55">
         <v>100700</v>
       </c>
-      <c r="C49" s="35"/>
+      <c r="C49" s="55"/>
       <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="35" t="s">
+      <c r="E49" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -3609,10 +3707,10 @@
       <c r="G49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="I49" s="63" t="s">
+      <c r="I49" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K49" s="56"/>
@@ -3621,14 +3719,14 @@
       <c r="A50" s="3">
         <v>10070038</v>
       </c>
-      <c r="B50" s="35">
+      <c r="B50" s="55">
         <v>100700</v>
       </c>
-      <c r="C50" s="35"/>
+      <c r="C50" s="55"/>
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="35" t="s">
+      <c r="E50" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -3637,10 +3735,10 @@
       <c r="G50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="35" t="s">
+      <c r="H50" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="63" t="s">
+      <c r="I50" s="65" t="s">
         <v>138</v>
       </c>
       <c r="K50" s="56"/>
@@ -3649,13 +3747,13 @@
       <c r="A51" s="4">
         <v>10120011</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="16">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="16" t="s">
         <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -3664,26 +3762,26 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="16" t="s">
         <v>160</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J51" s="4"/>
-      <c r="K51" s="43"/>
+      <c r="K51" s="19"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
         <v>10120021</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="16">
         <v>101200</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="16" t="s">
         <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -3692,27 +3790,27 @@
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="10"/>
-      <c r="I52" s="62" t="s">
+      <c r="H52" s="16"/>
+      <c r="I52" s="64" t="s">
         <v>109</v>
       </c>
       <c r="J52" s="4"/>
-      <c r="K52" s="43"/>
+      <c r="K52" s="19"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
         <v>10120031</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="16">
         <v>101200</v>
       </c>
-      <c r="C53" s="36" t="s">
+      <c r="C53" s="57" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="16" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -3721,29 +3819,29 @@
       <c r="G53" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I53" s="62" t="s">
+      <c r="I53" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
-      <c r="K53" s="43"/>
+      <c r="K53" s="19"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
         <v>10120032</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="16">
         <v>101200</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="57" t="s">
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="16" t="s">
         <v>140</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -3752,29 +3850,29 @@
       <c r="G54" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="62" t="s">
+      <c r="I54" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="43"/>
+      <c r="K54" s="19"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
         <v>10120033</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="16">
         <v>101200</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="57" t="s">
         <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="16" t="s">
         <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -3783,29 +3881,29 @@
       <c r="G55" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J55" s="4"/>
-      <c r="K55" s="43"/>
+      <c r="K55" s="19"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
         <v>10120034</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="16">
         <v>101200</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="57" t="s">
         <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="16" t="s">
         <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -3814,29 +3912,29 @@
       <c r="G56" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I56" s="62" t="s">
+      <c r="I56" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="43"/>
+      <c r="K56" s="19"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
         <v>10120035</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="16">
         <v>101200</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="57" t="s">
         <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="16" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -3845,29 +3943,29 @@
       <c r="G57" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="62" t="s">
+      <c r="I57" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J57" s="4"/>
-      <c r="K57" s="43"/>
+      <c r="K57" s="19"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="4">
         <v>10120036</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="16">
         <v>101200</v>
       </c>
-      <c r="C58" s="36" t="s">
+      <c r="C58" s="57" t="s">
         <v>172</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -3876,29 +3974,29 @@
       <c r="G58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="62" t="s">
+      <c r="I58" s="64" t="s">
         <v>39</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="43"/>
+      <c r="K58" s="19"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
         <v>10120041</v>
       </c>
-      <c r="B59" s="36">
+      <c r="B59" s="57">
         <v>101200</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="57" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="36" t="s">
+      <c r="E59" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -3907,29 +4005,29 @@
       <c r="G59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="57">
         <v>10</v>
       </c>
-      <c r="I59" s="64" t="s">
+      <c r="I59" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="57"/>
+      <c r="K59" s="58"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
         <v>10120042</v>
       </c>
-      <c r="B60" s="36">
+      <c r="B60" s="57">
         <v>101200</v>
       </c>
-      <c r="C60" s="36" t="s">
+      <c r="C60" s="57" t="s">
         <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="36" t="s">
+      <c r="E60" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -3938,29 +4036,29 @@
       <c r="G60" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H60" s="36">
+      <c r="H60" s="57">
         <v>10</v>
       </c>
-      <c r="I60" s="64" t="s">
+      <c r="I60" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="57"/>
+      <c r="K60" s="58"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
         <v>10120043</v>
       </c>
-      <c r="B61" s="36">
+      <c r="B61" s="57">
         <v>101200</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="57" t="s">
         <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="36" t="s">
+      <c r="E61" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
@@ -3969,29 +4067,29 @@
       <c r="G61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H61" s="36">
+      <c r="H61" s="57">
         <v>10</v>
       </c>
-      <c r="I61" s="64" t="s">
+      <c r="I61" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="57"/>
+      <c r="K61" s="58"/>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
         <v>10120044</v>
       </c>
-      <c r="B62" s="36">
+      <c r="B62" s="57">
         <v>101200</v>
       </c>
-      <c r="C62" s="36" t="s">
+      <c r="C62" s="57" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E62" s="36" t="s">
+      <c r="E62" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -4000,29 +4098,29 @@
       <c r="G62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H62" s="36">
+      <c r="H62" s="57">
         <v>10</v>
       </c>
-      <c r="I62" s="64" t="s">
+      <c r="I62" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="57"/>
+      <c r="K62" s="58"/>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
         <v>10120045</v>
       </c>
-      <c r="B63" s="36">
+      <c r="B63" s="57">
         <v>101200</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="57" t="s">
         <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="36" t="s">
+      <c r="E63" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -4031,29 +4129,29 @@
       <c r="G63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="36">
+      <c r="H63" s="57">
         <v>10</v>
       </c>
-      <c r="I63" s="64" t="s">
+      <c r="I63" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="57"/>
+      <c r="K63" s="58"/>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
         <v>10120046</v>
       </c>
-      <c r="B64" s="36">
+      <c r="B64" s="57">
         <v>101200</v>
       </c>
-      <c r="C64" s="36" t="s">
+      <c r="C64" s="57" t="s">
         <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="36" t="s">
+      <c r="E64" s="57" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -4062,29 +4160,29 @@
       <c r="G64" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H64" s="36">
+      <c r="H64" s="57">
         <v>10</v>
       </c>
-      <c r="I64" s="64" t="s">
+      <c r="I64" s="66" t="s">
         <v>107</v>
       </c>
       <c r="J64" s="5"/>
-      <c r="K64" s="57"/>
+      <c r="K64" s="58"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
         <v>10120051</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="16">
         <v>101200</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="C65" s="57" t="s">
         <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="16" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4093,29 +4191,29 @@
       <c r="G65" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="62" t="s">
+      <c r="I65" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="43"/>
+      <c r="K65" s="19"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
         <v>10120052</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="16">
         <v>101200</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C66" s="57" t="s">
         <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="16" t="s">
         <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4124,29 +4222,29 @@
       <c r="G66" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="10" t="s">
+      <c r="H66" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I66" s="62" t="s">
+      <c r="I66" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J66" s="4"/>
-      <c r="K66" s="43"/>
+      <c r="K66" s="19"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
         <v>10120053</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="16">
         <v>101200</v>
       </c>
-      <c r="C67" s="36" t="s">
+      <c r="C67" s="57" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="16" t="s">
         <v>193</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4155,29 +4253,29 @@
       <c r="G67" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J67" s="4"/>
-      <c r="K67" s="43"/>
+      <c r="K67" s="19"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
         <v>10120054</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="16">
         <v>101200</v>
       </c>
-      <c r="C68" s="36" t="s">
+      <c r="C68" s="57" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="16" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4186,29 +4284,29 @@
       <c r="G68" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="62" t="s">
+      <c r="I68" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="43"/>
+      <c r="K68" s="19"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
         <v>10120055</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="16">
         <v>101200</v>
       </c>
-      <c r="C69" s="36" t="s">
+      <c r="C69" s="57" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="16" t="s">
         <v>196</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -4217,29 +4315,29 @@
       <c r="G69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="62" t="s">
+      <c r="I69" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="43"/>
+      <c r="K69" s="19"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="4">
         <v>10120056</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="16">
         <v>101200</v>
       </c>
-      <c r="C70" s="36" t="s">
+      <c r="C70" s="57" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="16" t="s">
         <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -4248,29 +4346,29 @@
       <c r="G70" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="62" t="s">
+      <c r="I70" s="64" t="s">
         <v>192</v>
       </c>
       <c r="J70" s="4"/>
-      <c r="K70" s="43"/>
+      <c r="K70" s="19"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
         <v>10120061</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="16">
         <v>101200</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="26" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" s="26" t="s">
         <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -4279,29 +4377,29 @@
       <c r="G71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="15" t="s">
+      <c r="H71" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="59" t="s">
+      <c r="I71" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="46"/>
+      <c r="K71" s="27"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
         <v>10120062</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="16">
         <v>101200</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="26" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="26" t="s">
         <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -4310,29 +4408,29 @@
       <c r="G72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H72" s="15" t="s">
+      <c r="H72" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I72" s="59" t="s">
+      <c r="I72" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J72" s="6"/>
-      <c r="K72" s="46"/>
+      <c r="K72" s="27"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
         <v>10120063</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="16">
         <v>101200</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="26" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="26" t="s">
         <v>203</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -4341,29 +4439,29 @@
       <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H73" s="15" t="s">
+      <c r="H73" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I73" s="59" t="s">
+      <c r="I73" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="46"/>
+      <c r="K73" s="27"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <v>10120064</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="16">
         <v>101200</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="26" t="s">
         <v>204</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="26" t="s">
         <v>205</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -4372,29 +4470,29 @@
       <c r="G74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H74" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I74" s="59" t="s">
+      <c r="I74" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="46"/>
+      <c r="K74" s="27"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <v>10120065</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="16">
         <v>101200</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="26" t="s">
         <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="26" t="s">
         <v>206</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -4403,29 +4501,29 @@
       <c r="G75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="15" t="s">
+      <c r="H75" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I75" s="59" t="s">
+      <c r="I75" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="46"/>
+      <c r="K75" s="27"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <v>10120066</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="16">
         <v>101200</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="26" t="s">
         <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="26" t="s">
         <v>207</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -4434,29 +4532,29 @@
       <c r="G76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H76" s="15" t="s">
+      <c r="H76" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="59" t="s">
+      <c r="I76" s="61" t="s">
         <v>201</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="46"/>
+      <c r="K76" s="27"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
         <v>10140001</v>
       </c>
-      <c r="B77" s="35">
+      <c r="B77" s="55">
         <v>101400</v>
       </c>
-      <c r="C77" s="35" t="s">
+      <c r="C77" s="55" t="s">
         <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="35" t="s">
+      <c r="E77" s="55" t="s">
         <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -4465,10 +4563,10 @@
       <c r="G77" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H77" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="I77" s="63" t="s">
+      <c r="I77" s="65" t="s">
         <v>212</v>
       </c>
       <c r="K77" s="56"/>
@@ -4477,16 +4575,16 @@
       <c r="A78" s="3">
         <v>10140011</v>
       </c>
-      <c r="B78" s="35">
+      <c r="B78" s="55">
         <v>101400</v>
       </c>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="55" t="s">
         <v>208</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="35" t="s">
+      <c r="E78" s="55" t="s">
         <v>140</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -4495,7 +4593,7 @@
       <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="H78" s="21" t="s">
         <v>211</v>
       </c>
       <c r="I78" s="3" t="s">
@@ -4507,16 +4605,16 @@
       <c r="A79" s="7">
         <v>10140021</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="21">
         <v>101400</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="21" t="s">
         <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="21" t="s">
         <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -4525,28 +4623,28 @@
       <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H79" s="21" t="s">
         <v>143</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K79" s="44"/>
+      <c r="K79" s="22"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
         <v>10140022</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="21">
         <v>101400</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="21" t="s">
         <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="21" t="s">
         <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -4555,28 +4653,28 @@
       <c r="G80" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="I80" s="63" t="s">
+      <c r="I80" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="K80" s="44"/>
+      <c r="K80" s="22"/>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="7">
         <v>10140023</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="21">
         <v>101400</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="21" t="s">
         <v>217</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="21" t="s">
         <v>143</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -4585,28 +4683,28 @@
       <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="H81" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="I81" s="63" t="s">
+      <c r="I81" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="K81" s="44"/>
+      <c r="K81" s="22"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="1">
         <v>10240011</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="10">
         <v>102400</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="16" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -4615,16 +4713,16 @@
       <c r="G82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="10" t="s">
+      <c r="H82" s="16" t="s">
         <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J82" s="41" t="s">
+      <c r="J82" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K82" s="42" t="s">
+      <c r="K82" s="18" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4632,16 +4730,16 @@
       <c r="A83" s="1">
         <v>10240012</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="10">
         <v>102400</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="16" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -4650,29 +4748,29 @@
       <c r="G83" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="16" t="s">
         <v>26</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J83" s="4"/>
-      <c r="K83" s="43"/>
+      <c r="K83" s="19"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="1">
         <v>10240021</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="10">
         <v>102400</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="21" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -4681,27 +4779,27 @@
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="12"/>
-      <c r="I84" s="58" t="s">
+      <c r="H84" s="21"/>
+      <c r="I84" s="60" t="s">
         <v>39</v>
       </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="44"/>
+      <c r="K84" s="22"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="1">
         <v>10240022</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="10">
         <v>102400</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="21" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -4710,27 +4808,27 @@
       <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="12"/>
+      <c r="H85" s="21"/>
       <c r="I85" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J85" s="12"/>
-      <c r="K85" s="45"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="23"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="1">
         <v>10240023</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="10">
         <v>102400</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="21" t="s">
         <v>46</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -4739,27 +4837,27 @@
       <c r="G86" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="12"/>
+      <c r="H86" s="21"/>
       <c r="I86" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J86" s="12"/>
-      <c r="K86" s="45"/>
+      <c r="J86" s="21"/>
+      <c r="K86" s="23"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="1">
         <v>10240024</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="10">
         <v>102400</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="21" t="s">
         <v>51</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -4768,27 +4866,27 @@
       <c r="G87" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="12"/>
+      <c r="H87" s="21"/>
       <c r="I87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J87" s="12"/>
-      <c r="K87" s="45"/>
+      <c r="J87" s="21"/>
+      <c r="K87" s="23"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="1">
         <v>10240025</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="10">
         <v>102400</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="21" t="s">
         <v>56</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -4797,27 +4895,27 @@
       <c r="G88" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H88" s="12"/>
+      <c r="H88" s="21"/>
       <c r="I88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="12"/>
-      <c r="K88" s="45"/>
+      <c r="J88" s="21"/>
+      <c r="K88" s="23"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="1">
         <v>10240026</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="10">
         <v>102400</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="21" t="s">
         <v>61</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -4826,16 +4924,16 @@
       <c r="G89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H89" s="12" t="s">
+      <c r="H89" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="41" t="s">
+      <c r="J89" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K89" s="45" t="s">
+      <c r="K89" s="23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4843,16 +4941,16 @@
       <c r="A90" s="1">
         <v>10240031</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="10">
         <v>102400</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F90" s="6" t="s">
@@ -4861,14 +4959,14 @@
       <c r="G90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="15"/>
+      <c r="H90" s="26"/>
       <c r="I90" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J90" s="41" t="s">
+      <c r="J90" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K90" s="46" t="s">
+      <c r="K90" s="27" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4876,16 +4974,16 @@
       <c r="A91" s="1">
         <v>10240032</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="10">
         <v>102400</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="24" t="s">
         <v>62</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E91" s="26" t="s">
         <v>67</v>
       </c>
       <c r="F91" s="6" t="s">
@@ -4894,147 +4992,147 @@
       <c r="G91" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="15"/>
-      <c r="I91" s="59" t="s">
+      <c r="H91" s="26"/>
+      <c r="I91" s="61" t="s">
         <v>39</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="46"/>
+      <c r="K91" s="27"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="1">
         <v>10240041</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="10">
         <v>102400</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="18" t="s">
+      <c r="E92" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="17" t="s">
+      <c r="F92" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="17" t="s">
+      <c r="G92" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="H92" s="18"/>
-      <c r="I92" s="17" t="s">
+      <c r="H92" s="30"/>
+      <c r="I92" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="J92" s="17"/>
-      <c r="K92" s="47"/>
+      <c r="J92" s="29"/>
+      <c r="K92" s="31"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="1">
         <v>10240051</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="10">
         <v>102400</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="20" t="s">
+      <c r="D93" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="21" t="s">
+      <c r="E93" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="20" t="s">
+      <c r="F93" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="20" t="s">
+      <c r="G93" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="21"/>
-      <c r="I93" s="60" t="s">
+      <c r="H93" s="34"/>
+      <c r="I93" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="20"/>
-      <c r="K93" s="48"/>
+      <c r="J93" s="33"/>
+      <c r="K93" s="35"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="1">
         <v>10240052</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="10">
         <v>102400</v>
       </c>
-      <c r="C94" s="19" t="s">
+      <c r="C94" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="22" t="s">
+      <c r="D94" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="21" t="s">
+      <c r="E94" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="20" t="s">
+      <c r="F94" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="20" t="s">
+      <c r="G94" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="21"/>
-      <c r="I94" s="20" t="s">
+      <c r="H94" s="34"/>
+      <c r="I94" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="J94" s="41" t="s">
+      <c r="J94" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K94" s="48" t="s">
+      <c r="K94" s="35" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A95" s="23">
+      <c r="A95" s="37">
         <v>10240061</v>
       </c>
-      <c r="B95" s="24">
+      <c r="B95" s="11">
         <v>102400</v>
       </c>
-      <c r="C95" s="25" t="s">
+      <c r="C95" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="26" t="s">
+      <c r="D95" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="24" t="s">
+      <c r="E95" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F95" s="23" t="s">
+      <c r="F95" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="G95" s="23" t="s">
+      <c r="G95" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="24"/>
-      <c r="I95" s="23" t="s">
+      <c r="H95" s="11"/>
+      <c r="I95" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J95" s="23"/>
-      <c r="K95" s="49"/>
+      <c r="J95" s="37"/>
+      <c r="K95" s="40"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="2">
         <v>10240071</v>
       </c>
-      <c r="B96" s="27">
+      <c r="B96" s="41">
         <v>102400</v>
       </c>
-      <c r="C96" s="28" t="s">
+      <c r="C96" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="27" t="s">
+      <c r="E96" s="41" t="s">
         <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -5043,26 +5141,26 @@
       <c r="G96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H96" s="27"/>
-      <c r="I96" s="61" t="s">
+      <c r="H96" s="41"/>
+      <c r="I96" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="K96" s="50"/>
+      <c r="K96" s="43"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="2">
         <v>10240072</v>
       </c>
-      <c r="B97" s="27">
+      <c r="B97" s="41">
         <v>102400</v>
       </c>
-      <c r="C97" s="28" t="s">
+      <c r="C97" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="27" t="s">
+      <c r="E97" s="41" t="s">
         <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -5071,27 +5169,27 @@
       <c r="G97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="27"/>
+      <c r="H97" s="41"/>
       <c r="I97" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="27"/>
-      <c r="K97" s="51"/>
+      <c r="J97" s="41"/>
+      <c r="K97" s="44"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="2">
         <v>10240073</v>
       </c>
-      <c r="B98" s="27">
+      <c r="B98" s="41">
         <v>102400</v>
       </c>
-      <c r="C98" s="28" t="s">
+      <c r="C98" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E98" s="27" t="s">
+      <c r="E98" s="41" t="s">
         <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -5100,27 +5198,27 @@
       <c r="G98" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="27"/>
+      <c r="H98" s="41"/>
       <c r="I98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J98" s="27"/>
-      <c r="K98" s="51"/>
+      <c r="J98" s="41"/>
+      <c r="K98" s="44"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="2">
         <v>10240074</v>
       </c>
-      <c r="B99" s="27">
+      <c r="B99" s="41">
         <v>102400</v>
       </c>
-      <c r="C99" s="28" t="s">
+      <c r="C99" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="27" t="s">
+      <c r="E99" s="41" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -5129,27 +5227,27 @@
       <c r="G99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H99" s="27"/>
+      <c r="H99" s="41"/>
       <c r="I99" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J99" s="27"/>
-      <c r="K99" s="51"/>
+      <c r="J99" s="41"/>
+      <c r="K99" s="44"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="2">
         <v>10240075</v>
       </c>
-      <c r="B100" s="27">
+      <c r="B100" s="41">
         <v>102400</v>
       </c>
-      <c r="C100" s="28" t="s">
+      <c r="C100" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="27" t="s">
+      <c r="E100" s="41" t="s">
         <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -5158,27 +5256,27 @@
       <c r="G100" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="27"/>
+      <c r="H100" s="41"/>
       <c r="I100" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J100" s="27"/>
-      <c r="K100" s="51"/>
+      <c r="J100" s="41"/>
+      <c r="K100" s="44"/>
     </row>
     <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="2">
         <v>10240076</v>
       </c>
-      <c r="B101" s="27">
+      <c r="B101" s="41">
         <v>102400</v>
       </c>
-      <c r="C101" s="28" t="s">
+      <c r="C101" s="42" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E101" s="27" t="s">
+      <c r="E101" s="41" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -5187,47 +5285,681 @@
       <c r="G101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="27" t="s">
+      <c r="H101" s="41" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J101" s="41" t="s">
+      <c r="J101" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="51" t="s">
+      <c r="K101" s="44" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A102" s="29">
+      <c r="A102" s="45">
         <v>10240091</v>
       </c>
-      <c r="B102" s="30">
+      <c r="B102" s="46">
         <v>102400</v>
       </c>
-      <c r="C102" s="30"/>
-      <c r="D102" s="29" t="s">
+      <c r="C102" s="46"/>
+      <c r="D102" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E102" s="30" t="s">
+      <c r="E102" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="F102" s="29" t="s">
+      <c r="F102" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="G102" s="29" t="s">
+      <c r="G102" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="H102" s="30" t="s">
+      <c r="H102" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="I102" s="29" t="s">
+      <c r="I102" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="J102" s="30"/>
-      <c r="K102" s="52"/>
+      <c r="J102" s="46"/>
+      <c r="K102" s="47"/>
+    </row>
+    <row r="103" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A103" s="8">
+        <v>10170010</v>
+      </c>
+      <c r="B103" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K103" s="59"/>
+    </row>
+    <row r="104" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A104" s="8">
+        <v>10170011</v>
+      </c>
+      <c r="B104" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="K104" s="59"/>
+    </row>
+    <row r="105" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A105" s="8">
+        <v>10170012</v>
+      </c>
+      <c r="B105" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="K105" s="59"/>
+    </row>
+    <row r="106" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A106" s="8">
+        <v>10170021</v>
+      </c>
+      <c r="B106" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K106" s="59"/>
+    </row>
+    <row r="107" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A107" s="8">
+        <v>10170022</v>
+      </c>
+      <c r="B107" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K107" s="59"/>
+    </row>
+    <row r="108" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A108" s="8">
+        <v>10170023</v>
+      </c>
+      <c r="B108" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K108" s="59"/>
+    </row>
+    <row r="109" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A109" s="8">
+        <v>10170024</v>
+      </c>
+      <c r="B109" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K109" s="59"/>
+    </row>
+    <row r="110" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A110" s="8">
+        <v>10170030</v>
+      </c>
+      <c r="B110" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I110" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="K110" s="59"/>
+    </row>
+    <row r="111" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A111" s="8">
+        <v>10170031</v>
+      </c>
+      <c r="B111" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K111" s="59"/>
+    </row>
+    <row r="112" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A112" s="8">
+        <v>10170032</v>
+      </c>
+      <c r="B112" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K112" s="59"/>
+    </row>
+    <row r="113" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A113" s="8">
+        <v>10170033</v>
+      </c>
+      <c r="B113" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K113" s="59"/>
+    </row>
+    <row r="114" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A114" s="8">
+        <v>10170034</v>
+      </c>
+      <c r="B114" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K114" s="59"/>
+    </row>
+    <row r="115" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A115" s="8">
+        <v>10170035</v>
+      </c>
+      <c r="B115" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K115" s="59"/>
+    </row>
+    <row r="116" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A116" s="8">
+        <v>10170036</v>
+      </c>
+      <c r="B116" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K116" s="59"/>
+    </row>
+    <row r="117" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A117" s="8">
+        <v>10170037</v>
+      </c>
+      <c r="B117" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K117" s="59"/>
+    </row>
+    <row r="118" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A118" s="8">
+        <v>10170038</v>
+      </c>
+      <c r="B118" s="8">
+        <v>101700</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K118" s="59"/>
+    </row>
+    <row r="119" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A119" s="8">
+        <v>10170039</v>
+      </c>
+      <c r="B119" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K119" s="59"/>
+    </row>
+    <row r="120" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A120" s="8">
+        <v>10170040</v>
+      </c>
+      <c r="B120" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K120" s="59"/>
+    </row>
+    <row r="121" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A121" s="8">
+        <v>10220011</v>
+      </c>
+      <c r="B121" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K121" s="59"/>
+    </row>
+    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A122" s="8">
+        <v>10220021</v>
+      </c>
+      <c r="B122" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K122" s="59"/>
+    </row>
+    <row r="123" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A123" s="8">
+        <v>10220099</v>
+      </c>
+      <c r="B123" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K123" s="59"/>
+    </row>
+    <row r="124" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A124" s="8">
+        <v>10220031</v>
+      </c>
+      <c r="B124" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F124" s="8"/>
+      <c r="G124" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K124" s="59"/>
+    </row>
+    <row r="125" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A125" s="8">
+        <v>10220032</v>
+      </c>
+      <c r="B125" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="K125" s="59"/>
+    </row>
+    <row r="126" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A126" s="8">
+        <v>10220012</v>
+      </c>
+      <c r="B126" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F126" s="8"/>
+      <c r="G126" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H126" s="8"/>
+      <c r="I126" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K126" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5245,26 +5977,26 @@
     <col min="5" max="5" width="31.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5272,16 +6004,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5289,16 +6021,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5306,104 +6038,104 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="F5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5411,7 +6143,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5419,7 +6151,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5427,7 +6159,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5435,7 +6167,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5443,7 +6175,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5451,7 +6183,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5459,7 +6191,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5467,7 +6199,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -5475,7 +6207,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -5483,7 +6215,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5491,7 +6223,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5499,7 +6231,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5507,7 +6239,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -5515,7 +6247,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5523,7 +6255,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -5531,7 +6263,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5539,7 +6271,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5547,7 +6279,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5555,7 +6287,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5563,7 +6295,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5571,7 +6303,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5579,7 +6311,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5587,7 +6319,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5595,7 +6327,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5603,7 +6335,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5611,7 +6343,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5619,7 +6351,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5627,7 +6359,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5635,7 +6367,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5643,7 +6375,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5651,7 +6383,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -5659,7 +6391,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="309">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -905,6 +905,18 @@
   </si>
   <si>
     <t>3_1_1|9_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_20|3_10</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2267,7 +2279,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5961,6 +5973,30 @@
       </c>
       <c r="K126" s="59"/>
     </row>
+    <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="8">
+        <v>10220033</v>
+      </c>
+      <c r="B127" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="K127" s="59"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5979,24 +6015,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6004,16 +6040,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6021,16 +6057,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6038,16 +6074,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6055,7 +6091,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6063,7 +6099,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6071,7 +6107,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6079,7 +6115,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6087,7 +6123,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6095,7 +6131,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6103,7 +6139,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6111,7 +6147,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6119,7 +6155,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6127,7 +6163,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6135,7 +6171,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6143,7 +6179,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6151,7 +6187,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6159,7 +6195,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6167,7 +6203,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6175,7 +6211,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6183,7 +6219,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6191,7 +6227,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6199,7 +6235,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6207,7 +6243,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6215,7 +6251,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6223,7 +6259,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6231,7 +6267,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6239,7 +6275,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6247,7 +6283,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6255,7 +6291,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6263,7 +6299,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6271,7 +6307,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6279,7 +6315,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6287,7 +6323,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6295,7 +6331,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6303,7 +6339,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6311,7 +6347,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6319,7 +6355,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6327,7 +6363,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6335,7 +6371,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6343,7 +6379,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6351,7 +6387,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6359,7 +6395,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6367,7 +6403,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6375,7 +6411,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6383,7 +6419,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6391,7 +6427,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="308">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -914,9 +914,6 @@
   </si>
   <si>
     <t>11_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>0_40|1_30|2_20|3_10</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -5891,7 +5888,7 @@
       </c>
       <c r="H123" s="8"/>
       <c r="I123" s="8" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="K123" s="59"/>
     </row>
@@ -5917,7 +5914,7 @@
         <v>240</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="K124" s="59"/>
     </row>
@@ -5993,7 +5990,7 @@
         <v>251</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="K127" s="59"/>
     </row>
@@ -6015,24 +6012,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" t="s">
         <v>253</v>
-      </c>
-      <c r="D1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" t="s">
         <v>255</v>
       </c>
-      <c r="B2" t="s">
-        <v>256</v>
-      </c>
       <c r="D2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" t="s">
         <v>255</v>
-      </c>
-      <c r="E2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6040,16 +6037,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" t="s">
         <v>258</v>
-      </c>
-      <c r="F3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6057,16 +6054,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" t="s">
         <v>261</v>
-      </c>
-      <c r="F4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6074,16 +6071,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" t="s">
         <v>264</v>
-      </c>
-      <c r="F5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6091,7 +6088,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6099,7 +6096,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6107,7 +6104,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6115,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6123,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6131,7 +6128,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6139,7 +6136,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6147,7 +6144,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6155,7 +6152,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6163,7 +6160,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6171,7 +6168,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6179,7 +6176,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6187,7 +6184,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6195,7 +6192,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6203,7 +6200,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6211,7 +6208,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6219,7 +6216,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6227,7 +6224,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6235,7 +6232,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6243,7 +6240,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6251,7 +6248,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6259,7 +6256,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6267,7 +6264,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6275,7 +6272,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6283,7 +6280,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6291,7 +6288,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6299,7 +6296,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6307,7 +6304,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6315,7 +6312,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6323,7 +6320,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6331,7 +6328,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6339,7 +6336,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6347,7 +6344,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6355,7 +6352,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6363,7 +6360,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6371,7 +6368,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6379,7 +6376,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6387,7 +6384,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6395,7 +6392,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6403,7 +6400,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6411,7 +6408,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6419,7 +6416,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6427,7 +6424,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="311">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -883,6 +883,9 @@
     <t>11_14</t>
   </si>
   <si>
+    <t>2_20</t>
+  </si>
+  <si>
     <t>改出1个大奖</t>
   </si>
   <si>
@@ -898,6 +901,9 @@
     <t>11_12_13_14_15_16_17_18</t>
   </si>
   <si>
+    <t>1_20</t>
+  </si>
+  <si>
     <t>异形位置改为不中奖图案</t>
   </si>
   <si>
@@ -905,6 +911,18 @@
   </si>
   <si>
     <t>3_1_1|9_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>3_10</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2267,7 +2285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5905,7 +5923,7 @@
         <v>240</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="K124" s="59"/>
     </row>
@@ -5917,23 +5935,23 @@
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="K125" s="59"/>
     </row>
@@ -5945,21 +5963,45 @@
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H126" s="8"/>
       <c r="I126" s="8" t="s">
         <v>107</v>
       </c>
       <c r="K126" s="59"/>
+    </row>
+    <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="8">
+        <v>10220033</v>
+      </c>
+      <c r="B127" s="8">
+        <v>102200</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="K127" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5979,24 +6021,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6004,16 +6046,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6021,16 +6063,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6038,16 +6080,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6055,7 +6097,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6063,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6071,7 +6113,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6079,7 +6121,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6087,7 +6129,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6095,7 +6137,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6103,7 +6145,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6111,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6119,7 +6161,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6127,7 +6169,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6135,7 +6177,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6143,7 +6185,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6151,7 +6193,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6159,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6167,7 +6209,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6175,7 +6217,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6183,7 +6225,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6191,7 +6233,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6199,7 +6241,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6207,7 +6249,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6215,7 +6257,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6223,7 +6265,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6231,7 +6273,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6239,7 +6281,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6247,7 +6289,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6255,7 +6297,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6263,7 +6305,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6271,7 +6313,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6279,7 +6321,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6287,7 +6329,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6295,7 +6337,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6303,7 +6345,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6311,7 +6353,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6319,7 +6361,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6327,7 +6369,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6335,7 +6377,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6343,7 +6385,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6351,7 +6393,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6359,7 +6401,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6367,7 +6409,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6375,7 +6417,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6383,7 +6425,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6391,7 +6433,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialGird" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="308">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -883,9 +883,6 @@
     <t>11_14</t>
   </si>
   <si>
-    <t>2_20</t>
-  </si>
-  <si>
     <t>改出1个大奖</t>
   </si>
   <si>
@@ -901,9 +898,6 @@
     <t>11_12_13_14_15_16_17_18</t>
   </si>
   <si>
-    <t>1_20</t>
-  </si>
-  <si>
     <t>异形位置改为不中奖图案</t>
   </si>
   <si>
@@ -920,9 +914,6 @@
   </si>
   <si>
     <t>11_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>3_10</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -5897,7 +5888,7 @@
       </c>
       <c r="H123" s="8"/>
       <c r="I123" s="8" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="K123" s="59"/>
     </row>
@@ -5923,7 +5914,7 @@
         <v>240</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>241</v>
+        <v>106</v>
       </c>
       <c r="K124" s="59"/>
     </row>
@@ -5935,23 +5926,23 @@
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="E125" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>244</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H125" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="H125" s="8" t="s">
-        <v>246</v>
-      </c>
       <c r="I125" s="8" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="K125" s="59"/>
     </row>
@@ -5963,15 +5954,15 @@
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H126" s="8"/>
       <c r="I126" s="8" t="s">
@@ -5987,19 +5978,19 @@
         <v>102200</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>254</v>
+        <v>107</v>
       </c>
       <c r="K127" s="59"/>
     </row>
@@ -6021,24 +6012,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6046,16 +6037,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6063,16 +6054,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6080,16 +6071,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6097,7 +6088,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6105,7 +6096,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6113,7 +6104,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6121,7 +6112,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6129,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6137,7 +6128,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6145,7 +6136,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6153,7 +6144,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6161,7 +6152,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6169,7 +6160,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6177,7 +6168,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6185,7 +6176,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6193,7 +6184,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6201,7 +6192,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6209,7 +6200,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6217,7 +6208,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6225,7 +6216,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6233,7 +6224,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6241,7 +6232,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6249,7 +6240,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6257,7 +6248,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6265,7 +6256,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6273,7 +6264,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6281,7 +6272,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6289,7 +6280,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6297,7 +6288,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6305,7 +6296,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6313,7 +6304,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6321,7 +6312,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6329,7 +6320,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6337,7 +6328,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6345,7 +6336,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6353,7 +6344,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6361,7 +6352,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6369,7 +6360,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6377,7 +6368,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6385,7 +6376,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6393,7 +6384,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6401,7 +6392,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6409,7 +6400,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6417,7 +6408,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6425,7 +6416,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6433,7 +6424,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="315">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -877,7 +877,10 @@
     <t>结束特殊玩法</t>
   </si>
   <si>
-    <t>6_1_1|7_1_1</t>
+    <t>7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>0_50|1_40|2_10</t>
   </si>
   <si>
     <t>11_14</t>
@@ -914,6 +917,24 @@
   </si>
   <si>
     <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>10_11_12</t>
+  </si>
+  <si>
+    <t>13_10|14_5|15_2|16_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>0_50|1_35|2_10|3_5</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2276,7 +2297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5834,7 +5855,7 @@
       </c>
       <c r="K121" s="59"/>
     </row>
-    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
+    <row r="122" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A122" s="8">
         <v>10220021</v>
       </c>
@@ -5888,7 +5909,7 @@
       </c>
       <c r="H123" s="8"/>
       <c r="I123" s="8" t="s">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="K123" s="59"/>
     </row>
@@ -5911,7 +5932,7 @@
         <v>233</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I124" s="8" t="s">
         <v>106</v>
@@ -5926,20 +5947,20 @@
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I125" s="8" t="s">
         <v>201</v>
@@ -5954,15 +5975,15 @@
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H126" s="8"/>
       <c r="I126" s="8" t="s">
@@ -5978,21 +5999,165 @@
         <v>102200</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>107</v>
       </c>
       <c r="K127" s="59"/>
+    </row>
+    <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="8">
+        <v>10210001</v>
+      </c>
+      <c r="B128" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K128" s="59"/>
+    </row>
+    <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="8">
+        <v>10210011</v>
+      </c>
+      <c r="B129" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K129" s="59"/>
+    </row>
+    <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="8">
+        <v>10210021</v>
+      </c>
+      <c r="B130" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H130" s="8">
+        <v>12</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="K130" s="59"/>
+    </row>
+    <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="8">
+        <v>10210031</v>
+      </c>
+      <c r="B131" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K131" s="59"/>
+    </row>
+    <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="8">
+        <v>10210041</v>
+      </c>
+      <c r="B132" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K132" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6012,24 +6177,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6037,16 +6202,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6054,16 +6219,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6071,16 +6236,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="F5" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6088,7 +6253,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6096,7 +6261,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6104,7 +6269,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6112,7 +6277,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6120,7 +6285,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6128,7 +6293,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6136,7 +6301,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6144,7 +6309,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6152,7 +6317,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6160,7 +6325,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6168,7 +6333,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6176,7 +6341,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6184,7 +6349,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6192,7 +6357,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6200,7 +6365,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6208,7 +6373,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6216,7 +6381,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6224,7 +6389,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6232,7 +6397,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6240,7 +6405,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6248,7 +6413,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6256,7 +6421,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6264,7 +6429,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6272,7 +6437,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6280,7 +6445,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6288,7 +6453,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6296,7 +6461,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6304,7 +6469,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6312,7 +6477,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6320,7 +6485,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6328,7 +6493,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6336,7 +6501,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6344,7 +6509,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6352,7 +6517,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6360,7 +6525,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6368,7 +6533,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6376,7 +6541,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6384,7 +6549,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6392,7 +6557,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6400,7 +6565,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6408,7 +6573,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6416,7 +6581,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6424,7 +6589,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="314">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -914,6 +914,24 @@
   </si>
   <si>
     <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>10_11_12</t>
+  </si>
+  <si>
+    <t>13_10|14_5|15_2|16_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>0_50|1_35|2_10|3_5</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1269,12 +1287,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2276,7 +2294,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5994,6 +6012,150 @@
       </c>
       <c r="K127" s="59"/>
     </row>
+    <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="8">
+        <v>10210001</v>
+      </c>
+      <c r="B128" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K128" s="59"/>
+    </row>
+    <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="8">
+        <v>10210011</v>
+      </c>
+      <c r="B129" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K129" s="59"/>
+    </row>
+    <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="8">
+        <v>10210021</v>
+      </c>
+      <c r="B130" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="H130" s="8">
+        <v>12</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="K130" s="59"/>
+    </row>
+    <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="8">
+        <v>10210031</v>
+      </c>
+      <c r="B131" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K131" s="59"/>
+    </row>
+    <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="8">
+        <v>10210041</v>
+      </c>
+      <c r="B132" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K132" s="59"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -6012,24 +6174,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6037,16 +6199,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6054,16 +6216,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6071,16 +6233,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6088,7 +6250,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6096,7 +6258,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6104,7 +6266,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6112,7 +6274,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6120,7 +6282,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6128,7 +6290,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6136,7 +6298,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6144,7 +6306,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6152,7 +6314,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6160,7 +6322,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6168,7 +6330,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6176,7 +6338,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6184,7 +6346,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6192,7 +6354,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6200,7 +6362,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6208,7 +6370,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6216,7 +6378,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6224,7 +6386,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6232,7 +6394,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6240,7 +6402,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6248,7 +6410,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6256,7 +6418,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6264,7 +6426,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6272,7 +6434,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6280,7 +6442,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6288,7 +6450,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6296,7 +6458,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6304,7 +6466,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6312,7 +6474,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6320,7 +6482,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6328,7 +6490,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6336,7 +6498,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6344,7 +6506,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6352,7 +6514,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6360,7 +6522,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6368,7 +6530,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6376,7 +6538,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6384,7 +6546,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6392,7 +6554,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6400,7 +6562,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6408,7 +6570,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6416,7 +6578,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6424,7 +6586,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="329">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -877,7 +877,28 @@
     <t>结束特殊玩法</t>
   </si>
   <si>
-    <t>6_1_1|7_1_1</t>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>概率改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>常规模式出现</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_50|1_40_2_10</t>
+  </si>
+  <si>
+    <t>用于触发奖池</t>
   </si>
   <si>
     <t>11_14</t>
@@ -895,9 +916,6 @@
     <t>13_1_1|14_1_1|15_1_1</t>
   </si>
   <si>
-    <t>11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
     <t>异形位置改为不中奖图案</t>
   </si>
   <si>
@@ -910,12 +928,15 @@
     <t>改出3个SCATTER</t>
   </si>
   <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
     <t>11_14_15_16_17_18</t>
   </si>
   <si>
+    <t>改出1个19符号</t>
+  </si>
+  <si>
+    <t>改出1个20符号</t>
+  </si>
+  <si>
     <t>10_11_12</t>
   </si>
   <si>
@@ -932,6 +953,30 @@
   </si>
   <si>
     <t>改出3个bonus</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17</t>
+  </si>
+  <si>
+    <t>14_10|14_5|16_2|17_1</t>
+  </si>
+  <si>
+    <t>21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_15|3_10|4_7|5_3</t>
+  </si>
+  <si>
+    <t>免费游戏</t>
+  </si>
+  <si>
+    <t>改出+1免费符号</t>
+  </si>
+  <si>
+    <t>11_12_13</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1287,12 +1332,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2294,7 +2339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5852,7 +5897,7 @@
       </c>
       <c r="K121" s="59"/>
     </row>
-    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
+    <row r="122" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A122" s="8">
         <v>10220021</v>
       </c>
@@ -5896,13 +5941,13 @@
         <v>238</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>238</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H123" s="8"/>
       <c r="I123" s="8" t="s">
@@ -5912,101 +5957,106 @@
     </row>
     <row r="124" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="8">
-        <v>10220031</v>
+        <v>10220030</v>
       </c>
       <c r="B124" s="8">
         <v>102200</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D124" s="8"/>
+        <v>241</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>242</v>
+      </c>
       <c r="E124" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F124" s="8"/>
       <c r="G124" s="8" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="K124" s="59"/>
     </row>
     <row r="125" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="8">
-        <v>10220032</v>
+        <v>10220031</v>
       </c>
       <c r="B125" s="8">
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>243</v>
+        <v>146</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="8" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>201</v>
+        <v>106</v>
       </c>
       <c r="K125" s="59"/>
     </row>
     <row r="126" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A126" s="8">
-        <v>10220012</v>
+        <v>10220032</v>
       </c>
       <c r="B126" s="8">
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D126" s="8"/>
+        <v>248</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>249</v>
+      </c>
       <c r="E126" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="H126" s="8"/>
+        <v>251</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>244</v>
+      </c>
       <c r="I126" s="8" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K126" s="59"/>
     </row>
     <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A127" s="8">
-        <v>10220033</v>
+        <v>10220012</v>
       </c>
       <c r="B127" s="8">
         <v>102200</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>249</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="D127" s="8"/>
       <c r="E127" s="8" t="s">
-        <v>146</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F127" s="8"/>
       <c r="G127" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="H127" s="8" t="s">
-        <v>251</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="H127" s="8"/>
       <c r="I127" s="8" t="s">
         <v>107</v>
       </c>
@@ -6014,58 +6064,43 @@
     </row>
     <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A128" s="8">
-        <v>10210001</v>
+        <v>10220033</v>
       </c>
       <c r="B128" s="8">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K128" s="59"/>
     </row>
     <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A129" s="8">
-        <v>10210011</v>
+        <v>10220019</v>
       </c>
       <c r="B129" s="8">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="H129" s="8" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="I129" s="8" t="s">
         <v>39</v>
@@ -6074,43 +6109,37 @@
     </row>
     <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A130" s="8">
-        <v>10210021</v>
+        <v>10220020</v>
       </c>
       <c r="B130" s="8">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="H130" s="8">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>256</v>
+        <v>39</v>
       </c>
       <c r="K130" s="59"/>
     </row>
     <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A131" s="8">
-        <v>10210031</v>
+        <v>10210001</v>
       </c>
       <c r="B131" s="8">
         <v>102100</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>249</v>
+        <v>21</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>140</v>
@@ -6119,42 +6148,276 @@
         <v>133</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K131" s="59"/>
     </row>
     <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A132" s="8">
-        <v>10210041</v>
+        <v>10210011</v>
       </c>
       <c r="B132" s="8">
         <v>102100</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>257</v>
+        <v>21</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H132" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K132" s="59"/>
+    </row>
+    <row r="133" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A133" s="8">
+        <v>10210021</v>
+      </c>
+      <c r="B133" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H133" s="8">
+        <v>12</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K133" s="59"/>
+    </row>
+    <row r="134" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A134" s="8">
+        <v>10210031</v>
+      </c>
+      <c r="B134" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H134" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I134" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K132" s="59"/>
+      <c r="K134" s="59"/>
+    </row>
+    <row r="135" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A135" s="8">
+        <v>10210041</v>
+      </c>
+      <c r="B135" s="8">
+        <v>102100</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K135" s="59"/>
+    </row>
+    <row r="136" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A136" s="8">
+        <v>10180001</v>
+      </c>
+      <c r="B136" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K136" s="59"/>
+    </row>
+    <row r="137" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A137" s="8">
+        <v>10180011</v>
+      </c>
+      <c r="B137" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K137" s="59"/>
+    </row>
+    <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A138" s="8">
+        <v>10180021</v>
+      </c>
+      <c r="B138" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="K138" s="59"/>
+    </row>
+    <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A139" s="8">
+        <v>10180031</v>
+      </c>
+      <c r="B139" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K139" s="59"/>
+    </row>
+    <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="8">
+        <v>10180041</v>
+      </c>
+      <c r="B140" s="8">
+        <v>101801</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K140" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6174,24 +6437,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6199,16 +6462,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="F3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6216,16 +6479,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="F4" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6233,16 +6496,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="F5" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6250,7 +6513,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6258,7 +6521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6266,7 +6529,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6274,7 +6537,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6282,7 +6545,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6290,7 +6553,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6298,7 +6561,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6306,7 +6569,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6314,7 +6577,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6322,7 +6585,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6330,7 +6593,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6338,7 +6601,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6346,7 +6609,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6354,7 +6617,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6362,7 +6625,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6370,7 +6633,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6378,7 +6641,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6386,7 +6649,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6394,7 +6657,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6402,7 +6665,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6410,7 +6673,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6418,7 +6681,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6426,7 +6689,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6434,7 +6697,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6442,7 +6705,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6450,7 +6713,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6458,7 +6721,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6466,7 +6729,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6474,7 +6737,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6482,7 +6745,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6490,7 +6753,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6498,7 +6761,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6506,7 +6769,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6514,7 +6777,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6522,7 +6785,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6530,7 +6793,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6538,7 +6801,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6546,7 +6809,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6554,7 +6817,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6562,7 +6825,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6570,7 +6833,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6578,7 +6841,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6586,7 +6849,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="329">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -2339,7 +2339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -6274,16 +6274,16 @@
     </row>
     <row r="136" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A136" s="8">
-        <v>10180001</v>
+        <v>10210051</v>
       </c>
       <c r="B136" s="8">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="E136" s="8" t="s">
         <v>140</v>
@@ -6292,19 +6292,19 @@
         <v>133</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="K136" s="59"/>
     </row>
     <row r="137" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A137" s="8">
-        <v>10180011</v>
+        <v>10180001</v>
       </c>
       <c r="B137" s="8">
         <v>101800</v>
@@ -6313,97 +6313,97 @@
         <v>21</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H137" s="8" t="s">
         <v>266</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K137" s="59"/>
     </row>
     <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="8">
-        <v>10180021</v>
+        <v>10180011</v>
       </c>
       <c r="B138" s="8">
         <v>101800</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>71</v>
+        <v>268</v>
       </c>
       <c r="H138" s="8" t="s">
         <v>266</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>269</v>
+        <v>39</v>
       </c>
       <c r="K138" s="59"/>
     </row>
     <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="8">
-        <v>10180031</v>
+        <v>10180021</v>
       </c>
       <c r="B139" s="8">
         <v>101800</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>255</v>
+        <v>261</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>266</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="K139" s="59"/>
     </row>
     <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A140" s="8">
-        <v>10180041</v>
+        <v>10180031</v>
       </c>
       <c r="B140" s="8">
-        <v>101801</v>
+        <v>101800</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>133</v>
@@ -6412,12 +6412,42 @@
         <v>265</v>
       </c>
       <c r="H140" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K140" s="59"/>
+    </row>
+    <row r="141" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A141" s="8">
+        <v>10180041</v>
+      </c>
+      <c r="B141" s="8">
+        <v>101801</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H141" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="I140" s="8" t="s">
+      <c r="I141" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K140" s="59"/>
+      <c r="K141" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="333">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -850,15 +850,27 @@
     <t>19_10|20_5|21_2|22_1</t>
   </si>
   <si>
+    <t>概率改出百搭</t>
+  </si>
+  <si>
+    <t>百搭出现</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>0_50|1_35|2_10|3_5</t>
+  </si>
+  <si>
     <t>冰冻玩法改出百搭</t>
   </si>
   <si>
     <t>改出百搭</t>
   </si>
   <si>
-    <t>百搭出现</t>
-  </si>
-  <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
   </si>
   <si>
@@ -889,12 +901,6 @@
     <t>常规模式出现</t>
   </si>
   <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16_17_18</t>
-  </si>
-  <si>
     <t>0_50|1_40_2_10</t>
   </si>
   <si>
@@ -949,12 +955,15 @@
     <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
   </si>
   <si>
-    <t>0_50|1_35|2_10|3_5</t>
-  </si>
-  <si>
     <t>改出3个bonus</t>
   </si>
   <si>
+    <t>概率出现3个bonus</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_15|3_5</t>
+  </si>
+  <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
   </si>
   <si>
@@ -973,10 +982,13 @@
     <t>免费游戏</t>
   </si>
   <si>
-    <t>改出+1免费符号</t>
+    <t>概率改出+1免费符号</t>
   </si>
   <si>
     <t>11_12_13</t>
+  </si>
+  <si>
+    <t>0_70|1_30</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2339,7 +2351,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -5869,37 +5881,37 @@
     </row>
     <row r="121" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A121" s="8">
-        <v>10220011</v>
+        <v>10220001</v>
       </c>
       <c r="B121" s="8">
         <v>102200</v>
       </c>
       <c r="C121" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="E121" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F121" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E121" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F121" s="8" t="s">
+      <c r="G121" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="H121" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="I121" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="I121" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="K121" s="59"/>
     </row>
-    <row r="122" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
+    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A122" s="8">
-        <v>10220021</v>
+        <v>10220011</v>
       </c>
       <c r="B122" s="8">
         <v>102200</v>
@@ -5908,56 +5920,58 @@
         <v>235</v>
       </c>
       <c r="D122" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E122" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>232</v>
-      </c>
       <c r="G122" s="8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I122" s="8" t="s">
         <v>212</v>
       </c>
       <c r="K122" s="59"/>
     </row>
-    <row r="123" s="8" customFormat="1" ht="16.5" spans="1:11">
+    <row r="123" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A123" s="8">
-        <v>10220099</v>
+        <v>10220021</v>
       </c>
       <c r="B123" s="8">
         <v>102200</v>
       </c>
       <c r="C123" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="G123" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="D123" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F123" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G123" s="8" t="s">
+      <c r="H123" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="H123" s="8"/>
       <c r="I123" s="8" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="K123" s="59"/>
     </row>
     <row r="124" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="8">
-        <v>10220030</v>
+        <v>10220099</v>
       </c>
       <c r="B124" s="8">
         <v>102200</v>
@@ -5969,28 +5983,29 @@
         <v>242</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>146</v>
+        <v>243</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H124" s="8" t="s">
         <v>244</v>
       </c>
+      <c r="H124" s="8"/>
       <c r="I124" s="8" t="s">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="K124" s="59"/>
     </row>
     <row r="125" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="8">
-        <v>10220031</v>
+        <v>10220030</v>
       </c>
       <c r="B125" s="8">
         <v>102200</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>246</v>
@@ -5998,89 +6013,92 @@
       <c r="E125" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F125" s="8"/>
       <c r="G125" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H125" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="H125" s="8" t="s">
+      <c r="I125" s="8" t="s">
         <v>247</v>
-      </c>
-      <c r="I125" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="K125" s="59"/>
     </row>
     <row r="126" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A126" s="8">
-        <v>10220032</v>
+        <v>10220031</v>
       </c>
       <c r="B126" s="8">
         <v>102200</v>
       </c>
       <c r="C126" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D126" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D126" s="8" t="s">
-        <v>249</v>
-      </c>
       <c r="E126" s="8" t="s">
-        <v>250</v>
+        <v>146</v>
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K126" s="59"/>
     </row>
     <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A127" s="8">
-        <v>10220012</v>
+        <v>10220032</v>
       </c>
       <c r="B127" s="8">
         <v>102200</v>
       </c>
       <c r="C127" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E127" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8" t="s">
-        <v>253</v>
       </c>
       <c r="F127" s="8"/>
       <c r="G127" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="H127" s="8"/>
+        <v>253</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>233</v>
+      </c>
       <c r="I127" s="8" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K127" s="59"/>
     </row>
     <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A128" s="8">
-        <v>10220033</v>
+        <v>10220012</v>
       </c>
       <c r="B128" s="8">
         <v>102200</v>
       </c>
       <c r="C128" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E128" s="8" t="s">
-        <v>146</v>
-      </c>
+      <c r="F128" s="8"/>
       <c r="G128" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H128" s="8" t="s">
         <v>256</v>
       </c>
+      <c r="H128" s="8"/>
       <c r="I128" s="8" t="s">
         <v>107</v>
       </c>
@@ -6088,7 +6106,7 @@
     </row>
     <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A129" s="8">
-        <v>10220019</v>
+        <v>10220033</v>
       </c>
       <c r="B129" s="8">
         <v>102200</v>
@@ -6097,31 +6115,34 @@
         <v>257</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="K129" s="59"/>
     </row>
     <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A130" s="8">
-        <v>10220020</v>
+        <v>10220019</v>
       </c>
       <c r="B130" s="8">
         <v>102200</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="I130" s="8" t="s">
         <v>39</v>
@@ -6130,37 +6151,28 @@
     </row>
     <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A131" s="8">
-        <v>10210001</v>
+        <v>10220020</v>
       </c>
       <c r="B131" s="8">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K131" s="59"/>
     </row>
     <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A132" s="8">
-        <v>10210011</v>
+        <v>10210001</v>
       </c>
       <c r="B132" s="8">
         <v>102100</v>
@@ -6169,100 +6181,103 @@
         <v>21</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K132" s="59"/>
     </row>
     <row r="133" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A133" s="8">
-        <v>10210021</v>
+        <v>10210011</v>
       </c>
       <c r="B133" s="8">
         <v>102100</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="F133" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H133" s="8">
-        <v>12</v>
+        <v>253</v>
+      </c>
+      <c r="H133" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>263</v>
+        <v>39</v>
       </c>
       <c r="K133" s="59"/>
     </row>
     <row r="134" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A134" s="8">
-        <v>10210031</v>
+        <v>10210021</v>
       </c>
       <c r="B134" s="8">
         <v>102100</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H134" s="8" t="s">
-        <v>160</v>
+        <v>264</v>
+      </c>
+      <c r="H134" s="8">
+        <v>12</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="K134" s="59"/>
     </row>
     <row r="135" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A135" s="8">
-        <v>10210041</v>
+        <v>10210031</v>
       </c>
       <c r="B135" s="8">
         <v>102100</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>160</v>
@@ -6274,133 +6289,130 @@
     </row>
     <row r="136" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A136" s="8">
-        <v>10210051</v>
+        <v>10210041</v>
       </c>
       <c r="B136" s="8">
         <v>102100</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>245</v>
+        <v>107</v>
       </c>
       <c r="K136" s="59"/>
     </row>
     <row r="137" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A137" s="8">
-        <v>10180001</v>
+        <v>10210042</v>
       </c>
       <c r="B137" s="8">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>106</v>
+        <v>267</v>
       </c>
       <c r="K137" s="59"/>
     </row>
     <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="8">
-        <v>10180011</v>
+        <v>10210051</v>
       </c>
       <c r="B138" s="8">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="K138" s="59"/>
     </row>
     <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="8">
-        <v>10180021</v>
+        <v>10180001</v>
       </c>
       <c r="B139" s="8">
         <v>101800</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>71</v>
+        <v>268</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>269</v>
+        <v>106</v>
       </c>
       <c r="K139" s="59"/>
     </row>
     <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A140" s="8">
-        <v>10180031</v>
+        <v>10180002</v>
       </c>
       <c r="B140" s="8">
         <v>101800</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>255</v>
+        <v>21</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="E140" s="8" t="s">
         <v>140</v>
@@ -6409,45 +6421,132 @@
         <v>133</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="K140" s="59"/>
     </row>
     <row r="141" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A141" s="8">
-        <v>10180041</v>
+        <v>10180011</v>
       </c>
       <c r="B141" s="8">
-        <v>101801</v>
+        <v>101800</v>
       </c>
       <c r="C141" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E141" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>143</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>39</v>
       </c>
       <c r="K141" s="59"/>
+    </row>
+    <row r="142" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A142" s="8">
+        <v>10180021</v>
+      </c>
+      <c r="B142" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K142" s="59"/>
+    </row>
+    <row r="143" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A143" s="8">
+        <v>10180031</v>
+      </c>
+      <c r="B143" s="8">
+        <v>101800</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K143" s="59"/>
+    </row>
+    <row r="144" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A144" s="8">
+        <v>10180041</v>
+      </c>
+      <c r="B144" s="8">
+        <v>101801</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="K144" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6467,24 +6566,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6492,16 +6591,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6509,16 +6608,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6526,16 +6625,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6543,7 +6642,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6551,7 +6650,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6559,7 +6658,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6567,7 +6666,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6575,7 +6674,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6583,7 +6682,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6591,7 +6690,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6599,7 +6698,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6607,7 +6706,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6615,7 +6714,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6623,7 +6722,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6631,7 +6730,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6639,7 +6738,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6647,7 +6746,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6655,7 +6754,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6663,7 +6762,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6671,7 +6770,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6679,7 +6778,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6687,7 +6786,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6695,7 +6794,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6703,7 +6802,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6711,7 +6810,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6719,7 +6818,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6727,7 +6826,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6735,7 +6834,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6743,7 +6842,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6751,7 +6850,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6759,7 +6858,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6767,7 +6866,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6775,7 +6874,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6783,7 +6882,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6791,7 +6890,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6799,7 +6898,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6807,7 +6906,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6815,7 +6914,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6823,7 +6922,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6831,7 +6930,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6839,7 +6938,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6847,7 +6946,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6855,7 +6954,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6863,7 +6962,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6871,7 +6970,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6879,7 +6978,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="334">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -962,6 +962,9 @@
   </si>
   <si>
     <t>0_50|1_30|2_15|3_5</t>
+  </si>
+  <si>
+    <t>概率出现3个SCATTER</t>
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
@@ -2351,7 +2354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -6343,16 +6346,13 @@
     </row>
     <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="8">
-        <v>10210051</v>
+        <v>10210032</v>
       </c>
       <c r="B138" s="8">
         <v>102100</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="E138" s="8" t="s">
         <v>140</v>
@@ -6364,25 +6364,25 @@
         <v>232</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>261</v>
+        <v>160</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="K138" s="59"/>
     </row>
     <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="8">
-        <v>10180001</v>
+        <v>10210051</v>
       </c>
       <c r="B139" s="8">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>140</v>
@@ -6391,19 +6391,19 @@
         <v>133</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="K139" s="59"/>
     </row>
     <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A140" s="8">
-        <v>10180002</v>
+        <v>10180001</v>
       </c>
       <c r="B140" s="8">
         <v>101800</v>
@@ -6412,7 +6412,7 @@
         <v>21</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="E140" s="8" t="s">
         <v>140</v>
@@ -6421,19 +6421,19 @@
         <v>133</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="K140" s="59"/>
     </row>
     <row r="141" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A141" s="8">
-        <v>10180011</v>
+        <v>10180002</v>
       </c>
       <c r="B141" s="8">
         <v>101800</v>
@@ -6442,111 +6442,141 @@
         <v>21</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="K141" s="59"/>
     </row>
     <row r="142" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A142" s="8">
-        <v>10180021</v>
+        <v>10180011</v>
       </c>
       <c r="B142" s="8">
         <v>101800</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="K142" s="59"/>
     </row>
     <row r="143" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A143" s="8">
-        <v>10180031</v>
+        <v>10180021</v>
       </c>
       <c r="B143" s="8">
         <v>101800</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>257</v>
+        <v>263</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="K143" s="59"/>
     </row>
     <row r="144" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A144" s="8">
-        <v>10180041</v>
+        <v>10180031</v>
       </c>
       <c r="B144" s="8">
-        <v>101801</v>
+        <v>101800</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H144" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K144" s="59"/>
+    </row>
+    <row r="145" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A145" s="8">
+        <v>10180041</v>
+      </c>
+      <c r="B145" s="8">
+        <v>101801</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D145" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I144" s="8" t="s">
+      <c r="E145" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="H145" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="K144" s="59"/>
+      <c r="I145" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="K145" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6566,24 +6596,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" t="s">
         <v>280</v>
       </c>
-      <c r="D2" t="s">
-        <v>279</v>
-      </c>
       <c r="E2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6591,16 +6621,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6608,16 +6638,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6625,16 +6655,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6642,7 +6672,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6650,7 +6680,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6658,7 +6688,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6666,7 +6696,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6674,7 +6704,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6682,7 +6712,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6690,7 +6720,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6698,7 +6728,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6706,7 +6736,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6714,7 +6744,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6722,7 +6752,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6730,7 +6760,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6738,7 +6768,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6746,7 +6776,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6754,7 +6784,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6762,7 +6792,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6770,7 +6800,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6778,7 +6808,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6786,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6794,7 +6824,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6802,7 +6832,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6810,7 +6840,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6818,7 +6848,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6826,7 +6856,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6834,7 +6864,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6842,7 +6872,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6850,7 +6880,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6858,7 +6888,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6866,7 +6896,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6874,7 +6904,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6882,7 +6912,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6890,7 +6920,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6898,7 +6928,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6906,7 +6936,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6914,7 +6944,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6922,7 +6952,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6930,7 +6960,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6938,7 +6968,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6946,7 +6976,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6954,7 +6984,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6962,7 +6992,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6970,7 +7000,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6978,7 +7008,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="342">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -992,6 +992,30 @@
   </si>
   <si>
     <t>0_70|1_30</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15</t>
+  </si>
+  <si>
+    <t>12_10|13_5|14_2|15_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10次&amp;15次&amp;20次免费</t>
+  </si>
+  <si>
+    <t>3_70|4_25|5_5</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号</t>
+  </si>
+  <si>
+    <t>免费游戏中概率出现</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2354,7 +2378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -6531,6 +6555,9 @@
       <c r="C144" s="8" t="s">
         <v>257</v>
       </c>
+      <c r="D144" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="E144" s="8" t="s">
         <v>140</v>
       </c>
@@ -6553,7 +6580,7 @@
         <v>10180041</v>
       </c>
       <c r="B145" s="8">
-        <v>101801</v>
+        <v>101800</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>274</v>
@@ -6577,6 +6604,187 @@
         <v>277</v>
       </c>
       <c r="K145" s="59"/>
+    </row>
+    <row r="146" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="8">
+        <v>10250001</v>
+      </c>
+      <c r="B146" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="K146" s="59"/>
+    </row>
+    <row r="147" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A147" s="8">
+        <v>10250002</v>
+      </c>
+      <c r="B147" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K147" s="59"/>
+    </row>
+    <row r="148" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A148" s="8">
+        <v>10250011</v>
+      </c>
+      <c r="B148" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H148" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K148" s="59"/>
+    </row>
+    <row r="149" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A149" s="8">
+        <v>10250021</v>
+      </c>
+      <c r="B149" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="H149" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="K149" s="59"/>
+    </row>
+    <row r="150" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A150" s="8">
+        <v>10250031</v>
+      </c>
+      <c r="B150" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K150" s="59"/>
+    </row>
+    <row r="151" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A151" s="8">
+        <v>10250032</v>
+      </c>
+      <c r="B151" s="8">
+        <v>102500</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I151" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="K151" s="59"/>
+    </row>
+    <row r="152" s="8" customFormat="1" ht="16.5" spans="1:11">
+      <c r="K152" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6596,24 +6804,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6621,16 +6829,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6638,16 +6846,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6655,16 +6863,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F5" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6672,7 +6880,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6680,7 +6888,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6688,7 +6896,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6696,7 +6904,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6704,7 +6912,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6712,7 +6920,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6720,7 +6928,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6728,7 +6936,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6736,7 +6944,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6744,7 +6952,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6752,7 +6960,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6760,7 +6968,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6768,7 +6976,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6776,7 +6984,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6784,7 +6992,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6792,7 +7000,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6800,7 +7008,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6808,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6816,7 +7024,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6824,7 +7032,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6832,7 +7040,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6840,7 +7048,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6848,7 +7056,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6856,7 +7064,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6864,7 +7072,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6872,7 +7080,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6880,7 +7088,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6888,7 +7096,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6896,7 +7104,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6904,7 +7112,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6912,7 +7120,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6920,7 +7128,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6928,7 +7136,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6936,7 +7144,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6944,7 +7152,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6952,7 +7160,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6960,7 +7168,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6968,7 +7176,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6976,7 +7184,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6984,7 +7192,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6992,7 +7200,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7000,7 +7208,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7008,7 +7216,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="343">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>概率出现3个SCATTER</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_19|3_1</t>
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
@@ -5851,7 +5854,7 @@
         <v>10170039</v>
       </c>
       <c r="B119" s="8">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>21</v>
@@ -5881,7 +5884,7 @@
         <v>10170040</v>
       </c>
       <c r="B120" s="8">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>21</v>
@@ -6391,7 +6394,7 @@
         <v>160</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K138" s="59"/>
     </row>
@@ -6445,10 +6448,10 @@
         <v>133</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I140" s="8" t="s">
         <v>106</v>
@@ -6475,10 +6478,10 @@
         <v>133</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>247</v>
@@ -6499,16 +6502,16 @@
         <v>228</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I142" s="8" t="s">
         <v>39</v>
@@ -6538,10 +6541,10 @@
         <v>71</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K143" s="59"/>
     </row>
@@ -6565,10 +6568,10 @@
         <v>133</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I144" s="8" t="s">
         <v>107</v>
@@ -6583,10 +6586,10 @@
         <v>101800</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E145" s="8" t="s">
         <v>143</v>
@@ -6595,13 +6598,13 @@
         <v>133</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K145" s="59"/>
     </row>
@@ -6628,7 +6631,7 @@
         <v>232</v>
       </c>
       <c r="H146" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I146" s="8" t="s">
         <v>247</v>
@@ -6658,7 +6661,7 @@
         <v>232</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I147" s="8" t="s">
         <v>106</v>
@@ -6679,7 +6682,7 @@
         <v>228</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>133</v>
@@ -6688,7 +6691,7 @@
         <v>253</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I148" s="8" t="s">
         <v>39</v>
@@ -6715,13 +6718,13 @@
         <v>133</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K149" s="59"/>
     </row>
@@ -6736,22 +6739,22 @@
         <v>21</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E150" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>232</v>
       </c>
       <c r="H150" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K150" s="59"/>
     </row>
@@ -6763,23 +6766,23 @@
         <v>102500</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>232</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K151" s="59"/>
     </row>
@@ -6804,24 +6807,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" t="s">
         <v>289</v>
       </c>
-      <c r="D2" t="s">
-        <v>288</v>
-      </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6829,16 +6832,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6846,16 +6849,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6863,16 +6866,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6880,7 +6883,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6888,7 +6891,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6896,7 +6899,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6904,7 +6907,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6912,7 +6915,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6920,7 +6923,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6928,7 +6931,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6936,7 +6939,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6944,7 +6947,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6952,7 +6955,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6960,7 +6963,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6968,7 +6971,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6976,7 +6979,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6984,7 +6987,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6992,7 +6995,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7000,7 +7003,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7008,7 +7011,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7016,7 +7019,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7024,7 +7027,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7032,7 +7035,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7040,7 +7043,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7048,7 +7051,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7056,7 +7059,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7064,7 +7067,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7072,7 +7075,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7080,7 +7083,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7088,7 +7091,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7096,7 +7099,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7104,7 +7107,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7112,7 +7115,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7120,7 +7123,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7128,7 +7131,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7136,7 +7139,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7144,7 +7147,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7152,7 +7155,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7160,7 +7163,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7168,7 +7171,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7176,7 +7179,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7184,7 +7187,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7192,7 +7195,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7200,7 +7203,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7208,7 +7211,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7216,7 +7219,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="345">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1019,6 +1019,12 @@
   </si>
   <si>
     <t>免费游戏中概率出现</t>
+  </si>
+  <si>
+    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1385,7 +1391,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1430,6 +1436,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1437,12 +1461,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1781,7 +1799,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1805,16 +1823,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1823,92 +1841,92 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1918,25 +1936,30 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1973,14 +1996,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1994,12 +2017,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2013,27 +2036,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2049,6 +2072,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
@@ -2381,7 +2419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2394,7 +2432,7 @@
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="9" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="14" customWidth="1"/>
     <col min="12" max="12" width="9.375"/>
     <col min="13" max="13" width="12.5"/>
     <col min="14" max="14" width="9.375"/>
@@ -2402,121 +2440,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="13"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="15">
         <v>100100</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="21" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2525,16 +2563,16 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2542,16 +2580,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="15">
         <v>100100</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="21" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2560,29 +2598,29 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="19"/>
+      <c r="K6" s="24"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="15">
         <v>100100</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="26" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -2591,27 +2629,27 @@
       <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="60" t="s">
+      <c r="H7" s="26"/>
+      <c r="I7" s="70" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="22"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="15">
         <v>100100</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="26" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2620,27 +2658,27 @@
       <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="21"/>
+      <c r="H8" s="26"/>
       <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="23"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="28"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="15">
         <v>100100</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="26" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2649,27 +2687,27 @@
       <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="26"/>
       <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="23"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="28"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="15">
         <v>100100</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="26" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2678,27 +2716,27 @@
       <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="26"/>
       <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="23"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="28"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="15">
         <v>100100</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="26" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2707,27 +2745,27 @@
       <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="21"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="23"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="28"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="15">
         <v>100100</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2736,16 +2774,16 @@
       <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="26" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="28" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2753,16 +2791,16 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="15">
         <v>100100</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="31" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -2771,14 +2809,14 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="31"/>
       <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="32" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2786,16 +2824,16 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="15">
         <v>100100</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="29" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="31" t="s">
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -2804,147 +2842,147 @@
       <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="31"/>
+      <c r="I14" s="71" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="27"/>
+      <c r="K14" s="32"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="15">
         <v>100100</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="29" t="s">
+      <c r="H15" s="35"/>
+      <c r="I15" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="31"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="15">
         <v>100100</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="62" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="35"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="15">
         <v>100100</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="40" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A18" s="37">
+      <c r="A18" s="42">
         <v>10010061</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="16">
         <v>100100</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="37" t="s">
+      <c r="H18" s="16"/>
+      <c r="I18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="37"/>
-      <c r="K18" s="40"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="45"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="46">
         <v>100100</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="46" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2953,27 +2991,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="41"/>
-      <c r="I19" s="63" t="s">
+      <c r="H19" s="46"/>
+      <c r="I19" s="73" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="43"/>
+      <c r="K19" s="48"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="41">
+      <c r="B20" s="46">
         <v>100100</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="46" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2982,27 +3020,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="41"/>
+      <c r="H20" s="46"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="41"/>
-      <c r="K20" s="44"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="49"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="46">
         <v>100100</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="46" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -3011,27 +3049,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="41"/>
+      <c r="H21" s="46"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="44"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="46">
         <v>100100</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="46" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -3040,27 +3078,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="41"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="41"/>
-      <c r="K22" s="44"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="49"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="46">
         <v>100100</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="46" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -3069,27 +3107,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="41"/>
+      <c r="H23" s="46"/>
       <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="41"/>
-      <c r="K23" s="44"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="49"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="46">
         <v>100100</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="46" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -3098,62 +3136,62 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="46" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A25" s="45">
+      <c r="A25" s="50">
         <v>10010091</v>
       </c>
-      <c r="B25" s="46">
+      <c r="B25" s="51">
         <v>100100</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="45" t="s">
+      <c r="C25" s="51"/>
+      <c r="D25" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="45" t="s">
+      <c r="G25" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="45" t="s">
+      <c r="I25" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="46"/>
-      <c r="K25" s="47"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="52"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="15">
         <v>100300</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="21" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="21" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3162,29 +3200,29 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="21" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="17"/>
-      <c r="K26" s="18"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="23"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="15">
         <v>100300</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="21" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="21" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3193,29 +3231,29 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="21" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="17"/>
-      <c r="K27" s="18"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="23"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="15">
         <v>100300</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="21" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="21" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3224,28 +3262,28 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="16"/>
-      <c r="I28" s="64" t="s">
+      <c r="H28" s="21"/>
+      <c r="I28" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
-      <c r="K28" s="44"/>
+      <c r="K28" s="49"/>
       <c r="L28"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A29" s="1">
         <v>10030041</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="15">
         <v>100300</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="21" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3254,28 +3292,28 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="64" t="s">
+      <c r="H29" s="21"/>
+      <c r="I29" s="74" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="44"/>
+      <c r="K29" s="49"/>
       <c r="L29"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A30" s="1">
         <v>10030042</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="15">
         <v>100300</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="21" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3284,28 +3322,28 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="64" t="s">
+      <c r="H30" s="21"/>
+      <c r="I30" s="74" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="44"/>
+      <c r="K30" s="49"/>
       <c r="L30"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A31" s="1">
         <v>10030043</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="15">
         <v>100300</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="21" t="s">
         <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3314,28 +3352,28 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="64" t="s">
+      <c r="H31" s="21"/>
+      <c r="I31" s="74" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="44"/>
+      <c r="K31" s="49"/>
       <c r="L31"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <v>10030044</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="15">
         <v>100300</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="21" t="s">
         <v>108</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -3344,28 +3382,28 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="64" t="s">
+      <c r="H32" s="21"/>
+      <c r="I32" s="74" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
-      <c r="K32" s="44"/>
+      <c r="K32" s="49"/>
       <c r="L32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="15">
         <v>100300</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="21" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="21" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -3374,30 +3412,30 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="64" t="s">
+      <c r="H33" s="21"/>
+      <c r="I33" s="74" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>10030050</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="15">
         <v>100300</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="21" t="s">
         <v>112</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -3406,217 +3444,217 @@
       <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="64" t="s">
+      <c r="H34" s="21"/>
+      <c r="I34" s="74" t="s">
         <v>108</v>
       </c>
       <c r="J34" s="4"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A35" s="49">
+      <c r="A35" s="54">
         <v>10070010</v>
       </c>
-      <c r="B35" s="50">
+      <c r="B35" s="55">
         <v>100700</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="49" t="s">
+      <c r="C35" s="55"/>
+      <c r="D35" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="50"/>
-      <c r="I35" s="49" t="s">
+      <c r="H35" s="55"/>
+      <c r="I35" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="51"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A36" s="49">
+      <c r="A36" s="54">
         <v>10070011</v>
       </c>
-      <c r="B36" s="50">
+      <c r="B36" s="55">
         <v>100700</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="49" t="s">
+      <c r="C36" s="55"/>
+      <c r="D36" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="F36" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="49" t="s">
+      <c r="G36" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="50"/>
-      <c r="I36" s="49" t="s">
+      <c r="H36" s="55"/>
+      <c r="I36" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="51"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="56"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A37" s="49">
+      <c r="A37" s="54">
         <v>10070012</v>
       </c>
-      <c r="B37" s="50">
+      <c r="B37" s="55">
         <v>100700</v>
       </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="49" t="s">
+      <c r="C37" s="55"/>
+      <c r="D37" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="50"/>
-      <c r="I37" s="49" t="s">
+      <c r="H37" s="55"/>
+      <c r="I37" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="51"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="56"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A38" s="52">
+      <c r="A38" s="57">
         <v>10070021</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="58">
         <v>100700</v>
       </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="52" t="s">
+      <c r="C38" s="58"/>
+      <c r="D38" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="E38" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="53"/>
-      <c r="I38" s="52" t="s">
+      <c r="H38" s="58"/>
+      <c r="I38" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="52"/>
-      <c r="K38" s="54"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="59"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A39" s="52">
+      <c r="A39" s="57">
         <v>10070022</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="58">
         <v>100700</v>
       </c>
-      <c r="C39" s="53"/>
-      <c r="D39" s="52" t="s">
+      <c r="C39" s="58"/>
+      <c r="D39" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="53" t="s">
+      <c r="E39" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="52" t="s">
+      <c r="H39" s="58"/>
+      <c r="I39" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="52"/>
-      <c r="K39" s="54"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="59"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A40" s="52">
+      <c r="A40" s="57">
         <v>10070023</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="58">
         <v>100700</v>
       </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="52" t="s">
+      <c r="C40" s="58"/>
+      <c r="D40" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="53"/>
-      <c r="I40" s="52" t="s">
+      <c r="H40" s="58"/>
+      <c r="I40" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="52"/>
-      <c r="K40" s="54"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="59"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A41" s="52">
+      <c r="A41" s="57">
         <v>10070024</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="58">
         <v>100700</v>
       </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="52" t="s">
+      <c r="C41" s="58"/>
+      <c r="D41" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="52" t="s">
+      <c r="G41" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="53"/>
-      <c r="I41" s="52" t="s">
+      <c r="H41" s="58"/>
+      <c r="I41" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="52"/>
-      <c r="K41" s="54"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="59"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="3">
         <v>10070030</v>
       </c>
-      <c r="B42" s="55">
+      <c r="B42" s="60">
         <v>100700</v>
       </c>
-      <c r="C42" s="55"/>
+      <c r="C42" s="60"/>
       <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="55" t="s">
+      <c r="E42" s="60" t="s">
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -3625,25 +3663,25 @@
       <c r="G42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="55"/>
-      <c r="I42" s="65" t="s">
+      <c r="H42" s="60"/>
+      <c r="I42" s="75" t="s">
         <v>134</v>
       </c>
       <c r="J42" s="3"/>
-      <c r="K42" s="56"/>
+      <c r="K42" s="61"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="3">
         <v>10070031</v>
       </c>
-      <c r="B43" s="55">
+      <c r="B43" s="60">
         <v>100700</v>
       </c>
-      <c r="C43" s="55"/>
+      <c r="C43" s="60"/>
       <c r="D43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E43" s="55" t="s">
+      <c r="E43" s="60" t="s">
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -3652,27 +3690,27 @@
       <c r="G43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="55" t="s">
+      <c r="H43" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="65" t="s">
+      <c r="I43" s="75" t="s">
         <v>138</v>
       </c>
       <c r="J43" s="3"/>
-      <c r="K43" s="56"/>
+      <c r="K43" s="61"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="3">
         <v>10070032</v>
       </c>
-      <c r="B44" s="55">
+      <c r="B44" s="60">
         <v>100700</v>
       </c>
-      <c r="C44" s="55"/>
+      <c r="C44" s="60"/>
       <c r="D44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="55" t="s">
+      <c r="E44" s="60" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -3681,26 +3719,26 @@
       <c r="G44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="55" t="s">
+      <c r="H44" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="65" t="s">
+      <c r="I44" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K44" s="56"/>
+      <c r="K44" s="61"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="3">
         <v>10070033</v>
       </c>
-      <c r="B45" s="55">
+      <c r="B45" s="60">
         <v>100700</v>
       </c>
-      <c r="C45" s="55"/>
+      <c r="C45" s="60"/>
       <c r="D45" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="55" t="s">
+      <c r="E45" s="60" t="s">
         <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -3709,26 +3747,26 @@
       <c r="G45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H45" s="55" t="s">
+      <c r="H45" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="65" t="s">
+      <c r="I45" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K45" s="56"/>
+      <c r="K45" s="61"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="3">
         <v>10070034</v>
       </c>
-      <c r="B46" s="55">
+      <c r="B46" s="60">
         <v>100700</v>
       </c>
-      <c r="C46" s="55"/>
+      <c r="C46" s="60"/>
       <c r="D46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="55" t="s">
+      <c r="E46" s="60" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -3737,26 +3775,26 @@
       <c r="G46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="55" t="s">
+      <c r="H46" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="I46" s="65" t="s">
+      <c r="I46" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K46" s="56"/>
+      <c r="K46" s="61"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="3">
         <v>10070035</v>
       </c>
-      <c r="B47" s="55">
+      <c r="B47" s="60">
         <v>100700</v>
       </c>
-      <c r="C47" s="55"/>
+      <c r="C47" s="60"/>
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="55" t="s">
+      <c r="E47" s="60" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -3765,26 +3803,26 @@
       <c r="G47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="55" t="s">
+      <c r="H47" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="65" t="s">
+      <c r="I47" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K47" s="56"/>
+      <c r="K47" s="61"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="3">
         <v>10070036</v>
       </c>
-      <c r="B48" s="55">
+      <c r="B48" s="60">
         <v>100700</v>
       </c>
-      <c r="C48" s="55"/>
+      <c r="C48" s="60"/>
       <c r="D48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="55" t="s">
+      <c r="E48" s="60" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -3793,26 +3831,26 @@
       <c r="G48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="55" t="s">
+      <c r="H48" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="65" t="s">
+      <c r="I48" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K48" s="56"/>
+      <c r="K48" s="61"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A49" s="3">
         <v>10070037</v>
       </c>
-      <c r="B49" s="55">
+      <c r="B49" s="60">
         <v>100700</v>
       </c>
-      <c r="C49" s="55"/>
+      <c r="C49" s="60"/>
       <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="55" t="s">
+      <c r="E49" s="60" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -3821,26 +3859,26 @@
       <c r="G49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="55" t="s">
+      <c r="H49" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="I49" s="65" t="s">
+      <c r="I49" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K49" s="56"/>
+      <c r="K49" s="61"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A50" s="3">
         <v>10070038</v>
       </c>
-      <c r="B50" s="55">
+      <c r="B50" s="60">
         <v>100700</v>
       </c>
-      <c r="C50" s="55"/>
+      <c r="C50" s="60"/>
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="55" t="s">
+      <c r="E50" s="60" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -3849,25 +3887,25 @@
       <c r="G50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="55" t="s">
+      <c r="H50" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="65" t="s">
+      <c r="I50" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K50" s="56"/>
+      <c r="K50" s="61"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
         <v>10120011</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="21">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="21" t="s">
         <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -3876,26 +3914,26 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="21" t="s">
         <v>160</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J51" s="4"/>
-      <c r="K51" s="19"/>
+      <c r="K51" s="24"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
         <v>10120021</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="21">
         <v>101200</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="21" t="s">
         <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -3904,27 +3942,27 @@
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="64" t="s">
+      <c r="H52" s="21"/>
+      <c r="I52" s="74" t="s">
         <v>109</v>
       </c>
       <c r="J52" s="4"/>
-      <c r="K52" s="19"/>
+      <c r="K52" s="24"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
         <v>10120031</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="21">
         <v>101200</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="62" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="21" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -3933,29 +3971,29 @@
       <c r="G53" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I53" s="64" t="s">
+      <c r="I53" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
-      <c r="K53" s="19"/>
+      <c r="K53" s="24"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
         <v>10120032</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="21">
         <v>101200</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="62" t="s">
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="21" t="s">
         <v>140</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -3964,29 +4002,29 @@
       <c r="G54" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="16" t="s">
+      <c r="H54" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="64" t="s">
+      <c r="I54" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="19"/>
+      <c r="K54" s="24"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
         <v>10120033</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="21">
         <v>101200</v>
       </c>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="62" t="s">
         <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="16" t="s">
+      <c r="E55" s="21" t="s">
         <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -3995,29 +4033,29 @@
       <c r="G55" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J55" s="4"/>
-      <c r="K55" s="19"/>
+      <c r="K55" s="24"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
         <v>10120034</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="21">
         <v>101200</v>
       </c>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="62" t="s">
         <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="21" t="s">
         <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -4026,29 +4064,29 @@
       <c r="G56" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I56" s="64" t="s">
+      <c r="I56" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="19"/>
+      <c r="K56" s="24"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
         <v>10120035</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="21">
         <v>101200</v>
       </c>
-      <c r="C57" s="57" t="s">
+      <c r="C57" s="62" t="s">
         <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="16" t="s">
+      <c r="E57" s="21" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -4057,29 +4095,29 @@
       <c r="G57" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="64" t="s">
+      <c r="I57" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J57" s="4"/>
-      <c r="K57" s="19"/>
+      <c r="K57" s="24"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="4">
         <v>10120036</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="21">
         <v>101200</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="62" t="s">
         <v>172</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E58" s="16" t="s">
+      <c r="E58" s="21" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -4088,29 +4126,29 @@
       <c r="G58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="64" t="s">
+      <c r="I58" s="74" t="s">
         <v>39</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="19"/>
+      <c r="K58" s="24"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
         <v>10120041</v>
       </c>
-      <c r="B59" s="57">
+      <c r="B59" s="62">
         <v>101200</v>
       </c>
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="62" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="57" t="s">
+      <c r="E59" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -4119,29 +4157,29 @@
       <c r="G59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="57">
+      <c r="H59" s="62">
         <v>10</v>
       </c>
-      <c r="I59" s="66" t="s">
+      <c r="I59" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="58"/>
+      <c r="K59" s="63"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
         <v>10120042</v>
       </c>
-      <c r="B60" s="57">
+      <c r="B60" s="62">
         <v>101200</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="62" t="s">
         <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -4150,29 +4188,29 @@
       <c r="G60" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H60" s="57">
+      <c r="H60" s="62">
         <v>10</v>
       </c>
-      <c r="I60" s="66" t="s">
+      <c r="I60" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="58"/>
+      <c r="K60" s="63"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
         <v>10120043</v>
       </c>
-      <c r="B61" s="57">
+      <c r="B61" s="62">
         <v>101200</v>
       </c>
-      <c r="C61" s="57" t="s">
+      <c r="C61" s="62" t="s">
         <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
@@ -4181,29 +4219,29 @@
       <c r="G61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H61" s="57">
+      <c r="H61" s="62">
         <v>10</v>
       </c>
-      <c r="I61" s="66" t="s">
+      <c r="I61" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="58"/>
+      <c r="K61" s="63"/>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
         <v>10120044</v>
       </c>
-      <c r="B62" s="57">
+      <c r="B62" s="62">
         <v>101200</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="62" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -4212,29 +4250,29 @@
       <c r="G62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H62" s="57">
+      <c r="H62" s="62">
         <v>10</v>
       </c>
-      <c r="I62" s="66" t="s">
+      <c r="I62" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="58"/>
+      <c r="K62" s="63"/>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
         <v>10120045</v>
       </c>
-      <c r="B63" s="57">
+      <c r="B63" s="62">
         <v>101200</v>
       </c>
-      <c r="C63" s="57" t="s">
+      <c r="C63" s="62" t="s">
         <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="57" t="s">
+      <c r="E63" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -4243,29 +4281,29 @@
       <c r="G63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="57">
+      <c r="H63" s="62">
         <v>10</v>
       </c>
-      <c r="I63" s="66" t="s">
+      <c r="I63" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="58"/>
+      <c r="K63" s="63"/>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
         <v>10120046</v>
       </c>
-      <c r="B64" s="57">
+      <c r="B64" s="62">
         <v>101200</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="62" t="s">
         <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="57" t="s">
+      <c r="E64" s="62" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -4274,29 +4312,29 @@
       <c r="G64" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H64" s="57">
+      <c r="H64" s="62">
         <v>10</v>
       </c>
-      <c r="I64" s="66" t="s">
+      <c r="I64" s="76" t="s">
         <v>107</v>
       </c>
       <c r="J64" s="5"/>
-      <c r="K64" s="58"/>
+      <c r="K64" s="63"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
         <v>10120051</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="21">
         <v>101200</v>
       </c>
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="62" t="s">
         <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="21" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4305,29 +4343,29 @@
       <c r="G65" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="64" t="s">
+      <c r="I65" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="19"/>
+      <c r="K65" s="24"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
         <v>10120052</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="21">
         <v>101200</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="62" t="s">
         <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E66" s="21" t="s">
         <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4336,29 +4374,29 @@
       <c r="G66" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I66" s="64" t="s">
+      <c r="I66" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J66" s="4"/>
-      <c r="K66" s="19"/>
+      <c r="K66" s="24"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
         <v>10120053</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="21">
         <v>101200</v>
       </c>
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="62" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="16" t="s">
+      <c r="E67" s="21" t="s">
         <v>193</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4367,29 +4405,29 @@
       <c r="G67" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J67" s="4"/>
-      <c r="K67" s="19"/>
+      <c r="K67" s="24"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
         <v>10120054</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="21">
         <v>101200</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="62" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="16" t="s">
+      <c r="E68" s="21" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4398,29 +4436,29 @@
       <c r="G68" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="64" t="s">
+      <c r="I68" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="19"/>
+      <c r="K68" s="24"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
         <v>10120055</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="21">
         <v>101200</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="62" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="E69" s="21" t="s">
         <v>196</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -4429,29 +4467,29 @@
       <c r="G69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="64" t="s">
+      <c r="I69" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="19"/>
+      <c r="K69" s="24"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="4">
         <v>10120056</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="21">
         <v>101200</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="62" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="E70" s="21" t="s">
         <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -4460,29 +4498,29 @@
       <c r="G70" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="64" t="s">
+      <c r="I70" s="74" t="s">
         <v>192</v>
       </c>
       <c r="J70" s="4"/>
-      <c r="K70" s="19"/>
+      <c r="K70" s="24"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
         <v>10120061</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="21">
         <v>101200</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="31" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="E71" s="31" t="s">
         <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -4491,29 +4529,29 @@
       <c r="G71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="61" t="s">
+      <c r="I71" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="27"/>
+      <c r="K71" s="32"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
         <v>10120062</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="21">
         <v>101200</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="31" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="E72" s="31" t="s">
         <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -4522,29 +4560,29 @@
       <c r="G72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I72" s="61" t="s">
+      <c r="I72" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J72" s="6"/>
-      <c r="K72" s="27"/>
+      <c r="K72" s="32"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
         <v>10120063</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="21">
         <v>101200</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="31" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="E73" s="31" t="s">
         <v>203</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -4553,29 +4591,29 @@
       <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I73" s="61" t="s">
+      <c r="I73" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="27"/>
+      <c r="K73" s="32"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <v>10120064</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="21">
         <v>101200</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="31" t="s">
         <v>204</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="E74" s="31" t="s">
         <v>205</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -4584,29 +4622,29 @@
       <c r="G74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I74" s="61" t="s">
+      <c r="I74" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="27"/>
+      <c r="K74" s="32"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <v>10120065</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="21">
         <v>101200</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="31" t="s">
         <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="26" t="s">
+      <c r="E75" s="31" t="s">
         <v>206</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -4615,29 +4653,29 @@
       <c r="G75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="26" t="s">
+      <c r="H75" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I75" s="61" t="s">
+      <c r="I75" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="27"/>
+      <c r="K75" s="32"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <v>10120066</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="21">
         <v>101200</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="31" t="s">
         <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E76" s="31" t="s">
         <v>207</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -4646,29 +4684,29 @@
       <c r="G76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H76" s="26" t="s">
+      <c r="H76" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="61" t="s">
+      <c r="I76" s="71" t="s">
         <v>201</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="27"/>
+      <c r="K76" s="32"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
         <v>10140001</v>
       </c>
-      <c r="B77" s="55">
+      <c r="B77" s="60">
         <v>101400</v>
       </c>
-      <c r="C77" s="55" t="s">
+      <c r="C77" s="60" t="s">
         <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="55" t="s">
+      <c r="E77" s="60" t="s">
         <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -4677,28 +4715,28 @@
       <c r="G77" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="21" t="s">
+      <c r="H77" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="I77" s="65" t="s">
+      <c r="I77" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="K77" s="56"/>
+      <c r="K77" s="61"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="3">
         <v>10140011</v>
       </c>
-      <c r="B78" s="55">
+      <c r="B78" s="60">
         <v>101400</v>
       </c>
-      <c r="C78" s="55" t="s">
+      <c r="C78" s="60" t="s">
         <v>208</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="55" t="s">
+      <c r="E78" s="60" t="s">
         <v>140</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -4707,28 +4745,28 @@
       <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="21" t="s">
+      <c r="H78" s="26" t="s">
         <v>211</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K78" s="56"/>
+      <c r="K78" s="61"/>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="7">
         <v>10140021</v>
       </c>
-      <c r="B79" s="21">
+      <c r="B79" s="26">
         <v>101400</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="C79" s="26" t="s">
         <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="21" t="s">
+      <c r="E79" s="26" t="s">
         <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -4737,28 +4775,28 @@
       <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="21" t="s">
+      <c r="H79" s="26" t="s">
         <v>143</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K79" s="22"/>
+      <c r="K79" s="27"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
         <v>10140022</v>
       </c>
-      <c r="B80" s="21">
+      <c r="B80" s="26">
         <v>101400</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="26" t="s">
         <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="21" t="s">
+      <c r="E80" s="26" t="s">
         <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -4767,28 +4805,28 @@
       <c r="G80" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="21" t="s">
+      <c r="H80" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="I80" s="65" t="s">
+      <c r="I80" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="K80" s="22"/>
+      <c r="K80" s="27"/>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="7">
         <v>10140023</v>
       </c>
-      <c r="B81" s="21">
+      <c r="B81" s="26">
         <v>101400</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="26" t="s">
         <v>217</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="21" t="s">
+      <c r="E81" s="26" t="s">
         <v>143</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -4797,28 +4835,28 @@
       <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="21" t="s">
+      <c r="H81" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="I81" s="65" t="s">
+      <c r="I81" s="75" t="s">
         <v>117</v>
       </c>
-      <c r="K81" s="22"/>
+      <c r="K81" s="27"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="1">
         <v>10240011</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="15">
         <v>102400</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="16" t="s">
+      <c r="E82" s="21" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -4827,16 +4865,16 @@
       <c r="G82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="16" t="s">
+      <c r="H82" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J82" s="17" t="s">
+      <c r="J82" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K82" s="18" t="s">
+      <c r="K82" s="23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4844,16 +4882,16 @@
       <c r="A83" s="1">
         <v>10240012</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="15">
         <v>102400</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="16" t="s">
+      <c r="E83" s="21" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -4862,29 +4900,29 @@
       <c r="G83" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J83" s="4"/>
-      <c r="K83" s="19"/>
+      <c r="K83" s="24"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="1">
         <v>10240021</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="15">
         <v>102400</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="21" t="s">
+      <c r="E84" s="26" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -4893,27 +4931,27 @@
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="21"/>
-      <c r="I84" s="60" t="s">
+      <c r="H84" s="26"/>
+      <c r="I84" s="70" t="s">
         <v>39</v>
       </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="22"/>
+      <c r="K84" s="27"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="1">
         <v>10240022</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="15">
         <v>102400</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E85" s="21" t="s">
+      <c r="E85" s="26" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -4922,27 +4960,27 @@
       <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="21"/>
+      <c r="H85" s="26"/>
       <c r="I85" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J85" s="21"/>
-      <c r="K85" s="23"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="28"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="1">
         <v>10240023</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="15">
         <v>102400</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="21" t="s">
+      <c r="E86" s="26" t="s">
         <v>46</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -4951,27 +4989,27 @@
       <c r="G86" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="21"/>
+      <c r="H86" s="26"/>
       <c r="I86" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J86" s="21"/>
-      <c r="K86" s="23"/>
+      <c r="J86" s="26"/>
+      <c r="K86" s="28"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="1">
         <v>10240024</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="15">
         <v>102400</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="21" t="s">
+      <c r="E87" s="26" t="s">
         <v>51</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -4980,27 +5018,27 @@
       <c r="G87" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="21"/>
+      <c r="H87" s="26"/>
       <c r="I87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J87" s="21"/>
-      <c r="K87" s="23"/>
+      <c r="J87" s="26"/>
+      <c r="K87" s="28"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="1">
         <v>10240025</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="15">
         <v>102400</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="21" t="s">
+      <c r="E88" s="26" t="s">
         <v>56</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -5009,27 +5047,27 @@
       <c r="G88" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H88" s="21"/>
+      <c r="H88" s="26"/>
       <c r="I88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="21"/>
-      <c r="K88" s="23"/>
+      <c r="J88" s="26"/>
+      <c r="K88" s="28"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="1">
         <v>10240026</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="15">
         <v>102400</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="21" t="s">
+      <c r="E89" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -5038,16 +5076,16 @@
       <c r="G89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H89" s="21" t="s">
+      <c r="H89" s="26" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="17" t="s">
+      <c r="J89" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K89" s="23" t="s">
+      <c r="K89" s="28" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5055,16 +5093,16 @@
       <c r="A90" s="1">
         <v>10240031</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="15">
         <v>102400</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D90" s="25" t="s">
+      <c r="D90" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="26" t="s">
+      <c r="E90" s="31" t="s">
         <v>61</v>
       </c>
       <c r="F90" s="6" t="s">
@@ -5073,14 +5111,14 @@
       <c r="G90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="26"/>
+      <c r="H90" s="31"/>
       <c r="I90" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J90" s="17" t="s">
+      <c r="J90" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K90" s="27" t="s">
+      <c r="K90" s="32" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5088,16 +5126,16 @@
       <c r="A91" s="1">
         <v>10240032</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="15">
         <v>102400</v>
       </c>
-      <c r="C91" s="24" t="s">
+      <c r="C91" s="29" t="s">
         <v>62</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="26" t="s">
+      <c r="E91" s="31" t="s">
         <v>67</v>
       </c>
       <c r="F91" s="6" t="s">
@@ -5106,147 +5144,147 @@
       <c r="G91" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="26"/>
-      <c r="I91" s="61" t="s">
+      <c r="H91" s="31"/>
+      <c r="I91" s="71" t="s">
         <v>39</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="27"/>
+      <c r="K91" s="32"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="1">
         <v>10240041</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="15">
         <v>102400</v>
       </c>
-      <c r="C92" s="28" t="s">
+      <c r="C92" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="29" t="s">
+      <c r="D92" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="30" t="s">
+      <c r="E92" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="29" t="s">
+      <c r="G92" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H92" s="30"/>
-      <c r="I92" s="29" t="s">
+      <c r="H92" s="35"/>
+      <c r="I92" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="J92" s="29"/>
-      <c r="K92" s="31"/>
+      <c r="J92" s="34"/>
+      <c r="K92" s="36"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="1">
         <v>10240051</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="15">
         <v>102400</v>
       </c>
-      <c r="C93" s="32" t="s">
+      <c r="C93" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="34" t="s">
+      <c r="E93" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="33" t="s">
+      <c r="F93" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="33" t="s">
+      <c r="G93" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="34"/>
-      <c r="I93" s="62" t="s">
+      <c r="H93" s="39"/>
+      <c r="I93" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="33"/>
-      <c r="K93" s="35"/>
+      <c r="J93" s="38"/>
+      <c r="K93" s="40"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="1">
         <v>10240052</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="15">
         <v>102400</v>
       </c>
-      <c r="C94" s="32" t="s">
+      <c r="C94" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="36" t="s">
+      <c r="D94" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="34" t="s">
+      <c r="E94" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="33" t="s">
+      <c r="F94" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="33" t="s">
+      <c r="G94" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="34"/>
-      <c r="I94" s="33" t="s">
+      <c r="H94" s="39"/>
+      <c r="I94" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="J94" s="17" t="s">
+      <c r="J94" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K94" s="35" t="s">
+      <c r="K94" s="40" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A95" s="37">
+      <c r="A95" s="42">
         <v>10240061</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="16">
         <v>102400</v>
       </c>
-      <c r="C95" s="38" t="s">
+      <c r="C95" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="39" t="s">
+      <c r="D95" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F95" s="37" t="s">
+      <c r="F95" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="G95" s="37" t="s">
+      <c r="G95" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="11"/>
-      <c r="I95" s="37" t="s">
+      <c r="H95" s="16"/>
+      <c r="I95" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J95" s="37"/>
-      <c r="K95" s="40"/>
+      <c r="J95" s="42"/>
+      <c r="K95" s="45"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="2">
         <v>10240071</v>
       </c>
-      <c r="B96" s="41">
+      <c r="B96" s="46">
         <v>102400</v>
       </c>
-      <c r="C96" s="42" t="s">
+      <c r="C96" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="41" t="s">
+      <c r="E96" s="46" t="s">
         <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -5255,26 +5293,26 @@
       <c r="G96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H96" s="41"/>
-      <c r="I96" s="63" t="s">
+      <c r="H96" s="46"/>
+      <c r="I96" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="K96" s="43"/>
+      <c r="K96" s="48"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="2">
         <v>10240072</v>
       </c>
-      <c r="B97" s="41">
+      <c r="B97" s="46">
         <v>102400</v>
       </c>
-      <c r="C97" s="42" t="s">
+      <c r="C97" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="41" t="s">
+      <c r="E97" s="46" t="s">
         <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -5283,27 +5321,27 @@
       <c r="G97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="41"/>
+      <c r="H97" s="46"/>
       <c r="I97" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="41"/>
-      <c r="K97" s="44"/>
+      <c r="J97" s="46"/>
+      <c r="K97" s="49"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="2">
         <v>10240073</v>
       </c>
-      <c r="B98" s="41">
+      <c r="B98" s="46">
         <v>102400</v>
       </c>
-      <c r="C98" s="42" t="s">
+      <c r="C98" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E98" s="41" t="s">
+      <c r="E98" s="46" t="s">
         <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -5312,27 +5350,27 @@
       <c r="G98" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="41"/>
+      <c r="H98" s="46"/>
       <c r="I98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J98" s="41"/>
-      <c r="K98" s="44"/>
+      <c r="J98" s="46"/>
+      <c r="K98" s="49"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="2">
         <v>10240074</v>
       </c>
-      <c r="B99" s="41">
+      <c r="B99" s="46">
         <v>102400</v>
       </c>
-      <c r="C99" s="42" t="s">
+      <c r="C99" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="41" t="s">
+      <c r="E99" s="46" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -5341,27 +5379,27 @@
       <c r="G99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H99" s="41"/>
+      <c r="H99" s="46"/>
       <c r="I99" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J99" s="41"/>
-      <c r="K99" s="44"/>
+      <c r="J99" s="46"/>
+      <c r="K99" s="49"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="2">
         <v>10240075</v>
       </c>
-      <c r="B100" s="41">
+      <c r="B100" s="46">
         <v>102400</v>
       </c>
-      <c r="C100" s="42" t="s">
+      <c r="C100" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="41" t="s">
+      <c r="E100" s="46" t="s">
         <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -5370,27 +5408,27 @@
       <c r="G100" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="41"/>
+      <c r="H100" s="46"/>
       <c r="I100" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J100" s="41"/>
-      <c r="K100" s="44"/>
+      <c r="J100" s="46"/>
+      <c r="K100" s="49"/>
     </row>
     <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="2">
         <v>10240076</v>
       </c>
-      <c r="B101" s="41">
+      <c r="B101" s="46">
         <v>102400</v>
       </c>
-      <c r="C101" s="42" t="s">
+      <c r="C101" s="47" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E101" s="41" t="s">
+      <c r="E101" s="46" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -5399,47 +5437,47 @@
       <c r="G101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="41" t="s">
+      <c r="H101" s="46" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J101" s="17" t="s">
+      <c r="J101" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="44" t="s">
+      <c r="K101" s="49" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A102" s="45">
+      <c r="A102" s="50">
         <v>10240091</v>
       </c>
-      <c r="B102" s="46">
+      <c r="B102" s="51">
         <v>102400</v>
       </c>
-      <c r="C102" s="46"/>
-      <c r="D102" s="45" t="s">
+      <c r="C102" s="51"/>
+      <c r="D102" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="E102" s="46" t="s">
+      <c r="E102" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="F102" s="45" t="s">
+      <c r="F102" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="G102" s="45" t="s">
+      <c r="G102" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="H102" s="46" t="s">
+      <c r="H102" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="I102" s="45" t="s">
+      <c r="I102" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="J102" s="46"/>
-      <c r="K102" s="47"/>
+      <c r="J102" s="51"/>
+      <c r="K102" s="52"/>
     </row>
     <row r="103" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A103" s="8">
@@ -5463,7 +5501,7 @@
       <c r="I103" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K103" s="59"/>
+      <c r="K103" s="64"/>
     </row>
     <row r="104" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A104" s="8">
@@ -5487,7 +5525,7 @@
       <c r="I104" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K104" s="59"/>
+      <c r="K104" s="64"/>
     </row>
     <row r="105" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A105" s="8">
@@ -5511,7 +5549,7 @@
       <c r="I105" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K105" s="59"/>
+      <c r="K105" s="64"/>
     </row>
     <row r="106" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A106" s="8">
@@ -5535,7 +5573,7 @@
       <c r="I106" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K106" s="59"/>
+      <c r="K106" s="64"/>
     </row>
     <row r="107" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A107" s="8">
@@ -5559,7 +5597,7 @@
       <c r="I107" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K107" s="59"/>
+      <c r="K107" s="64"/>
     </row>
     <row r="108" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="8">
@@ -5583,7 +5621,7 @@
       <c r="I108" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K108" s="59"/>
+      <c r="K108" s="64"/>
     </row>
     <row r="109" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A109" s="8">
@@ -5607,7 +5645,7 @@
       <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K109" s="59"/>
+      <c r="K109" s="64"/>
     </row>
     <row r="110" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A110" s="8">
@@ -5628,10 +5666,10 @@
       <c r="G110" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I110" s="67" t="s">
+      <c r="I110" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="K110" s="59"/>
+      <c r="K110" s="64"/>
     </row>
     <row r="111" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A111" s="8">
@@ -5658,7 +5696,7 @@
       <c r="I111" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K111" s="59"/>
+      <c r="K111" s="64"/>
     </row>
     <row r="112" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A112" s="8">
@@ -5685,7 +5723,7 @@
       <c r="I112" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K112" s="59"/>
+      <c r="K112" s="64"/>
     </row>
     <row r="113" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A113" s="8">
@@ -5712,7 +5750,7 @@
       <c r="I113" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K113" s="59"/>
+      <c r="K113" s="64"/>
     </row>
     <row r="114" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A114" s="8">
@@ -5739,7 +5777,7 @@
       <c r="I114" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K114" s="59"/>
+      <c r="K114" s="64"/>
     </row>
     <row r="115" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A115" s="8">
@@ -5766,7 +5804,7 @@
       <c r="I115" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K115" s="59"/>
+      <c r="K115" s="64"/>
     </row>
     <row r="116" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A116" s="8">
@@ -5793,7 +5831,7 @@
       <c r="I116" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K116" s="59"/>
+      <c r="K116" s="64"/>
     </row>
     <row r="117" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A117" s="8">
@@ -5820,7 +5858,7 @@
       <c r="I117" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K117" s="59"/>
+      <c r="K117" s="64"/>
     </row>
     <row r="118" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A118" s="8">
@@ -5847,7 +5885,7 @@
       <c r="I118" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K118" s="59"/>
+      <c r="K118" s="64"/>
     </row>
     <row r="119" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A119" s="8">
@@ -5877,7 +5915,7 @@
       <c r="I119" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K119" s="59"/>
+      <c r="K119" s="64"/>
     </row>
     <row r="120" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="8">
@@ -5907,887 +5945,1064 @@
       <c r="I120" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K120" s="59"/>
-    </row>
-    <row r="121" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A121" s="8">
+      <c r="K120" s="64"/>
+    </row>
+    <row r="121" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A121" s="9">
         <v>10220001</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="9">
         <v>102200</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="G121" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I121" s="8" t="s">
+      <c r="I121" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="K121" s="59"/>
-    </row>
-    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A122" s="8">
+      <c r="K121" s="65"/>
+    </row>
+    <row r="122" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A122" s="9">
         <v>10220011</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="9">
         <v>102200</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F122" s="8" t="s">
+      <c r="F122" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="G122" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="H122" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="I122" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K122" s="59"/>
-    </row>
-    <row r="123" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
-      <c r="A123" s="8">
+      <c r="K122" s="65"/>
+    </row>
+    <row r="123" s="9" customFormat="1" ht="17" customHeight="1" spans="1:11">
+      <c r="A123" s="9">
         <v>10220021</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="9">
         <v>102200</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E123" s="8" t="s">
+      <c r="E123" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F123" s="8" t="s">
+      <c r="F123" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G123" s="8" t="s">
+      <c r="G123" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H123" s="8" t="s">
+      <c r="H123" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I123" s="8" t="s">
+      <c r="I123" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K123" s="59"/>
-    </row>
-    <row r="124" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A124" s="8">
+      <c r="K123" s="65"/>
+    </row>
+    <row r="124" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A124" s="9">
         <v>10220099</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="9">
         <v>102200</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="D124" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="8" t="s">
+      <c r="F124" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="G124" s="8" t="s">
+      <c r="G124" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8" t="s">
+      <c r="H124" s="9"/>
+      <c r="I124" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K124" s="59"/>
-    </row>
-    <row r="125" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A125" s="8">
+      <c r="K124" s="65"/>
+    </row>
+    <row r="125" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A125" s="9">
         <v>10220030</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="9">
         <v>102200</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D125" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G125" s="8" t="s">
+      <c r="G125" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H125" s="8" t="s">
+      <c r="H125" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I125" s="8" t="s">
+      <c r="I125" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="K125" s="59"/>
-    </row>
-    <row r="126" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A126" s="8">
+      <c r="K125" s="65"/>
+    </row>
+    <row r="126" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A126" s="9">
         <v>10220031</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="9">
         <v>102200</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D126" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8" t="s">
+      <c r="F126" s="9"/>
+      <c r="G126" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="H126" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="I126" s="8" t="s">
+      <c r="I126" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K126" s="59"/>
-    </row>
-    <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A127" s="8">
+      <c r="K126" s="65"/>
+    </row>
+    <row r="127" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="9">
         <v>10220032</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="9">
         <v>102200</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D127" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E127" s="8" t="s">
+      <c r="E127" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8" t="s">
+      <c r="F127" s="9"/>
+      <c r="G127" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="H127" s="8" t="s">
+      <c r="H127" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I127" s="8" t="s">
+      <c r="I127" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K127" s="59"/>
-    </row>
-    <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A128" s="8">
+      <c r="K127" s="65"/>
+    </row>
+    <row r="128" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="9">
         <v>10220012</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="9">
         <v>102200</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8" t="s">
+      <c r="D128" s="9"/>
+      <c r="E128" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8" t="s">
+      <c r="F128" s="9"/>
+      <c r="G128" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8" t="s">
+      <c r="H128" s="9"/>
+      <c r="I128" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K128" s="59"/>
-    </row>
-    <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A129" s="8">
+      <c r="K128" s="65"/>
+    </row>
+    <row r="129" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="9">
         <v>10220033</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="9">
         <v>102200</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E129" s="8" t="s">
+      <c r="E129" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G129" s="8" t="s">
+      <c r="G129" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H129" s="8" t="s">
+      <c r="H129" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="I129" s="8" t="s">
+      <c r="I129" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K129" s="59"/>
-    </row>
-    <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A130" s="8">
+      <c r="K129" s="65"/>
+    </row>
+    <row r="130" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="9">
         <v>10220019</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="9">
         <v>102200</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G130" s="8" t="s">
+      <c r="G130" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="I130" s="8" t="s">
+      <c r="I130" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K130" s="59"/>
-    </row>
-    <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A131" s="8">
+      <c r="K130" s="65"/>
+    </row>
+    <row r="131" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="9">
         <v>10220020</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="9">
         <v>102200</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E131" s="8" t="s">
+      <c r="E131" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G131" s="8" t="s">
+      <c r="G131" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="I131" s="8" t="s">
+      <c r="I131" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K131" s="59"/>
-    </row>
-    <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A132" s="8">
+      <c r="K131" s="65"/>
+    </row>
+    <row r="132" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="10">
         <v>10210001</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="10">
         <v>102100</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="E132" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G132" s="8" t="s">
+      <c r="G132" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="H132" s="8" t="s">
+      <c r="H132" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I132" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K132" s="59"/>
-    </row>
-    <row r="133" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A133" s="8">
+      <c r="K132" s="66"/>
+    </row>
+    <row r="133" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A133" s="10">
         <v>10210011</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="10">
         <v>102100</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="D133" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E133" s="8" t="s">
+      <c r="E133" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G133" s="8" t="s">
+      <c r="G133" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="H133" s="8" t="s">
+      <c r="H133" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I133" s="8" t="s">
+      <c r="I133" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K133" s="59"/>
-    </row>
-    <row r="134" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A134" s="8">
+      <c r="K133" s="66"/>
+    </row>
+    <row r="134" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A134" s="10">
         <v>10210021</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="10">
         <v>102100</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="D134" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="F134" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G134" s="8" t="s">
+      <c r="G134" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="10">
         <v>12</v>
       </c>
-      <c r="I134" s="8" t="s">
+      <c r="I134" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K134" s="59"/>
-    </row>
-    <row r="135" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A135" s="8">
+      <c r="K134" s="66"/>
+    </row>
+    <row r="135" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A135" s="10">
         <v>10210031</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="10">
         <v>102100</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="E135" s="8" t="s">
+      <c r="E135" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="F135" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G135" s="8" t="s">
+      <c r="G135" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H135" s="8" t="s">
+      <c r="H135" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I135" s="8" t="s">
+      <c r="I135" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K135" s="59"/>
-    </row>
-    <row r="136" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A136" s="8">
+      <c r="K135" s="66"/>
+    </row>
+    <row r="136" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A136" s="10">
         <v>10210041</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="10">
         <v>102100</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="E136" s="8" t="s">
+      <c r="E136" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F136" s="8" t="s">
+      <c r="F136" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G136" s="8" t="s">
+      <c r="G136" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H136" s="8" t="s">
+      <c r="H136" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I136" s="8" t="s">
+      <c r="I136" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K136" s="59"/>
-    </row>
-    <row r="137" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A137" s="8">
+      <c r="K136" s="66"/>
+    </row>
+    <row r="137" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A137" s="10">
         <v>10210042</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="10">
         <v>102100</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="E137" s="8" t="s">
+      <c r="E137" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="F137" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G137" s="8" t="s">
+      <c r="G137" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H137" s="8" t="s">
+      <c r="H137" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I137" s="8" t="s">
+      <c r="I137" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K137" s="59"/>
-    </row>
-    <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A138" s="8">
+      <c r="K137" s="66"/>
+    </row>
+    <row r="138" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A138" s="10">
         <v>10210032</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="10">
         <v>102100</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G138" s="8" t="s">
+      <c r="G138" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H138" s="8" t="s">
+      <c r="H138" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I138" s="8" t="s">
+      <c r="I138" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K138" s="59"/>
-    </row>
-    <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A139" s="8">
+      <c r="K138" s="66"/>
+    </row>
+    <row r="139" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A139" s="10">
         <v>10210051</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="10">
         <v>102100</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D139" s="8" t="s">
+      <c r="D139" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F139" s="8" t="s">
+      <c r="F139" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G139" s="8" t="s">
+      <c r="G139" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H139" s="8" t="s">
+      <c r="H139" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I139" s="8" t="s">
+      <c r="I139" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="K139" s="59"/>
-    </row>
-    <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A140" s="8">
+      <c r="K139" s="66"/>
+    </row>
+    <row r="140" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="11">
         <v>10180001</v>
       </c>
-      <c r="B140" s="8">
+      <c r="B140" s="11">
         <v>101800</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D140" s="8" t="s">
+      <c r="D140" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="F140" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G140" s="8" t="s">
+      <c r="G140" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H140" s="8" t="s">
+      <c r="H140" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I140" s="8" t="s">
+      <c r="I140" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K140" s="59"/>
-    </row>
-    <row r="141" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A141" s="8">
+      <c r="K140" s="67"/>
+    </row>
+    <row r="141" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A141" s="11">
         <v>10180002</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="11">
         <v>101800</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D141" s="8" t="s">
+      <c r="D141" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E141" s="8" t="s">
+      <c r="E141" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F141" s="8" t="s">
+      <c r="F141" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G141" s="8" t="s">
+      <c r="G141" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H141" s="8" t="s">
+      <c r="H141" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I141" s="8" t="s">
+      <c r="I141" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K141" s="59"/>
-    </row>
-    <row r="142" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A142" s="8">
+      <c r="K141" s="67"/>
+    </row>
+    <row r="142" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A142" s="11">
         <v>10180011</v>
       </c>
-      <c r="B142" s="8">
+      <c r="B142" s="11">
         <v>101800</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="F142" s="8" t="s">
+      <c r="F142" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G142" s="8" t="s">
+      <c r="G142" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="H142" s="8" t="s">
+      <c r="H142" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I142" s="8" t="s">
+      <c r="I142" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K142" s="59"/>
-    </row>
-    <row r="143" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A143" s="8">
+      <c r="K142" s="67"/>
+    </row>
+    <row r="143" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A143" s="11">
         <v>10180021</v>
       </c>
-      <c r="B143" s="8">
+      <c r="B143" s="11">
         <v>101800</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D143" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="E143" s="8" t="s">
+      <c r="E143" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F143" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G143" s="8" t="s">
+      <c r="G143" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="H143" s="8" t="s">
+      <c r="H143" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I143" s="8" t="s">
+      <c r="I143" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="K143" s="59"/>
-    </row>
-    <row r="144" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A144" s="8">
+      <c r="K143" s="67"/>
+    </row>
+    <row r="144" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A144" s="11">
         <v>10180031</v>
       </c>
-      <c r="B144" s="8">
+      <c r="B144" s="11">
         <v>101800</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="D144" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="E144" s="8" t="s">
+      <c r="E144" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F144" s="8" t="s">
+      <c r="F144" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G144" s="8" t="s">
+      <c r="G144" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H144" s="8" t="s">
+      <c r="H144" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I144" s="8" t="s">
+      <c r="I144" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K144" s="59"/>
-    </row>
-    <row r="145" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A145" s="8">
+      <c r="K144" s="67"/>
+    </row>
+    <row r="145" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A145" s="11">
         <v>10180041</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="11">
         <v>101800</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D145" s="8" t="s">
+      <c r="D145" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E145" s="8" t="s">
+      <c r="E145" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F145" s="8" t="s">
+      <c r="F145" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G145" s="8" t="s">
+      <c r="G145" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H145" s="8" t="s">
+      <c r="H145" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="I145" s="8" t="s">
+      <c r="I145" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="K145" s="59"/>
-    </row>
-    <row r="146" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A146" s="8">
+      <c r="K145" s="67"/>
+    </row>
+    <row r="146" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="12">
         <v>10250001</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="12">
         <v>102500</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D146" s="8" t="s">
+      <c r="D146" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F146" s="8" t="s">
+      <c r="F146" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G146" s="8" t="s">
+      <c r="G146" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H146" s="8" t="s">
+      <c r="H146" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I146" s="8" t="s">
+      <c r="I146" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K146" s="59"/>
-    </row>
-    <row r="147" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A147" s="8">
+      <c r="K146" s="68"/>
+    </row>
+    <row r="147" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A147" s="12">
         <v>10250002</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="12">
         <v>102500</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D147" s="8" t="s">
+      <c r="D147" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="E147" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F147" s="8" t="s">
+      <c r="F147" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G147" s="8" t="s">
+      <c r="G147" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H147" s="8" t="s">
+      <c r="H147" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I147" s="8" t="s">
+      <c r="I147" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K147" s="59"/>
-    </row>
-    <row r="148" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A148" s="8">
+      <c r="K147" s="68"/>
+    </row>
+    <row r="148" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A148" s="12">
         <v>10250011</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="12">
         <v>102500</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D148" s="8" t="s">
+      <c r="D148" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="E148" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="F148" s="8" t="s">
+      <c r="F148" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G148" s="8" t="s">
+      <c r="G148" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="H148" s="8" t="s">
+      <c r="H148" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I148" s="8" t="s">
+      <c r="I148" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K148" s="59"/>
-    </row>
-    <row r="149" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A149" s="8">
+      <c r="K148" s="68"/>
+    </row>
+    <row r="149" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A149" s="12">
         <v>10250021</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="12">
         <v>102500</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D149" s="8" t="s">
+      <c r="D149" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="E149" s="8" t="s">
+      <c r="E149" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F149" s="8" t="s">
+      <c r="F149" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G149" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="H149" s="8" t="s">
+      <c r="H149" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I149" s="8" t="s">
+      <c r="I149" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K149" s="59"/>
-    </row>
-    <row r="150" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A150" s="8">
+      <c r="K149" s="68"/>
+    </row>
+    <row r="150" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A150" s="12">
         <v>10250031</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="12">
         <v>102500</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="D150" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F150" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="G150" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H150" s="8" t="s">
+      <c r="H150" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I150" s="8" t="s">
+      <c r="I150" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K150" s="59"/>
-    </row>
-    <row r="151" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A151" s="8">
+      <c r="K150" s="68"/>
+    </row>
+    <row r="151" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A151" s="12">
         <v>10250032</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="12">
         <v>102500</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8" t="s">
+      <c r="D151" s="12"/>
+      <c r="E151" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F151" s="8" t="s">
+      <c r="F151" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="G151" s="8" t="s">
+      <c r="G151" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="H151" s="8" t="s">
+      <c r="H151" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="I151" s="8" t="s">
+      <c r="I151" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="K151" s="68"/>
+    </row>
+    <row r="152" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A152" s="13">
+        <v>10230001</v>
+      </c>
+      <c r="B152" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F152" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="K152" s="69"/>
+    </row>
+    <row r="153" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A153" s="13">
+        <v>10230002</v>
+      </c>
+      <c r="B153" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F153" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G153" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H153" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I153" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K153" s="69"/>
+    </row>
+    <row r="154" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A154" s="13">
+        <v>10230003</v>
+      </c>
+      <c r="B154" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F154" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G154" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I154" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="K154" s="69"/>
+    </row>
+    <row r="155" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A155" s="13">
+        <v>10230011</v>
+      </c>
+      <c r="B155" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G155" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H155" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I155" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K155" s="69"/>
+    </row>
+    <row r="156" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A156" s="13">
+        <v>10230021</v>
+      </c>
+      <c r="B156" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C156" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F156" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G156" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I156" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="K151" s="59"/>
-    </row>
-    <row r="152" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="K152" s="59"/>
+      <c r="K156" s="69"/>
+    </row>
+    <row r="157" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A157" s="13">
+        <v>10230031</v>
+      </c>
+      <c r="B157" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E157" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F157" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G157" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H157" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I157" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="K157" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6807,24 +7022,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6832,16 +7047,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6849,16 +7064,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6866,16 +7081,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6883,7 +7098,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6891,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6899,7 +7114,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6907,7 +7122,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6915,7 +7130,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6923,7 +7138,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6931,7 +7146,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6939,7 +7154,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6947,7 +7162,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6955,7 +7170,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6963,7 +7178,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6971,7 +7186,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6979,7 +7194,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6987,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6995,7 +7210,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7003,7 +7218,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7011,7 +7226,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7019,7 +7234,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7027,7 +7242,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7035,7 +7250,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7043,7 +7258,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7051,7 +7266,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7059,7 +7274,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7067,7 +7282,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7075,7 +7290,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7083,7 +7298,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7091,7 +7306,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7099,7 +7314,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7107,7 +7322,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7115,7 +7330,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7123,7 +7338,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7131,7 +7346,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7139,7 +7354,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7147,7 +7362,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7155,7 +7370,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7163,7 +7378,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7171,7 +7386,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7179,7 +7394,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7187,7 +7402,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7195,7 +7410,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7203,7 +7418,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7211,7 +7426,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7219,7 +7434,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -5851,7 +5851,7 @@
         <v>10170039</v>
       </c>
       <c r="B119" s="8">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>21</v>
@@ -5881,7 +5881,7 @@
         <v>10170040</v>
       </c>
       <c r="B120" s="8">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>21</v>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="392">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -967,6 +967,9 @@
     <t>概率出现3个SCATTER</t>
   </si>
   <si>
+    <t>0_50|1_30|2_19|3_1</t>
+  </si>
+  <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
   </si>
   <si>
@@ -1016,6 +1019,153 @@
   </si>
   <si>
     <t>免费游戏中概率出现</t>
+  </si>
+  <si>
+    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>橘子福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个橘子or两个wind符号</t>
+  </si>
+  <si>
+    <t>1_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>1_7</t>
+  </si>
+  <si>
+    <t>橘子福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个橘子or1个wind符号</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>鞭炮福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个鞭炮or两个wind符号</t>
+  </si>
+  <si>
+    <t>2_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>鞭炮福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个鞭炮or1个wind符号</t>
+  </si>
+  <si>
+    <t>红包福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个红包or两个wind符号</t>
+  </si>
+  <si>
+    <t>3_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>3_7</t>
+  </si>
+  <si>
+    <t>红包福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个红包or1个wind符号</t>
+  </si>
+  <si>
+    <t>福袋福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个福袋or两个wind符号</t>
+  </si>
+  <si>
+    <t>4_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>4_7</t>
+  </si>
+  <si>
+    <t>福袋福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个福袋or1个wind符号</t>
+  </si>
+  <si>
+    <t>玉如意福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个玉如意or两个wind符号</t>
+  </si>
+  <si>
+    <t>5_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>5_7</t>
+  </si>
+  <si>
+    <t>玉如意福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个玉如意or1个wind符号</t>
+  </si>
+  <si>
+    <t>元宝福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个元宝or两个wind符号</t>
+  </si>
+  <si>
+    <t>1_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>6_7</t>
+  </si>
+  <si>
+    <t>元宝福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个元宝or1个wind符号</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>福马模式</t>
+  </si>
+  <si>
+    <t>改出一个大奖符号</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1382,7 +1532,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1427,13 +1577,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1446,6 +1596,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1648,12 +1810,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B050"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1778,7 +1955,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1790,122 +1967,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1915,25 +2092,32 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1970,14 +2154,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1991,12 +2175,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2011,7 +2195,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2019,18 +2202,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2048,6 +2231,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
@@ -2378,7 +2585,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2391,7 +2598,7 @@
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="9" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="16" customWidth="1"/>
     <col min="12" max="12" width="9.375"/>
     <col min="13" max="13" width="12.5"/>
     <col min="14" max="14" width="9.375"/>
@@ -2399,121 +2606,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="17"/>
+      <c r="G2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="17"/>
+      <c r="G3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="13"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="17">
         <v>100100</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="23" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2522,16 +2729,16 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="25" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2539,16 +2746,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="17">
         <v>100100</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="23" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2557,29 +2764,29 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="19"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="17">
         <v>100100</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="28" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -2588,27 +2795,27 @@
       <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="60" t="s">
+      <c r="H7" s="28"/>
+      <c r="I7" s="76" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="22"/>
+      <c r="K7" s="29"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="17">
         <v>100100</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="28" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2617,27 +2824,27 @@
       <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="21"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="23"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="30"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="17">
         <v>100100</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="28" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2646,27 +2853,27 @@
       <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="28"/>
       <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="23"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="17">
         <v>100100</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="28" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2675,27 +2882,27 @@
       <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="28"/>
       <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="23"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="17">
         <v>100100</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="28" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2704,27 +2911,27 @@
       <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="21"/>
+      <c r="H11" s="28"/>
       <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="23"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="30"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="17">
         <v>100100</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="28" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2733,16 +2940,16 @@
       <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="30" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2750,16 +2957,16 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="17">
         <v>100100</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="33" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -2768,14 +2975,14 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="26"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="34" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2783,16 +2990,16 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="17">
         <v>100100</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="31" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="33" t="s">
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -2801,147 +3008,147 @@
       <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="33"/>
+      <c r="I14" s="77" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="27"/>
+      <c r="K14" s="34"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="17">
         <v>100100</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="29" t="s">
+      <c r="H15" s="37"/>
+      <c r="I15" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="31"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="38"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="17">
         <v>100100</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="62" t="s">
+      <c r="H16" s="41"/>
+      <c r="I16" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="35"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="42"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="17">
         <v>100100</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="42" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A18" s="37">
+      <c r="A18" s="44">
         <v>10010061</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="18">
         <v>100100</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="37" t="s">
+      <c r="H18" s="18"/>
+      <c r="I18" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="37"/>
-      <c r="K18" s="40"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="47"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="48">
         <v>100100</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="48" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2950,27 +3157,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="41"/>
-      <c r="I19" s="63" t="s">
+      <c r="H19" s="48"/>
+      <c r="I19" s="79" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="43"/>
+      <c r="K19" s="50"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="41">
+      <c r="B20" s="48">
         <v>100100</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="48" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2979,27 +3186,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="41"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="41"/>
-      <c r="K20" s="44"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="51"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="48">
         <v>100100</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="48" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -3008,27 +3215,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="41"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="44"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="51"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="48">
         <v>100100</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="48" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -3037,27 +3244,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="41"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="41"/>
-      <c r="K22" s="44"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="51"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="48">
         <v>100100</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="48" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -3066,27 +3273,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="41"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="41"/>
-      <c r="K23" s="44"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="51"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="48">
         <v>100100</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="48" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -3095,62 +3302,62 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="48" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="51" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="16.5" spans="1:12">
-      <c r="A25" s="45">
+      <c r="A25" s="15">
         <v>10010091</v>
       </c>
-      <c r="B25" s="46">
+      <c r="B25" s="52">
         <v>100100</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="45" t="s">
+      <c r="C25" s="52"/>
+      <c r="D25" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="45" t="s">
+      <c r="G25" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="45" t="s">
+      <c r="I25" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="46"/>
-      <c r="K25" s="47"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="53"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="17">
         <v>100300</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="23" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3159,29 +3366,29 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="23" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="17"/>
-      <c r="K26" s="18"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="25"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="17">
         <v>100300</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="23" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="23" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3190,29 +3397,29 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="23" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="17"/>
-      <c r="K27" s="18"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="25"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="17">
         <v>100300</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="23" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="23" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3221,28 +3428,28 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="16"/>
-      <c r="I28" s="64" t="s">
+      <c r="H28" s="23"/>
+      <c r="I28" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
-      <c r="K28" s="44"/>
+      <c r="K28" s="51"/>
       <c r="L28"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A29" s="1">
         <v>10030041</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="17">
         <v>100300</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="23" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3251,28 +3458,28 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="64" t="s">
+      <c r="H29" s="23"/>
+      <c r="I29" s="80" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="44"/>
+      <c r="K29" s="51"/>
       <c r="L29"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A30" s="1">
         <v>10030042</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="17">
         <v>100300</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="23" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3281,28 +3488,28 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="64" t="s">
+      <c r="H30" s="23"/>
+      <c r="I30" s="80" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="44"/>
+      <c r="K30" s="51"/>
       <c r="L30"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A31" s="1">
         <v>10030043</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="17">
         <v>100300</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="23" t="s">
         <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3311,28 +3518,28 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="64" t="s">
+      <c r="H31" s="23"/>
+      <c r="I31" s="80" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="44"/>
+      <c r="K31" s="51"/>
       <c r="L31"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <v>10030044</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="17">
         <v>100300</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="23" t="s">
         <v>108</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -3341,28 +3548,28 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="64" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="80" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
-      <c r="K32" s="44"/>
+      <c r="K32" s="51"/>
       <c r="L32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="17">
         <v>100300</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="23" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="23" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -3371,30 +3578,30 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="64" t="s">
+      <c r="H33" s="23"/>
+      <c r="I33" s="80" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="54"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>10030050</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="17">
         <v>100300</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="23" t="s">
         <v>112</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -3403,217 +3610,217 @@
       <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="64" t="s">
+      <c r="H34" s="23"/>
+      <c r="I34" s="80" t="s">
         <v>108</v>
       </c>
       <c r="J34" s="4"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="54"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A35" s="49">
+      <c r="A35" s="55">
         <v>10070010</v>
       </c>
-      <c r="B35" s="50">
+      <c r="B35" s="56">
         <v>100700</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="49" t="s">
+      <c r="C35" s="56"/>
+      <c r="D35" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="50"/>
-      <c r="I35" s="49" t="s">
+      <c r="H35" s="56"/>
+      <c r="I35" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="51"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="57"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A36" s="49">
+      <c r="A36" s="55">
         <v>10070011</v>
       </c>
-      <c r="B36" s="50">
+      <c r="B36" s="56">
         <v>100700</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="49" t="s">
+      <c r="C36" s="56"/>
+      <c r="D36" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="49" t="s">
+      <c r="F36" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="49" t="s">
+      <c r="G36" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="50"/>
-      <c r="I36" s="49" t="s">
+      <c r="H36" s="56"/>
+      <c r="I36" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="51"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="57"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A37" s="49">
+      <c r="A37" s="55">
         <v>10070012</v>
       </c>
-      <c r="B37" s="50">
+      <c r="B37" s="56">
         <v>100700</v>
       </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="49" t="s">
+      <c r="C37" s="56"/>
+      <c r="D37" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="50"/>
-      <c r="I37" s="49" t="s">
+      <c r="H37" s="56"/>
+      <c r="I37" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="51"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="57"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A38" s="52">
+      <c r="A38" s="58">
         <v>10070021</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="59">
         <v>100700</v>
       </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="52" t="s">
+      <c r="C38" s="59"/>
+      <c r="D38" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="E38" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="53"/>
-      <c r="I38" s="52" t="s">
+      <c r="H38" s="59"/>
+      <c r="I38" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="52"/>
-      <c r="K38" s="54"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="60"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A39" s="52">
+      <c r="A39" s="58">
         <v>10070022</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="59">
         <v>100700</v>
       </c>
-      <c r="C39" s="53"/>
-      <c r="D39" s="52" t="s">
+      <c r="C39" s="59"/>
+      <c r="D39" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="53" t="s">
+      <c r="E39" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="53"/>
-      <c r="I39" s="52" t="s">
+      <c r="H39" s="59"/>
+      <c r="I39" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="52"/>
-      <c r="K39" s="54"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="60"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A40" s="52">
+      <c r="A40" s="58">
         <v>10070023</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="59">
         <v>100700</v>
       </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="52" t="s">
+      <c r="C40" s="59"/>
+      <c r="D40" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="53"/>
-      <c r="I40" s="52" t="s">
+      <c r="H40" s="59"/>
+      <c r="I40" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="52"/>
-      <c r="K40" s="54"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="60"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A41" s="52">
+      <c r="A41" s="58">
         <v>10070024</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="59">
         <v>100700</v>
       </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="52" t="s">
+      <c r="C41" s="59"/>
+      <c r="D41" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="52" t="s">
+      <c r="G41" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="53"/>
-      <c r="I41" s="52" t="s">
+      <c r="H41" s="59"/>
+      <c r="I41" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="52"/>
-      <c r="K41" s="54"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="60"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="3">
         <v>10070030</v>
       </c>
-      <c r="B42" s="55">
+      <c r="B42" s="61">
         <v>100700</v>
       </c>
-      <c r="C42" s="55"/>
+      <c r="C42" s="61"/>
       <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="55" t="s">
+      <c r="E42" s="61" t="s">
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -3622,25 +3829,25 @@
       <c r="G42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="55"/>
-      <c r="I42" s="65" t="s">
+      <c r="H42" s="61"/>
+      <c r="I42" s="81" t="s">
         <v>134</v>
       </c>
       <c r="J42" s="3"/>
-      <c r="K42" s="56"/>
+      <c r="K42" s="62"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="3">
         <v>10070031</v>
       </c>
-      <c r="B43" s="55">
+      <c r="B43" s="61">
         <v>100700</v>
       </c>
-      <c r="C43" s="55"/>
+      <c r="C43" s="61"/>
       <c r="D43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E43" s="55" t="s">
+      <c r="E43" s="61" t="s">
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -3649,27 +3856,27 @@
       <c r="G43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="55" t="s">
+      <c r="H43" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="65" t="s">
+      <c r="I43" s="81" t="s">
         <v>138</v>
       </c>
       <c r="J43" s="3"/>
-      <c r="K43" s="56"/>
+      <c r="K43" s="62"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="3">
         <v>10070032</v>
       </c>
-      <c r="B44" s="55">
+      <c r="B44" s="61">
         <v>100700</v>
       </c>
-      <c r="C44" s="55"/>
+      <c r="C44" s="61"/>
       <c r="D44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="55" t="s">
+      <c r="E44" s="61" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -3678,26 +3885,26 @@
       <c r="G44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="55" t="s">
+      <c r="H44" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="65" t="s">
+      <c r="I44" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K44" s="56"/>
+      <c r="K44" s="62"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="3">
         <v>10070033</v>
       </c>
-      <c r="B45" s="55">
+      <c r="B45" s="61">
         <v>100700</v>
       </c>
-      <c r="C45" s="55"/>
+      <c r="C45" s="61"/>
       <c r="D45" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="55" t="s">
+      <c r="E45" s="61" t="s">
         <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -3706,26 +3913,26 @@
       <c r="G45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H45" s="55" t="s">
+      <c r="H45" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="65" t="s">
+      <c r="I45" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K45" s="56"/>
+      <c r="K45" s="62"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="3">
         <v>10070034</v>
       </c>
-      <c r="B46" s="55">
+      <c r="B46" s="61">
         <v>100700</v>
       </c>
-      <c r="C46" s="55"/>
+      <c r="C46" s="61"/>
       <c r="D46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="55" t="s">
+      <c r="E46" s="61" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -3734,26 +3941,26 @@
       <c r="G46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="55" t="s">
+      <c r="H46" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="I46" s="65" t="s">
+      <c r="I46" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K46" s="56"/>
+      <c r="K46" s="62"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="3">
         <v>10070035</v>
       </c>
-      <c r="B47" s="55">
+      <c r="B47" s="61">
         <v>100700</v>
       </c>
-      <c r="C47" s="55"/>
+      <c r="C47" s="61"/>
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="55" t="s">
+      <c r="E47" s="61" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -3762,26 +3969,26 @@
       <c r="G47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="55" t="s">
+      <c r="H47" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="65" t="s">
+      <c r="I47" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K47" s="56"/>
+      <c r="K47" s="62"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="3">
         <v>10070036</v>
       </c>
-      <c r="B48" s="55">
+      <c r="B48" s="61">
         <v>100700</v>
       </c>
-      <c r="C48" s="55"/>
+      <c r="C48" s="61"/>
       <c r="D48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="55" t="s">
+      <c r="E48" s="61" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -3790,26 +3997,26 @@
       <c r="G48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="55" t="s">
+      <c r="H48" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="65" t="s">
+      <c r="I48" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K48" s="56"/>
+      <c r="K48" s="62"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A49" s="3">
         <v>10070037</v>
       </c>
-      <c r="B49" s="55">
+      <c r="B49" s="61">
         <v>100700</v>
       </c>
-      <c r="C49" s="55"/>
+      <c r="C49" s="61"/>
       <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="55" t="s">
+      <c r="E49" s="61" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -3818,26 +4025,26 @@
       <c r="G49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="55" t="s">
+      <c r="H49" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="I49" s="65" t="s">
+      <c r="I49" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K49" s="56"/>
+      <c r="K49" s="62"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A50" s="3">
         <v>10070038</v>
       </c>
-      <c r="B50" s="55">
+      <c r="B50" s="61">
         <v>100700</v>
       </c>
-      <c r="C50" s="55"/>
+      <c r="C50" s="61"/>
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="55" t="s">
+      <c r="E50" s="61" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -3846,25 +4053,25 @@
       <c r="G50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="55" t="s">
+      <c r="H50" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="65" t="s">
+      <c r="I50" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K50" s="56"/>
+      <c r="K50" s="62"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
         <v>10120011</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="23">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="23" t="s">
         <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -3873,26 +4080,26 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="23" t="s">
         <v>160</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J51" s="4"/>
-      <c r="K51" s="19"/>
+      <c r="K51" s="26"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
         <v>10120021</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="23">
         <v>101200</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="23" t="s">
         <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -3901,27 +4108,27 @@
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="64" t="s">
+      <c r="H52" s="23"/>
+      <c r="I52" s="80" t="s">
         <v>109</v>
       </c>
       <c r="J52" s="4"/>
-      <c r="K52" s="19"/>
+      <c r="K52" s="26"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
         <v>10120031</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="23">
         <v>101200</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="63" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="23" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -3930,29 +4137,29 @@
       <c r="G53" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I53" s="64" t="s">
+      <c r="I53" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
-      <c r="K53" s="19"/>
+      <c r="K53" s="26"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
         <v>10120032</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="23">
         <v>101200</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="63" t="s">
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="23" t="s">
         <v>140</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -3961,29 +4168,29 @@
       <c r="G54" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="16" t="s">
+      <c r="H54" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="64" t="s">
+      <c r="I54" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="19"/>
+      <c r="K54" s="26"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
         <v>10120033</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="23">
         <v>101200</v>
       </c>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="63" t="s">
         <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="16" t="s">
+      <c r="E55" s="23" t="s">
         <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -3992,29 +4199,29 @@
       <c r="G55" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J55" s="4"/>
-      <c r="K55" s="19"/>
+      <c r="K55" s="26"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
         <v>10120034</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="23">
         <v>101200</v>
       </c>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="63" t="s">
         <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="23" t="s">
         <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -4023,29 +4230,29 @@
       <c r="G56" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I56" s="64" t="s">
+      <c r="I56" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="19"/>
+      <c r="K56" s="26"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
         <v>10120035</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="23">
         <v>101200</v>
       </c>
-      <c r="C57" s="57" t="s">
+      <c r="C57" s="63" t="s">
         <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="16" t="s">
+      <c r="E57" s="23" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -4054,29 +4261,29 @@
       <c r="G57" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="64" t="s">
+      <c r="I57" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J57" s="4"/>
-      <c r="K57" s="19"/>
+      <c r="K57" s="26"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="4">
         <v>10120036</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="23">
         <v>101200</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="63" t="s">
         <v>172</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E58" s="16" t="s">
+      <c r="E58" s="23" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -4085,29 +4292,29 @@
       <c r="G58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="64" t="s">
+      <c r="I58" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="19"/>
+      <c r="K58" s="26"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
         <v>10120041</v>
       </c>
-      <c r="B59" s="57">
+      <c r="B59" s="63">
         <v>101200</v>
       </c>
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="63" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="57" t="s">
+      <c r="E59" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -4116,29 +4323,29 @@
       <c r="G59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="57">
+      <c r="H59" s="63">
         <v>10</v>
       </c>
-      <c r="I59" s="66" t="s">
+      <c r="I59" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="58"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
         <v>10120042</v>
       </c>
-      <c r="B60" s="57">
+      <c r="B60" s="63">
         <v>101200</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="63" t="s">
         <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="57" t="s">
+      <c r="E60" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -4147,29 +4354,29 @@
       <c r="G60" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H60" s="57">
+      <c r="H60" s="63">
         <v>10</v>
       </c>
-      <c r="I60" s="66" t="s">
+      <c r="I60" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="58"/>
+      <c r="K60" s="64"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
         <v>10120043</v>
       </c>
-      <c r="B61" s="57">
+      <c r="B61" s="63">
         <v>101200</v>
       </c>
-      <c r="C61" s="57" t="s">
+      <c r="C61" s="63" t="s">
         <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
@@ -4178,29 +4385,29 @@
       <c r="G61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H61" s="57">
+      <c r="H61" s="63">
         <v>10</v>
       </c>
-      <c r="I61" s="66" t="s">
+      <c r="I61" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="58"/>
+      <c r="K61" s="64"/>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
         <v>10120044</v>
       </c>
-      <c r="B62" s="57">
+      <c r="B62" s="63">
         <v>101200</v>
       </c>
-      <c r="C62" s="57" t="s">
+      <c r="C62" s="63" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E62" s="57" t="s">
+      <c r="E62" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -4209,29 +4416,29 @@
       <c r="G62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H62" s="57">
+      <c r="H62" s="63">
         <v>10</v>
       </c>
-      <c r="I62" s="66" t="s">
+      <c r="I62" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="58"/>
+      <c r="K62" s="64"/>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
         <v>10120045</v>
       </c>
-      <c r="B63" s="57">
+      <c r="B63" s="63">
         <v>101200</v>
       </c>
-      <c r="C63" s="57" t="s">
+      <c r="C63" s="63" t="s">
         <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="57" t="s">
+      <c r="E63" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -4240,29 +4447,29 @@
       <c r="G63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="57">
+      <c r="H63" s="63">
         <v>10</v>
       </c>
-      <c r="I63" s="66" t="s">
+      <c r="I63" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="58"/>
+      <c r="K63" s="64"/>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
         <v>10120046</v>
       </c>
-      <c r="B64" s="57">
+      <c r="B64" s="63">
         <v>101200</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="63" t="s">
         <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="57" t="s">
+      <c r="E64" s="63" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -4271,29 +4478,29 @@
       <c r="G64" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H64" s="57">
+      <c r="H64" s="63">
         <v>10</v>
       </c>
-      <c r="I64" s="66" t="s">
+      <c r="I64" s="82" t="s">
         <v>107</v>
       </c>
       <c r="J64" s="5"/>
-      <c r="K64" s="58"/>
+      <c r="K64" s="64"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
         <v>10120051</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="23">
         <v>101200</v>
       </c>
-      <c r="C65" s="57" t="s">
+      <c r="C65" s="63" t="s">
         <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="23" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4302,29 +4509,29 @@
       <c r="G65" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="64" t="s">
+      <c r="I65" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="19"/>
+      <c r="K65" s="26"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
         <v>10120052</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="23">
         <v>101200</v>
       </c>
-      <c r="C66" s="57" t="s">
+      <c r="C66" s="63" t="s">
         <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E66" s="23" t="s">
         <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4333,29 +4540,29 @@
       <c r="G66" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I66" s="64" t="s">
+      <c r="I66" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J66" s="4"/>
-      <c r="K66" s="19"/>
+      <c r="K66" s="26"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
         <v>10120053</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="23">
         <v>101200</v>
       </c>
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="63" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="16" t="s">
+      <c r="E67" s="23" t="s">
         <v>193</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4364,29 +4571,29 @@
       <c r="G67" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J67" s="4"/>
-      <c r="K67" s="19"/>
+      <c r="K67" s="26"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
         <v>10120054</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="23">
         <v>101200</v>
       </c>
-      <c r="C68" s="57" t="s">
+      <c r="C68" s="63" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="16" t="s">
+      <c r="E68" s="23" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4395,29 +4602,29 @@
       <c r="G68" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="64" t="s">
+      <c r="I68" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="19"/>
+      <c r="K68" s="26"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
         <v>10120055</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="23">
         <v>101200</v>
       </c>
-      <c r="C69" s="57" t="s">
+      <c r="C69" s="63" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="E69" s="23" t="s">
         <v>196</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -4426,29 +4633,29 @@
       <c r="G69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="64" t="s">
+      <c r="I69" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="19"/>
+      <c r="K69" s="26"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="4">
         <v>10120056</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="23">
         <v>101200</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="63" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="E70" s="23" t="s">
         <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -4457,29 +4664,29 @@
       <c r="G70" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="64" t="s">
+      <c r="I70" s="80" t="s">
         <v>192</v>
       </c>
       <c r="J70" s="4"/>
-      <c r="K70" s="19"/>
+      <c r="K70" s="26"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
         <v>10120061</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="23">
         <v>101200</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="33" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="E71" s="33" t="s">
         <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -4488,29 +4695,29 @@
       <c r="G71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="61" t="s">
+      <c r="I71" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="27"/>
+      <c r="K71" s="34"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
         <v>10120062</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="23">
         <v>101200</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="33" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="E72" s="33" t="s">
         <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -4519,29 +4726,29 @@
       <c r="G72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I72" s="61" t="s">
+      <c r="I72" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J72" s="6"/>
-      <c r="K72" s="27"/>
+      <c r="K72" s="34"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
         <v>10120063</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="23">
         <v>101200</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="33" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="E73" s="33" t="s">
         <v>203</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -4550,29 +4757,29 @@
       <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I73" s="61" t="s">
+      <c r="I73" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="27"/>
+      <c r="K73" s="34"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <v>10120064</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="23">
         <v>101200</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="33" t="s">
         <v>204</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="E74" s="33" t="s">
         <v>205</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -4581,29 +4788,29 @@
       <c r="G74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I74" s="61" t="s">
+      <c r="I74" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="27"/>
+      <c r="K74" s="34"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <v>10120065</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="23">
         <v>101200</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="33" t="s">
         <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="26" t="s">
+      <c r="E75" s="33" t="s">
         <v>206</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -4612,29 +4819,29 @@
       <c r="G75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="26" t="s">
+      <c r="H75" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I75" s="61" t="s">
+      <c r="I75" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="27"/>
+      <c r="K75" s="34"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <v>10120066</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="23">
         <v>101200</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="33" t="s">
         <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E76" s="33" t="s">
         <v>207</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -4643,29 +4850,29 @@
       <c r="G76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H76" s="26" t="s">
+      <c r="H76" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="61" t="s">
+      <c r="I76" s="77" t="s">
         <v>201</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="27"/>
+      <c r="K76" s="34"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
         <v>10140001</v>
       </c>
-      <c r="B77" s="55">
+      <c r="B77" s="61">
         <v>101400</v>
       </c>
-      <c r="C77" s="55" t="s">
+      <c r="C77" s="61" t="s">
         <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="55" t="s">
+      <c r="E77" s="61" t="s">
         <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -4674,28 +4881,28 @@
       <c r="G77" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="21" t="s">
+      <c r="H77" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="I77" s="65" t="s">
+      <c r="I77" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="K77" s="56"/>
+      <c r="K77" s="62"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="3">
         <v>10140011</v>
       </c>
-      <c r="B78" s="55">
+      <c r="B78" s="61">
         <v>101400</v>
       </c>
-      <c r="C78" s="55" t="s">
+      <c r="C78" s="61" t="s">
         <v>208</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="55" t="s">
+      <c r="E78" s="61" t="s">
         <v>140</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -4704,28 +4911,28 @@
       <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="21" t="s">
+      <c r="H78" s="28" t="s">
         <v>211</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K78" s="56"/>
+      <c r="K78" s="62"/>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="7">
         <v>10140021</v>
       </c>
-      <c r="B79" s="21">
+      <c r="B79" s="28">
         <v>101400</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="C79" s="28" t="s">
         <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="21" t="s">
+      <c r="E79" s="28" t="s">
         <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -4734,28 +4941,28 @@
       <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="21" t="s">
+      <c r="H79" s="28" t="s">
         <v>143</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K79" s="22"/>
+      <c r="K79" s="29"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
         <v>10140022</v>
       </c>
-      <c r="B80" s="21">
+      <c r="B80" s="28">
         <v>101400</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="28" t="s">
         <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="21" t="s">
+      <c r="E80" s="28" t="s">
         <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -4764,28 +4971,28 @@
       <c r="G80" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="21" t="s">
+      <c r="H80" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="I80" s="65" t="s">
+      <c r="I80" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="K80" s="22"/>
+      <c r="K80" s="29"/>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="7">
         <v>10140023</v>
       </c>
-      <c r="B81" s="21">
+      <c r="B81" s="28">
         <v>101400</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="28" t="s">
         <v>217</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="21" t="s">
+      <c r="E81" s="28" t="s">
         <v>143</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -4794,28 +5001,28 @@
       <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="21" t="s">
+      <c r="H81" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="I81" s="65" t="s">
+      <c r="I81" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="K81" s="22"/>
+      <c r="K81" s="29"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="1">
         <v>10240011</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="17">
         <v>102400</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="16" t="s">
+      <c r="E82" s="23" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -4824,16 +5031,16 @@
       <c r="G82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="16" t="s">
+      <c r="H82" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J82" s="17" t="s">
+      <c r="J82" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K82" s="18" t="s">
+      <c r="K82" s="25" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4841,16 +5048,16 @@
       <c r="A83" s="1">
         <v>10240012</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="17">
         <v>102400</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="16" t="s">
+      <c r="E83" s="23" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -4859,29 +5066,29 @@
       <c r="G83" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="23" t="s">
         <v>26</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J83" s="4"/>
-      <c r="K83" s="19"/>
+      <c r="K83" s="26"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="1">
         <v>10240021</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="17">
         <v>102400</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="21" t="s">
+      <c r="E84" s="28" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -4890,27 +5097,27 @@
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="21"/>
-      <c r="I84" s="60" t="s">
+      <c r="H84" s="28"/>
+      <c r="I84" s="76" t="s">
         <v>39</v>
       </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="22"/>
+      <c r="K84" s="29"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="1">
         <v>10240022</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="17">
         <v>102400</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E85" s="21" t="s">
+      <c r="E85" s="28" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -4919,27 +5126,27 @@
       <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="21"/>
+      <c r="H85" s="28"/>
       <c r="I85" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J85" s="21"/>
-      <c r="K85" s="23"/>
+      <c r="J85" s="28"/>
+      <c r="K85" s="30"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="1">
         <v>10240023</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="17">
         <v>102400</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="21" t="s">
+      <c r="E86" s="28" t="s">
         <v>46</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -4948,27 +5155,27 @@
       <c r="G86" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="21"/>
+      <c r="H86" s="28"/>
       <c r="I86" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J86" s="21"/>
-      <c r="K86" s="23"/>
+      <c r="J86" s="28"/>
+      <c r="K86" s="30"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="1">
         <v>10240024</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="17">
         <v>102400</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C87" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="21" t="s">
+      <c r="E87" s="28" t="s">
         <v>51</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -4977,27 +5184,27 @@
       <c r="G87" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="21"/>
+      <c r="H87" s="28"/>
       <c r="I87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J87" s="21"/>
-      <c r="K87" s="23"/>
+      <c r="J87" s="28"/>
+      <c r="K87" s="30"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="1">
         <v>10240025</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="17">
         <v>102400</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="21" t="s">
+      <c r="E88" s="28" t="s">
         <v>56</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -5006,27 +5213,27 @@
       <c r="G88" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H88" s="21"/>
+      <c r="H88" s="28"/>
       <c r="I88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="21"/>
-      <c r="K88" s="23"/>
+      <c r="J88" s="28"/>
+      <c r="K88" s="30"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="1">
         <v>10240026</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="17">
         <v>102400</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="27" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="21" t="s">
+      <c r="E89" s="28" t="s">
         <v>61</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -5035,16 +5242,16 @@
       <c r="G89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H89" s="21" t="s">
+      <c r="H89" s="28" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="17" t="s">
+      <c r="J89" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K89" s="23" t="s">
+      <c r="K89" s="30" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5052,16 +5259,16 @@
       <c r="A90" s="1">
         <v>10240031</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="17">
         <v>102400</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D90" s="25" t="s">
+      <c r="D90" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="26" t="s">
+      <c r="E90" s="33" t="s">
         <v>61</v>
       </c>
       <c r="F90" s="6" t="s">
@@ -5070,14 +5277,14 @@
       <c r="G90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="26"/>
+      <c r="H90" s="33"/>
       <c r="I90" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J90" s="17" t="s">
+      <c r="J90" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K90" s="27" t="s">
+      <c r="K90" s="34" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5085,16 +5292,16 @@
       <c r="A91" s="1">
         <v>10240032</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="17">
         <v>102400</v>
       </c>
-      <c r="C91" s="24" t="s">
+      <c r="C91" s="31" t="s">
         <v>62</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="26" t="s">
+      <c r="E91" s="33" t="s">
         <v>67</v>
       </c>
       <c r="F91" s="6" t="s">
@@ -5103,147 +5310,147 @@
       <c r="G91" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="26"/>
-      <c r="I91" s="61" t="s">
+      <c r="H91" s="33"/>
+      <c r="I91" s="77" t="s">
         <v>39</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="27"/>
+      <c r="K91" s="34"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="1">
         <v>10240041</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="17">
         <v>102400</v>
       </c>
-      <c r="C92" s="28" t="s">
+      <c r="C92" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="29" t="s">
+      <c r="D92" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="30" t="s">
+      <c r="E92" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="29" t="s">
+      <c r="G92" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="H92" s="30"/>
-      <c r="I92" s="29" t="s">
+      <c r="H92" s="37"/>
+      <c r="I92" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="J92" s="29"/>
-      <c r="K92" s="31"/>
+      <c r="J92" s="36"/>
+      <c r="K92" s="38"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="1">
         <v>10240051</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="17">
         <v>102400</v>
       </c>
-      <c r="C93" s="32" t="s">
+      <c r="C93" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="34" t="s">
+      <c r="E93" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="33" t="s">
+      <c r="F93" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="33" t="s">
+      <c r="G93" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="34"/>
-      <c r="I93" s="62" t="s">
+      <c r="H93" s="41"/>
+      <c r="I93" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="33"/>
-      <c r="K93" s="35"/>
+      <c r="J93" s="40"/>
+      <c r="K93" s="42"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="1">
         <v>10240052</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="17">
         <v>102400</v>
       </c>
-      <c r="C94" s="32" t="s">
+      <c r="C94" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="36" t="s">
+      <c r="D94" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="34" t="s">
+      <c r="E94" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="33" t="s">
+      <c r="F94" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="33" t="s">
+      <c r="G94" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="34"/>
-      <c r="I94" s="33" t="s">
+      <c r="H94" s="41"/>
+      <c r="I94" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="J94" s="17" t="s">
+      <c r="J94" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K94" s="35" t="s">
+      <c r="K94" s="42" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A95" s="37">
+      <c r="A95" s="44">
         <v>10240061</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="18">
         <v>102400</v>
       </c>
-      <c r="C95" s="38" t="s">
+      <c r="C95" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="39" t="s">
+      <c r="D95" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F95" s="37" t="s">
+      <c r="F95" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="G95" s="37" t="s">
+      <c r="G95" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="11"/>
-      <c r="I95" s="37" t="s">
+      <c r="H95" s="18"/>
+      <c r="I95" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="J95" s="37"/>
-      <c r="K95" s="40"/>
+      <c r="J95" s="44"/>
+      <c r="K95" s="47"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="2">
         <v>10240071</v>
       </c>
-      <c r="B96" s="41">
+      <c r="B96" s="48">
         <v>102400</v>
       </c>
-      <c r="C96" s="42" t="s">
+      <c r="C96" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="41" t="s">
+      <c r="E96" s="48" t="s">
         <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -5252,26 +5459,26 @@
       <c r="G96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H96" s="41"/>
-      <c r="I96" s="63" t="s">
+      <c r="H96" s="48"/>
+      <c r="I96" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="K96" s="43"/>
+      <c r="K96" s="50"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="2">
         <v>10240072</v>
       </c>
-      <c r="B97" s="41">
+      <c r="B97" s="48">
         <v>102400</v>
       </c>
-      <c r="C97" s="42" t="s">
+      <c r="C97" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="41" t="s">
+      <c r="E97" s="48" t="s">
         <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -5280,27 +5487,27 @@
       <c r="G97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="41"/>
+      <c r="H97" s="48"/>
       <c r="I97" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="41"/>
-      <c r="K97" s="44"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="51"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="2">
         <v>10240073</v>
       </c>
-      <c r="B98" s="41">
+      <c r="B98" s="48">
         <v>102400</v>
       </c>
-      <c r="C98" s="42" t="s">
+      <c r="C98" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E98" s="41" t="s">
+      <c r="E98" s="48" t="s">
         <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -5309,27 +5516,27 @@
       <c r="G98" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="41"/>
+      <c r="H98" s="48"/>
       <c r="I98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J98" s="41"/>
-      <c r="K98" s="44"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="51"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="2">
         <v>10240074</v>
       </c>
-      <c r="B99" s="41">
+      <c r="B99" s="48">
         <v>102400</v>
       </c>
-      <c r="C99" s="42" t="s">
+      <c r="C99" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="41" t="s">
+      <c r="E99" s="48" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -5338,27 +5545,27 @@
       <c r="G99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H99" s="41"/>
+      <c r="H99" s="48"/>
       <c r="I99" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J99" s="41"/>
-      <c r="K99" s="44"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="51"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="2">
         <v>10240075</v>
       </c>
-      <c r="B100" s="41">
+      <c r="B100" s="48">
         <v>102400</v>
       </c>
-      <c r="C100" s="42" t="s">
+      <c r="C100" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="41" t="s">
+      <c r="E100" s="48" t="s">
         <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -5367,27 +5574,27 @@
       <c r="G100" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="41"/>
+      <c r="H100" s="48"/>
       <c r="I100" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J100" s="41"/>
-      <c r="K100" s="44"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="51"/>
     </row>
     <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="2">
         <v>10240076</v>
       </c>
-      <c r="B101" s="41">
+      <c r="B101" s="48">
         <v>102400</v>
       </c>
-      <c r="C101" s="42" t="s">
+      <c r="C101" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E101" s="41" t="s">
+      <c r="E101" s="48" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -5396,47 +5603,47 @@
       <c r="G101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="41" t="s">
+      <c r="H101" s="48" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J101" s="17" t="s">
+      <c r="J101" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="44" t="s">
+      <c r="K101" s="51" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A102" s="45">
+      <c r="A102" s="15">
         <v>10240091</v>
       </c>
-      <c r="B102" s="46">
+      <c r="B102" s="52">
         <v>102400</v>
       </c>
-      <c r="C102" s="46"/>
-      <c r="D102" s="45" t="s">
+      <c r="C102" s="52"/>
+      <c r="D102" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E102" s="46" t="s">
+      <c r="E102" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="F102" s="45" t="s">
+      <c r="F102" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G102" s="45" t="s">
+      <c r="G102" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H102" s="46" t="s">
+      <c r="H102" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="I102" s="45" t="s">
+      <c r="I102" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J102" s="46"/>
-      <c r="K102" s="47"/>
+      <c r="J102" s="52"/>
+      <c r="K102" s="53"/>
     </row>
     <row r="103" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A103" s="8">
@@ -5460,7 +5667,7 @@
       <c r="I103" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K103" s="59"/>
+      <c r="K103" s="65"/>
     </row>
     <row r="104" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A104" s="8">
@@ -5484,7 +5691,7 @@
       <c r="I104" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K104" s="59"/>
+      <c r="K104" s="65"/>
     </row>
     <row r="105" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A105" s="8">
@@ -5508,7 +5715,7 @@
       <c r="I105" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K105" s="59"/>
+      <c r="K105" s="65"/>
     </row>
     <row r="106" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A106" s="8">
@@ -5532,7 +5739,7 @@
       <c r="I106" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K106" s="59"/>
+      <c r="K106" s="65"/>
     </row>
     <row r="107" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A107" s="8">
@@ -5556,7 +5763,7 @@
       <c r="I107" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K107" s="59"/>
+      <c r="K107" s="65"/>
     </row>
     <row r="108" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="8">
@@ -5580,7 +5787,7 @@
       <c r="I108" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K108" s="59"/>
+      <c r="K108" s="65"/>
     </row>
     <row r="109" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A109" s="8">
@@ -5604,7 +5811,7 @@
       <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K109" s="59"/>
+      <c r="K109" s="65"/>
     </row>
     <row r="110" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A110" s="8">
@@ -5625,10 +5832,10 @@
       <c r="G110" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I110" s="67" t="s">
+      <c r="I110" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="K110" s="59"/>
+      <c r="K110" s="65"/>
     </row>
     <row r="111" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A111" s="8">
@@ -5655,7 +5862,7 @@
       <c r="I111" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K111" s="59"/>
+      <c r="K111" s="65"/>
     </row>
     <row r="112" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A112" s="8">
@@ -5682,7 +5889,7 @@
       <c r="I112" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K112" s="59"/>
+      <c r="K112" s="65"/>
     </row>
     <row r="113" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A113" s="8">
@@ -5709,7 +5916,7 @@
       <c r="I113" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K113" s="59"/>
+      <c r="K113" s="65"/>
     </row>
     <row r="114" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A114" s="8">
@@ -5736,7 +5943,7 @@
       <c r="I114" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K114" s="59"/>
+      <c r="K114" s="65"/>
     </row>
     <row r="115" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A115" s="8">
@@ -5763,7 +5970,7 @@
       <c r="I115" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K115" s="59"/>
+      <c r="K115" s="65"/>
     </row>
     <row r="116" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A116" s="8">
@@ -5790,7 +5997,7 @@
       <c r="I116" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K116" s="59"/>
+      <c r="K116" s="65"/>
     </row>
     <row r="117" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A117" s="8">
@@ -5817,7 +6024,7 @@
       <c r="I117" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K117" s="59"/>
+      <c r="K117" s="65"/>
     </row>
     <row r="118" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A118" s="8">
@@ -5844,7 +6051,7 @@
       <c r="I118" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K118" s="59"/>
+      <c r="K118" s="65"/>
     </row>
     <row r="119" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A119" s="8">
@@ -5874,7 +6081,7 @@
       <c r="I119" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K119" s="59"/>
+      <c r="K119" s="65"/>
     </row>
     <row r="120" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="8">
@@ -5904,887 +6111,1656 @@
       <c r="I120" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K120" s="59"/>
-    </row>
-    <row r="121" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A121" s="8">
+      <c r="K120" s="65"/>
+    </row>
+    <row r="121" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A121" s="9">
         <v>10220001</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="9">
         <v>102200</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="G121" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I121" s="8" t="s">
+      <c r="I121" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="K121" s="59"/>
-    </row>
-    <row r="122" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A122" s="8">
+      <c r="K121" s="66"/>
+    </row>
+    <row r="122" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A122" s="9">
         <v>10220011</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="9">
         <v>102200</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F122" s="8" t="s">
+      <c r="F122" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="G122" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H122" s="8" t="s">
+      <c r="H122" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="I122" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K122" s="59"/>
-    </row>
-    <row r="123" s="8" customFormat="1" ht="17" customHeight="1" spans="1:11">
-      <c r="A123" s="8">
+      <c r="K122" s="66"/>
+    </row>
+    <row r="123" s="9" customFormat="1" ht="17" customHeight="1" spans="1:11">
+      <c r="A123" s="9">
         <v>10220021</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="9">
         <v>102200</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E123" s="8" t="s">
+      <c r="E123" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F123" s="8" t="s">
+      <c r="F123" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G123" s="8" t="s">
+      <c r="G123" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H123" s="8" t="s">
+      <c r="H123" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I123" s="8" t="s">
+      <c r="I123" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K123" s="59"/>
-    </row>
-    <row r="124" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A124" s="8">
+      <c r="K123" s="66"/>
+    </row>
+    <row r="124" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A124" s="9">
         <v>10220099</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="9">
         <v>102200</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="D124" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="8" t="s">
+      <c r="F124" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="G124" s="8" t="s">
+      <c r="G124" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="8" t="s">
+      <c r="H124" s="9"/>
+      <c r="I124" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K124" s="59"/>
-    </row>
-    <row r="125" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A125" s="8">
+      <c r="K124" s="66"/>
+    </row>
+    <row r="125" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A125" s="9">
         <v>10220030</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="9">
         <v>102200</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D125" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G125" s="8" t="s">
+      <c r="G125" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H125" s="8" t="s">
+      <c r="H125" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I125" s="8" t="s">
+      <c r="I125" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="K125" s="59"/>
-    </row>
-    <row r="126" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A126" s="8">
+      <c r="K125" s="66"/>
+    </row>
+    <row r="126" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A126" s="9">
         <v>10220031</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="9">
         <v>102200</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D126" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8" t="s">
+      <c r="F126" s="9"/>
+      <c r="G126" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="H126" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="I126" s="8" t="s">
+      <c r="I126" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K126" s="59"/>
-    </row>
-    <row r="127" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A127" s="8">
+      <c r="K126" s="66"/>
+    </row>
+    <row r="127" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A127" s="9">
         <v>10220032</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="9">
         <v>102200</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D127" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E127" s="8" t="s">
+      <c r="E127" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8" t="s">
+      <c r="F127" s="9"/>
+      <c r="G127" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="H127" s="8" t="s">
+      <c r="H127" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I127" s="8" t="s">
+      <c r="I127" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K127" s="59"/>
-    </row>
-    <row r="128" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A128" s="8">
+      <c r="K127" s="66"/>
+    </row>
+    <row r="128" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A128" s="9">
         <v>10220012</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="9">
         <v>102200</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8" t="s">
+      <c r="D128" s="9"/>
+      <c r="E128" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8" t="s">
+      <c r="F128" s="9"/>
+      <c r="G128" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8" t="s">
+      <c r="H128" s="9"/>
+      <c r="I128" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K128" s="59"/>
-    </row>
-    <row r="129" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A129" s="8">
+      <c r="K128" s="66"/>
+    </row>
+    <row r="129" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A129" s="9">
         <v>10220033</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="9">
         <v>102200</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E129" s="8" t="s">
+      <c r="E129" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G129" s="8" t="s">
+      <c r="G129" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H129" s="8" t="s">
+      <c r="H129" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="I129" s="8" t="s">
+      <c r="I129" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K129" s="59"/>
-    </row>
-    <row r="130" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A130" s="8">
+      <c r="K129" s="66"/>
+    </row>
+    <row r="130" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A130" s="9">
         <v>10220019</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="9">
         <v>102200</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G130" s="8" t="s">
+      <c r="G130" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="I130" s="8" t="s">
+      <c r="I130" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K130" s="59"/>
-    </row>
-    <row r="131" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A131" s="8">
+      <c r="K130" s="66"/>
+    </row>
+    <row r="131" s="9" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A131" s="9">
         <v>10220020</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="9">
         <v>102200</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E131" s="8" t="s">
+      <c r="E131" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G131" s="8" t="s">
+      <c r="G131" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="I131" s="8" t="s">
+      <c r="I131" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K131" s="59"/>
-    </row>
-    <row r="132" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A132" s="8">
+      <c r="K131" s="66"/>
+    </row>
+    <row r="132" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A132" s="10">
         <v>10210001</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="10">
         <v>102100</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="E132" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F132" s="8" t="s">
+      <c r="F132" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G132" s="8" t="s">
+      <c r="G132" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="H132" s="8" t="s">
+      <c r="H132" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I132" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K132" s="59"/>
-    </row>
-    <row r="133" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A133" s="8">
+      <c r="K132" s="67"/>
+    </row>
+    <row r="133" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A133" s="10">
         <v>10210011</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="10">
         <v>102100</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="D133" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="E133" s="8" t="s">
+      <c r="E133" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="F133" s="8" t="s">
+      <c r="F133" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G133" s="8" t="s">
+      <c r="G133" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="H133" s="8" t="s">
+      <c r="H133" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I133" s="8" t="s">
+      <c r="I133" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K133" s="59"/>
-    </row>
-    <row r="134" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A134" s="8">
+      <c r="K133" s="67"/>
+    </row>
+    <row r="134" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A134" s="10">
         <v>10210021</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="10">
         <v>102100</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="D134" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="F134" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G134" s="8" t="s">
+      <c r="G134" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="10">
         <v>12</v>
       </c>
-      <c r="I134" s="8" t="s">
+      <c r="I134" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K134" s="59"/>
-    </row>
-    <row r="135" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A135" s="8">
+      <c r="K134" s="67"/>
+    </row>
+    <row r="135" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A135" s="10">
         <v>10210031</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="10">
         <v>102100</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="E135" s="8" t="s">
+      <c r="E135" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F135" s="8" t="s">
+      <c r="F135" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G135" s="8" t="s">
+      <c r="G135" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H135" s="8" t="s">
+      <c r="H135" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I135" s="8" t="s">
+      <c r="I135" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K135" s="59"/>
-    </row>
-    <row r="136" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A136" s="8">
+      <c r="K135" s="67"/>
+    </row>
+    <row r="136" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A136" s="10">
         <v>10210041</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="10">
         <v>102100</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="E136" s="8" t="s">
+      <c r="E136" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F136" s="8" t="s">
+      <c r="F136" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G136" s="8" t="s">
+      <c r="G136" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H136" s="8" t="s">
+      <c r="H136" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I136" s="8" t="s">
+      <c r="I136" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K136" s="59"/>
-    </row>
-    <row r="137" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A137" s="8">
+      <c r="K136" s="67"/>
+    </row>
+    <row r="137" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A137" s="10">
         <v>10210042</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="10">
         <v>102100</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="E137" s="8" t="s">
+      <c r="E137" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="F137" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G137" s="8" t="s">
+      <c r="G137" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H137" s="8" t="s">
+      <c r="H137" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I137" s="8" t="s">
+      <c r="I137" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K137" s="59"/>
-    </row>
-    <row r="138" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A138" s="8">
+      <c r="K137" s="67"/>
+    </row>
+    <row r="138" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A138" s="10">
         <v>10210032</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="10">
         <v>102100</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G138" s="8" t="s">
+      <c r="G138" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H138" s="8" t="s">
+      <c r="H138" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I138" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="K138" s="59"/>
-    </row>
-    <row r="139" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A139" s="8">
+      <c r="I138" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="K138" s="67"/>
+    </row>
+    <row r="139" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A139" s="10">
         <v>10210051</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="10">
         <v>102100</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D139" s="8" t="s">
+      <c r="D139" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F139" s="8" t="s">
+      <c r="F139" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="G139" s="8" t="s">
+      <c r="G139" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H139" s="8" t="s">
+      <c r="H139" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I139" s="8" t="s">
+      <c r="I139" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="K139" s="59"/>
-    </row>
-    <row r="140" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A140" s="8">
+      <c r="K139" s="67"/>
+    </row>
+    <row r="140" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="11">
         <v>10180001</v>
       </c>
-      <c r="B140" s="8">
+      <c r="B140" s="11">
         <v>101800</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D140" s="8" t="s">
+      <c r="D140" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F140" s="8" t="s">
+      <c r="F140" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G140" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H140" s="8" t="s">
+      <c r="G140" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="I140" s="8" t="s">
+      <c r="H140" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="I140" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K140" s="59"/>
-    </row>
-    <row r="141" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A141" s="8">
+      <c r="K140" s="68"/>
+    </row>
+    <row r="141" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A141" s="11">
         <v>10180002</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="11">
         <v>101800</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D141" s="8" t="s">
+      <c r="D141" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E141" s="8" t="s">
+      <c r="E141" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F141" s="8" t="s">
+      <c r="F141" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G141" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H141" s="8" t="s">
+      <c r="G141" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="I141" s="8" t="s">
+      <c r="H141" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="I141" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K141" s="59"/>
-    </row>
-    <row r="142" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A142" s="8">
+      <c r="K141" s="68"/>
+    </row>
+    <row r="142" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A142" s="11">
         <v>10180011</v>
       </c>
-      <c r="B142" s="8">
+      <c r="B142" s="11">
         <v>101800</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="F142" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G142" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="H142" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="F142" s="8" t="s">
+      <c r="I142" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K142" s="68"/>
+    </row>
+    <row r="143" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A143" s="11">
+        <v>10180021</v>
+      </c>
+      <c r="B143" s="11">
+        <v>101800</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E143" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F143" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G142" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="H142" s="8" t="s">
+      <c r="G143" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="I143" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="K143" s="68"/>
+    </row>
+    <row r="144" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A144" s="11">
+        <v>10180031</v>
+      </c>
+      <c r="B144" s="11">
+        <v>101800</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E144" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G144" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="I142" s="8" t="s">
+      <c r="H144" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="I144" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K144" s="68"/>
+    </row>
+    <row r="145" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A145" s="11">
+        <v>10180041</v>
+      </c>
+      <c r="B145" s="11">
+        <v>101800</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F145" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G145" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="I145" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="K145" s="68"/>
+    </row>
+    <row r="146" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="12">
+        <v>10250001</v>
+      </c>
+      <c r="B146" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G146" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="K146" s="69"/>
+    </row>
+    <row r="147" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A147" s="12">
+        <v>10250002</v>
+      </c>
+      <c r="B147" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G147" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K147" s="69"/>
+    </row>
+    <row r="148" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A148" s="12">
+        <v>10250011</v>
+      </c>
+      <c r="B148" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G148" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I148" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K142" s="59"/>
-    </row>
-    <row r="143" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A143" s="8">
-        <v>10180021</v>
-      </c>
-      <c r="B143" s="8">
-        <v>101800</v>
-      </c>
-      <c r="C143" s="8" t="s">
+      <c r="K148" s="69"/>
+    </row>
+    <row r="149" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A149" s="12">
+        <v>10250021</v>
+      </c>
+      <c r="B149" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C149" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D149" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="E143" s="8" t="s">
+      <c r="E149" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G149" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="K149" s="69"/>
+    </row>
+    <row r="150" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A150" s="12">
+        <v>10250031</v>
+      </c>
+      <c r="B150" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="E150" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F150" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G150" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="K150" s="69"/>
+    </row>
+    <row r="151" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A151" s="12">
+        <v>10250032</v>
+      </c>
+      <c r="B151" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="G151" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="K151" s="69"/>
+    </row>
+    <row r="152" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A152" s="13">
+        <v>10230001</v>
+      </c>
+      <c r="B152" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C152" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F152" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="G143" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H143" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I143" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K143" s="59"/>
-    </row>
-    <row r="144" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A144" s="8">
-        <v>10180031</v>
-      </c>
-      <c r="B144" s="8">
-        <v>101800</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="E144" s="8" t="s">
+      <c r="G152" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="K152" s="70"/>
+    </row>
+    <row r="153" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A153" s="13">
+        <v>10230002</v>
+      </c>
+      <c r="B153" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C153" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F153" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G153" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H153" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I153" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K153" s="70"/>
+    </row>
+    <row r="154" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A154" s="13">
+        <v>10230003</v>
+      </c>
+      <c r="B154" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C154" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F154" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G154" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I154" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="K154" s="70"/>
+    </row>
+    <row r="155" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A155" s="13">
+        <v>10230011</v>
+      </c>
+      <c r="B155" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G155" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H155" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I155" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K155" s="70"/>
+    </row>
+    <row r="156" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A156" s="13">
+        <v>10230021</v>
+      </c>
+      <c r="B156" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C156" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F156" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G156" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I156" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="K156" s="70"/>
+    </row>
+    <row r="157" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A157" s="13">
+        <v>10230031</v>
+      </c>
+      <c r="B157" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C157" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E157" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F144" s="8" t="s">
+      <c r="F157" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="G144" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H144" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I144" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="K144" s="59"/>
-    </row>
-    <row r="145" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A145" s="8">
-        <v>10180041</v>
-      </c>
-      <c r="B145" s="8">
-        <v>101800</v>
-      </c>
-      <c r="C145" s="8" t="s">
+      <c r="G157" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="H157" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I157" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="K157" s="70"/>
+    </row>
+    <row r="158" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A158" s="71">
+        <v>10340001</v>
+      </c>
+      <c r="B158" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C158" s="71" t="s">
+        <v>289</v>
+      </c>
+      <c r="D158" s="71" t="s">
+        <v>290</v>
+      </c>
+      <c r="E158" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="F158" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G158" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="H158" s="71" t="s">
+        <v>293</v>
+      </c>
+      <c r="I158" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K158" s="72"/>
+    </row>
+    <row r="159" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A159" s="71">
+        <v>10340011</v>
+      </c>
+      <c r="B159" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C159" s="71" t="s">
+        <v>294</v>
+      </c>
+      <c r="D159" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="E159" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="F159" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G159" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="H159" s="71"/>
+      <c r="I159" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K159" s="72"/>
+    </row>
+    <row r="160" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A160" s="71">
+        <v>10340021</v>
+      </c>
+      <c r="B160" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C160" s="71" t="s">
+        <v>289</v>
+      </c>
+      <c r="D160" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="E160" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="F160" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G160" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H160" s="71" t="s">
+        <v>293</v>
+      </c>
+      <c r="I160" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K160" s="73"/>
+    </row>
+    <row r="161" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A161" s="71">
+        <v>10340002</v>
+      </c>
+      <c r="B161" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C161" s="71" t="s">
+        <v>297</v>
+      </c>
+      <c r="D161" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="E161" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="F161" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G161" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="H161" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="I161" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K161" s="73"/>
+    </row>
+    <row r="162" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A162" s="71">
+        <v>10340012</v>
+      </c>
+      <c r="B162" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C162" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="D162" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="E162" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="F162" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G162" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="H162" s="71"/>
+      <c r="I162" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K162" s="73"/>
+    </row>
+    <row r="163" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A163" s="71">
+        <v>10340022</v>
+      </c>
+      <c r="B163" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C163" s="71" t="s">
+        <v>297</v>
+      </c>
+      <c r="D163" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="E163" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="F163" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G163" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H163" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="I163" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K163" s="73"/>
+    </row>
+    <row r="164" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A164" s="71">
+        <v>10340003</v>
+      </c>
+      <c r="B164" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C164" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="D164" s="71" t="s">
+        <v>305</v>
+      </c>
+      <c r="E164" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="F164" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G164" s="71" t="s">
+        <v>307</v>
+      </c>
+      <c r="H164" s="71" t="s">
+        <v>308</v>
+      </c>
+      <c r="I164" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K164" s="73"/>
+    </row>
+    <row r="165" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A165" s="71">
+        <v>10340013</v>
+      </c>
+      <c r="B165" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C165" s="71" t="s">
+        <v>309</v>
+      </c>
+      <c r="D165" s="71" t="s">
+        <v>310</v>
+      </c>
+      <c r="E165" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="F165" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G165" s="71" t="s">
+        <v>307</v>
+      </c>
+      <c r="H165" s="71"/>
+      <c r="I165" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K165" s="73"/>
+    </row>
+    <row r="166" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A166" s="71">
+        <v>10340023</v>
+      </c>
+      <c r="B166" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C166" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="D166" s="71" t="s">
+        <v>310</v>
+      </c>
+      <c r="E166" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="F166" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G166" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H166" s="71" t="s">
+        <v>308</v>
+      </c>
+      <c r="I166" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K166" s="73"/>
+    </row>
+    <row r="167" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A167" s="71">
+        <v>10340004</v>
+      </c>
+      <c r="B167" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C167" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D167" s="71" t="s">
+        <v>312</v>
+      </c>
+      <c r="E167" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="F167" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G167" s="71" t="s">
+        <v>314</v>
+      </c>
+      <c r="H167" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="I167" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K167" s="73"/>
+    </row>
+    <row r="168" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A168" s="71">
+        <v>10340014</v>
+      </c>
+      <c r="B168" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C168" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="D168" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E168" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="F168" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G168" s="71" t="s">
+        <v>314</v>
+      </c>
+      <c r="H168" s="71"/>
+      <c r="I168" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K168" s="73"/>
+    </row>
+    <row r="169" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A169" s="71">
+        <v>10340024</v>
+      </c>
+      <c r="B169" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C169" s="71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D169" s="71" t="s">
+        <v>317</v>
+      </c>
+      <c r="E169" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="F169" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G169" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H169" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="I169" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K169" s="73"/>
+    </row>
+    <row r="170" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A170" s="71">
+        <v>10340005</v>
+      </c>
+      <c r="B170" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C170" s="71" t="s">
+        <v>318</v>
+      </c>
+      <c r="D170" s="71" t="s">
+        <v>319</v>
+      </c>
+      <c r="E170" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F170" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G170" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="H170" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="I170" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K170" s="73"/>
+    </row>
+    <row r="171" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A171" s="71">
+        <v>10340015</v>
+      </c>
+      <c r="B171" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C171" s="71" t="s">
+        <v>323</v>
+      </c>
+      <c r="D171" s="71" t="s">
+        <v>324</v>
+      </c>
+      <c r="E171" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F171" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G171" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="H171" s="71"/>
+      <c r="I171" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K171" s="73"/>
+    </row>
+    <row r="172" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A172" s="71">
+        <v>10340025</v>
+      </c>
+      <c r="B172" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C172" s="71" t="s">
+        <v>318</v>
+      </c>
+      <c r="D172" s="71" t="s">
+        <v>324</v>
+      </c>
+      <c r="E172" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F172" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G172" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H172" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="I172" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K172" s="73"/>
+    </row>
+    <row r="173" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A173" s="71">
+        <v>10340006</v>
+      </c>
+      <c r="B173" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C173" s="71" t="s">
+        <v>325</v>
+      </c>
+      <c r="D173" s="71" t="s">
+        <v>326</v>
+      </c>
+      <c r="E173" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F173" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G173" s="71" t="s">
+        <v>327</v>
+      </c>
+      <c r="H173" s="71" t="s">
+        <v>328</v>
+      </c>
+      <c r="I173" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K173" s="73"/>
+    </row>
+    <row r="174" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A174" s="71">
+        <v>10340016</v>
+      </c>
+      <c r="B174" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C174" s="71" t="s">
+        <v>329</v>
+      </c>
+      <c r="D174" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="E174" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F174" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G174" s="71" t="s">
+        <v>327</v>
+      </c>
+      <c r="H174" s="71"/>
+      <c r="I174" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K174" s="73"/>
+    </row>
+    <row r="175" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A175" s="71">
+        <v>10340026</v>
+      </c>
+      <c r="B175" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C175" s="71" t="s">
+        <v>325</v>
+      </c>
+      <c r="D175" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="E175" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F175" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G175" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H175" s="71" t="s">
+        <v>328</v>
+      </c>
+      <c r="I175" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K175" s="73"/>
+    </row>
+    <row r="176" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A176" s="71">
+        <v>10340007</v>
+      </c>
+      <c r="B176" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C176" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="D176" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="E176" s="71" t="s">
+        <v>332</v>
+      </c>
+      <c r="F176" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G176" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H176" s="15"/>
+      <c r="I176" s="71" t="s">
         <v>274</v>
       </c>
-      <c r="D145" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="E145" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F145" s="8" t="s">
+      <c r="K176" s="73"/>
+    </row>
+    <row r="177" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A177" s="71">
+        <v>10340008</v>
+      </c>
+      <c r="B177" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C177" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="D177" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="E177" s="71" t="s">
+        <v>243</v>
+      </c>
+      <c r="F177" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="G145" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="H145" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="I145" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="K145" s="59"/>
-    </row>
-    <row r="146" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A146" s="8">
-        <v>10250001</v>
-      </c>
-      <c r="B146" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F146" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H146" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I146" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="K146" s="59"/>
-    </row>
-    <row r="147" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A147" s="8">
-        <v>10250002</v>
-      </c>
-      <c r="B147" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F147" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H147" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I147" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K147" s="59"/>
-    </row>
-    <row r="148" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A148" s="8">
-        <v>10250011</v>
-      </c>
-      <c r="B148" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="H148" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I148" s="8" t="s">
+      <c r="G177" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H177" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="I177" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="K148" s="59"/>
-    </row>
-    <row r="149" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A149" s="8">
-        <v>10250021</v>
-      </c>
-      <c r="B149" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="H149" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I149" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K149" s="59"/>
-    </row>
-    <row r="150" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A150" s="8">
-        <v>10250031</v>
-      </c>
-      <c r="B150" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I150" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="K150" s="59"/>
-    </row>
-    <row r="151" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A151" s="8">
-        <v>10250032</v>
-      </c>
-      <c r="B151" s="8">
-        <v>102500</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="I151" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K151" s="59"/>
-    </row>
-    <row r="152" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="K152" s="59"/>
+      <c r="K177" s="72"/>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="E184" s="74"/>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="E186" s="75"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6804,24 +7780,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="D1" t="s">
-        <v>287</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6829,16 +7805,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="F3" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6846,16 +7822,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6863,16 +7839,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>347</v>
       </c>
       <c r="F5" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6880,7 +7856,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6888,7 +7864,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6896,7 +7872,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6904,7 +7880,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6912,7 +7888,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6920,7 +7896,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6928,7 +7904,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6936,7 +7912,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6944,7 +7920,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6952,7 +7928,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6960,7 +7936,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>309</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6968,7 +7944,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6976,7 +7952,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6984,7 +7960,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6992,7 +7968,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7000,7 +7976,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7008,7 +7984,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7016,7 +7992,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7024,7 +8000,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7032,7 +8008,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7040,7 +8016,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>319</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7048,7 +8024,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7056,7 +8032,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7064,7 +8040,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7072,7 +8048,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7080,7 +8056,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7088,7 +8064,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7096,7 +8072,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7104,7 +8080,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7112,7 +8088,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7120,7 +8096,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7128,7 +8104,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7136,7 +8112,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7144,7 +8120,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7152,7 +8128,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>333</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7160,7 +8136,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7168,7 +8144,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7176,7 +8152,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7184,7 +8160,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7192,7 +8168,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7200,7 +8176,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7208,7 +8184,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7216,7 +8192,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="393">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1166,6 +1166,9 @@
   </si>
   <si>
     <t>1_2_3_4_5_6_7</t>
+  </si>
+  <si>
+    <t>改出一个空格符号</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -7756,6 +7759,34 @@
       </c>
       <c r="K177" s="72"/>
     </row>
+    <row r="178" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A178" s="71">
+        <v>10340009</v>
+      </c>
+      <c r="B178" s="71">
+        <v>103400</v>
+      </c>
+      <c r="C178" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="D178" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="E178" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="F178" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G178" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="H178" s="71"/>
+      <c r="I178" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="K178" s="72"/>
+    </row>
     <row r="184" spans="1:11">
       <c r="E184" s="74"/>
     </row>
@@ -7780,24 +7811,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" t="s">
         <v>339</v>
       </c>
-      <c r="D2" t="s">
-        <v>338</v>
-      </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7805,16 +7836,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7822,16 +7853,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7839,16 +7870,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7856,7 +7887,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7864,7 +7895,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7872,7 +7903,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7880,7 +7911,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7888,7 +7919,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7896,7 +7927,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7904,7 +7935,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7912,7 +7943,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7920,7 +7951,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7928,7 +7959,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7936,7 +7967,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7944,7 +7975,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7952,7 +7983,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7960,7 +7991,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7968,7 +7999,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7976,7 +8007,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7984,7 +8015,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7992,7 +8023,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8000,7 +8031,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8008,7 +8039,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8016,7 +8047,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -8024,7 +8055,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -8032,7 +8063,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -8040,7 +8071,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -8048,7 +8079,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -8056,7 +8087,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -8064,7 +8095,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8072,7 +8103,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8080,7 +8111,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8088,7 +8119,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8096,7 +8127,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8104,7 +8135,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8112,7 +8143,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8120,7 +8151,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8128,7 +8159,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8136,7 +8167,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8144,7 +8175,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8152,7 +8183,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8160,7 +8191,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8168,7 +8199,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8176,7 +8207,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8184,7 +8215,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8192,7 +8223,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="405">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1169,6 +1169,42 @@
   </si>
   <si>
     <t>改出一个空格符号</t>
+  </si>
+  <si>
+    <t>改出奖金符号</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1</t>
+  </si>
+  <si>
+    <t>7_9_10_11_12</t>
+  </si>
+  <si>
+    <t>0_500|1_150|2_150|3_100|4_80|5_15|6_5</t>
+  </si>
+  <si>
+    <t>10_5000|20_3000|30_1000|40_500|50_400|80_50|100_40|200_10</t>
+  </si>
+  <si>
+    <t>金钱兔模式</t>
+  </si>
+  <si>
+    <t>0_100|1_350|2_350|3_100|4_80|5_15|6_5</t>
+  </si>
+  <si>
+    <t>9_10|10_5|11_2|12_1</t>
+  </si>
+  <si>
+    <t>7_9</t>
+  </si>
+  <si>
+    <t>改出隐藏符号</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖符号</t>
+  </si>
+  <si>
+    <t>4_1_1|12_1_1</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1604,6 +1640,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1617,12 +1659,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1813,27 +1849,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF00B050"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF00B050"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF00B050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF00B050"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1958,7 +1979,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1970,34 +1991,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2085,7 +2106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2102,25 +2123,26 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2157,14 +2179,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2178,12 +2200,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2205,13 +2227,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2219,6 +2234,13 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2256,8 +2278,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
@@ -2588,7 +2612,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N186"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -2600,8 +2624,8 @@
     <col min="7" max="7" width="27.7833333333333" customWidth="1"/>
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="25.5916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="16" customWidth="1"/>
+    <col min="10" max="10" width="40.5833333333333" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="17" customWidth="1"/>
     <col min="12" max="12" width="9.375"/>
     <col min="13" max="13" width="12.5"/>
     <col min="14" max="14" width="9.375"/>
@@ -2609,121 +2633,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="F2" s="18"/>
+      <c r="G2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="20"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="18">
         <v>100100</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2732,16 +2756,16 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="26" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2749,16 +2773,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <v>100100</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2767,29 +2791,29 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="26"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <v>100100</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="29" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -2798,27 +2822,27 @@
       <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="76" t="s">
+      <c r="H7" s="29"/>
+      <c r="I7" s="77" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="29"/>
+      <c r="K7" s="30"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <v>100100</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2827,27 +2851,27 @@
       <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="29"/>
       <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="30"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="31"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <v>100100</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="29" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2856,27 +2880,27 @@
       <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="29"/>
       <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="30"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="31"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <v>100100</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="29" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2885,27 +2909,27 @@
       <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="29"/>
       <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="30"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="31"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <v>100100</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="29" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2914,27 +2938,27 @@
       <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="29"/>
       <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="30"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="31"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <v>100100</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="29" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2943,16 +2967,16 @@
       <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="29" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="30" t="s">
+      <c r="K12" s="31" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2960,16 +2984,16 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="18">
         <v>100100</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="34" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -2978,14 +3002,14 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="34" t="s">
+      <c r="K13" s="35" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2993,16 +3017,16 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="18">
         <v>100100</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="32" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="34" t="s">
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -3011,147 +3035,147 @@
       <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="77" t="s">
+      <c r="H14" s="34"/>
+      <c r="I14" s="78" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="34"/>
+      <c r="K14" s="35"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <v>100100</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="37"/>
-      <c r="I15" s="36" t="s">
+      <c r="H15" s="38"/>
+      <c r="I15" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="38"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="39"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="18">
         <v>100100</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="78" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="42"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="43"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="18">
         <v>100100</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="40" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="43" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A18" s="44">
+      <c r="A18" s="45">
         <v>10010061</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="19">
         <v>100100</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G18" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="44" t="s">
+      <c r="H18" s="19"/>
+      <c r="I18" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="44"/>
-      <c r="K18" s="47"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="48"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="49">
         <v>100100</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="49" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -3160,27 +3184,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="48"/>
-      <c r="I19" s="79" t="s">
+      <c r="H19" s="49"/>
+      <c r="I19" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="50"/>
+      <c r="K19" s="51"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="48">
+      <c r="B20" s="49">
         <v>100100</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="E20" s="49" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -3189,27 +3213,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="48"/>
+      <c r="H20" s="49"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="48"/>
-      <c r="K20" s="51"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="52"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="48">
+      <c r="B21" s="49">
         <v>100100</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -3218,27 +3242,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="48"/>
+      <c r="H21" s="49"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="48"/>
-      <c r="K21" s="51"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="52"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="49">
         <v>100100</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="49" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -3247,27 +3271,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="48"/>
+      <c r="H22" s="49"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="48"/>
-      <c r="K22" s="51"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="52"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="49">
         <v>100100</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="48" t="s">
+      <c r="E23" s="49" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -3276,27 +3300,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="48"/>
+      <c r="H23" s="49"/>
       <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="48"/>
-      <c r="K23" s="51"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="52"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="48">
+      <c r="B24" s="49">
         <v>100100</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="49" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -3305,16 +3329,16 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="48" t="s">
+      <c r="H24" s="49" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="J24" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="51" t="s">
+      <c r="K24" s="52" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3322,14 +3346,14 @@
       <c r="A25" s="15">
         <v>10010091</v>
       </c>
-      <c r="B25" s="52">
+      <c r="B25" s="53">
         <v>100100</v>
       </c>
-      <c r="C25" s="52"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="53" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="15" t="s">
@@ -3338,29 +3362,29 @@
       <c r="G25" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="53" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="52"/>
-      <c r="K25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="54"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="18">
         <v>100300</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="24" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="24" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3369,29 +3393,29 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="24" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="26"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="18">
         <v>100300</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="24" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3400,29 +3424,29 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="24" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="24"/>
-      <c r="K27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="26"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="18">
         <v>100300</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="24" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3431,28 +3455,28 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="23"/>
-      <c r="I28" s="80" t="s">
+      <c r="H28" s="24"/>
+      <c r="I28" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
-      <c r="K28" s="51"/>
+      <c r="K28" s="52"/>
       <c r="L28"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A29" s="1">
         <v>10030041</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="18">
         <v>100300</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="24" t="s">
         <v>104</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="24" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3461,28 +3485,28 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="80" t="s">
+      <c r="H29" s="24"/>
+      <c r="I29" s="81" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="51"/>
+      <c r="K29" s="52"/>
       <c r="L29"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A30" s="1">
         <v>10030042</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="18">
         <v>100300</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="24" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="24" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3491,28 +3515,28 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="23"/>
-      <c r="I30" s="80" t="s">
+      <c r="H30" s="24"/>
+      <c r="I30" s="81" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="51"/>
+      <c r="K30" s="52"/>
       <c r="L30"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A31" s="1">
         <v>10030043</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="18">
         <v>100300</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="24" t="s">
         <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="24" t="s">
         <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3521,28 +3545,28 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="23"/>
-      <c r="I31" s="80" t="s">
+      <c r="H31" s="24"/>
+      <c r="I31" s="81" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="51"/>
+      <c r="K31" s="52"/>
       <c r="L31"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <v>10030044</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="18">
         <v>100300</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="24" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="24" t="s">
         <v>108</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -3551,28 +3575,28 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="80" t="s">
+      <c r="H32" s="24"/>
+      <c r="I32" s="81" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
-      <c r="K32" s="51"/>
+      <c r="K32" s="52"/>
       <c r="L32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="18">
         <v>100300</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="24" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="24" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -3581,30 +3605,30 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="23"/>
-      <c r="I33" s="80" t="s">
+      <c r="H33" s="24"/>
+      <c r="I33" s="81" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="54"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>10030050</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="18">
         <v>100300</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="24" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="24" t="s">
         <v>112</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -3613,217 +3637,217 @@
       <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="23"/>
-      <c r="I34" s="80" t="s">
+      <c r="H34" s="24"/>
+      <c r="I34" s="81" t="s">
         <v>108</v>
       </c>
       <c r="J34" s="4"/>
-      <c r="K34" s="51"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="54"/>
-      <c r="N34" s="54"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A35" s="55">
+      <c r="A35" s="56">
         <v>10070010</v>
       </c>
-      <c r="B35" s="56">
+      <c r="B35" s="57">
         <v>100700</v>
       </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="55" t="s">
+      <c r="C35" s="57"/>
+      <c r="D35" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="56" t="s">
+      <c r="E35" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="55" t="s">
+      <c r="F35" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="55" t="s">
+      <c r="G35" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="56"/>
-      <c r="I35" s="55" t="s">
+      <c r="H35" s="57"/>
+      <c r="I35" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="55"/>
-      <c r="K35" s="57"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="58"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A36" s="55">
+      <c r="A36" s="56">
         <v>10070011</v>
       </c>
-      <c r="B36" s="56">
+      <c r="B36" s="57">
         <v>100700</v>
       </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="55" t="s">
+      <c r="C36" s="57"/>
+      <c r="D36" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="55" t="s">
+      <c r="F36" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="55" t="s">
+      <c r="G36" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="56"/>
-      <c r="I36" s="55" t="s">
+      <c r="H36" s="57"/>
+      <c r="I36" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="55"/>
-      <c r="K36" s="57"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="58"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A37" s="55">
+      <c r="A37" s="56">
         <v>10070012</v>
       </c>
-      <c r="B37" s="56">
+      <c r="B37" s="57">
         <v>100700</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="55" t="s">
+      <c r="C37" s="57"/>
+      <c r="D37" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="55" t="s">
+      <c r="F37" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="55" t="s">
+      <c r="G37" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="56"/>
-      <c r="I37" s="55" t="s">
+      <c r="H37" s="57"/>
+      <c r="I37" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="55"/>
-      <c r="K37" s="57"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="58"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A38" s="58">
+      <c r="A38" s="59">
         <v>10070021</v>
       </c>
-      <c r="B38" s="59">
+      <c r="B38" s="60">
         <v>100700</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="58" t="s">
+      <c r="C38" s="60"/>
+      <c r="D38" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="58" t="s">
+      <c r="F38" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="58" t="s">
+      <c r="G38" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="59"/>
-      <c r="I38" s="58" t="s">
+      <c r="H38" s="60"/>
+      <c r="I38" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="58"/>
-      <c r="K38" s="60"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="61"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A39" s="58">
+      <c r="A39" s="59">
         <v>10070022</v>
       </c>
-      <c r="B39" s="59">
+      <c r="B39" s="60">
         <v>100700</v>
       </c>
-      <c r="C39" s="59"/>
-      <c r="D39" s="58" t="s">
+      <c r="C39" s="60"/>
+      <c r="D39" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="59" t="s">
+      <c r="E39" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="G39" s="58" t="s">
+      <c r="G39" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="59"/>
-      <c r="I39" s="58" t="s">
+      <c r="H39" s="60"/>
+      <c r="I39" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="58"/>
-      <c r="K39" s="60"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="61"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A40" s="58">
+      <c r="A40" s="59">
         <v>10070023</v>
       </c>
-      <c r="B40" s="59">
+      <c r="B40" s="60">
         <v>100700</v>
       </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="60"/>
+      <c r="D40" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="58" t="s">
+      <c r="F40" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="58" t="s">
+      <c r="G40" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="59"/>
-      <c r="I40" s="58" t="s">
+      <c r="H40" s="60"/>
+      <c r="I40" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="58"/>
-      <c r="K40" s="60"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="61"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A41" s="58">
+      <c r="A41" s="59">
         <v>10070024</v>
       </c>
-      <c r="B41" s="59">
+      <c r="B41" s="60">
         <v>100700</v>
       </c>
-      <c r="C41" s="59"/>
-      <c r="D41" s="58" t="s">
+      <c r="C41" s="60"/>
+      <c r="D41" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="59" t="s">
+      <c r="E41" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="58" t="s">
+      <c r="F41" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="59"/>
-      <c r="I41" s="58" t="s">
+      <c r="H41" s="60"/>
+      <c r="I41" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="58"/>
-      <c r="K41" s="60"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="61"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="3">
         <v>10070030</v>
       </c>
-      <c r="B42" s="61">
+      <c r="B42" s="62">
         <v>100700</v>
       </c>
-      <c r="C42" s="61"/>
+      <c r="C42" s="62"/>
       <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="62" t="s">
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -3832,25 +3856,25 @@
       <c r="G42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="61"/>
-      <c r="I42" s="81" t="s">
+      <c r="H42" s="62"/>
+      <c r="I42" s="82" t="s">
         <v>134</v>
       </c>
       <c r="J42" s="3"/>
-      <c r="K42" s="62"/>
+      <c r="K42" s="63"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="3">
         <v>10070031</v>
       </c>
-      <c r="B43" s="61">
+      <c r="B43" s="62">
         <v>100700</v>
       </c>
-      <c r="C43" s="61"/>
+      <c r="C43" s="62"/>
       <c r="D43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="62" t="s">
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -3859,27 +3883,27 @@
       <c r="G43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="61" t="s">
+      <c r="H43" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="81" t="s">
+      <c r="I43" s="82" t="s">
         <v>138</v>
       </c>
       <c r="J43" s="3"/>
-      <c r="K43" s="62"/>
+      <c r="K43" s="63"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="3">
         <v>10070032</v>
       </c>
-      <c r="B44" s="61">
+      <c r="B44" s="62">
         <v>100700</v>
       </c>
-      <c r="C44" s="61"/>
+      <c r="C44" s="62"/>
       <c r="D44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="61" t="s">
+      <c r="E44" s="62" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -3888,26 +3912,26 @@
       <c r="G44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="61" t="s">
+      <c r="H44" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="81" t="s">
+      <c r="I44" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K44" s="62"/>
+      <c r="K44" s="63"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="3">
         <v>10070033</v>
       </c>
-      <c r="B45" s="61">
+      <c r="B45" s="62">
         <v>100700</v>
       </c>
-      <c r="C45" s="61"/>
+      <c r="C45" s="62"/>
       <c r="D45" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="62" t="s">
         <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -3916,26 +3940,26 @@
       <c r="G45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H45" s="61" t="s">
+      <c r="H45" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="81" t="s">
+      <c r="I45" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K45" s="62"/>
+      <c r="K45" s="63"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="3">
         <v>10070034</v>
       </c>
-      <c r="B46" s="61">
+      <c r="B46" s="62">
         <v>100700</v>
       </c>
-      <c r="C46" s="61"/>
+      <c r="C46" s="62"/>
       <c r="D46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="62" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -3944,26 +3968,26 @@
       <c r="G46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="61" t="s">
+      <c r="H46" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="I46" s="81" t="s">
+      <c r="I46" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K46" s="62"/>
+      <c r="K46" s="63"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="3">
         <v>10070035</v>
       </c>
-      <c r="B47" s="61">
+      <c r="B47" s="62">
         <v>100700</v>
       </c>
-      <c r="C47" s="61"/>
+      <c r="C47" s="62"/>
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="61" t="s">
+      <c r="E47" s="62" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -3972,26 +3996,26 @@
       <c r="G47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="61" t="s">
+      <c r="H47" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="81" t="s">
+      <c r="I47" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K47" s="62"/>
+      <c r="K47" s="63"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="3">
         <v>10070036</v>
       </c>
-      <c r="B48" s="61">
+      <c r="B48" s="62">
         <v>100700</v>
       </c>
-      <c r="C48" s="61"/>
+      <c r="C48" s="62"/>
       <c r="D48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="61" t="s">
+      <c r="E48" s="62" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -4000,26 +4024,26 @@
       <c r="G48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="61" t="s">
+      <c r="H48" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="81" t="s">
+      <c r="I48" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K48" s="62"/>
+      <c r="K48" s="63"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A49" s="3">
         <v>10070037</v>
       </c>
-      <c r="B49" s="61">
+      <c r="B49" s="62">
         <v>100700</v>
       </c>
-      <c r="C49" s="61"/>
+      <c r="C49" s="62"/>
       <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="61" t="s">
+      <c r="E49" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -4028,26 +4052,26 @@
       <c r="G49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="61" t="s">
+      <c r="H49" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="I49" s="81" t="s">
+      <c r="I49" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K49" s="62"/>
+      <c r="K49" s="63"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A50" s="3">
         <v>10070038</v>
       </c>
-      <c r="B50" s="61">
+      <c r="B50" s="62">
         <v>100700</v>
       </c>
-      <c r="C50" s="61"/>
+      <c r="C50" s="62"/>
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="62" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -4056,25 +4080,25 @@
       <c r="G50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="61" t="s">
+      <c r="H50" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="81" t="s">
+      <c r="I50" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K50" s="62"/>
+      <c r="K50" s="63"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
         <v>10120011</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="24">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="23" t="s">
+      <c r="E51" s="24" t="s">
         <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -4083,26 +4107,26 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="23" t="s">
+      <c r="H51" s="24" t="s">
         <v>160</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J51" s="4"/>
-      <c r="K51" s="26"/>
+      <c r="K51" s="27"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
         <v>10120021</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B52" s="24">
         <v>101200</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="23" t="s">
+      <c r="E52" s="24" t="s">
         <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -4111,27 +4135,27 @@
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="23"/>
-      <c r="I52" s="80" t="s">
+      <c r="H52" s="24"/>
+      <c r="I52" s="81" t="s">
         <v>109</v>
       </c>
       <c r="J52" s="4"/>
-      <c r="K52" s="26"/>
+      <c r="K52" s="27"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
         <v>10120031</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="24">
         <v>101200</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="64" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="23" t="s">
+      <c r="E53" s="24" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -4140,29 +4164,29 @@
       <c r="G53" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="23" t="s">
+      <c r="H53" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I53" s="80" t="s">
+      <c r="I53" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
-      <c r="K53" s="26"/>
+      <c r="K53" s="27"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
         <v>10120032</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="24">
         <v>101200</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="64" t="s">
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="24" t="s">
         <v>140</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -4171,29 +4195,29 @@
       <c r="G54" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="23" t="s">
+      <c r="H54" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="80" t="s">
+      <c r="I54" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="26"/>
+      <c r="K54" s="27"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
         <v>10120033</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="24">
         <v>101200</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="64" t="s">
         <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="24" t="s">
         <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -4202,29 +4226,29 @@
       <c r="G55" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H55" s="23" t="s">
+      <c r="H55" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I55" s="80" t="s">
+      <c r="I55" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J55" s="4"/>
-      <c r="K55" s="26"/>
+      <c r="K55" s="27"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
         <v>10120034</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B56" s="24">
         <v>101200</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="64" t="s">
         <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="23" t="s">
+      <c r="E56" s="24" t="s">
         <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -4233,29 +4257,29 @@
       <c r="G56" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H56" s="23" t="s">
+      <c r="H56" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I56" s="80" t="s">
+      <c r="I56" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="26"/>
+      <c r="K56" s="27"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
         <v>10120035</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B57" s="24">
         <v>101200</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="64" t="s">
         <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="24" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -4264,29 +4288,29 @@
       <c r="G57" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="23" t="s">
+      <c r="H57" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="80" t="s">
+      <c r="I57" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J57" s="4"/>
-      <c r="K57" s="26"/>
+      <c r="K57" s="27"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="4">
         <v>10120036</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="24">
         <v>101200</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="64" t="s">
         <v>172</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="E58" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -4295,29 +4319,29 @@
       <c r="G58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="23" t="s">
+      <c r="H58" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="80" t="s">
+      <c r="I58" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="26"/>
+      <c r="K58" s="27"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
         <v>10120041</v>
       </c>
-      <c r="B59" s="63">
+      <c r="B59" s="64">
         <v>101200</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="64" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="63" t="s">
+      <c r="E59" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -4326,29 +4350,29 @@
       <c r="G59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="63">
+      <c r="H59" s="64">
         <v>10</v>
       </c>
-      <c r="I59" s="82" t="s">
+      <c r="I59" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="65"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
         <v>10120042</v>
       </c>
-      <c r="B60" s="63">
+      <c r="B60" s="64">
         <v>101200</v>
       </c>
-      <c r="C60" s="63" t="s">
+      <c r="C60" s="64" t="s">
         <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="63" t="s">
+      <c r="E60" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -4357,29 +4381,29 @@
       <c r="G60" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H60" s="63">
+      <c r="H60" s="64">
         <v>10</v>
       </c>
-      <c r="I60" s="82" t="s">
+      <c r="I60" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="64"/>
+      <c r="K60" s="65"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
         <v>10120043</v>
       </c>
-      <c r="B61" s="63">
+      <c r="B61" s="64">
         <v>101200</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="64" t="s">
         <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="63" t="s">
+      <c r="E61" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
@@ -4388,29 +4412,29 @@
       <c r="G61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H61" s="63">
+      <c r="H61" s="64">
         <v>10</v>
       </c>
-      <c r="I61" s="82" t="s">
+      <c r="I61" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="64"/>
+      <c r="K61" s="65"/>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
         <v>10120044</v>
       </c>
-      <c r="B62" s="63">
+      <c r="B62" s="64">
         <v>101200</v>
       </c>
-      <c r="C62" s="63" t="s">
+      <c r="C62" s="64" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E62" s="63" t="s">
+      <c r="E62" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -4419,29 +4443,29 @@
       <c r="G62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H62" s="63">
+      <c r="H62" s="64">
         <v>10</v>
       </c>
-      <c r="I62" s="82" t="s">
+      <c r="I62" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="64"/>
+      <c r="K62" s="65"/>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
         <v>10120045</v>
       </c>
-      <c r="B63" s="63">
+      <c r="B63" s="64">
         <v>101200</v>
       </c>
-      <c r="C63" s="63" t="s">
+      <c r="C63" s="64" t="s">
         <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="63" t="s">
+      <c r="E63" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -4450,29 +4474,29 @@
       <c r="G63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="63">
+      <c r="H63" s="64">
         <v>10</v>
       </c>
-      <c r="I63" s="82" t="s">
+      <c r="I63" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="64"/>
+      <c r="K63" s="65"/>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
         <v>10120046</v>
       </c>
-      <c r="B64" s="63">
+      <c r="B64" s="64">
         <v>101200</v>
       </c>
-      <c r="C64" s="63" t="s">
+      <c r="C64" s="64" t="s">
         <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="63" t="s">
+      <c r="E64" s="64" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -4481,29 +4505,29 @@
       <c r="G64" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H64" s="63">
+      <c r="H64" s="64">
         <v>10</v>
       </c>
-      <c r="I64" s="82" t="s">
+      <c r="I64" s="83" t="s">
         <v>107</v>
       </c>
       <c r="J64" s="5"/>
-      <c r="K64" s="64"/>
+      <c r="K64" s="65"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
         <v>10120051</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="24">
         <v>101200</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="64" t="s">
         <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="E65" s="24" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4512,29 +4536,29 @@
       <c r="G65" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="23" t="s">
+      <c r="H65" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="80" t="s">
+      <c r="I65" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="26"/>
+      <c r="K65" s="27"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
         <v>10120052</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="24">
         <v>101200</v>
       </c>
-      <c r="C66" s="63" t="s">
+      <c r="C66" s="64" t="s">
         <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E66" s="23" t="s">
+      <c r="E66" s="24" t="s">
         <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4543,29 +4567,29 @@
       <c r="G66" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="23" t="s">
+      <c r="H66" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I66" s="80" t="s">
+      <c r="I66" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J66" s="4"/>
-      <c r="K66" s="26"/>
+      <c r="K66" s="27"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
         <v>10120053</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B67" s="24">
         <v>101200</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="64" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="23" t="s">
+      <c r="E67" s="24" t="s">
         <v>193</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4574,29 +4598,29 @@
       <c r="G67" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="23" t="s">
+      <c r="H67" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I67" s="80" t="s">
+      <c r="I67" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J67" s="4"/>
-      <c r="K67" s="26"/>
+      <c r="K67" s="27"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
         <v>10120054</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B68" s="24">
         <v>101200</v>
       </c>
-      <c r="C68" s="63" t="s">
+      <c r="C68" s="64" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="23" t="s">
+      <c r="E68" s="24" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4605,29 +4629,29 @@
       <c r="G68" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="23" t="s">
+      <c r="H68" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="80" t="s">
+      <c r="I68" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="26"/>
+      <c r="K68" s="27"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
         <v>10120055</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="24">
         <v>101200</v>
       </c>
-      <c r="C69" s="63" t="s">
+      <c r="C69" s="64" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="23" t="s">
+      <c r="E69" s="24" t="s">
         <v>196</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -4636,29 +4660,29 @@
       <c r="G69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="23" t="s">
+      <c r="H69" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="80" t="s">
+      <c r="I69" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="26"/>
+      <c r="K69" s="27"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="4">
         <v>10120056</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B70" s="24">
         <v>101200</v>
       </c>
-      <c r="C70" s="63" t="s">
+      <c r="C70" s="64" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="23" t="s">
+      <c r="E70" s="24" t="s">
         <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -4667,29 +4691,29 @@
       <c r="G70" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H70" s="23" t="s">
+      <c r="H70" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="80" t="s">
+      <c r="I70" s="81" t="s">
         <v>192</v>
       </c>
       <c r="J70" s="4"/>
-      <c r="K70" s="26"/>
+      <c r="K70" s="27"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
         <v>10120061</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B71" s="24">
         <v>101200</v>
       </c>
-      <c r="C71" s="33" t="s">
+      <c r="C71" s="34" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="33" t="s">
+      <c r="E71" s="34" t="s">
         <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -4698,29 +4722,29 @@
       <c r="G71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="33" t="s">
+      <c r="H71" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="77" t="s">
+      <c r="I71" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="34"/>
+      <c r="K71" s="35"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
         <v>10120062</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B72" s="24">
         <v>101200</v>
       </c>
-      <c r="C72" s="33" t="s">
+      <c r="C72" s="34" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="33" t="s">
+      <c r="E72" s="34" t="s">
         <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -4729,29 +4753,29 @@
       <c r="G72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H72" s="33" t="s">
+      <c r="H72" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I72" s="77" t="s">
+      <c r="I72" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J72" s="6"/>
-      <c r="K72" s="34"/>
+      <c r="K72" s="35"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
         <v>10120063</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="24">
         <v>101200</v>
       </c>
-      <c r="C73" s="33" t="s">
+      <c r="C73" s="34" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="33" t="s">
+      <c r="E73" s="34" t="s">
         <v>203</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -4760,29 +4784,29 @@
       <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H73" s="33" t="s">
+      <c r="H73" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I73" s="77" t="s">
+      <c r="I73" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="34"/>
+      <c r="K73" s="35"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <v>10120064</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B74" s="24">
         <v>101200</v>
       </c>
-      <c r="C74" s="33" t="s">
+      <c r="C74" s="34" t="s">
         <v>204</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="34" t="s">
         <v>205</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -4791,29 +4815,29 @@
       <c r="G74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="33" t="s">
+      <c r="H74" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I74" s="77" t="s">
+      <c r="I74" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="34"/>
+      <c r="K74" s="35"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <v>10120065</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B75" s="24">
         <v>101200</v>
       </c>
-      <c r="C75" s="33" t="s">
+      <c r="C75" s="34" t="s">
         <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="33" t="s">
+      <c r="E75" s="34" t="s">
         <v>206</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -4822,29 +4846,29 @@
       <c r="G75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="33" t="s">
+      <c r="H75" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I75" s="77" t="s">
+      <c r="I75" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="34"/>
+      <c r="K75" s="35"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <v>10120066</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B76" s="24">
         <v>101200</v>
       </c>
-      <c r="C76" s="33" t="s">
+      <c r="C76" s="34" t="s">
         <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="33" t="s">
+      <c r="E76" s="34" t="s">
         <v>207</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -4853,29 +4877,29 @@
       <c r="G76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H76" s="33" t="s">
+      <c r="H76" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="77" t="s">
+      <c r="I76" s="78" t="s">
         <v>201</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="34"/>
+      <c r="K76" s="35"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
         <v>10140001</v>
       </c>
-      <c r="B77" s="61">
+      <c r="B77" s="62">
         <v>101400</v>
       </c>
-      <c r="C77" s="61" t="s">
+      <c r="C77" s="62" t="s">
         <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="61" t="s">
+      <c r="E77" s="62" t="s">
         <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -4884,28 +4908,28 @@
       <c r="G77" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="28" t="s">
+      <c r="H77" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="I77" s="81" t="s">
+      <c r="I77" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="K77" s="62"/>
+      <c r="K77" s="63"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="3">
         <v>10140011</v>
       </c>
-      <c r="B78" s="61">
+      <c r="B78" s="62">
         <v>101400</v>
       </c>
-      <c r="C78" s="61" t="s">
+      <c r="C78" s="62" t="s">
         <v>208</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="61" t="s">
+      <c r="E78" s="62" t="s">
         <v>140</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -4914,28 +4938,28 @@
       <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="28" t="s">
+      <c r="H78" s="29" t="s">
         <v>211</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K78" s="62"/>
+      <c r="K78" s="63"/>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="7">
         <v>10140021</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="29">
         <v>101400</v>
       </c>
-      <c r="C79" s="28" t="s">
+      <c r="C79" s="29" t="s">
         <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="28" t="s">
+      <c r="E79" s="29" t="s">
         <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -4944,28 +4968,28 @@
       <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="28" t="s">
+      <c r="H79" s="29" t="s">
         <v>143</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K79" s="29"/>
+      <c r="K79" s="30"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
         <v>10140022</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="29">
         <v>101400</v>
       </c>
-      <c r="C80" s="28" t="s">
+      <c r="C80" s="29" t="s">
         <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="28" t="s">
+      <c r="E80" s="29" t="s">
         <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -4974,28 +4998,28 @@
       <c r="G80" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="28" t="s">
+      <c r="H80" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I80" s="81" t="s">
+      <c r="I80" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="K80" s="29"/>
+      <c r="K80" s="30"/>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="7">
         <v>10140023</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="29">
         <v>101400</v>
       </c>
-      <c r="C81" s="28" t="s">
+      <c r="C81" s="29" t="s">
         <v>217</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="28" t="s">
+      <c r="E81" s="29" t="s">
         <v>143</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -5004,28 +5028,28 @@
       <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="28" t="s">
+      <c r="H81" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I81" s="81" t="s">
+      <c r="I81" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="K81" s="29"/>
+      <c r="K81" s="30"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="1">
         <v>10240011</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="18">
         <v>102400</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="23" t="s">
+      <c r="E82" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -5034,16 +5058,16 @@
       <c r="G82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="23" t="s">
+      <c r="H82" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J82" s="24" t="s">
+      <c r="J82" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K82" s="25" t="s">
+      <c r="K82" s="26" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5051,16 +5075,16 @@
       <c r="A83" s="1">
         <v>10240012</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="18">
         <v>102400</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="23" t="s">
+      <c r="E83" s="24" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -5069,29 +5093,29 @@
       <c r="G83" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="23" t="s">
+      <c r="H83" s="24" t="s">
         <v>26</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J83" s="4"/>
-      <c r="K83" s="26"/>
+      <c r="K83" s="27"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="1">
         <v>10240021</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="18">
         <v>102400</v>
       </c>
-      <c r="C84" s="27" t="s">
+      <c r="C84" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="28" t="s">
+      <c r="E84" s="29" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -5100,27 +5124,27 @@
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="28"/>
-      <c r="I84" s="76" t="s">
+      <c r="H84" s="29"/>
+      <c r="I84" s="77" t="s">
         <v>39</v>
       </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="29"/>
+      <c r="K84" s="30"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="1">
         <v>10240022</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="18">
         <v>102400</v>
       </c>
-      <c r="C85" s="27" t="s">
+      <c r="C85" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E85" s="28" t="s">
+      <c r="E85" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -5129,27 +5153,27 @@
       <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="28"/>
+      <c r="H85" s="29"/>
       <c r="I85" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J85" s="28"/>
-      <c r="K85" s="30"/>
+      <c r="J85" s="29"/>
+      <c r="K85" s="31"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="1">
         <v>10240023</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="18">
         <v>102400</v>
       </c>
-      <c r="C86" s="27" t="s">
+      <c r="C86" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="28" t="s">
+      <c r="E86" s="29" t="s">
         <v>46</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -5158,27 +5182,27 @@
       <c r="G86" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="28"/>
+      <c r="H86" s="29"/>
       <c r="I86" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J86" s="28"/>
-      <c r="K86" s="30"/>
+      <c r="J86" s="29"/>
+      <c r="K86" s="31"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="1">
         <v>10240024</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="18">
         <v>102400</v>
       </c>
-      <c r="C87" s="27" t="s">
+      <c r="C87" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="28" t="s">
+      <c r="E87" s="29" t="s">
         <v>51</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -5187,27 +5211,27 @@
       <c r="G87" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="28"/>
+      <c r="H87" s="29"/>
       <c r="I87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J87" s="28"/>
-      <c r="K87" s="30"/>
+      <c r="J87" s="29"/>
+      <c r="K87" s="31"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="1">
         <v>10240025</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="18">
         <v>102400</v>
       </c>
-      <c r="C88" s="27" t="s">
+      <c r="C88" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="28" t="s">
+      <c r="E88" s="29" t="s">
         <v>56</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -5216,27 +5240,27 @@
       <c r="G88" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H88" s="28"/>
+      <c r="H88" s="29"/>
       <c r="I88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="28"/>
-      <c r="K88" s="30"/>
+      <c r="J88" s="29"/>
+      <c r="K88" s="31"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="1">
         <v>10240026</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B89" s="18">
         <v>102400</v>
       </c>
-      <c r="C89" s="27" t="s">
+      <c r="C89" s="28" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="28" t="s">
+      <c r="E89" s="29" t="s">
         <v>61</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -5245,16 +5269,16 @@
       <c r="G89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H89" s="28" t="s">
+      <c r="H89" s="29" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="24" t="s">
+      <c r="J89" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K89" s="30" t="s">
+      <c r="K89" s="31" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5262,16 +5286,16 @@
       <c r="A90" s="1">
         <v>10240031</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B90" s="18">
         <v>102400</v>
       </c>
-      <c r="C90" s="31" t="s">
+      <c r="C90" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D90" s="32" t="s">
+      <c r="D90" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="33" t="s">
+      <c r="E90" s="34" t="s">
         <v>61</v>
       </c>
       <c r="F90" s="6" t="s">
@@ -5280,14 +5304,14 @@
       <c r="G90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="33"/>
+      <c r="H90" s="34"/>
       <c r="I90" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J90" s="24" t="s">
+      <c r="J90" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K90" s="34" t="s">
+      <c r="K90" s="35" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5295,16 +5319,16 @@
       <c r="A91" s="1">
         <v>10240032</v>
       </c>
-      <c r="B91" s="17">
+      <c r="B91" s="18">
         <v>102400</v>
       </c>
-      <c r="C91" s="31" t="s">
+      <c r="C91" s="32" t="s">
         <v>62</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="33" t="s">
+      <c r="E91" s="34" t="s">
         <v>67</v>
       </c>
       <c r="F91" s="6" t="s">
@@ -5313,147 +5337,147 @@
       <c r="G91" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="33"/>
-      <c r="I91" s="77" t="s">
+      <c r="H91" s="34"/>
+      <c r="I91" s="78" t="s">
         <v>39</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="34"/>
+      <c r="K91" s="35"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="1">
         <v>10240041</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B92" s="18">
         <v>102400</v>
       </c>
-      <c r="C92" s="35" t="s">
+      <c r="C92" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="36" t="s">
+      <c r="D92" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="37" t="s">
+      <c r="E92" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="36" t="s">
+      <c r="F92" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="36" t="s">
+      <c r="G92" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="H92" s="37"/>
-      <c r="I92" s="36" t="s">
+      <c r="H92" s="38"/>
+      <c r="I92" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="J92" s="36"/>
-      <c r="K92" s="38"/>
+      <c r="J92" s="37"/>
+      <c r="K92" s="39"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="1">
         <v>10240051</v>
       </c>
-      <c r="B93" s="17">
+      <c r="B93" s="18">
         <v>102400</v>
       </c>
-      <c r="C93" s="39" t="s">
+      <c r="C93" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="40" t="s">
+      <c r="D93" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="41" t="s">
+      <c r="E93" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="40" t="s">
+      <c r="F93" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="40" t="s">
+      <c r="G93" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="41"/>
-      <c r="I93" s="78" t="s">
+      <c r="H93" s="42"/>
+      <c r="I93" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="40"/>
-      <c r="K93" s="42"/>
+      <c r="J93" s="41"/>
+      <c r="K93" s="43"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="1">
         <v>10240052</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B94" s="18">
         <v>102400</v>
       </c>
-      <c r="C94" s="39" t="s">
+      <c r="C94" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="43" t="s">
+      <c r="D94" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="41" t="s">
+      <c r="E94" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="40" t="s">
+      <c r="F94" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="40" t="s">
+      <c r="G94" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="41"/>
-      <c r="I94" s="40" t="s">
+      <c r="H94" s="42"/>
+      <c r="I94" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="J94" s="24" t="s">
+      <c r="J94" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K94" s="42" t="s">
+      <c r="K94" s="43" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A95" s="44">
+      <c r="A95" s="45">
         <v>10240061</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="19">
         <v>102400</v>
       </c>
-      <c r="C95" s="45" t="s">
+      <c r="C95" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="46" t="s">
+      <c r="D95" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F95" s="44" t="s">
+      <c r="F95" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="G95" s="44" t="s">
+      <c r="G95" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="18"/>
-      <c r="I95" s="44" t="s">
+      <c r="H95" s="19"/>
+      <c r="I95" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="J95" s="44"/>
-      <c r="K95" s="47"/>
+      <c r="J95" s="45"/>
+      <c r="K95" s="48"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="2">
         <v>10240071</v>
       </c>
-      <c r="B96" s="48">
+      <c r="B96" s="49">
         <v>102400</v>
       </c>
-      <c r="C96" s="49" t="s">
+      <c r="C96" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="48" t="s">
+      <c r="E96" s="49" t="s">
         <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -5462,26 +5486,26 @@
       <c r="G96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H96" s="48"/>
-      <c r="I96" s="79" t="s">
+      <c r="H96" s="49"/>
+      <c r="I96" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="K96" s="50"/>
+      <c r="K96" s="51"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="2">
         <v>10240072</v>
       </c>
-      <c r="B97" s="48">
+      <c r="B97" s="49">
         <v>102400</v>
       </c>
-      <c r="C97" s="49" t="s">
+      <c r="C97" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="48" t="s">
+      <c r="E97" s="49" t="s">
         <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -5490,27 +5514,27 @@
       <c r="G97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="48"/>
+      <c r="H97" s="49"/>
       <c r="I97" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="48"/>
-      <c r="K97" s="51"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="52"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="2">
         <v>10240073</v>
       </c>
-      <c r="B98" s="48">
+      <c r="B98" s="49">
         <v>102400</v>
       </c>
-      <c r="C98" s="49" t="s">
+      <c r="C98" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E98" s="48" t="s">
+      <c r="E98" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -5519,27 +5543,27 @@
       <c r="G98" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="48"/>
+      <c r="H98" s="49"/>
       <c r="I98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J98" s="48"/>
-      <c r="K98" s="51"/>
+      <c r="J98" s="49"/>
+      <c r="K98" s="52"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="2">
         <v>10240074</v>
       </c>
-      <c r="B99" s="48">
+      <c r="B99" s="49">
         <v>102400</v>
       </c>
-      <c r="C99" s="49" t="s">
+      <c r="C99" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="48" t="s">
+      <c r="E99" s="49" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -5548,27 +5572,27 @@
       <c r="G99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H99" s="48"/>
+      <c r="H99" s="49"/>
       <c r="I99" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J99" s="48"/>
-      <c r="K99" s="51"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="52"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="2">
         <v>10240075</v>
       </c>
-      <c r="B100" s="48">
+      <c r="B100" s="49">
         <v>102400</v>
       </c>
-      <c r="C100" s="49" t="s">
+      <c r="C100" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="48" t="s">
+      <c r="E100" s="49" t="s">
         <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -5577,27 +5601,27 @@
       <c r="G100" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="48"/>
+      <c r="H100" s="49"/>
       <c r="I100" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J100" s="48"/>
-      <c r="K100" s="51"/>
+      <c r="J100" s="49"/>
+      <c r="K100" s="52"/>
     </row>
     <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="2">
         <v>10240076</v>
       </c>
-      <c r="B101" s="48">
+      <c r="B101" s="49">
         <v>102400</v>
       </c>
-      <c r="C101" s="49" t="s">
+      <c r="C101" s="50" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E101" s="48" t="s">
+      <c r="E101" s="49" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -5606,16 +5630,16 @@
       <c r="G101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="48" t="s">
+      <c r="H101" s="49" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J101" s="24" t="s">
+      <c r="J101" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="51" t="s">
+      <c r="K101" s="52" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5623,14 +5647,14 @@
       <c r="A102" s="15">
         <v>10240091</v>
       </c>
-      <c r="B102" s="52">
+      <c r="B102" s="53">
         <v>102400</v>
       </c>
-      <c r="C102" s="52"/>
+      <c r="C102" s="53"/>
       <c r="D102" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E102" s="52" t="s">
+      <c r="E102" s="53" t="s">
         <v>84</v>
       </c>
       <c r="F102" s="15" t="s">
@@ -5639,14 +5663,14 @@
       <c r="G102" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H102" s="52" t="s">
+      <c r="H102" s="53" t="s">
         <v>26</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J102" s="52"/>
-      <c r="K102" s="53"/>
+      <c r="J102" s="53"/>
+      <c r="K102" s="54"/>
     </row>
     <row r="103" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A103" s="8">
@@ -5670,7 +5694,7 @@
       <c r="I103" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K103" s="65"/>
+      <c r="K103" s="66"/>
     </row>
     <row r="104" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A104" s="8">
@@ -5694,7 +5718,7 @@
       <c r="I104" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K104" s="65"/>
+      <c r="K104" s="66"/>
     </row>
     <row r="105" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A105" s="8">
@@ -5718,7 +5742,7 @@
       <c r="I105" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K105" s="65"/>
+      <c r="K105" s="66"/>
     </row>
     <row r="106" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A106" s="8">
@@ -5742,7 +5766,7 @@
       <c r="I106" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K106" s="65"/>
+      <c r="K106" s="66"/>
     </row>
     <row r="107" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A107" s="8">
@@ -5766,7 +5790,7 @@
       <c r="I107" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K107" s="65"/>
+      <c r="K107" s="66"/>
     </row>
     <row r="108" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="8">
@@ -5790,7 +5814,7 @@
       <c r="I108" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K108" s="65"/>
+      <c r="K108" s="66"/>
     </row>
     <row r="109" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A109" s="8">
@@ -5814,7 +5838,7 @@
       <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K109" s="65"/>
+      <c r="K109" s="66"/>
     </row>
     <row r="110" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A110" s="8">
@@ -5835,10 +5859,10 @@
       <c r="G110" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I110" s="83" t="s">
+      <c r="I110" s="84" t="s">
         <v>134</v>
       </c>
-      <c r="K110" s="65"/>
+      <c r="K110" s="66"/>
     </row>
     <row r="111" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A111" s="8">
@@ -5865,7 +5889,7 @@
       <c r="I111" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K111" s="65"/>
+      <c r="K111" s="66"/>
     </row>
     <row r="112" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A112" s="8">
@@ -5892,7 +5916,7 @@
       <c r="I112" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K112" s="65"/>
+      <c r="K112" s="66"/>
     </row>
     <row r="113" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A113" s="8">
@@ -5919,7 +5943,7 @@
       <c r="I113" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K113" s="65"/>
+      <c r="K113" s="66"/>
     </row>
     <row r="114" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A114" s="8">
@@ -5946,7 +5970,7 @@
       <c r="I114" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K114" s="65"/>
+      <c r="K114" s="66"/>
     </row>
     <row r="115" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A115" s="8">
@@ -5973,7 +5997,7 @@
       <c r="I115" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K115" s="65"/>
+      <c r="K115" s="66"/>
     </row>
     <row r="116" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A116" s="8">
@@ -6000,7 +6024,7 @@
       <c r="I116" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K116" s="65"/>
+      <c r="K116" s="66"/>
     </row>
     <row r="117" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A117" s="8">
@@ -6027,7 +6051,7 @@
       <c r="I117" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K117" s="65"/>
+      <c r="K117" s="66"/>
     </row>
     <row r="118" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A118" s="8">
@@ -6054,7 +6078,7 @@
       <c r="I118" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K118" s="65"/>
+      <c r="K118" s="66"/>
     </row>
     <row r="119" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A119" s="8">
@@ -6084,7 +6108,7 @@
       <c r="I119" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K119" s="65"/>
+      <c r="K119" s="66"/>
     </row>
     <row r="120" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="8">
@@ -6114,7 +6138,7 @@
       <c r="I120" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K120" s="65"/>
+      <c r="K120" s="66"/>
     </row>
     <row r="121" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A121" s="9">
@@ -6144,7 +6168,7 @@
       <c r="I121" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="K121" s="66"/>
+      <c r="K121" s="67"/>
     </row>
     <row r="122" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A122" s="9">
@@ -6174,7 +6198,7 @@
       <c r="I122" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K122" s="66"/>
+      <c r="K122" s="67"/>
     </row>
     <row r="123" s="9" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A123" s="9">
@@ -6204,7 +6228,7 @@
       <c r="I123" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K123" s="66"/>
+      <c r="K123" s="67"/>
     </row>
     <row r="124" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="9">
@@ -6232,7 +6256,7 @@
       <c r="I124" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K124" s="66"/>
+      <c r="K124" s="67"/>
     </row>
     <row r="125" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="9">
@@ -6259,7 +6283,7 @@
       <c r="I125" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="K125" s="66"/>
+      <c r="K125" s="67"/>
     </row>
     <row r="126" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A126" s="9">
@@ -6287,7 +6311,7 @@
       <c r="I126" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K126" s="66"/>
+      <c r="K126" s="67"/>
     </row>
     <row r="127" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A127" s="9">
@@ -6315,7 +6339,7 @@
       <c r="I127" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K127" s="66"/>
+      <c r="K127" s="67"/>
     </row>
     <row r="128" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A128" s="9">
@@ -6339,7 +6363,7 @@
       <c r="I128" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K128" s="66"/>
+      <c r="K128" s="67"/>
     </row>
     <row r="129" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A129" s="9">
@@ -6363,7 +6387,7 @@
       <c r="I129" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K129" s="66"/>
+      <c r="K129" s="67"/>
     </row>
     <row r="130" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A130" s="9">
@@ -6384,7 +6408,7 @@
       <c r="I130" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K130" s="66"/>
+      <c r="K130" s="67"/>
     </row>
     <row r="131" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A131" s="9">
@@ -6405,7 +6429,7 @@
       <c r="I131" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K131" s="66"/>
+      <c r="K131" s="67"/>
     </row>
     <row r="132" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A132" s="10">
@@ -6435,7 +6459,7 @@
       <c r="I132" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K132" s="67"/>
+      <c r="K132" s="68"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A133" s="10">
@@ -6465,7 +6489,7 @@
       <c r="I133" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K133" s="67"/>
+      <c r="K133" s="68"/>
     </row>
     <row r="134" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A134" s="10">
@@ -6495,7 +6519,7 @@
       <c r="I134" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K134" s="67"/>
+      <c r="K134" s="68"/>
     </row>
     <row r="135" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A135" s="10">
@@ -6522,7 +6546,7 @@
       <c r="I135" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K135" s="67"/>
+      <c r="K135" s="68"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A136" s="10">
@@ -6549,7 +6573,7 @@
       <c r="I136" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K136" s="67"/>
+      <c r="K136" s="68"/>
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A137" s="10">
@@ -6576,7 +6600,7 @@
       <c r="I137" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K137" s="67"/>
+      <c r="K137" s="68"/>
     </row>
     <row r="138" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="10">
@@ -6603,7 +6627,7 @@
       <c r="I138" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K138" s="67"/>
+      <c r="K138" s="68"/>
     </row>
     <row r="139" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="10">
@@ -6633,7 +6657,7 @@
       <c r="I139" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="K139" s="67"/>
+      <c r="K139" s="68"/>
     </row>
     <row r="140" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A140" s="11">
@@ -6663,7 +6687,7 @@
       <c r="I140" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K140" s="68"/>
+      <c r="K140" s="69"/>
     </row>
     <row r="141" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A141" s="11">
@@ -6693,7 +6717,7 @@
       <c r="I141" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K141" s="68"/>
+      <c r="K141" s="69"/>
     </row>
     <row r="142" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A142" s="11">
@@ -6723,7 +6747,7 @@
       <c r="I142" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K142" s="68"/>
+      <c r="K142" s="69"/>
     </row>
     <row r="143" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A143" s="11">
@@ -6753,7 +6777,7 @@
       <c r="I143" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="K143" s="68"/>
+      <c r="K143" s="69"/>
     </row>
     <row r="144" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A144" s="11">
@@ -6783,7 +6807,7 @@
       <c r="I144" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K144" s="68"/>
+      <c r="K144" s="69"/>
     </row>
     <row r="145" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A145" s="11">
@@ -6813,7 +6837,7 @@
       <c r="I145" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="K145" s="68"/>
+      <c r="K145" s="69"/>
     </row>
     <row r="146" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A146" s="12">
@@ -6843,7 +6867,7 @@
       <c r="I146" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K146" s="69"/>
+      <c r="K146" s="70"/>
     </row>
     <row r="147" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A147" s="12">
@@ -6873,7 +6897,7 @@
       <c r="I147" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K147" s="69"/>
+      <c r="K147" s="70"/>
     </row>
     <row r="148" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A148" s="12">
@@ -6903,7 +6927,7 @@
       <c r="I148" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K148" s="69"/>
+      <c r="K148" s="70"/>
     </row>
     <row r="149" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A149" s="12">
@@ -6933,7 +6957,7 @@
       <c r="I149" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K149" s="69"/>
+      <c r="K149" s="70"/>
     </row>
     <row r="150" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A150" s="12">
@@ -6963,7 +6987,7 @@
       <c r="I150" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K150" s="69"/>
+      <c r="K150" s="70"/>
     </row>
     <row r="151" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A151" s="12">
@@ -6991,7 +7015,7 @@
       <c r="I151" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="K151" s="69"/>
+      <c r="K151" s="70"/>
     </row>
     <row r="152" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A152" s="13">
@@ -7021,7 +7045,7 @@
       <c r="I152" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="K152" s="70"/>
+      <c r="K152" s="71"/>
     </row>
     <row r="153" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A153" s="13">
@@ -7051,7 +7075,7 @@
       <c r="I153" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K153" s="70"/>
+      <c r="K153" s="71"/>
     </row>
     <row r="154" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A154" s="13">
@@ -7081,7 +7105,7 @@
       <c r="I154" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="K154" s="70"/>
+      <c r="K154" s="71"/>
     </row>
     <row r="155" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A155" s="13">
@@ -7111,7 +7135,7 @@
       <c r="I155" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="K155" s="70"/>
+      <c r="K155" s="71"/>
     </row>
     <row r="156" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A156" s="13">
@@ -7141,7 +7165,7 @@
       <c r="I156" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="K156" s="70"/>
+      <c r="K156" s="71"/>
     </row>
     <row r="157" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A157" s="13">
@@ -7171,627 +7195,999 @@
       <c r="I157" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="K157" s="70"/>
+      <c r="K157" s="71"/>
     </row>
     <row r="158" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A158" s="71">
+      <c r="A158" s="72">
         <v>10340001</v>
       </c>
-      <c r="B158" s="71">
+      <c r="B158" s="72">
         <v>103400</v>
       </c>
-      <c r="C158" s="71" t="s">
+      <c r="C158" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="D158" s="71" t="s">
+      <c r="D158" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="E158" s="71" t="s">
+      <c r="E158" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="F158" s="71" t="s">
+      <c r="F158" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G158" s="71" t="s">
+      <c r="G158" s="72" t="s">
         <v>292</v>
       </c>
-      <c r="H158" s="71" t="s">
+      <c r="H158" s="72" t="s">
         <v>293</v>
       </c>
-      <c r="I158" s="71" t="s">
+      <c r="I158" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K158" s="72"/>
+      <c r="K158" s="73"/>
     </row>
     <row r="159" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A159" s="71">
+      <c r="A159" s="72">
         <v>10340011</v>
       </c>
-      <c r="B159" s="71">
+      <c r="B159" s="72">
         <v>103400</v>
       </c>
-      <c r="C159" s="71" t="s">
+      <c r="C159" s="72" t="s">
         <v>294</v>
       </c>
-      <c r="D159" s="71" t="s">
+      <c r="D159" s="72" t="s">
         <v>295</v>
       </c>
-      <c r="E159" s="71" t="s">
+      <c r="E159" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="F159" s="71" t="s">
+      <c r="F159" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G159" s="71" t="s">
+      <c r="G159" s="72" t="s">
         <v>292</v>
       </c>
-      <c r="H159" s="71"/>
-      <c r="I159" s="71" t="s">
+      <c r="H159" s="72"/>
+      <c r="I159" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K159" s="72"/>
+      <c r="K159" s="73"/>
     </row>
     <row r="160" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A160" s="71">
+      <c r="A160" s="72">
         <v>10340021</v>
       </c>
-      <c r="B160" s="71">
+      <c r="B160" s="72">
         <v>103400</v>
       </c>
-      <c r="C160" s="71" t="s">
+      <c r="C160" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="D160" s="71" t="s">
+      <c r="D160" s="72" t="s">
         <v>295</v>
       </c>
-      <c r="E160" s="71" t="s">
+      <c r="E160" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="F160" s="71" t="s">
+      <c r="F160" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G160" s="71" t="s">
+      <c r="G160" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H160" s="71" t="s">
+      <c r="H160" s="72" t="s">
         <v>293</v>
       </c>
-      <c r="I160" s="71" t="s">
+      <c r="I160" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K160" s="73"/>
+      <c r="K160" s="74"/>
     </row>
     <row r="161" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A161" s="71">
+      <c r="A161" s="72">
         <v>10340002</v>
       </c>
-      <c r="B161" s="71">
+      <c r="B161" s="72">
         <v>103400</v>
       </c>
-      <c r="C161" s="71" t="s">
+      <c r="C161" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="D161" s="71" t="s">
+      <c r="D161" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="E161" s="71" t="s">
+      <c r="E161" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="F161" s="71" t="s">
+      <c r="F161" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G161" s="71" t="s">
+      <c r="G161" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="H161" s="71" t="s">
+      <c r="H161" s="72" t="s">
         <v>301</v>
       </c>
-      <c r="I161" s="71" t="s">
+      <c r="I161" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K161" s="73"/>
+      <c r="K161" s="74"/>
     </row>
     <row r="162" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A162" s="71">
+      <c r="A162" s="72">
         <v>10340012</v>
       </c>
-      <c r="B162" s="71">
+      <c r="B162" s="72">
         <v>103400</v>
       </c>
-      <c r="C162" s="71" t="s">
+      <c r="C162" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="D162" s="71" t="s">
+      <c r="D162" s="72" t="s">
         <v>303</v>
       </c>
-      <c r="E162" s="71" t="s">
+      <c r="E162" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="F162" s="71" t="s">
+      <c r="F162" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G162" s="71" t="s">
+      <c r="G162" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="H162" s="71"/>
-      <c r="I162" s="71" t="s">
+      <c r="H162" s="72"/>
+      <c r="I162" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K162" s="73"/>
+      <c r="K162" s="74"/>
     </row>
     <row r="163" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A163" s="71">
+      <c r="A163" s="72">
         <v>10340022</v>
       </c>
-      <c r="B163" s="71">
+      <c r="B163" s="72">
         <v>103400</v>
       </c>
-      <c r="C163" s="71" t="s">
+      <c r="C163" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="D163" s="71" t="s">
+      <c r="D163" s="72" t="s">
         <v>303</v>
       </c>
-      <c r="E163" s="71" t="s">
+      <c r="E163" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="F163" s="71" t="s">
+      <c r="F163" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G163" s="71" t="s">
+      <c r="G163" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H163" s="71" t="s">
+      <c r="H163" s="72" t="s">
         <v>301</v>
       </c>
-      <c r="I163" s="71" t="s">
+      <c r="I163" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K163" s="73"/>
+      <c r="K163" s="74"/>
     </row>
     <row r="164" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A164" s="71">
+      <c r="A164" s="72">
         <v>10340003</v>
       </c>
-      <c r="B164" s="71">
+      <c r="B164" s="72">
         <v>103400</v>
       </c>
-      <c r="C164" s="71" t="s">
+      <c r="C164" s="72" t="s">
         <v>304</v>
       </c>
-      <c r="D164" s="71" t="s">
+      <c r="D164" s="72" t="s">
         <v>305</v>
       </c>
-      <c r="E164" s="71" t="s">
+      <c r="E164" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="F164" s="71" t="s">
+      <c r="F164" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G164" s="71" t="s">
+      <c r="G164" s="72" t="s">
         <v>307</v>
       </c>
-      <c r="H164" s="71" t="s">
+      <c r="H164" s="72" t="s">
         <v>308</v>
       </c>
-      <c r="I164" s="71" t="s">
+      <c r="I164" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K164" s="73"/>
+      <c r="K164" s="74"/>
     </row>
     <row r="165" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A165" s="71">
+      <c r="A165" s="72">
         <v>10340013</v>
       </c>
-      <c r="B165" s="71">
+      <c r="B165" s="72">
         <v>103400</v>
       </c>
-      <c r="C165" s="71" t="s">
+      <c r="C165" s="72" t="s">
         <v>309</v>
       </c>
-      <c r="D165" s="71" t="s">
+      <c r="D165" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="E165" s="71" t="s">
+      <c r="E165" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="F165" s="71" t="s">
+      <c r="F165" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G165" s="71" t="s">
+      <c r="G165" s="72" t="s">
         <v>307</v>
       </c>
-      <c r="H165" s="71"/>
-      <c r="I165" s="71" t="s">
+      <c r="H165" s="72"/>
+      <c r="I165" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K165" s="73"/>
+      <c r="K165" s="74"/>
     </row>
     <row r="166" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A166" s="71">
+      <c r="A166" s="72">
         <v>10340023</v>
       </c>
-      <c r="B166" s="71">
+      <c r="B166" s="72">
         <v>103400</v>
       </c>
-      <c r="C166" s="71" t="s">
+      <c r="C166" s="72" t="s">
         <v>304</v>
       </c>
-      <c r="D166" s="71" t="s">
+      <c r="D166" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="E166" s="71" t="s">
+      <c r="E166" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="F166" s="71" t="s">
+      <c r="F166" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G166" s="71" t="s">
+      <c r="G166" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H166" s="71" t="s">
+      <c r="H166" s="72" t="s">
         <v>308</v>
       </c>
-      <c r="I166" s="71" t="s">
+      <c r="I166" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K166" s="73"/>
+      <c r="K166" s="74"/>
     </row>
     <row r="167" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A167" s="71">
+      <c r="A167" s="72">
         <v>10340004</v>
       </c>
-      <c r="B167" s="71">
+      <c r="B167" s="72">
         <v>103400</v>
       </c>
-      <c r="C167" s="71" t="s">
+      <c r="C167" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="D167" s="71" t="s">
+      <c r="D167" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E167" s="71" t="s">
+      <c r="E167" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="F167" s="71" t="s">
+      <c r="F167" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G167" s="71" t="s">
+      <c r="G167" s="72" t="s">
         <v>314</v>
       </c>
-      <c r="H167" s="71" t="s">
+      <c r="H167" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="I167" s="71" t="s">
+      <c r="I167" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K167" s="73"/>
+      <c r="K167" s="74"/>
     </row>
     <row r="168" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A168" s="71">
+      <c r="A168" s="72">
         <v>10340014</v>
       </c>
-      <c r="B168" s="71">
+      <c r="B168" s="72">
         <v>103400</v>
       </c>
-      <c r="C168" s="71" t="s">
+      <c r="C168" s="72" t="s">
         <v>316</v>
       </c>
-      <c r="D168" s="71" t="s">
+      <c r="D168" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="E168" s="71" t="s">
+      <c r="E168" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="F168" s="71" t="s">
+      <c r="F168" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G168" s="71" t="s">
+      <c r="G168" s="72" t="s">
         <v>314</v>
       </c>
-      <c r="H168" s="71"/>
-      <c r="I168" s="71" t="s">
+      <c r="H168" s="72"/>
+      <c r="I168" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K168" s="73"/>
+      <c r="K168" s="74"/>
     </row>
     <row r="169" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A169" s="71">
+      <c r="A169" s="72">
         <v>10340024</v>
       </c>
-      <c r="B169" s="71">
+      <c r="B169" s="72">
         <v>103400</v>
       </c>
-      <c r="C169" s="71" t="s">
+      <c r="C169" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="D169" s="71" t="s">
+      <c r="D169" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="E169" s="71" t="s">
+      <c r="E169" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="F169" s="71" t="s">
+      <c r="F169" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G169" s="71" t="s">
+      <c r="G169" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H169" s="71" t="s">
+      <c r="H169" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="I169" s="71" t="s">
+      <c r="I169" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K169" s="73"/>
+      <c r="K169" s="74"/>
     </row>
     <row r="170" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A170" s="71">
+      <c r="A170" s="72">
         <v>10340005</v>
       </c>
-      <c r="B170" s="71">
+      <c r="B170" s="72">
         <v>103400</v>
       </c>
-      <c r="C170" s="71" t="s">
+      <c r="C170" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="D170" s="71" t="s">
+      <c r="D170" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="E170" s="71" t="s">
+      <c r="E170" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F170" s="71" t="s">
+      <c r="F170" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G170" s="71" t="s">
+      <c r="G170" s="72" t="s">
         <v>321</v>
       </c>
-      <c r="H170" s="71" t="s">
+      <c r="H170" s="72" t="s">
         <v>322</v>
       </c>
-      <c r="I170" s="71" t="s">
+      <c r="I170" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K170" s="73"/>
+      <c r="K170" s="74"/>
     </row>
     <row r="171" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A171" s="71">
+      <c r="A171" s="72">
         <v>10340015</v>
       </c>
-      <c r="B171" s="71">
+      <c r="B171" s="72">
         <v>103400</v>
       </c>
-      <c r="C171" s="71" t="s">
+      <c r="C171" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="D171" s="71" t="s">
+      <c r="D171" s="72" t="s">
         <v>324</v>
       </c>
-      <c r="E171" s="71" t="s">
+      <c r="E171" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F171" s="71" t="s">
+      <c r="F171" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G171" s="71" t="s">
+      <c r="G171" s="72" t="s">
         <v>321</v>
       </c>
-      <c r="H171" s="71"/>
-      <c r="I171" s="71" t="s">
+      <c r="H171" s="72"/>
+      <c r="I171" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K171" s="73"/>
+      <c r="K171" s="74"/>
     </row>
     <row r="172" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A172" s="71">
+      <c r="A172" s="72">
         <v>10340025</v>
       </c>
-      <c r="B172" s="71">
+      <c r="B172" s="72">
         <v>103400</v>
       </c>
-      <c r="C172" s="71" t="s">
+      <c r="C172" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="D172" s="71" t="s">
+      <c r="D172" s="72" t="s">
         <v>324</v>
       </c>
-      <c r="E172" s="71" t="s">
+      <c r="E172" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F172" s="71" t="s">
+      <c r="F172" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G172" s="71" t="s">
+      <c r="G172" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H172" s="71" t="s">
+      <c r="H172" s="72" t="s">
         <v>322</v>
       </c>
-      <c r="I172" s="71" t="s">
+      <c r="I172" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K172" s="73"/>
+      <c r="K172" s="74"/>
     </row>
     <row r="173" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A173" s="71">
+      <c r="A173" s="72">
         <v>10340006</v>
       </c>
-      <c r="B173" s="71">
+      <c r="B173" s="72">
         <v>103400</v>
       </c>
-      <c r="C173" s="71" t="s">
+      <c r="C173" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="D173" s="71" t="s">
+      <c r="D173" s="72" t="s">
         <v>326</v>
       </c>
-      <c r="E173" s="71" t="s">
+      <c r="E173" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F173" s="71" t="s">
+      <c r="F173" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G173" s="71" t="s">
+      <c r="G173" s="72" t="s">
         <v>327</v>
       </c>
-      <c r="H173" s="71" t="s">
+      <c r="H173" s="72" t="s">
         <v>328</v>
       </c>
-      <c r="I173" s="71" t="s">
+      <c r="I173" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="K173" s="73"/>
+      <c r="K173" s="74"/>
     </row>
     <row r="174" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A174" s="71">
+      <c r="A174" s="72">
         <v>10340016</v>
       </c>
-      <c r="B174" s="71">
+      <c r="B174" s="72">
         <v>103400</v>
       </c>
-      <c r="C174" s="71" t="s">
+      <c r="C174" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="D174" s="71" t="s">
+      <c r="D174" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="E174" s="71" t="s">
+      <c r="E174" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F174" s="71" t="s">
+      <c r="F174" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G174" s="71" t="s">
+      <c r="G174" s="72" t="s">
         <v>327</v>
       </c>
-      <c r="H174" s="71"/>
-      <c r="I174" s="71" t="s">
+      <c r="H174" s="72"/>
+      <c r="I174" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K174" s="73"/>
+      <c r="K174" s="74"/>
     </row>
     <row r="175" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A175" s="71">
+      <c r="A175" s="72">
         <v>10340026</v>
       </c>
-      <c r="B175" s="71">
+      <c r="B175" s="72">
         <v>103400</v>
       </c>
-      <c r="C175" s="71" t="s">
+      <c r="C175" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="D175" s="71" t="s">
+      <c r="D175" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="E175" s="71" t="s">
+      <c r="E175" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="F175" s="71" t="s">
+      <c r="F175" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G175" s="71" t="s">
+      <c r="G175" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H175" s="71" t="s">
+      <c r="H175" s="72" t="s">
         <v>328</v>
       </c>
-      <c r="I175" s="71" t="s">
+      <c r="I175" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K175" s="73"/>
+      <c r="K175" s="74"/>
     </row>
     <row r="176" s="15" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A176" s="71">
+      <c r="A176" s="72">
         <v>10340007</v>
       </c>
-      <c r="B176" s="71">
+      <c r="B176" s="72">
         <v>103400</v>
       </c>
-      <c r="C176" s="71" t="s">
+      <c r="C176" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="D176" s="71" t="s">
+      <c r="D176" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="E176" s="71" t="s">
+      <c r="E176" s="72" t="s">
         <v>332</v>
       </c>
-      <c r="F176" s="71" t="s">
+      <c r="F176" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G176" s="71" t="s">
+      <c r="G176" s="72" t="s">
         <v>296</v>
       </c>
       <c r="H176" s="15"/>
-      <c r="I176" s="71" t="s">
+      <c r="I176" s="72" t="s">
         <v>274</v>
       </c>
-      <c r="K176" s="73"/>
+      <c r="K176" s="74"/>
     </row>
     <row r="177" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A177" s="71">
+      <c r="A177" s="72">
         <v>10340008</v>
       </c>
-      <c r="B177" s="71">
+      <c r="B177" s="72">
         <v>103400</v>
       </c>
-      <c r="C177" s="71" t="s">
+      <c r="C177" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="D177" s="71" t="s">
+      <c r="D177" s="72" t="s">
         <v>334</v>
       </c>
-      <c r="E177" s="71" t="s">
+      <c r="E177" s="72" t="s">
         <v>243</v>
       </c>
-      <c r="F177" s="71" t="s">
+      <c r="F177" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G177" s="71" t="s">
+      <c r="G177" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H177" s="71" t="s">
+      <c r="H177" s="72" t="s">
         <v>335</v>
       </c>
-      <c r="I177" s="71" t="s">
+      <c r="I177" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K177" s="72"/>
+      <c r="K177" s="73"/>
     </row>
     <row r="178" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A178" s="71">
+      <c r="A178" s="72">
         <v>10340009</v>
       </c>
-      <c r="B178" s="71">
+      <c r="B178" s="72">
         <v>103400</v>
       </c>
-      <c r="C178" s="71" t="s">
+      <c r="C178" s="72" t="s">
         <v>333</v>
       </c>
-      <c r="D178" s="71" t="s">
+      <c r="D178" s="72" t="s">
         <v>336</v>
       </c>
-      <c r="E178" s="71" t="s">
+      <c r="E178" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="F178" s="71" t="s">
+      <c r="F178" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G178" s="71" t="s">
+      <c r="G178" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="H178" s="71"/>
-      <c r="I178" s="71" t="s">
+      <c r="H178" s="72"/>
+      <c r="I178" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="K178" s="72"/>
-    </row>
-    <row r="184" spans="1:11">
-      <c r="E184" s="74"/>
-    </row>
-    <row r="186" spans="1:11">
-      <c r="E186" s="75"/>
+      <c r="K178" s="73"/>
+    </row>
+    <row r="179" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A179" s="75">
+        <v>10350001</v>
+      </c>
+      <c r="B179" s="75">
+        <v>103500</v>
+      </c>
+      <c r="C179" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D179" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="E179" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="F179" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G179" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H179" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="I179" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="J179" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="K179" s="76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A180" s="75">
+        <v>10350002</v>
+      </c>
+      <c r="B180" s="75">
+        <v>103500</v>
+      </c>
+      <c r="C180" s="75" t="s">
+        <v>342</v>
+      </c>
+      <c r="D180" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="E180" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="F180" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G180" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H180" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="I180" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="J180" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="K180" s="76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A181" s="75">
+        <v>10350012</v>
+      </c>
+      <c r="B181" s="75">
+        <v>103500</v>
+      </c>
+      <c r="C181" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D181" s="75" t="s">
+        <v>251</v>
+      </c>
+      <c r="E181" s="75" t="s">
+        <v>344</v>
+      </c>
+      <c r="F181" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G181" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H181" s="75" t="s">
+        <v>345</v>
+      </c>
+      <c r="I181" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="K181" s="76"/>
+    </row>
+    <row r="182" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A182" s="75">
+        <v>10350013</v>
+      </c>
+      <c r="B182" s="75">
+        <v>103500</v>
+      </c>
+      <c r="C182" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="75" t="s">
+        <v>346</v>
+      </c>
+      <c r="E182" s="75" t="s">
+        <v>146</v>
+      </c>
+      <c r="F182" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G182" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H182" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="I182" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="K182" s="76"/>
+    </row>
+    <row r="183" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A183" s="75">
+        <v>10350014</v>
+      </c>
+      <c r="B183" s="75">
+        <v>103500</v>
+      </c>
+      <c r="C183" s="75"/>
+      <c r="D183" s="75" t="s">
+        <v>347</v>
+      </c>
+      <c r="E183" s="75" t="s">
+        <v>255</v>
+      </c>
+      <c r="F183" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G183" s="75" t="s">
+        <v>348</v>
+      </c>
+      <c r="H183" s="75"/>
+      <c r="I183" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="K183" s="76"/>
+    </row>
+    <row r="184" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A184" s="75">
+        <v>10350101</v>
+      </c>
+      <c r="B184" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C184" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D184" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="E184" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="F184" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G184" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H184" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="I184" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="K184" s="76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="185" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A185" s="75">
+        <v>10350102</v>
+      </c>
+      <c r="B185" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C185" s="75" t="s">
+        <v>342</v>
+      </c>
+      <c r="D185" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="E185" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="F185" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G185" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H185" s="75" t="s">
+        <v>339</v>
+      </c>
+      <c r="I185" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="K185" s="76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A186" s="75">
+        <v>10350112</v>
+      </c>
+      <c r="B186" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C186" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="75" t="s">
+        <v>251</v>
+      </c>
+      <c r="E186" s="75" t="s">
+        <v>344</v>
+      </c>
+      <c r="F186" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G186" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H186" s="75" t="s">
+        <v>345</v>
+      </c>
+      <c r="I186" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="K186" s="76"/>
+    </row>
+    <row r="187" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A187" s="75">
+        <v>10350113</v>
+      </c>
+      <c r="B187" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C187" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" s="75" t="s">
+        <v>346</v>
+      </c>
+      <c r="E187" s="75" t="s">
+        <v>146</v>
+      </c>
+      <c r="F187" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G187" s="75" t="s">
+        <v>338</v>
+      </c>
+      <c r="H187" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="I187" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="K187" s="76"/>
+    </row>
+    <row r="188" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A188" s="75">
+        <v>10350114</v>
+      </c>
+      <c r="B188" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C188" s="75"/>
+      <c r="D188" s="75" t="s">
+        <v>347</v>
+      </c>
+      <c r="E188" s="75" t="s">
+        <v>255</v>
+      </c>
+      <c r="F188" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G188" s="75" t="s">
+        <v>348</v>
+      </c>
+      <c r="H188" s="75"/>
+      <c r="I188" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="K188" s="76"/>
+    </row>
+    <row r="189" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A189" s="75"/>
+      <c r="B189" s="75"/>
+      <c r="C189" s="75"/>
+      <c r="D189" s="75"/>
+      <c r="E189" s="75"/>
+      <c r="F189" s="75"/>
+      <c r="G189" s="75"/>
+      <c r="H189" s="75"/>
+      <c r="I189" s="75"/>
+      <c r="K189" s="76"/>
+    </row>
+    <row r="190" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A190" s="75"/>
+      <c r="B190" s="75"/>
+      <c r="C190" s="75"/>
+      <c r="D190" s="75"/>
+      <c r="E190" s="75"/>
+      <c r="F190" s="75"/>
+      <c r="G190" s="75"/>
+      <c r="H190" s="75"/>
+      <c r="I190" s="75"/>
+      <c r="K190" s="76"/>
+    </row>
+    <row r="191" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A191" s="75"/>
+      <c r="B191" s="75"/>
+      <c r="C191" s="75"/>
+      <c r="D191" s="75"/>
+      <c r="E191" s="75"/>
+      <c r="F191" s="75"/>
+      <c r="G191" s="75"/>
+      <c r="H191" s="75"/>
+      <c r="I191" s="75"/>
+      <c r="K191" s="76"/>
+    </row>
+    <row r="192" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A192" s="75"/>
+      <c r="B192" s="75"/>
+      <c r="C192" s="75"/>
+      <c r="D192" s="75"/>
+      <c r="E192" s="75"/>
+      <c r="F192" s="75"/>
+      <c r="G192" s="75"/>
+      <c r="H192" s="75"/>
+      <c r="I192" s="75"/>
+      <c r="K192" s="76"/>
+    </row>
+    <row r="193" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A193" s="75"/>
+      <c r="B193" s="75"/>
+      <c r="C193" s="75"/>
+      <c r="D193" s="75"/>
+      <c r="E193" s="75"/>
+      <c r="F193" s="75"/>
+      <c r="G193" s="75"/>
+      <c r="H193" s="75"/>
+      <c r="I193" s="75"/>
+      <c r="K193" s="76"/>
+    </row>
+    <row r="194" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A194" s="75"/>
+      <c r="B194" s="75"/>
+      <c r="C194" s="75"/>
+      <c r="D194" s="75"/>
+      <c r="E194" s="75"/>
+      <c r="F194" s="75"/>
+      <c r="G194" s="75"/>
+      <c r="H194" s="75"/>
+      <c r="I194" s="75"/>
+      <c r="K194" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7811,24 +8207,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7836,16 +8232,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="F3" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7853,16 +8249,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="F4" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7870,16 +8266,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F5" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7887,7 +8283,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7895,7 +8291,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7903,7 +8299,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7911,7 +8307,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7919,7 +8315,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7927,7 +8323,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7935,7 +8331,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7943,7 +8339,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7951,7 +8347,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7959,7 +8355,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7967,7 +8363,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7975,7 +8371,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7983,7 +8379,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7991,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7999,7 +8395,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8007,7 +8403,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8015,7 +8411,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -8023,7 +8419,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8031,7 +8427,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8039,7 +8435,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8047,7 +8443,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -8055,7 +8451,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -8063,7 +8459,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -8071,7 +8467,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -8079,7 +8475,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -8087,7 +8483,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -8095,7 +8491,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8103,7 +8499,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8111,7 +8507,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8119,7 +8515,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8127,7 +8523,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8135,7 +8531,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8143,7 +8539,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8151,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8159,7 +8555,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8167,7 +8563,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8175,7 +8571,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8183,7 +8579,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8191,7 +8587,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8199,7 +8595,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8207,7 +8603,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8215,7 +8611,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8223,7 +8619,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="406">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -901,73 +901,76 @@
     <t>常规模式出现</t>
   </si>
   <si>
+    <t>0_50|1_40|2_10</t>
+  </si>
+  <si>
+    <t>用于触发奖池</t>
+  </si>
+  <si>
+    <t>11_14</t>
+  </si>
+  <si>
+    <t>改出1个大奖</t>
+  </si>
+  <si>
+    <t>改出奖池符号</t>
+  </si>
+  <si>
+    <t>15_10|16_5|17_2|18_1</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>99999_1</t>
+  </si>
+  <si>
+    <t>3_1_1|9_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>改出1个19符号</t>
+  </si>
+  <si>
+    <t>改出1个20符号</t>
+  </si>
+  <si>
+    <t>10_11_12</t>
+  </si>
+  <si>
+    <t>13_10|14_5|15_2|16_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
+  </si>
+  <si>
+    <t>概率出现3个bonus</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_15|3_5</t>
+  </si>
+  <si>
+    <t>概率出现3个SCATTER</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_19|3_1</t>
+  </si>
+  <si>
     <t>0_50|1_40_2_10</t>
-  </si>
-  <si>
-    <t>用于触发奖池</t>
-  </si>
-  <si>
-    <t>11_14</t>
-  </si>
-  <si>
-    <t>改出1个大奖</t>
-  </si>
-  <si>
-    <t>改出奖池符号</t>
-  </si>
-  <si>
-    <t>15_10|16_5|17_2|18_1</t>
-  </si>
-  <si>
-    <t>13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>99999_1</t>
-  </si>
-  <si>
-    <t>3_1_1|9_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个SCATTER</t>
-  </si>
-  <si>
-    <t>11_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>改出1个19符号</t>
-  </si>
-  <si>
-    <t>改出1个20符号</t>
-  </si>
-  <si>
-    <t>10_11_12</t>
-  </si>
-  <si>
-    <t>13_10|14_5|15_2|16_1</t>
-  </si>
-  <si>
-    <t>概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>改出3个bonus</t>
-  </si>
-  <si>
-    <t>概率出现3个bonus</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_15|3_5</t>
-  </si>
-  <si>
-    <t>概率出现3个SCATTER</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_19|3_1</t>
   </si>
   <si>
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
@@ -6655,7 +6658,7 @@
         <v>261</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="K139" s="68"/>
     </row>
@@ -6679,10 +6682,10 @@
         <v>133</v>
       </c>
       <c r="G140" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>106</v>
@@ -6709,13 +6712,13 @@
         <v>133</v>
       </c>
       <c r="G141" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="I141" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="H141" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="I141" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="K141" s="69"/>
     </row>
@@ -6733,16 +6736,16 @@
         <v>228</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>39</v>
@@ -6772,10 +6775,10 @@
         <v>71</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K143" s="69"/>
     </row>
@@ -6799,10 +6802,10 @@
         <v>133</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H144" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>107</v>
@@ -6817,10 +6820,10 @@
         <v>101800</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E145" s="11" t="s">
         <v>143</v>
@@ -6829,13 +6832,13 @@
         <v>133</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K145" s="69"/>
     </row>
@@ -6862,10 +6865,10 @@
         <v>232</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="K146" s="70"/>
     </row>
@@ -6892,7 +6895,7 @@
         <v>232</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>106</v>
@@ -6913,7 +6916,7 @@
         <v>228</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>133</v>
@@ -6922,7 +6925,7 @@
         <v>253</v>
       </c>
       <c r="H148" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>39</v>
@@ -6949,13 +6952,13 @@
         <v>133</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K149" s="70"/>
     </row>
@@ -6970,22 +6973,22 @@
         <v>21</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E150" s="12" t="s">
         <v>136</v>
       </c>
       <c r="F150" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>232</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K150" s="70"/>
     </row>
@@ -6997,23 +7000,23 @@
         <v>102500</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D151" s="12"/>
       <c r="E151" s="12" t="s">
         <v>136</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G151" s="12" t="s">
         <v>232</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K151" s="70"/>
     </row>
@@ -7037,13 +7040,13 @@
         <v>133</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H152" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I152" s="13" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="K152" s="71"/>
     </row>
@@ -7067,7 +7070,7 @@
         <v>133</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H153" s="13" t="s">
         <v>160</v>
@@ -7088,7 +7091,7 @@
         <v>21</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E154" s="13" t="s">
         <v>136</v>
@@ -7097,13 +7100,13 @@
         <v>133</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H154" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K154" s="71"/>
     </row>
@@ -7157,13 +7160,13 @@
         <v>133</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H156" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K156" s="71"/>
     </row>
@@ -7175,10 +7178,10 @@
         <v>102300</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E157" s="13" t="s">
         <v>140</v>
@@ -7187,13 +7190,13 @@
         <v>133</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H157" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K157" s="71"/>
     </row>
@@ -7205,22 +7208,22 @@
         <v>103400</v>
       </c>
       <c r="C158" s="72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D158" s="72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E158" s="72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F158" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G158" s="72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H158" s="72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I158" s="72" t="s">
         <v>106</v>
@@ -7235,19 +7238,19 @@
         <v>103400</v>
       </c>
       <c r="C159" s="72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D159" s="72" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E159" s="72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F159" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G159" s="72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H159" s="72"/>
       <c r="I159" s="72" t="s">
@@ -7263,22 +7266,22 @@
         <v>103400</v>
       </c>
       <c r="C160" s="72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D160" s="72" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E160" s="72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F160" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G160" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H160" s="72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I160" s="72" t="s">
         <v>39</v>
@@ -7293,22 +7296,22 @@
         <v>103400</v>
       </c>
       <c r="C161" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D161" s="72" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E161" s="72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F161" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G161" s="72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H161" s="72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I161" s="72" t="s">
         <v>106</v>
@@ -7323,19 +7326,19 @@
         <v>103400</v>
       </c>
       <c r="C162" s="72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D162" s="72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E162" s="72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F162" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G162" s="72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H162" s="72"/>
       <c r="I162" s="72" t="s">
@@ -7351,22 +7354,22 @@
         <v>103400</v>
       </c>
       <c r="C163" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D163" s="72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E163" s="72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F163" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G163" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H163" s="72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I163" s="72" t="s">
         <v>39</v>
@@ -7381,22 +7384,22 @@
         <v>103400</v>
       </c>
       <c r="C164" s="72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D164" s="72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E164" s="72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F164" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G164" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H164" s="72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I164" s="72" t="s">
         <v>106</v>
@@ -7411,19 +7414,19 @@
         <v>103400</v>
       </c>
       <c r="C165" s="72" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D165" s="72" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E165" s="72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F165" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G165" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H165" s="72"/>
       <c r="I165" s="72" t="s">
@@ -7439,22 +7442,22 @@
         <v>103400</v>
       </c>
       <c r="C166" s="72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D166" s="72" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E166" s="72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F166" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G166" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H166" s="72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I166" s="72" t="s">
         <v>39</v>
@@ -7469,22 +7472,22 @@
         <v>103400</v>
       </c>
       <c r="C167" s="72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D167" s="72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E167" s="72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F167" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G167" s="72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H167" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I167" s="72" t="s">
         <v>106</v>
@@ -7499,19 +7502,19 @@
         <v>103400</v>
       </c>
       <c r="C168" s="72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D168" s="72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E168" s="72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F168" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G168" s="72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H168" s="72"/>
       <c r="I168" s="72" t="s">
@@ -7527,22 +7530,22 @@
         <v>103400</v>
       </c>
       <c r="C169" s="72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D169" s="72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E169" s="72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F169" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G169" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H169" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I169" s="72" t="s">
         <v>39</v>
@@ -7557,22 +7560,22 @@
         <v>103400</v>
       </c>
       <c r="C170" s="72" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D170" s="72" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E170" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F170" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G170" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H170" s="72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I170" s="72" t="s">
         <v>106</v>
@@ -7587,19 +7590,19 @@
         <v>103400</v>
       </c>
       <c r="C171" s="72" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D171" s="72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E171" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F171" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G171" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H171" s="72"/>
       <c r="I171" s="72" t="s">
@@ -7615,22 +7618,22 @@
         <v>103400</v>
       </c>
       <c r="C172" s="72" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D172" s="72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E172" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F172" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G172" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H172" s="72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I172" s="72" t="s">
         <v>39</v>
@@ -7645,22 +7648,22 @@
         <v>103400</v>
       </c>
       <c r="C173" s="72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D173" s="72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E173" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F173" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G173" s="72" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H173" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I173" s="72" t="s">
         <v>106</v>
@@ -7675,19 +7678,19 @@
         <v>103400</v>
       </c>
       <c r="C174" s="72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D174" s="72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E174" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F174" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G174" s="72" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H174" s="72"/>
       <c r="I174" s="72" t="s">
@@ -7703,22 +7706,22 @@
         <v>103400</v>
       </c>
       <c r="C175" s="72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D175" s="72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E175" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F175" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G175" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H175" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I175" s="72" t="s">
         <v>39</v>
@@ -7733,23 +7736,23 @@
         <v>103400</v>
       </c>
       <c r="C176" s="72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D176" s="72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E176" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F176" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G176" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H176" s="15"/>
       <c r="I176" s="72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K176" s="74"/>
     </row>
@@ -7761,10 +7764,10 @@
         <v>103400</v>
       </c>
       <c r="C177" s="72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D177" s="72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E177" s="72" t="s">
         <v>243</v>
@@ -7773,10 +7776,10 @@
         <v>133</v>
       </c>
       <c r="G177" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H177" s="72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I177" s="72" t="s">
         <v>39</v>
@@ -7791,10 +7794,10 @@
         <v>103400</v>
       </c>
       <c r="C178" s="72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D178" s="72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E178" s="72" t="s">
         <v>157</v>
@@ -7803,7 +7806,7 @@
         <v>133</v>
       </c>
       <c r="G178" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H178" s="72"/>
       <c r="I178" s="72" t="s">
@@ -7822,7 +7825,7 @@
         <v>21</v>
       </c>
       <c r="D179" s="75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E179" s="75" t="s">
         <v>243</v>
@@ -7831,16 +7834,16 @@
         <v>133</v>
       </c>
       <c r="G179" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H179" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I179" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J179" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K179" s="76" t="s">
         <v>29</v>
@@ -7854,10 +7857,10 @@
         <v>103500</v>
       </c>
       <c r="C180" s="75" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D180" s="75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E180" s="75" t="s">
         <v>243</v>
@@ -7866,16 +7869,16 @@
         <v>133</v>
       </c>
       <c r="G180" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H180" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I180" s="75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J180" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K180" s="76" t="s">
         <v>29</v>
@@ -7895,16 +7898,16 @@
         <v>251</v>
       </c>
       <c r="E181" s="75" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F181" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G181" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H181" s="75" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I181" s="75" t="s">
         <v>39</v>
@@ -7922,7 +7925,7 @@
         <v>21</v>
       </c>
       <c r="D182" s="75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E182" s="75" t="s">
         <v>146</v>
@@ -7931,7 +7934,7 @@
         <v>133</v>
       </c>
       <c r="G182" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H182" s="75" t="s">
         <v>243</v>
@@ -7950,7 +7953,7 @@
       </c>
       <c r="C183" s="75"/>
       <c r="D183" s="75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E183" s="75" t="s">
         <v>255</v>
@@ -7959,7 +7962,7 @@
         <v>133</v>
       </c>
       <c r="G183" s="75" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H183" s="75"/>
       <c r="I183" s="75" t="s">
@@ -7978,7 +7981,7 @@
         <v>21</v>
       </c>
       <c r="D184" s="75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E184" s="75" t="s">
         <v>243</v>
@@ -7987,13 +7990,13 @@
         <v>133</v>
       </c>
       <c r="G184" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H184" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I184" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K184" s="76" t="s">
         <v>29</v>
@@ -8007,10 +8010,10 @@
         <v>103501</v>
       </c>
       <c r="C185" s="75" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D185" s="75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E185" s="75" t="s">
         <v>243</v>
@@ -8019,13 +8022,13 @@
         <v>133</v>
       </c>
       <c r="G185" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H185" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I185" s="75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K185" s="76" t="s">
         <v>29</v>
@@ -8045,16 +8048,16 @@
         <v>251</v>
       </c>
       <c r="E186" s="75" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F186" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G186" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H186" s="75" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I186" s="75" t="s">
         <v>39</v>
@@ -8072,7 +8075,7 @@
         <v>21</v>
       </c>
       <c r="D187" s="75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E187" s="75" t="s">
         <v>146</v>
@@ -8081,7 +8084,7 @@
         <v>133</v>
       </c>
       <c r="G187" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H187" s="75" t="s">
         <v>243</v>
@@ -8100,7 +8103,7 @@
       </c>
       <c r="C188" s="75"/>
       <c r="D188" s="75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E188" s="75" t="s">
         <v>255</v>
@@ -8109,7 +8112,7 @@
         <v>133</v>
       </c>
       <c r="G188" s="75" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H188" s="75"/>
       <c r="I188" s="75" t="s">
@@ -8207,24 +8210,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D2" t="s">
         <v>352</v>
       </c>
-      <c r="D2" t="s">
-        <v>351</v>
-      </c>
       <c r="E2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8232,16 +8235,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8249,16 +8252,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8266,16 +8269,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8283,7 +8286,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8291,7 +8294,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8299,7 +8302,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8307,7 +8310,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8315,7 +8318,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8323,7 +8326,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8331,7 +8334,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8339,7 +8342,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8347,7 +8350,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8355,7 +8358,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8363,7 +8366,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8371,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8379,7 +8382,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8387,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8395,7 +8398,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8403,7 +8406,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8411,7 +8414,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -8419,7 +8422,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8427,7 +8430,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8435,7 +8438,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8443,7 +8446,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -8451,7 +8454,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -8459,7 +8462,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -8467,7 +8470,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -8475,7 +8478,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -8483,7 +8486,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -8491,7 +8494,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8499,7 +8502,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8507,7 +8510,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8515,7 +8518,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8523,7 +8526,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8531,7 +8534,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8539,7 +8542,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8547,7 +8550,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8555,7 +8558,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8563,7 +8566,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8571,7 +8574,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8579,7 +8582,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8587,7 +8590,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8595,7 +8598,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8603,7 +8606,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8611,7 +8614,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8619,7 +8622,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="407">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -997,37 +997,40 @@
     <t>11_12_13</t>
   </si>
   <si>
+    <t>0_90|1_10</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15</t>
+  </si>
+  <si>
+    <t>12_10|13_5|14_2|15_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10次&amp;15次&amp;20次免费</t>
+  </si>
+  <si>
+    <t>3_70|4_25|5_5</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号</t>
+  </si>
+  <si>
+    <t>免费游戏中概率出现</t>
+  </si>
+  <si>
+    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
     <t>0_70|1_30</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15</t>
-  </si>
-  <si>
-    <t>12_10|13_5|14_2|15_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个以上SCATTER</t>
-  </si>
-  <si>
-    <t>10次&amp;15次&amp;20次免费</t>
-  </si>
-  <si>
-    <t>3_70|4_25|5_5</t>
-  </si>
-  <si>
-    <t>概率改出SCATTER符号</t>
-  </si>
-  <si>
-    <t>免费游戏中概率出现</t>
-  </si>
-  <si>
-    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
   </si>
   <si>
     <t>橘子福马模式(有不可替换元素)</t>
@@ -7196,7 +7199,7 @@
         <v>160</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K157" s="71"/>
     </row>
@@ -7208,22 +7211,22 @@
         <v>103400</v>
       </c>
       <c r="C158" s="72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D158" s="72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E158" s="72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F158" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G158" s="72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H158" s="72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I158" s="72" t="s">
         <v>106</v>
@@ -7238,19 +7241,19 @@
         <v>103400</v>
       </c>
       <c r="C159" s="72" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D159" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E159" s="72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F159" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G159" s="72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H159" s="72"/>
       <c r="I159" s="72" t="s">
@@ -7266,22 +7269,22 @@
         <v>103400</v>
       </c>
       <c r="C160" s="72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D160" s="72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E160" s="72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F160" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G160" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H160" s="72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I160" s="72" t="s">
         <v>39</v>
@@ -7296,22 +7299,22 @@
         <v>103400</v>
       </c>
       <c r="C161" s="72" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D161" s="72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E161" s="72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F161" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G161" s="72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H161" s="72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I161" s="72" t="s">
         <v>106</v>
@@ -7326,19 +7329,19 @@
         <v>103400</v>
       </c>
       <c r="C162" s="72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D162" s="72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E162" s="72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F162" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G162" s="72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H162" s="72"/>
       <c r="I162" s="72" t="s">
@@ -7354,22 +7357,22 @@
         <v>103400</v>
       </c>
       <c r="C163" s="72" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D163" s="72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E163" s="72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F163" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G163" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H163" s="72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I163" s="72" t="s">
         <v>39</v>
@@ -7384,22 +7387,22 @@
         <v>103400</v>
       </c>
       <c r="C164" s="72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D164" s="72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E164" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F164" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G164" s="72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H164" s="72" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I164" s="72" t="s">
         <v>106</v>
@@ -7414,19 +7417,19 @@
         <v>103400</v>
       </c>
       <c r="C165" s="72" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D165" s="72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E165" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F165" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G165" s="72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H165" s="72"/>
       <c r="I165" s="72" t="s">
@@ -7442,22 +7445,22 @@
         <v>103400</v>
       </c>
       <c r="C166" s="72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D166" s="72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E166" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F166" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G166" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H166" s="72" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I166" s="72" t="s">
         <v>39</v>
@@ -7472,22 +7475,22 @@
         <v>103400</v>
       </c>
       <c r="C167" s="72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D167" s="72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E167" s="72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F167" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G167" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H167" s="72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I167" s="72" t="s">
         <v>106</v>
@@ -7502,19 +7505,19 @@
         <v>103400</v>
       </c>
       <c r="C168" s="72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D168" s="72" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E168" s="72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F168" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G168" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H168" s="72"/>
       <c r="I168" s="72" t="s">
@@ -7530,22 +7533,22 @@
         <v>103400</v>
       </c>
       <c r="C169" s="72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D169" s="72" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E169" s="72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F169" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G169" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H169" s="72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I169" s="72" t="s">
         <v>39</v>
@@ -7560,22 +7563,22 @@
         <v>103400</v>
       </c>
       <c r="C170" s="72" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D170" s="72" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E170" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F170" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G170" s="72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H170" s="72" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I170" s="72" t="s">
         <v>106</v>
@@ -7590,19 +7593,19 @@
         <v>103400</v>
       </c>
       <c r="C171" s="72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D171" s="72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E171" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F171" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G171" s="72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H171" s="72"/>
       <c r="I171" s="72" t="s">
@@ -7618,22 +7621,22 @@
         <v>103400</v>
       </c>
       <c r="C172" s="72" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D172" s="72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E172" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F172" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G172" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H172" s="72" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I172" s="72" t="s">
         <v>39</v>
@@ -7648,22 +7651,22 @@
         <v>103400</v>
       </c>
       <c r="C173" s="72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D173" s="72" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E173" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F173" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G173" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H173" s="72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I173" s="72" t="s">
         <v>106</v>
@@ -7678,19 +7681,19 @@
         <v>103400</v>
       </c>
       <c r="C174" s="72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D174" s="72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E174" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F174" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G174" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H174" s="72"/>
       <c r="I174" s="72" t="s">
@@ -7706,22 +7709,22 @@
         <v>103400</v>
       </c>
       <c r="C175" s="72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D175" s="72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E175" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F175" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G175" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H175" s="72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I175" s="72" t="s">
         <v>39</v>
@@ -7736,19 +7739,19 @@
         <v>103400</v>
       </c>
       <c r="C176" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D176" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E176" s="72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F176" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G176" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H176" s="15"/>
       <c r="I176" s="72" t="s">
@@ -7764,10 +7767,10 @@
         <v>103400</v>
       </c>
       <c r="C177" s="72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D177" s="72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E177" s="72" t="s">
         <v>243</v>
@@ -7776,10 +7779,10 @@
         <v>133</v>
       </c>
       <c r="G177" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H177" s="72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I177" s="72" t="s">
         <v>39</v>
@@ -7794,10 +7797,10 @@
         <v>103400</v>
       </c>
       <c r="C178" s="72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D178" s="72" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E178" s="72" t="s">
         <v>157</v>
@@ -7806,7 +7809,7 @@
         <v>133</v>
       </c>
       <c r="G178" s="72" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H178" s="72"/>
       <c r="I178" s="72" t="s">
@@ -7825,7 +7828,7 @@
         <v>21</v>
       </c>
       <c r="D179" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E179" s="75" t="s">
         <v>243</v>
@@ -7834,16 +7837,16 @@
         <v>133</v>
       </c>
       <c r="G179" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H179" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I179" s="75" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J179" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K179" s="76" t="s">
         <v>29</v>
@@ -7857,10 +7860,10 @@
         <v>103500</v>
       </c>
       <c r="C180" s="75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D180" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E180" s="75" t="s">
         <v>243</v>
@@ -7869,16 +7872,16 @@
         <v>133</v>
       </c>
       <c r="G180" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H180" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I180" s="75" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J180" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K180" s="76" t="s">
         <v>29</v>
@@ -7898,16 +7901,16 @@
         <v>251</v>
       </c>
       <c r="E181" s="75" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F181" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G181" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H181" s="75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I181" s="75" t="s">
         <v>39</v>
@@ -7925,7 +7928,7 @@
         <v>21</v>
       </c>
       <c r="D182" s="75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E182" s="75" t="s">
         <v>146</v>
@@ -7934,7 +7937,7 @@
         <v>133</v>
       </c>
       <c r="G182" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H182" s="75" t="s">
         <v>243</v>
@@ -7953,7 +7956,7 @@
       </c>
       <c r="C183" s="75"/>
       <c r="D183" s="75" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E183" s="75" t="s">
         <v>255</v>
@@ -7962,7 +7965,7 @@
         <v>133</v>
       </c>
       <c r="G183" s="75" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H183" s="75"/>
       <c r="I183" s="75" t="s">
@@ -7981,7 +7984,7 @@
         <v>21</v>
       </c>
       <c r="D184" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E184" s="75" t="s">
         <v>243</v>
@@ -7990,13 +7993,13 @@
         <v>133</v>
       </c>
       <c r="G184" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H184" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I184" s="75" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K184" s="76" t="s">
         <v>29</v>
@@ -8010,10 +8013,10 @@
         <v>103501</v>
       </c>
       <c r="C185" s="75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D185" s="75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E185" s="75" t="s">
         <v>243</v>
@@ -8022,13 +8025,13 @@
         <v>133</v>
       </c>
       <c r="G185" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H185" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I185" s="75" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K185" s="76" t="s">
         <v>29</v>
@@ -8048,16 +8051,16 @@
         <v>251</v>
       </c>
       <c r="E186" s="75" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F186" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G186" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H186" s="75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I186" s="75" t="s">
         <v>39</v>
@@ -8075,7 +8078,7 @@
         <v>21</v>
       </c>
       <c r="D187" s="75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E187" s="75" t="s">
         <v>146</v>
@@ -8084,7 +8087,7 @@
         <v>133</v>
       </c>
       <c r="G187" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H187" s="75" t="s">
         <v>243</v>
@@ -8103,7 +8106,7 @@
       </c>
       <c r="C188" s="75"/>
       <c r="D188" s="75" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E188" s="75" t="s">
         <v>255</v>
@@ -8112,7 +8115,7 @@
         <v>133</v>
       </c>
       <c r="G188" s="75" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H188" s="75"/>
       <c r="I188" s="75" t="s">
@@ -8210,24 +8213,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" t="s">
         <v>353</v>
       </c>
-      <c r="D2" t="s">
-        <v>352</v>
-      </c>
       <c r="E2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8235,16 +8238,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8252,16 +8255,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8269,16 +8272,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8286,7 +8289,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8294,7 +8297,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8302,7 +8305,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8310,7 +8313,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8318,7 +8321,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8326,7 +8329,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8334,7 +8337,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8342,7 +8345,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8350,7 +8353,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8358,7 +8361,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8366,7 +8369,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8374,7 +8377,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8382,7 +8385,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8390,7 +8393,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8398,7 +8401,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8406,7 +8409,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8414,7 +8417,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -8422,7 +8425,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8430,7 +8433,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8438,7 +8441,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8446,7 +8449,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -8454,7 +8457,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -8462,7 +8465,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -8470,7 +8473,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -8478,7 +8481,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -8486,7 +8489,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -8494,7 +8497,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8502,7 +8505,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8510,7 +8513,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8518,7 +8521,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8526,7 +8529,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8534,7 +8537,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8542,7 +8545,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8550,7 +8553,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8558,7 +8561,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8566,7 +8569,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8574,7 +8577,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8582,7 +8585,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8590,7 +8593,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8598,7 +8601,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8606,7 +8609,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8614,7 +8617,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8622,7 +8625,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="407">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -955,19 +955,19 @@
     <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
   </si>
   <si>
+    <t>12_10</t>
+  </si>
+  <si>
     <t>改出3个bonus</t>
   </si>
   <si>
     <t>概率出现3个bonus</t>
   </si>
   <si>
-    <t>0_50|1_30|2_15|3_5</t>
+    <t>0_90|0_9|3_1</t>
   </si>
   <si>
     <t>概率出现3个SCATTER</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_19|3_1</t>
   </si>
   <si>
     <t>0_50|1_40_2_10</t>
@@ -1566,12 +1566,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6519,8 +6519,8 @@
       <c r="G134" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H134" s="10">
-        <v>12</v>
+      <c r="H134" s="10" t="s">
+        <v>265</v>
       </c>
       <c r="I134" s="10" t="s">
         <v>234</v>
@@ -6547,7 +6547,7 @@
         <v>232</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="I135" s="10" t="s">
         <v>107</v>
@@ -6562,7 +6562,7 @@
         <v>102100</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>114</v>
@@ -6574,7 +6574,7 @@
         <v>232</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>107</v>
@@ -6589,7 +6589,7 @@
         <v>102100</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>114</v>
@@ -6601,10 +6601,10 @@
         <v>232</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K137" s="68"/>
     </row>
@@ -6616,7 +6616,7 @@
         <v>102100</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>140</v>
@@ -6628,10 +6628,10 @@
         <v>232</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K138" s="68"/>
     </row>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="408">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -883,294 +883,297 @@
     <t>13_14</t>
   </si>
   <si>
-    <t>中央两个海姆</t>
+    <t>中央两个洛基</t>
   </si>
   <si>
     <t>结束特殊玩法</t>
   </si>
   <si>
+    <t>7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>概率改出2个SCATTER</t>
+  </si>
+  <si>
+    <t>常规模式出现</t>
+  </si>
+  <si>
+    <t>0_50|1_40|2_10</t>
+  </si>
+  <si>
+    <t>用于触发奖池</t>
+  </si>
+  <si>
+    <t>11_14</t>
+  </si>
+  <si>
+    <t>改出1个大奖</t>
+  </si>
+  <si>
+    <t>改出奖池符号</t>
+  </si>
+  <si>
+    <t>15_10|16_5|17_2|18_1</t>
+  </si>
+  <si>
+    <t>13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>异形位置改为不中奖图案</t>
+  </si>
+  <si>
+    <t>99999_1</t>
+  </si>
+  <si>
+    <t>3_1_1|9_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个SCATTER</t>
+  </si>
+  <si>
+    <t>11_14_15_16_17_18</t>
+  </si>
+  <si>
+    <t>改出1个19符号</t>
+  </si>
+  <si>
+    <t>改出1个20符号</t>
+  </si>
+  <si>
+    <t>10_11_12</t>
+  </si>
+  <si>
+    <t>13_10|14_5|15_2|16_1</t>
+  </si>
+  <si>
+    <t>概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>12_10</t>
+  </si>
+  <si>
+    <t>免费游戏概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>改出3个bonus</t>
+  </si>
+  <si>
+    <t>概率出现3个bonus</t>
+  </si>
+  <si>
+    <t>0_70|1_29|3_1</t>
+  </si>
+  <si>
+    <t>概率出现3个SCATTER</t>
+  </si>
+  <si>
+    <t>0_50|1_40_2_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>11_12_13_14_15_16_17</t>
+  </si>
+  <si>
+    <t>14_10|14_5|16_2|17_1</t>
+  </si>
+  <si>
+    <t>21_1_1|22_1_1|23_1_1|24_1_1</t>
+  </si>
+  <si>
+    <t>0_40|1_30|2_15|3_10|4_7|5_3</t>
+  </si>
+  <si>
+    <t>免费游戏</t>
+  </si>
+  <si>
+    <t>概率改出+1免费符号</t>
+  </si>
+  <si>
+    <t>11_12_13</t>
+  </si>
+  <si>
+    <t>0_90|1_10</t>
+  </si>
+  <si>
+    <t>10_11_12_13_14_15</t>
+  </si>
+  <si>
+    <t>12_10|13_5|14_2|15_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
+  </si>
+  <si>
+    <t>改出3个以上SCATTER</t>
+  </si>
+  <si>
+    <t>10次&amp;15次&amp;20次免费</t>
+  </si>
+  <si>
+    <t>3_70|4_25|5_5</t>
+  </si>
+  <si>
+    <t>概率改出SCATTER符号</t>
+  </si>
+  <si>
+    <t>免费游戏中概率出现</t>
+  </si>
+  <si>
+    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
+  </si>
+  <si>
+    <t>0_70|1_30</t>
+  </si>
+  <si>
+    <t>橘子福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个橘子or两个wind符号</t>
+  </si>
+  <si>
+    <t>1_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1</t>
+  </si>
+  <si>
+    <t>1_7</t>
+  </si>
+  <si>
+    <t>橘子福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个橘子or1个wind符号</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>鞭炮福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个鞭炮or两个wind符号</t>
+  </si>
+  <si>
+    <t>2_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>鞭炮福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个鞭炮or1个wind符号</t>
+  </si>
+  <si>
+    <t>红包福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个红包or两个wind符号</t>
+  </si>
+  <si>
+    <t>3_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>3_7</t>
+  </si>
+  <si>
+    <t>红包福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个红包or1个wind符号</t>
+  </si>
+  <si>
+    <t>福袋福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个福袋or两个wind符号</t>
+  </si>
+  <si>
+    <t>4_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>4_7</t>
+  </si>
+  <si>
+    <t>福袋福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个福袋or1个wind符号</t>
+  </si>
+  <si>
+    <t>玉如意福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个玉如意or两个wind符号</t>
+  </si>
+  <si>
+    <t>5_90|7_10</t>
+  </si>
+  <si>
+    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>5_7</t>
+  </si>
+  <si>
+    <t>玉如意福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个玉如意or1个wind符号</t>
+  </si>
+  <si>
+    <t>元宝福马模式(有不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出两个元宝or两个wind符号</t>
+  </si>
+  <si>
+    <t>1_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
+  </si>
+  <si>
+    <t>6_7</t>
+  </si>
+  <si>
+    <t>元宝福马模式(无不可替换元素)</t>
+  </si>
+  <si>
+    <t>改出1个元宝or1个wind符号</t>
+  </si>
+  <si>
+    <t>概率改出百搭符号</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>福马模式</t>
+  </si>
+  <si>
+    <t>改出一个大奖符号</t>
+  </si>
+  <si>
     <t>8_1</t>
   </si>
   <si>
-    <t>7_1_1|8_1_1</t>
-  </si>
-  <si>
-    <t>概率改出2个SCATTER</t>
-  </si>
-  <si>
-    <t>常规模式出现</t>
-  </si>
-  <si>
-    <t>0_50|1_40|2_10</t>
-  </si>
-  <si>
-    <t>用于触发奖池</t>
-  </si>
-  <si>
-    <t>11_14</t>
-  </si>
-  <si>
-    <t>改出1个大奖</t>
-  </si>
-  <si>
-    <t>改出奖池符号</t>
-  </si>
-  <si>
-    <t>15_10|16_5|17_2|18_1</t>
-  </si>
-  <si>
-    <t>13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>异形位置改为不中奖图案</t>
-  </si>
-  <si>
-    <t>99999_1</t>
-  </si>
-  <si>
-    <t>3_1_1|9_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个SCATTER</t>
-  </si>
-  <si>
-    <t>11_14_15_16_17_18</t>
-  </si>
-  <si>
-    <t>改出1个19符号</t>
-  </si>
-  <si>
-    <t>改出1个20符号</t>
-  </si>
-  <si>
-    <t>10_11_12</t>
-  </si>
-  <si>
-    <t>13_10|14_5|15_2|16_1</t>
-  </si>
-  <si>
-    <t>概率出现百搭符号</t>
-  </si>
-  <si>
-    <t>4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1</t>
-  </si>
-  <si>
-    <t>改出3个bonus</t>
-  </si>
-  <si>
-    <t>概率出现3个bonus</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_15|3_5</t>
-  </si>
-  <si>
-    <t>概率出现3个SCATTER</t>
-  </si>
-  <si>
-    <t>0_50|1_30|2_19|3_1</t>
-  </si>
-  <si>
-    <t>0_50|1_40_2_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1|21_1_1|22_1_1|23_1_1|24_1_1</t>
-  </si>
-  <si>
-    <t>11_12_13_14_15_16_17</t>
-  </si>
-  <si>
-    <t>14_10|14_5|16_2|17_1</t>
-  </si>
-  <si>
-    <t>21_1_1|22_1_1|23_1_1|24_1_1</t>
-  </si>
-  <si>
-    <t>0_40|1_30|2_15|3_10|4_7|5_3</t>
-  </si>
-  <si>
-    <t>免费游戏</t>
-  </si>
-  <si>
-    <t>概率改出+1免费符号</t>
-  </si>
-  <si>
-    <t>11_12_13</t>
-  </si>
-  <si>
-    <t>0_90|1_10</t>
-  </si>
-  <si>
-    <t>10_11_12_13_14_15</t>
-  </si>
-  <si>
-    <t>12_10|13_5|14_2|15_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1</t>
-  </si>
-  <si>
-    <t>改出3个以上SCATTER</t>
-  </si>
-  <si>
-    <t>10次&amp;15次&amp;20次免费</t>
-  </si>
-  <si>
-    <t>3_70|4_25|5_5</t>
-  </si>
-  <si>
-    <t>概率改出SCATTER符号</t>
-  </si>
-  <si>
-    <t>免费游戏中概率出现</t>
-  </si>
-  <si>
-    <t>0_1000|1_500|2_200|3_10|4_5|5_1</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
-  </si>
-  <si>
-    <t>0_70|1_30</t>
-  </si>
-  <si>
-    <t>橘子福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个橘子or两个wind符号</t>
-  </si>
-  <si>
-    <t>1_90|7_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1</t>
-  </si>
-  <si>
-    <t>1_7</t>
-  </si>
-  <si>
-    <t>橘子福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个橘子or1个wind符号</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>鞭炮福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个鞭炮or两个wind符号</t>
-  </si>
-  <si>
-    <t>2_90|7_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>鞭炮福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个鞭炮or1个wind符号</t>
-  </si>
-  <si>
-    <t>红包福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个红包or两个wind符号</t>
-  </si>
-  <si>
-    <t>3_90|7_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>3_7</t>
-  </si>
-  <si>
-    <t>红包福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个红包or1个wind符号</t>
-  </si>
-  <si>
-    <t>福袋福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个福袋or两个wind符号</t>
-  </si>
-  <si>
-    <t>4_90|7_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>4_7</t>
-  </si>
-  <si>
-    <t>福袋福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个福袋or1个wind符号</t>
-  </si>
-  <si>
-    <t>玉如意福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个玉如意or两个wind符号</t>
-  </si>
-  <si>
-    <t>5_90|7_10</t>
-  </si>
-  <si>
-    <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>5_7</t>
-  </si>
-  <si>
-    <t>玉如意福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个玉如意or1个wind符号</t>
-  </si>
-  <si>
-    <t>元宝福马模式(有不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出两个元宝or两个wind符号</t>
-  </si>
-  <si>
-    <t>1_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1</t>
-  </si>
-  <si>
-    <t>6_7</t>
-  </si>
-  <si>
-    <t>元宝福马模式(无不可替换元素)</t>
-  </si>
-  <si>
-    <t>改出1个元宝or1个wind符号</t>
-  </si>
-  <si>
-    <t>概率改出百搭符号</t>
-  </si>
-  <si>
-    <t>7_1</t>
-  </si>
-  <si>
-    <t>福马模式</t>
-  </si>
-  <si>
-    <t>改出一个大奖符号</t>
-  </si>
-  <si>
     <t>1_2_3_4_5_6_7</t>
   </si>
   <si>
@@ -1183,7 +1186,7 @@
     <t>1_1_1|2_1_1|3_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1</t>
   </si>
   <si>
-    <t>7_9_10_11_12</t>
+    <t>7_8_9_10_11_12</t>
   </si>
   <si>
     <t>0_500|1_150|2_150|3_100|4_80|5_15|6_5</t>
@@ -2618,7 +2621,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N194"/>
+  <dimension ref="A1:N195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -6250,13 +6253,13 @@
         <v>242</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>242</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H124" s="9"/>
       <c r="I124" s="9" t="s">
@@ -6272,10 +6275,10 @@
         <v>102200</v>
       </c>
       <c r="C125" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D125" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>146</v>
@@ -6287,7 +6290,7 @@
         <v>233</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K125" s="67"/>
     </row>
@@ -6302,7 +6305,7 @@
         <v>226</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>146</v>
@@ -6312,7 +6315,7 @@
         <v>237</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I126" s="9" t="s">
         <v>106</v>
@@ -6327,17 +6330,17 @@
         <v>102200</v>
       </c>
       <c r="C127" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D127" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="E127" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="E127" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="F127" s="9"/>
       <c r="G127" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H127" s="9" t="s">
         <v>233</v>
@@ -6355,15 +6358,15 @@
         <v>102200</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D128" s="9"/>
       <c r="E128" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F128" s="9"/>
       <c r="G128" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H128" s="9"/>
       <c r="I128" s="9" t="s">
@@ -6379,7 +6382,7 @@
         <v>102200</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>146</v>
@@ -6388,7 +6391,7 @@
         <v>232</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I129" s="9" t="s">
         <v>107</v>
@@ -6403,7 +6406,7 @@
         <v>102200</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>41</v>
@@ -6424,7 +6427,7 @@
         <v>102200</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>46</v>
@@ -6460,7 +6463,7 @@
         <v>237</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I132" s="10" t="s">
         <v>106</v>
@@ -6481,16 +6484,16 @@
         <v>228</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>133</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I133" s="10" t="s">
         <v>39</v>
@@ -6505,10 +6508,10 @@
         <v>102100</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>136</v>
@@ -6517,10 +6520,10 @@
         <v>133</v>
       </c>
       <c r="G134" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="H134" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="H134" s="10">
-        <v>12</v>
       </c>
       <c r="I134" s="10" t="s">
         <v>234</v>
@@ -6529,43 +6532,43 @@
     </row>
     <row r="135" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A135" s="10">
-        <v>10210031</v>
+        <v>10210022</v>
       </c>
       <c r="B135" s="10">
         <v>102100</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>133</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="K135" s="68"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A136" s="10">
-        <v>10210041</v>
+        <v>10210031</v>
       </c>
       <c r="B136" s="10">
         <v>102100</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>133</v>
@@ -6574,7 +6577,7 @@
         <v>232</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>107</v>
@@ -6583,7 +6586,7 @@
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A137" s="10">
-        <v>10210042</v>
+        <v>10210041</v>
       </c>
       <c r="B137" s="10">
         <v>102100</v>
@@ -6601,25 +6604,25 @@
         <v>232</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="K137" s="68"/>
     </row>
     <row r="138" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="10">
-        <v>10210032</v>
+        <v>10210042</v>
       </c>
       <c r="B138" s="10">
         <v>102100</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F138" s="10" t="s">
         <v>133</v>
@@ -6628,25 +6631,22 @@
         <v>232</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K138" s="68"/>
     </row>
     <row r="139" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="10">
-        <v>10210051</v>
+        <v>10210032</v>
       </c>
       <c r="B139" s="10">
         <v>102100</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>140</v>
@@ -6658,46 +6658,46 @@
         <v>232</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I139" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="K139" s="68"/>
+    </row>
+    <row r="140" s="10" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A140" s="10">
+        <v>10210051</v>
+      </c>
+      <c r="B140" s="10">
+        <v>102100</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I140" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="K139" s="68"/>
-    </row>
-    <row r="140" s="11" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A140" s="11">
-        <v>10180001</v>
-      </c>
-      <c r="B140" s="11">
-        <v>101800</v>
-      </c>
-      <c r="C140" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D140" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E140" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F140" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="H140" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="I140" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="K140" s="69"/>
+      <c r="K140" s="68"/>
     </row>
     <row r="141" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A141" s="11">
-        <v>10180002</v>
+        <v>10180001</v>
       </c>
       <c r="B141" s="11">
         <v>101800</v>
@@ -6706,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="E141" s="11" t="s">
         <v>140</v>
@@ -6721,13 +6721,13 @@
         <v>272</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>270</v>
+        <v>106</v>
       </c>
       <c r="K141" s="69"/>
     </row>
     <row r="142" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A142" s="11">
-        <v>10180011</v>
+        <v>10180002</v>
       </c>
       <c r="B142" s="11">
         <v>101800</v>
@@ -6736,100 +6736,100 @@
         <v>21</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H142" s="11" t="s">
         <v>272</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>39</v>
+        <v>270</v>
       </c>
       <c r="K142" s="69"/>
     </row>
     <row r="143" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A143" s="11">
-        <v>10180021</v>
+        <v>10180011</v>
       </c>
       <c r="B143" s="11">
         <v>101800</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>71</v>
+        <v>274</v>
       </c>
       <c r="H143" s="11" t="s">
         <v>272</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="K143" s="69"/>
     </row>
     <row r="144" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A144" s="11">
-        <v>10180031</v>
+        <v>10180021</v>
       </c>
       <c r="B144" s="11">
         <v>101800</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>271</v>
+        <v>71</v>
       </c>
       <c r="H144" s="11" t="s">
         <v>272</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>107</v>
+        <v>275</v>
       </c>
       <c r="K144" s="69"/>
     </row>
     <row r="145" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A145" s="11">
-        <v>10180041</v>
+        <v>10180031</v>
       </c>
       <c r="B145" s="11">
         <v>101800</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F145" s="11" t="s">
         <v>133</v>
@@ -6838,46 +6838,46 @@
         <v>271</v>
       </c>
       <c r="H145" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="I145" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K145" s="69"/>
+    </row>
+    <row r="146" s="11" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A146" s="11">
+        <v>10180041</v>
+      </c>
+      <c r="B146" s="11">
+        <v>101800</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G146" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H146" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="I145" s="11" t="s">
+      <c r="I146" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="K145" s="69"/>
-    </row>
-    <row r="146" s="12" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A146" s="12">
-        <v>10250001</v>
-      </c>
-      <c r="B146" s="12">
-        <v>102500</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E146" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="G146" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I146" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="K146" s="70"/>
+      <c r="K146" s="69"/>
     </row>
     <row r="147" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A147" s="12">
-        <v>10250002</v>
+        <v>10250001</v>
       </c>
       <c r="B147" s="12">
         <v>102500</v>
@@ -6886,7 +6886,7 @@
         <v>21</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="E147" s="12" t="s">
         <v>136</v>
@@ -6901,13 +6901,13 @@
         <v>280</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="K147" s="70"/>
     </row>
     <row r="148" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A148" s="12">
-        <v>10250011</v>
+        <v>10250002</v>
       </c>
       <c r="B148" s="12">
         <v>102500</v>
@@ -6916,101 +6916,103 @@
         <v>21</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>133</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="H148" s="12" t="s">
         <v>280</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K148" s="70"/>
     </row>
     <row r="149" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A149" s="12">
-        <v>10250021</v>
+        <v>10250011</v>
       </c>
       <c r="B149" s="12">
         <v>102500</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>114</v>
+        <v>281</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>133</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="H149" s="12" t="s">
         <v>280</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="K149" s="70"/>
     </row>
     <row r="150" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A150" s="12">
-        <v>10250031</v>
+        <v>10250021</v>
       </c>
       <c r="B150" s="12">
         <v>102500</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F150" s="12" t="s">
-        <v>284</v>
+        <v>133</v>
       </c>
       <c r="G150" s="12" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="H150" s="12" t="s">
         <v>280</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="K150" s="70"/>
     </row>
     <row r="151" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A151" s="12">
-        <v>10250032</v>
+        <v>10250031</v>
       </c>
       <c r="B151" s="12">
         <v>102500</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="D151" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>283</v>
+      </c>
       <c r="E151" s="12" t="s">
         <v>136</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G151" s="12" t="s">
         <v>232</v>
@@ -7019,43 +7021,41 @@
         <v>280</v>
       </c>
       <c r="I151" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="K151" s="70"/>
+    </row>
+    <row r="152" s="12" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A152" s="12">
+        <v>10250032</v>
+      </c>
+      <c r="B152" s="12">
+        <v>102500</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D152" s="12"/>
+      <c r="E152" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G152" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="H152" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I152" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="K151" s="70"/>
-    </row>
-    <row r="152" s="13" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A152" s="13">
-        <v>10230001</v>
-      </c>
-      <c r="B152" s="13">
-        <v>102300</v>
-      </c>
-      <c r="C152" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E152" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G152" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="H152" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="I152" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="K152" s="71"/>
+      <c r="K152" s="70"/>
     </row>
     <row r="153" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A153" s="13">
-        <v>10230002</v>
+        <v>10230001</v>
       </c>
       <c r="B153" s="13">
         <v>102300</v>
@@ -7064,7 +7064,7 @@
         <v>21</v>
       </c>
       <c r="D153" s="13" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="E153" s="13" t="s">
         <v>136</v>
@@ -7079,13 +7079,13 @@
         <v>160</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="K153" s="71"/>
     </row>
     <row r="154" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A154" s="13">
-        <v>10230003</v>
+        <v>10230002</v>
       </c>
       <c r="B154" s="13">
         <v>102300</v>
@@ -7094,7 +7094,7 @@
         <v>21</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="E154" s="13" t="s">
         <v>136</v>
@@ -7109,13 +7109,13 @@
         <v>160</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="K154" s="71"/>
     </row>
     <row r="155" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A155" s="13">
-        <v>10230011</v>
+        <v>10230003</v>
       </c>
       <c r="B155" s="13">
         <v>102300</v>
@@ -7124,70 +7124,70 @@
         <v>21</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="F155" s="13" t="s">
         <v>133</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>38</v>
+        <v>289</v>
       </c>
       <c r="H155" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="K155" s="71"/>
     </row>
     <row r="156" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A156" s="13">
-        <v>10230021</v>
+        <v>10230011</v>
       </c>
       <c r="B156" s="13">
         <v>102300</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>114</v>
+        <v>261</v>
       </c>
       <c r="F156" s="13" t="s">
         <v>133</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>289</v>
+        <v>38</v>
       </c>
       <c r="H156" s="13" t="s">
         <v>160</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="K156" s="71"/>
     </row>
     <row r="157" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A157" s="13">
-        <v>10230031</v>
+        <v>10230021</v>
       </c>
       <c r="B157" s="13">
         <v>102300</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F157" s="13" t="s">
         <v>133</v>
@@ -7199,52 +7199,52 @@
         <v>160</v>
       </c>
       <c r="I157" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="K157" s="71"/>
+    </row>
+    <row r="158" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A158" s="13">
+        <v>10230031</v>
+      </c>
+      <c r="B158" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C158" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F158" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G158" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="H158" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I158" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="K157" s="71"/>
-    </row>
-    <row r="158" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A158" s="72">
-        <v>10340001</v>
-      </c>
-      <c r="B158" s="72">
-        <v>103400</v>
-      </c>
-      <c r="C158" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="D158" s="72" t="s">
-        <v>292</v>
-      </c>
-      <c r="E158" s="72" t="s">
-        <v>293</v>
-      </c>
-      <c r="F158" s="72" t="s">
-        <v>133</v>
-      </c>
-      <c r="G158" s="72" t="s">
-        <v>294</v>
-      </c>
-      <c r="H158" s="72" t="s">
-        <v>295</v>
-      </c>
-      <c r="I158" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="K158" s="73"/>
+      <c r="K158" s="71"/>
     </row>
     <row r="159" s="14" customFormat="1" ht="16.5" spans="1:11">
       <c r="A159" s="72">
-        <v>10340011</v>
+        <v>10340001</v>
       </c>
       <c r="B159" s="72">
         <v>103400</v>
       </c>
       <c r="C159" s="72" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D159" s="72" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E159" s="72" t="s">
         <v>293</v>
@@ -7255,21 +7255,23 @@
       <c r="G159" s="72" t="s">
         <v>294</v>
       </c>
-      <c r="H159" s="72"/>
+      <c r="H159" s="72" t="s">
+        <v>295</v>
+      </c>
       <c r="I159" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K159" s="73"/>
     </row>
-    <row r="160" s="15" customFormat="1" ht="16.5" spans="1:11">
+    <row r="160" s="14" customFormat="1" ht="16.5" spans="1:11">
       <c r="A160" s="72">
-        <v>10340021</v>
+        <v>10340011</v>
       </c>
       <c r="B160" s="72">
         <v>103400</v>
       </c>
       <c r="C160" s="72" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D160" s="72" t="s">
         <v>297</v>
@@ -7281,58 +7283,56 @@
         <v>133</v>
       </c>
       <c r="G160" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H160" s="72" t="s">
-        <v>295</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="H160" s="72"/>
       <c r="I160" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="K160" s="74"/>
+      <c r="K160" s="73"/>
     </row>
     <row r="161" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A161" s="72">
-        <v>10340002</v>
+        <v>10340021</v>
       </c>
       <c r="B161" s="72">
         <v>103400</v>
       </c>
       <c r="C161" s="72" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D161" s="72" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E161" s="72" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="F161" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G161" s="72" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="H161" s="72" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I161" s="72" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K161" s="74"/>
     </row>
     <row r="162" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A162" s="72">
-        <v>10340012</v>
+        <v>10340002</v>
       </c>
       <c r="B162" s="72">
         <v>103400</v>
       </c>
       <c r="C162" s="72" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D162" s="72" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E162" s="72" t="s">
         <v>301</v>
@@ -7343,21 +7343,23 @@
       <c r="G162" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="H162" s="72"/>
+      <c r="H162" s="72" t="s">
+        <v>303</v>
+      </c>
       <c r="I162" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K162" s="74"/>
     </row>
     <row r="163" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A163" s="72">
-        <v>10340022</v>
+        <v>10340012</v>
       </c>
       <c r="B163" s="72">
         <v>103400</v>
       </c>
       <c r="C163" s="72" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D163" s="72" t="s">
         <v>305</v>
@@ -7369,11 +7371,9 @@
         <v>133</v>
       </c>
       <c r="G163" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H163" s="72" t="s">
-        <v>303</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="H163" s="72"/>
       <c r="I163" s="72" t="s">
         <v>39</v>
       </c>
@@ -7381,46 +7381,46 @@
     </row>
     <row r="164" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A164" s="72">
-        <v>10340003</v>
+        <v>10340022</v>
       </c>
       <c r="B164" s="72">
         <v>103400</v>
       </c>
       <c r="C164" s="72" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D164" s="72" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E164" s="72" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F164" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G164" s="72" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="H164" s="72" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="I164" s="72" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K164" s="74"/>
     </row>
     <row r="165" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A165" s="72">
-        <v>10340013</v>
+        <v>10340003</v>
       </c>
       <c r="B165" s="72">
         <v>103400</v>
       </c>
       <c r="C165" s="72" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D165" s="72" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E165" s="72" t="s">
         <v>308</v>
@@ -7431,21 +7431,23 @@
       <c r="G165" s="72" t="s">
         <v>309</v>
       </c>
-      <c r="H165" s="72"/>
+      <c r="H165" s="72" t="s">
+        <v>310</v>
+      </c>
       <c r="I165" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K165" s="74"/>
     </row>
     <row r="166" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A166" s="72">
-        <v>10340023</v>
+        <v>10340013</v>
       </c>
       <c r="B166" s="72">
         <v>103400</v>
       </c>
       <c r="C166" s="72" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D166" s="72" t="s">
         <v>312</v>
@@ -7457,11 +7459,9 @@
         <v>133</v>
       </c>
       <c r="G166" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H166" s="72" t="s">
-        <v>310</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H166" s="72"/>
       <c r="I166" s="72" t="s">
         <v>39</v>
       </c>
@@ -7469,46 +7469,46 @@
     </row>
     <row r="167" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A167" s="72">
-        <v>10340004</v>
+        <v>10340023</v>
       </c>
       <c r="B167" s="72">
         <v>103400</v>
       </c>
       <c r="C167" s="72" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D167" s="72" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E167" s="72" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F167" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G167" s="72" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="H167" s="72" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I167" s="72" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K167" s="74"/>
     </row>
     <row r="168" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A168" s="72">
-        <v>10340014</v>
+        <v>10340004</v>
       </c>
       <c r="B168" s="72">
         <v>103400</v>
       </c>
       <c r="C168" s="72" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D168" s="72" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E168" s="72" t="s">
         <v>315</v>
@@ -7519,21 +7519,23 @@
       <c r="G168" s="72" t="s">
         <v>316</v>
       </c>
-      <c r="H168" s="72"/>
+      <c r="H168" s="72" t="s">
+        <v>317</v>
+      </c>
       <c r="I168" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K168" s="74"/>
     </row>
     <row r="169" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A169" s="72">
-        <v>10340024</v>
+        <v>10340014</v>
       </c>
       <c r="B169" s="72">
         <v>103400</v>
       </c>
       <c r="C169" s="72" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D169" s="72" t="s">
         <v>319</v>
@@ -7545,11 +7547,9 @@
         <v>133</v>
       </c>
       <c r="G169" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H169" s="72" t="s">
-        <v>317</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="H169" s="72"/>
       <c r="I169" s="72" t="s">
         <v>39</v>
       </c>
@@ -7557,46 +7557,46 @@
     </row>
     <row r="170" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A170" s="72">
-        <v>10340005</v>
+        <v>10340024</v>
       </c>
       <c r="B170" s="72">
         <v>103400</v>
       </c>
       <c r="C170" s="72" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D170" s="72" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E170" s="72" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F170" s="72" t="s">
         <v>133</v>
       </c>
       <c r="G170" s="72" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="H170" s="72" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="I170" s="72" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K170" s="74"/>
     </row>
     <row r="171" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A171" s="72">
-        <v>10340015</v>
+        <v>10340005</v>
       </c>
       <c r="B171" s="72">
         <v>103400</v>
       </c>
       <c r="C171" s="72" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D171" s="72" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E171" s="72" t="s">
         <v>322</v>
@@ -7607,21 +7607,23 @@
       <c r="G171" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="H171" s="72"/>
+      <c r="H171" s="72" t="s">
+        <v>324</v>
+      </c>
       <c r="I171" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K171" s="74"/>
     </row>
     <row r="172" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A172" s="72">
-        <v>10340025</v>
+        <v>10340015</v>
       </c>
       <c r="B172" s="72">
         <v>103400</v>
       </c>
       <c r="C172" s="72" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D172" s="72" t="s">
         <v>326</v>
@@ -7633,11 +7635,9 @@
         <v>133</v>
       </c>
       <c r="G172" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H172" s="72" t="s">
-        <v>324</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="H172" s="72"/>
       <c r="I172" s="72" t="s">
         <v>39</v>
       </c>
@@ -7645,16 +7645,16 @@
     </row>
     <row r="173" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A173" s="72">
-        <v>10340006</v>
+        <v>10340025</v>
       </c>
       <c r="B173" s="72">
         <v>103400</v>
       </c>
       <c r="C173" s="72" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D173" s="72" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E173" s="72" t="s">
         <v>322</v>
@@ -7663,28 +7663,28 @@
         <v>133</v>
       </c>
       <c r="G173" s="72" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="H173" s="72" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="I173" s="72" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K173" s="74"/>
     </row>
     <row r="174" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A174" s="72">
-        <v>10340016</v>
+        <v>10340006</v>
       </c>
       <c r="B174" s="72">
         <v>103400</v>
       </c>
       <c r="C174" s="72" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D174" s="72" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E174" s="72" t="s">
         <v>322</v>
@@ -7695,21 +7695,23 @@
       <c r="G174" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="H174" s="72"/>
+      <c r="H174" s="72" t="s">
+        <v>330</v>
+      </c>
       <c r="I174" s="72" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="K174" s="74"/>
     </row>
     <row r="175" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A175" s="72">
-        <v>10340026</v>
+        <v>10340016</v>
       </c>
       <c r="B175" s="72">
         <v>103400</v>
       </c>
       <c r="C175" s="72" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D175" s="72" t="s">
         <v>332</v>
@@ -7721,11 +7723,9 @@
         <v>133</v>
       </c>
       <c r="G175" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="H175" s="72" t="s">
-        <v>330</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="H175" s="72"/>
       <c r="I175" s="72" t="s">
         <v>39</v>
       </c>
@@ -7733,19 +7733,19 @@
     </row>
     <row r="176" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A176" s="72">
-        <v>10340007</v>
+        <v>10340026</v>
       </c>
       <c r="B176" s="72">
         <v>103400</v>
       </c>
       <c r="C176" s="72" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D176" s="72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E176" s="72" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="F176" s="72" t="s">
         <v>133</v>
@@ -7753,27 +7753,29 @@
       <c r="G176" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="H176" s="15"/>
+      <c r="H176" s="72" t="s">
+        <v>330</v>
+      </c>
       <c r="I176" s="72" t="s">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="K176" s="74"/>
     </row>
-    <row r="177" s="14" customFormat="1" ht="16.5" spans="1:11">
+    <row r="177" s="15" customFormat="1" ht="16.5" spans="1:11">
       <c r="A177" s="72">
-        <v>10340008</v>
+        <v>10340007</v>
       </c>
       <c r="B177" s="72">
         <v>103400</v>
       </c>
       <c r="C177" s="72" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D177" s="72" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E177" s="72" t="s">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="F177" s="72" t="s">
         <v>133</v>
@@ -7781,17 +7783,15 @@
       <c r="G177" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="H177" s="72" t="s">
-        <v>337</v>
-      </c>
+      <c r="H177" s="15"/>
       <c r="I177" s="72" t="s">
-        <v>39</v>
-      </c>
-      <c r="K177" s="73"/>
+        <v>275</v>
+      </c>
+      <c r="K177" s="74"/>
     </row>
     <row r="178" s="14" customFormat="1" ht="16.5" spans="1:11">
       <c r="A178" s="72">
-        <v>10340009</v>
+        <v>10340008</v>
       </c>
       <c r="B178" s="72">
         <v>103400</v>
@@ -7800,10 +7800,10 @@
         <v>335</v>
       </c>
       <c r="D178" s="72" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E178" s="72" t="s">
-        <v>157</v>
+        <v>337</v>
       </c>
       <c r="F178" s="72" t="s">
         <v>133</v>
@@ -7811,77 +7811,72 @@
       <c r="G178" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="H178" s="72"/>
+      <c r="H178" s="72" t="s">
+        <v>338</v>
+      </c>
       <c r="I178" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="K178" s="73"/>
+    </row>
+    <row r="179" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A179" s="72">
+        <v>10340009</v>
+      </c>
+      <c r="B179" s="72">
+        <v>103400</v>
+      </c>
+      <c r="C179" s="72" t="s">
+        <v>335</v>
+      </c>
+      <c r="D179" s="72" t="s">
+        <v>339</v>
+      </c>
+      <c r="E179" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="K178" s="73"/>
-    </row>
-    <row r="179" s="16" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A179" s="75">
-        <v>10350001</v>
-      </c>
-      <c r="B179" s="75">
-        <v>103500</v>
-      </c>
-      <c r="C179" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D179" s="75" t="s">
-        <v>339</v>
-      </c>
-      <c r="E179" s="75" t="s">
-        <v>243</v>
-      </c>
-      <c r="F179" s="75" t="s">
+      <c r="F179" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="G179" s="75" t="s">
-        <v>340</v>
-      </c>
-      <c r="H179" s="75" t="s">
-        <v>341</v>
-      </c>
-      <c r="I179" s="75" t="s">
-        <v>342</v>
-      </c>
-      <c r="J179" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="K179" s="76" t="s">
-        <v>29</v>
-      </c>
+      <c r="G179" s="72" t="s">
+        <v>298</v>
+      </c>
+      <c r="H179" s="72"/>
+      <c r="I179" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="K179" s="73"/>
     </row>
     <row r="180" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A180" s="75">
-        <v>10350002</v>
+        <v>10350001</v>
       </c>
       <c r="B180" s="75">
         <v>103500</v>
       </c>
       <c r="C180" s="75" t="s">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="D180" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E180" s="75" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="F180" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G180" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H180" s="75" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I180" s="75" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J180" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K180" s="76" t="s">
         <v>29</v>
@@ -7889,37 +7884,42 @@
     </row>
     <row r="181" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A181" s="75">
-        <v>10350012</v>
+        <v>10350002</v>
       </c>
       <c r="B181" s="75">
         <v>103500</v>
       </c>
       <c r="C181" s="75" t="s">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="D181" s="75" t="s">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="E181" s="75" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F181" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G181" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H181" s="75" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I181" s="75" t="s">
-        <v>39</v>
-      </c>
-      <c r="K181" s="76"/>
+        <v>346</v>
+      </c>
+      <c r="J181" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="K181" s="76" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="182" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A182" s="75">
-        <v>10350013</v>
+        <v>10350012</v>
       </c>
       <c r="B182" s="75">
         <v>103500</v>
@@ -7928,19 +7928,19 @@
         <v>21</v>
       </c>
       <c r="D182" s="75" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="E182" s="75" t="s">
-        <v>146</v>
+        <v>347</v>
       </c>
       <c r="F182" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G182" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H182" s="75" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="I182" s="75" t="s">
         <v>39</v>
@@ -7949,89 +7949,90 @@
     </row>
     <row r="183" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A183" s="75">
-        <v>10350014</v>
+        <v>10350013</v>
       </c>
       <c r="B183" s="75">
         <v>103500</v>
       </c>
-      <c r="C183" s="75"/>
+      <c r="C183" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="D183" s="75" t="s">
         <v>349</v>
       </c>
       <c r="E183" s="75" t="s">
-        <v>255</v>
+        <v>146</v>
       </c>
       <c r="F183" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G183" s="75" t="s">
-        <v>350</v>
-      </c>
-      <c r="H183" s="75"/>
+        <v>341</v>
+      </c>
+      <c r="H183" s="75" t="s">
+        <v>337</v>
+      </c>
       <c r="I183" s="75" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="K183" s="76"/>
     </row>
     <row r="184" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A184" s="75">
-        <v>10350101</v>
+        <v>10350014</v>
       </c>
       <c r="B184" s="75">
-        <v>103501</v>
-      </c>
-      <c r="C184" s="75" t="s">
-        <v>21</v>
-      </c>
+        <v>103500</v>
+      </c>
+      <c r="C184" s="75"/>
       <c r="D184" s="75" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="E184" s="75" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F184" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G184" s="75" t="s">
-        <v>340</v>
-      </c>
-      <c r="H184" s="75" t="s">
-        <v>341</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H184" s="75"/>
       <c r="I184" s="75" t="s">
-        <v>342</v>
-      </c>
-      <c r="K184" s="76" t="s">
-        <v>29</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="K184" s="76"/>
     </row>
     <row r="185" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A185" s="75">
-        <v>10350102</v>
+        <v>10350101</v>
       </c>
       <c r="B185" s="75">
         <v>103501</v>
       </c>
       <c r="C185" s="75" t="s">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="D185" s="75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E185" s="75" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="F185" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G185" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H185" s="75" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I185" s="75" t="s">
-        <v>345</v>
+        <v>343</v>
+      </c>
+      <c r="J185" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="K185" s="76" t="s">
         <v>29</v>
@@ -8039,37 +8040,42 @@
     </row>
     <row r="186" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A186" s="75">
-        <v>10350112</v>
+        <v>10350102</v>
       </c>
       <c r="B186" s="75">
         <v>103501</v>
       </c>
       <c r="C186" s="75" t="s">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="D186" s="75" t="s">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="E186" s="75" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F186" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G186" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H186" s="75" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I186" s="75" t="s">
-        <v>39</v>
-      </c>
-      <c r="K186" s="76"/>
+        <v>346</v>
+      </c>
+      <c r="J186" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="K186" s="76" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="187" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A187" s="75">
-        <v>10350113</v>
+        <v>10350112</v>
       </c>
       <c r="B187" s="75">
         <v>103501</v>
@@ -8078,19 +8084,19 @@
         <v>21</v>
       </c>
       <c r="D187" s="75" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="E187" s="75" t="s">
-        <v>146</v>
+        <v>347</v>
       </c>
       <c r="F187" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G187" s="75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H187" s="75" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="I187" s="75" t="s">
         <v>39</v>
@@ -8099,40 +8105,58 @@
     </row>
     <row r="188" s="16" customFormat="1" ht="16.5" spans="1:11">
       <c r="A188" s="75">
-        <v>10350114</v>
+        <v>10350113</v>
       </c>
       <c r="B188" s="75">
         <v>103501</v>
       </c>
-      <c r="C188" s="75"/>
+      <c r="C188" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="D188" s="75" t="s">
         <v>349</v>
       </c>
       <c r="E188" s="75" t="s">
-        <v>255</v>
+        <v>146</v>
       </c>
       <c r="F188" s="75" t="s">
         <v>133</v>
       </c>
       <c r="G188" s="75" t="s">
+        <v>341</v>
+      </c>
+      <c r="H188" s="75" t="s">
+        <v>337</v>
+      </c>
+      <c r="I188" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="K188" s="76"/>
+    </row>
+    <row r="189" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A189" s="75">
+        <v>10350114</v>
+      </c>
+      <c r="B189" s="75">
+        <v>103501</v>
+      </c>
+      <c r="C189" s="75"/>
+      <c r="D189" s="75" t="s">
         <v>350</v>
       </c>
-      <c r="H188" s="75"/>
-      <c r="I188" s="75" t="s">
+      <c r="E189" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="F189" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="G189" s="75" t="s">
+        <v>351</v>
+      </c>
+      <c r="H189" s="75"/>
+      <c r="I189" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="K188" s="76"/>
-    </row>
-    <row r="189" s="16" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A189" s="75"/>
-      <c r="B189" s="75"/>
-      <c r="C189" s="75"/>
-      <c r="D189" s="75"/>
-      <c r="E189" s="75"/>
-      <c r="F189" s="75"/>
-      <c r="G189" s="75"/>
-      <c r="H189" s="75"/>
-      <c r="I189" s="75"/>
       <c r="K189" s="76"/>
     </row>
     <row r="190" s="16" customFormat="1" ht="16.5" spans="1:11">
@@ -8194,6 +8218,18 @@
       <c r="H194" s="75"/>
       <c r="I194" s="75"/>
       <c r="K194" s="76"/>
+    </row>
+    <row r="195" s="16" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A195" s="75"/>
+      <c r="B195" s="75"/>
+      <c r="C195" s="75"/>
+      <c r="D195" s="75"/>
+      <c r="E195" s="75"/>
+      <c r="F195" s="75"/>
+      <c r="G195" s="75"/>
+      <c r="H195" s="75"/>
+      <c r="I195" s="75"/>
+      <c r="K195" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8213,24 +8249,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D2" t="s">
         <v>354</v>
       </c>
-      <c r="D2" t="s">
-        <v>353</v>
-      </c>
       <c r="E2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8238,16 +8274,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8255,16 +8291,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8272,16 +8308,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8289,7 +8325,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8297,7 +8333,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8305,7 +8341,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8313,7 +8349,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8321,7 +8357,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8329,7 +8365,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8337,7 +8373,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8345,7 +8381,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8353,7 +8389,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8361,7 +8397,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8369,7 +8405,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8377,7 +8413,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8385,7 +8421,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8393,7 +8429,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8401,7 +8437,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -8409,7 +8445,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8417,7 +8453,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -8425,7 +8461,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8433,7 +8469,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -8441,7 +8477,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -8449,7 +8485,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -8457,7 +8493,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -8465,7 +8501,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -8473,7 +8509,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -8481,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -8489,7 +8525,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -8497,7 +8533,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8505,7 +8541,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -8513,7 +8549,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -8521,7 +8557,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8529,7 +8565,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -8537,7 +8573,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8545,7 +8581,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8553,7 +8589,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8561,7 +8597,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8569,7 +8605,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -8577,7 +8613,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -8585,7 +8621,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -8593,7 +8629,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -8601,7 +8637,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8609,7 +8645,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -8617,7 +8653,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8625,7 +8661,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialGird.xlsx
+++ b/slots/resources/sample/SpecialGird.xlsx
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="416">
   <si>
     <t>小游戏ID</t>
   </si>
@@ -1030,7 +1030,13 @@
     <t>1_1_1|2_1_1|3_1_1|4_1_1|5_1_1|6_1_1|7_1_1|8_1_1|9_1_1|10_1_1|11_1_1|12_1_1|13_1_1|14_1_1|15_1_1|16_1_1|17_1_1|18_1_1|19_1_1|20_1_1</t>
   </si>
   <si>
-    <t>0_70|1_30</t>
+    <t>普通模式概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>免费模式概率出现百搭符号</t>
+  </si>
+  <si>
+    <t>0_50|1_30|2_15|3_5</t>
   </si>
   <si>
     <t>橘子福马模式(有不可替换元素)</t>
@@ -1189,7 +1195,7 @@
     <t>7_8_9_10_11_12</t>
   </si>
   <si>
-    <t>0_500|1_150|2_150|3_100|4_80|5_15|6_5</t>
+    <t>0_500|1_200|2_200|3_50|4_30|5_15|6_5</t>
   </si>
   <si>
     <t>10_5000|20_3000|30_1000|40_500|50_400|80_50|100_40|200_10</t>
@@ -1214,6 +1220,24 @@
   </si>
   <si>
     <t>4_1_1|12_1_1</t>
+  </si>
+  <si>
+    <t>概率改出wild符号</t>
+  </si>
+  <si>
+    <t>必出现3个Jackpot符号</t>
+  </si>
+  <si>
+    <t>概率出现Jackpot符号</t>
+  </si>
+  <si>
+    <t>0_70|1_15|2_5</t>
+  </si>
+  <si>
+    <t>福鼠模式</t>
+  </si>
+  <si>
+    <t>第二轴改出三个wild符号</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -2115,7 +2139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2133,6 +2157,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2289,6 +2314,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
@@ -2634,7 +2663,7 @@
     <col min="8" max="8" width="27.625" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" customWidth="1"/>
     <col min="10" max="10" width="40.5833333333333" customWidth="1"/>
-    <col min="11" max="11" width="11.6166666666667" style="17" customWidth="1"/>
+    <col min="11" max="11" width="11.6166666666667" style="18" customWidth="1"/>
     <col min="12" max="12" width="9.375"/>
     <col min="13" max="13" width="12.5"/>
     <col min="14" max="14" width="9.375"/>
@@ -2642,121 +2671,121 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="21" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18" t="s">
+      <c r="F2" s="19"/>
+      <c r="G2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="21"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <v>10010011</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <v>100100</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2765,16 +2794,16 @@
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="27" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2782,16 +2811,16 @@
       <c r="A6" s="1">
         <v>10010012</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <v>100100</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="25" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2800,29 +2829,29 @@
       <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="27"/>
+      <c r="K6" s="28"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <v>10010021</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <v>100100</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="30" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -2831,27 +2860,27 @@
       <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="77" t="s">
+      <c r="H7" s="30"/>
+      <c r="I7" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="30"/>
+      <c r="K7" s="31"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <v>10010022</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <v>100100</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="30" t="s">
         <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -2860,27 +2889,27 @@
       <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="31"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="32"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <v>10010023</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <v>100100</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="30" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2889,27 +2918,27 @@
       <c r="G9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="29"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="31"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="32"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <v>10010024</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <v>100100</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="30" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -2918,27 +2947,27 @@
       <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="29"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="31"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="32"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <v>10010025</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <v>100100</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="30" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2947,27 +2976,27 @@
       <c r="G11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="29"/>
+      <c r="H11" s="30"/>
       <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="31"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="32"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <v>10010026</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>100100</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="30" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2976,16 +3005,16 @@
       <c r="G12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="30" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="31" t="s">
+      <c r="K12" s="32" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2993,16 +3022,16 @@
       <c r="A13" s="1">
         <v>10010031</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>100100</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="35" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -3011,14 +3040,14 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="35" t="s">
+      <c r="K13" s="36" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3026,16 +3055,16 @@
       <c r="A14" s="1">
         <v>10010032</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <v>100100</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="33" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="35" t="s">
         <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -3044,147 +3073,147 @@
       <c r="G14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="78" t="s">
+      <c r="H14" s="35"/>
+      <c r="I14" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="35"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <v>10010041</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <v>100100</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="37" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="37"/>
-      <c r="K15" s="39"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <v>10010051</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <v>100100</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="79" t="s">
+      <c r="H16" s="43"/>
+      <c r="I16" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="41"/>
-      <c r="K16" s="43"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="44"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <v>10010052</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="19">
         <v>100100</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="41" t="s">
+      <c r="H17" s="43"/>
+      <c r="I17" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="25" t="s">
+      <c r="J17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="43" t="s">
+      <c r="K17" s="44" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A18" s="45">
+      <c r="A18" s="46">
         <v>10010061</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>100100</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="45" t="s">
+      <c r="F18" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="G18" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="45" t="s">
+      <c r="H18" s="20"/>
+      <c r="I18" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="45"/>
-      <c r="K18" s="48"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="49"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A19" s="2">
         <v>10010071</v>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="50">
         <v>100100</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="50" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -3193,27 +3222,27 @@
       <c r="G19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="80" t="s">
+      <c r="H19" s="50"/>
+      <c r="I19" s="83" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="51"/>
+      <c r="K19" s="52"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A20" s="2">
         <v>10010072</v>
       </c>
-      <c r="B20" s="49">
+      <c r="B20" s="50">
         <v>100100</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="49" t="s">
+      <c r="E20" s="50" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -3222,27 +3251,27 @@
       <c r="G20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="49"/>
+      <c r="H20" s="50"/>
       <c r="I20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J20" s="49"/>
-      <c r="K20" s="52"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="53"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A21" s="2">
         <v>10010073</v>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="50">
         <v>100100</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="49" t="s">
+      <c r="E21" s="50" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -3251,27 +3280,27 @@
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="49"/>
+      <c r="H21" s="50"/>
       <c r="I21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="49"/>
-      <c r="K21" s="52"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="53"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A22" s="2">
         <v>10010074</v>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="50">
         <v>100100</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="49" t="s">
+      <c r="E22" s="50" t="s">
         <v>51</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -3280,27 +3309,27 @@
       <c r="G22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="49"/>
+      <c r="H22" s="50"/>
       <c r="I22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="49"/>
-      <c r="K22" s="52"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="53"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A23" s="2">
         <v>10010075</v>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="50">
         <v>100100</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="49" t="s">
+      <c r="E23" s="50" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -3309,27 +3338,27 @@
       <c r="G23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="49"/>
+      <c r="H23" s="50"/>
       <c r="I23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="49"/>
-      <c r="K23" s="52"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="53"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:12">
       <c r="A24" s="2">
         <v>10010076</v>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="50">
         <v>100100</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="E24" s="50" t="s">
         <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -3338,16 +3367,16 @@
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="50" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="25" t="s">
+      <c r="J24" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="52" t="s">
+      <c r="K24" s="53" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3355,14 +3384,14 @@
       <c r="A25" s="15">
         <v>10010091</v>
       </c>
-      <c r="B25" s="53">
+      <c r="B25" s="54">
         <v>100100</v>
       </c>
-      <c r="C25" s="53"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="54" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="15" t="s">
@@ -3371,29 +3400,29 @@
       <c r="G25" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="54" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J25" s="53"/>
-      <c r="K25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="55"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <v>10030021</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="19">
         <v>100300</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="25" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="25" t="s">
         <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -3402,29 +3431,29 @@
       <c r="G26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="24" t="s">
+      <c r="H26" s="25" t="s">
         <v>92</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="27"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A27" s="1">
         <v>10030022</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <v>100300</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="25" t="s">
         <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="25" t="s">
         <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -3433,29 +3462,29 @@
       <c r="G27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="25" t="s">
         <v>92</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J27" s="25"/>
-      <c r="K27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="27"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A28" s="1">
         <v>10030031</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="19">
         <v>100300</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="25" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
@@ -3464,28 +3493,28 @@
       <c r="G28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="24"/>
-      <c r="I28" s="81" t="s">
+      <c r="H28" s="25"/>
+      <c r="I28" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="4"/>
-      <c r="K28" s="52"/>
+      <c r="K28" s="53"/>
       <c r="L28"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A29" s="1">
         <v>10030041</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="19">
         <v>100300</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="25" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -3494,28 +3523,28 @@
       <c r="G29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H29" s="24"/>
-      <c r="I29" s="81" t="s">
+      <c r="H29" s="25"/>
+      <c r="I29" s="84" t="s">
         <v>106</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="52"/>
+      <c r="K29" s="53"/>
       <c r="L29"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A30" s="1">
         <v>10030042</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <v>100300</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="25" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -3524,28 +3553,28 @@
       <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="24"/>
-      <c r="I30" s="81" t="s">
+      <c r="H30" s="25"/>
+      <c r="I30" s="84" t="s">
         <v>106</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="52"/>
+      <c r="K30" s="53"/>
       <c r="L30"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A31" s="1">
         <v>10030043</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="19">
         <v>100300</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="25" t="s">
         <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -3554,28 +3583,28 @@
       <c r="G31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="24"/>
-      <c r="I31" s="81" t="s">
+      <c r="H31" s="25"/>
+      <c r="I31" s="84" t="s">
         <v>106</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="52"/>
+      <c r="K31" s="53"/>
       <c r="L31"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <v>10030044</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="19">
         <v>100300</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="25" t="s">
         <v>108</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -3584,28 +3613,28 @@
       <c r="G32" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="24"/>
-      <c r="I32" s="81" t="s">
+      <c r="H32" s="25"/>
+      <c r="I32" s="84" t="s">
         <v>106</v>
       </c>
       <c r="J32" s="4"/>
-      <c r="K32" s="52"/>
+      <c r="K32" s="53"/>
       <c r="L32"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>10030045</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="19">
         <v>100300</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="25" t="s">
         <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -3614,30 +3643,30 @@
       <c r="G33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H33" s="24"/>
-      <c r="I33" s="81" t="s">
+      <c r="H33" s="25"/>
+      <c r="I33" s="84" t="s">
         <v>106</v>
       </c>
       <c r="J33" s="4"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>10030050</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="19">
         <v>100300</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="25" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="25" t="s">
         <v>112</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -3646,217 +3675,217 @@
       <c r="G34" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="24"/>
-      <c r="I34" s="81" t="s">
+      <c r="H34" s="25"/>
+      <c r="I34" s="84" t="s">
         <v>108</v>
       </c>
       <c r="J34" s="4"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="55"/>
-      <c r="N34" s="55"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="56"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A35" s="56">
+      <c r="A35" s="57">
         <v>10070010</v>
       </c>
-      <c r="B35" s="57">
+      <c r="B35" s="58">
         <v>100700</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="56" t="s">
+      <c r="C35" s="58"/>
+      <c r="D35" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="56" t="s">
+      <c r="F35" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="56" t="s">
+      <c r="G35" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="57"/>
-      <c r="I35" s="56" t="s">
+      <c r="H35" s="58"/>
+      <c r="I35" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="56"/>
-      <c r="K35" s="58"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A36" s="56">
+      <c r="A36" s="57">
         <v>10070011</v>
       </c>
-      <c r="B36" s="57">
+      <c r="B36" s="58">
         <v>100700</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="56" t="s">
+      <c r="C36" s="58"/>
+      <c r="D36" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="56" t="s">
+      <c r="F36" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="57"/>
-      <c r="I36" s="56" t="s">
+      <c r="H36" s="58"/>
+      <c r="I36" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="56"/>
-      <c r="K36" s="58"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="59"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A37" s="56">
+      <c r="A37" s="57">
         <v>10070012</v>
       </c>
-      <c r="B37" s="57">
+      <c r="B37" s="58">
         <v>100700</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="56" t="s">
+      <c r="C37" s="58"/>
+      <c r="D37" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="56" t="s">
+      <c r="F37" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="G37" s="56" t="s">
+      <c r="G37" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="57"/>
-      <c r="I37" s="56" t="s">
+      <c r="H37" s="58"/>
+      <c r="I37" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="J37" s="56"/>
-      <c r="K37" s="58"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="59"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A38" s="59">
+      <c r="A38" s="60">
         <v>10070021</v>
       </c>
-      <c r="B38" s="60">
+      <c r="B38" s="61">
         <v>100700</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="59" t="s">
+      <c r="C38" s="61"/>
+      <c r="D38" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="59" t="s">
+      <c r="F38" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="59" t="s">
+      <c r="G38" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="60"/>
-      <c r="I38" s="59" t="s">
+      <c r="H38" s="61"/>
+      <c r="I38" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="59"/>
-      <c r="K38" s="61"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="62"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A39" s="59">
+      <c r="A39" s="60">
         <v>10070022</v>
       </c>
-      <c r="B39" s="60">
+      <c r="B39" s="61">
         <v>100700</v>
       </c>
-      <c r="C39" s="60"/>
-      <c r="D39" s="59" t="s">
+      <c r="C39" s="61"/>
+      <c r="D39" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="60" t="s">
+      <c r="E39" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="59" t="s">
+      <c r="F39" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="G39" s="59" t="s">
+      <c r="G39" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="60"/>
-      <c r="I39" s="59" t="s">
+      <c r="H39" s="61"/>
+      <c r="I39" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="59"/>
-      <c r="K39" s="61"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="62"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A40" s="59">
+      <c r="A40" s="60">
         <v>10070023</v>
       </c>
-      <c r="B40" s="60">
+      <c r="B40" s="61">
         <v>100700</v>
       </c>
-      <c r="C40" s="60"/>
-      <c r="D40" s="59" t="s">
+      <c r="C40" s="61"/>
+      <c r="D40" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="60" t="s">
+      <c r="E40" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="59" t="s">
+      <c r="F40" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="59" t="s">
+      <c r="G40" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="60"/>
-      <c r="I40" s="59" t="s">
+      <c r="H40" s="61"/>
+      <c r="I40" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="59"/>
-      <c r="K40" s="61"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="62"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
-      <c r="A41" s="59">
+      <c r="A41" s="60">
         <v>10070024</v>
       </c>
-      <c r="B41" s="60">
+      <c r="B41" s="61">
         <v>100700</v>
       </c>
-      <c r="C41" s="60"/>
-      <c r="D41" s="59" t="s">
+      <c r="C41" s="61"/>
+      <c r="D41" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="E41" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="59" t="s">
+      <c r="F41" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="59" t="s">
+      <c r="G41" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="H41" s="60"/>
-      <c r="I41" s="59" t="s">
+      <c r="H41" s="61"/>
+      <c r="I41" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="J41" s="59"/>
-      <c r="K41" s="61"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="62"/>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="3">
         <v>10070030</v>
       </c>
-      <c r="B42" s="62">
+      <c r="B42" s="63">
         <v>100700</v>
       </c>
-      <c r="C42" s="62"/>
+      <c r="C42" s="63"/>
       <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="62" t="s">
+      <c r="E42" s="63" t="s">
         <v>132</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -3865,25 +3894,25 @@
       <c r="G42" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="62"/>
-      <c r="I42" s="82" t="s">
+      <c r="H42" s="63"/>
+      <c r="I42" s="85" t="s">
         <v>134</v>
       </c>
       <c r="J42" s="3"/>
-      <c r="K42" s="63"/>
+      <c r="K42" s="64"/>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="3">
         <v>10070031</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="63">
         <v>100700</v>
       </c>
-      <c r="C43" s="62"/>
+      <c r="C43" s="63"/>
       <c r="D43" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="63" t="s">
         <v>136</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -3892,27 +3921,27 @@
       <c r="G43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H43" s="62" t="s">
+      <c r="H43" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="I43" s="82" t="s">
+      <c r="I43" s="85" t="s">
         <v>138</v>
       </c>
       <c r="J43" s="3"/>
-      <c r="K43" s="63"/>
+      <c r="K43" s="64"/>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="3">
         <v>10070032</v>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="63">
         <v>100700</v>
       </c>
-      <c r="C44" s="62"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="62" t="s">
+      <c r="E44" s="63" t="s">
         <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -3921,26 +3950,26 @@
       <c r="G44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="I44" s="82" t="s">
+      <c r="I44" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K44" s="63"/>
+      <c r="K44" s="64"/>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="3">
         <v>10070033</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="63">
         <v>100700</v>
       </c>
-      <c r="C45" s="62"/>
+      <c r="C45" s="63"/>
       <c r="D45" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="63" t="s">
         <v>143</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -3949,26 +3978,26 @@
       <c r="G45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H45" s="62" t="s">
+      <c r="H45" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="82" t="s">
+      <c r="I45" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K45" s="63"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="3">
         <v>10070034</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B46" s="63">
         <v>100700</v>
       </c>
-      <c r="C46" s="62"/>
+      <c r="C46" s="63"/>
       <c r="D46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="62" t="s">
+      <c r="E46" s="63" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -3977,26 +4006,26 @@
       <c r="G46" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="62" t="s">
+      <c r="H46" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="I46" s="82" t="s">
+      <c r="I46" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K46" s="63"/>
+      <c r="K46" s="64"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="3">
         <v>10070035</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="63">
         <v>100700</v>
       </c>
-      <c r="C47" s="62"/>
+      <c r="C47" s="63"/>
       <c r="D47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="62" t="s">
+      <c r="E47" s="63" t="s">
         <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -4005,26 +4034,26 @@
       <c r="G47" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="62" t="s">
+      <c r="H47" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="I47" s="82" t="s">
+      <c r="I47" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K47" s="63"/>
+      <c r="K47" s="64"/>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="3">
         <v>10070036</v>
       </c>
-      <c r="B48" s="62">
+      <c r="B48" s="63">
         <v>100700</v>
       </c>
-      <c r="C48" s="62"/>
+      <c r="C48" s="63"/>
       <c r="D48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="62" t="s">
+      <c r="E48" s="63" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -4033,26 +4062,26 @@
       <c r="G48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H48" s="62" t="s">
+      <c r="H48" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="82" t="s">
+      <c r="I48" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K48" s="63"/>
+      <c r="K48" s="64"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A49" s="3">
         <v>10070037</v>
       </c>
-      <c r="B49" s="62">
+      <c r="B49" s="63">
         <v>100700</v>
       </c>
-      <c r="C49" s="62"/>
+      <c r="C49" s="63"/>
       <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="62" t="s">
+      <c r="E49" s="63" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -4061,26 +4090,26 @@
       <c r="G49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="62" t="s">
+      <c r="H49" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="I49" s="82" t="s">
+      <c r="I49" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K49" s="63"/>
+      <c r="K49" s="64"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A50" s="3">
         <v>10070038</v>
       </c>
-      <c r="B50" s="62">
+      <c r="B50" s="63">
         <v>100700</v>
       </c>
-      <c r="C50" s="62"/>
+      <c r="C50" s="63"/>
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="62" t="s">
+      <c r="E50" s="63" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -4089,25 +4118,25 @@
       <c r="G50" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="62" t="s">
+      <c r="H50" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="82" t="s">
+      <c r="I50" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K50" s="63"/>
+      <c r="K50" s="64"/>
     </row>
     <row r="51" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A51" s="4">
         <v>10120011</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="25">
         <v>101200</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="25" t="s">
         <v>157</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -4116,26 +4145,26 @@
       <c r="G51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="24" t="s">
+      <c r="H51" s="25" t="s">
         <v>160</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J51" s="4"/>
-      <c r="K51" s="27"/>
+      <c r="K51" s="28"/>
     </row>
     <row r="52" s="4" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A52" s="4">
         <v>10120021</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="25">
         <v>101200</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="25" t="s">
         <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -4144,27 +4173,27 @@
       <c r="G52" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="24"/>
-      <c r="I52" s="81" t="s">
+      <c r="H52" s="25"/>
+      <c r="I52" s="84" t="s">
         <v>109</v>
       </c>
       <c r="J52" s="4"/>
-      <c r="K52" s="27"/>
+      <c r="K52" s="28"/>
     </row>
     <row r="53" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A53" s="4">
         <v>10120031</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="25">
         <v>101200</v>
       </c>
-      <c r="C53" s="64" t="s">
+      <c r="C53" s="65" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="25" t="s">
         <v>136</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -4173,29 +4202,29 @@
       <c r="G53" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H53" s="24" t="s">
+      <c r="H53" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I53" s="81" t="s">
+      <c r="I53" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J53" s="4"/>
-      <c r="K53" s="27"/>
+      <c r="K53" s="28"/>
     </row>
     <row r="54" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A54" s="4">
         <v>10120032</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="25">
         <v>101200</v>
       </c>
-      <c r="C54" s="64" t="s">
+      <c r="C54" s="65" t="s">
         <v>164</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="25" t="s">
         <v>140</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -4204,29 +4233,29 @@
       <c r="G54" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="24" t="s">
+      <c r="H54" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I54" s="81" t="s">
+      <c r="I54" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="27"/>
+      <c r="K54" s="28"/>
     </row>
     <row r="55" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A55" s="4">
         <v>10120033</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="25">
         <v>101200</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="65" t="s">
         <v>164</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="25" t="s">
         <v>143</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -4235,29 +4264,29 @@
       <c r="G55" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H55" s="24" t="s">
+      <c r="H55" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I55" s="81" t="s">
+      <c r="I55" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J55" s="4"/>
-      <c r="K55" s="27"/>
+      <c r="K55" s="28"/>
     </row>
     <row r="56" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A56" s="4">
         <v>10120034</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="25">
         <v>101200</v>
       </c>
-      <c r="C56" s="64" t="s">
+      <c r="C56" s="65" t="s">
         <v>172</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="25" t="s">
         <v>146</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -4266,29 +4295,29 @@
       <c r="G56" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H56" s="24" t="s">
+      <c r="H56" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I56" s="81" t="s">
+      <c r="I56" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J56" s="4"/>
-      <c r="K56" s="27"/>
+      <c r="K56" s="28"/>
     </row>
     <row r="57" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A57" s="4">
         <v>10120035</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B57" s="25">
         <v>101200</v>
       </c>
-      <c r="C57" s="64" t="s">
+      <c r="C57" s="65" t="s">
         <v>172</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="25" t="s">
         <v>67</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -4297,29 +4326,29 @@
       <c r="G57" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="24" t="s">
+      <c r="H57" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="81" t="s">
+      <c r="I57" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J57" s="4"/>
-      <c r="K57" s="27"/>
+      <c r="K57" s="28"/>
     </row>
     <row r="58" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A58" s="4">
         <v>10120036</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="25">
         <v>101200</v>
       </c>
-      <c r="C58" s="64" t="s">
+      <c r="C58" s="65" t="s">
         <v>172</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="25" t="s">
         <v>36</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -4328,29 +4357,29 @@
       <c r="G58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="24" t="s">
+      <c r="H58" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="I58" s="81" t="s">
+      <c r="I58" s="84" t="s">
         <v>39</v>
       </c>
       <c r="J58" s="4"/>
-      <c r="K58" s="27"/>
+      <c r="K58" s="28"/>
     </row>
     <row r="59" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A59" s="5">
         <v>10120041</v>
       </c>
-      <c r="B59" s="64">
+      <c r="B59" s="65">
         <v>101200</v>
       </c>
-      <c r="C59" s="64" t="s">
+      <c r="C59" s="65" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="64" t="s">
+      <c r="E59" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5" t="s">
@@ -4359,29 +4388,29 @@
       <c r="G59" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H59" s="64">
+      <c r="H59" s="65">
         <v>10</v>
       </c>
-      <c r="I59" s="83" t="s">
+      <c r="I59" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J59" s="5"/>
-      <c r="K59" s="65"/>
+      <c r="K59" s="66"/>
     </row>
     <row r="60" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A60" s="5">
         <v>10120042</v>
       </c>
-      <c r="B60" s="64">
+      <c r="B60" s="65">
         <v>101200</v>
       </c>
-      <c r="C60" s="64" t="s">
+      <c r="C60" s="65" t="s">
         <v>181</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="64" t="s">
+      <c r="E60" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F60" s="5" t="s">
@@ -4390,29 +4419,29 @@
       <c r="G60" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H60" s="64">
+      <c r="H60" s="65">
         <v>10</v>
       </c>
-      <c r="I60" s="83" t="s">
+      <c r="I60" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J60" s="5"/>
-      <c r="K60" s="65"/>
+      <c r="K60" s="66"/>
     </row>
     <row r="61" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A61" s="5">
         <v>10120043</v>
       </c>
-      <c r="B61" s="64">
+      <c r="B61" s="65">
         <v>101200</v>
       </c>
-      <c r="C61" s="64" t="s">
+      <c r="C61" s="65" t="s">
         <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E61" s="64" t="s">
+      <c r="E61" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F61" s="5" t="s">
@@ -4421,29 +4450,29 @@
       <c r="G61" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H61" s="64">
+      <c r="H61" s="65">
         <v>10</v>
       </c>
-      <c r="I61" s="83" t="s">
+      <c r="I61" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J61" s="5"/>
-      <c r="K61" s="65"/>
+      <c r="K61" s="66"/>
     </row>
     <row r="62" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A62" s="5">
         <v>10120044</v>
       </c>
-      <c r="B62" s="64">
+      <c r="B62" s="65">
         <v>101200</v>
       </c>
-      <c r="C62" s="64" t="s">
+      <c r="C62" s="65" t="s">
         <v>185</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -4452,29 +4481,29 @@
       <c r="G62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H62" s="64">
+      <c r="H62" s="65">
         <v>10</v>
       </c>
-      <c r="I62" s="83" t="s">
+      <c r="I62" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J62" s="5"/>
-      <c r="K62" s="65"/>
+      <c r="K62" s="66"/>
     </row>
     <row r="63" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A63" s="5">
         <v>10120045</v>
       </c>
-      <c r="B63" s="64">
+      <c r="B63" s="65">
         <v>101200</v>
       </c>
-      <c r="C63" s="64" t="s">
+      <c r="C63" s="65" t="s">
         <v>185</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F63" s="5" t="s">
@@ -4483,29 +4512,29 @@
       <c r="G63" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="64">
+      <c r="H63" s="65">
         <v>10</v>
       </c>
-      <c r="I63" s="83" t="s">
+      <c r="I63" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J63" s="5"/>
-      <c r="K63" s="65"/>
+      <c r="K63" s="66"/>
     </row>
     <row r="64" s="5" customFormat="1" ht="16.5" spans="1:11">
       <c r="A64" s="5">
         <v>10120046</v>
       </c>
-      <c r="B64" s="64">
+      <c r="B64" s="65">
         <v>101200</v>
       </c>
-      <c r="C64" s="64" t="s">
+      <c r="C64" s="65" t="s">
         <v>185</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E64" s="64" t="s">
+      <c r="E64" s="65" t="s">
         <v>114</v>
       </c>
       <c r="F64" s="5" t="s">
@@ -4514,29 +4543,29 @@
       <c r="G64" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H64" s="64">
+      <c r="H64" s="65">
         <v>10</v>
       </c>
-      <c r="I64" s="83" t="s">
+      <c r="I64" s="86" t="s">
         <v>107</v>
       </c>
       <c r="J64" s="5"/>
-      <c r="K64" s="65"/>
+      <c r="K64" s="66"/>
     </row>
     <row r="65" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A65" s="4">
         <v>10120051</v>
       </c>
-      <c r="B65" s="24">
+      <c r="B65" s="25">
         <v>101200</v>
       </c>
-      <c r="C65" s="64" t="s">
+      <c r="C65" s="65" t="s">
         <v>189</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="25" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -4545,29 +4574,29 @@
       <c r="G65" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="24" t="s">
+      <c r="H65" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I65" s="81" t="s">
+      <c r="I65" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J65" s="4"/>
-      <c r="K65" s="27"/>
+      <c r="K65" s="28"/>
     </row>
     <row r="66" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A66" s="4">
         <v>10120052</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B66" s="25">
         <v>101200</v>
       </c>
-      <c r="C66" s="64" t="s">
+      <c r="C66" s="65" t="s">
         <v>189</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -4576,29 +4605,29 @@
       <c r="G66" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="H66" s="24" t="s">
+      <c r="H66" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I66" s="81" t="s">
+      <c r="I66" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J66" s="4"/>
-      <c r="K66" s="27"/>
+      <c r="K66" s="28"/>
     </row>
     <row r="67" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A67" s="4">
         <v>10120053</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B67" s="25">
         <v>101200</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="65" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="25" t="s">
         <v>193</v>
       </c>
       <c r="F67" s="4" t="s">
@@ -4607,29 +4636,29 @@
       <c r="G67" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H67" s="24" t="s">
+      <c r="H67" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I67" s="81" t="s">
+      <c r="I67" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J67" s="4"/>
-      <c r="K67" s="27"/>
+      <c r="K67" s="28"/>
     </row>
     <row r="68" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A68" s="4">
         <v>10120054</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B68" s="25">
         <v>101200</v>
       </c>
-      <c r="C68" s="64" t="s">
+      <c r="C68" s="65" t="s">
         <v>194</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="25" t="s">
         <v>195</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -4638,29 +4667,29 @@
       <c r="G68" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H68" s="24" t="s">
+      <c r="H68" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="81" t="s">
+      <c r="I68" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J68" s="4"/>
-      <c r="K68" s="27"/>
+      <c r="K68" s="28"/>
     </row>
     <row r="69" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A69" s="4">
         <v>10120055</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B69" s="25">
         <v>101200</v>
       </c>
-      <c r="C69" s="64" t="s">
+      <c r="C69" s="65" t="s">
         <v>194</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="25" t="s">
         <v>196</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -4669,29 +4698,29 @@
       <c r="G69" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="24" t="s">
+      <c r="H69" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I69" s="81" t="s">
+      <c r="I69" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="27"/>
+      <c r="K69" s="28"/>
     </row>
     <row r="70" s="4" customFormat="1" ht="16.5" spans="1:11">
       <c r="A70" s="4">
         <v>10120056</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B70" s="25">
         <v>101200</v>
       </c>
-      <c r="C70" s="64" t="s">
+      <c r="C70" s="65" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="25" t="s">
         <v>197</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -4700,29 +4729,29 @@
       <c r="G70" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="H70" s="24" t="s">
+      <c r="H70" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="81" t="s">
+      <c r="I70" s="84" t="s">
         <v>192</v>
       </c>
       <c r="J70" s="4"/>
-      <c r="K70" s="27"/>
+      <c r="K70" s="28"/>
     </row>
     <row r="71" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A71" s="6">
         <v>10120061</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B71" s="25">
         <v>101200</v>
       </c>
-      <c r="C71" s="34" t="s">
+      <c r="C71" s="35" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="34" t="s">
+      <c r="E71" s="35" t="s">
         <v>199</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -4731,29 +4760,29 @@
       <c r="G71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="34" t="s">
+      <c r="H71" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I71" s="78" t="s">
+      <c r="I71" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="35"/>
+      <c r="K71" s="36"/>
     </row>
     <row r="72" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A72" s="6">
         <v>10120062</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B72" s="25">
         <v>101200</v>
       </c>
-      <c r="C72" s="34" t="s">
+      <c r="C72" s="35" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E72" s="34" t="s">
+      <c r="E72" s="35" t="s">
         <v>202</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -4762,29 +4791,29 @@
       <c r="G72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H72" s="34" t="s">
+      <c r="H72" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I72" s="78" t="s">
+      <c r="I72" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J72" s="6"/>
-      <c r="K72" s="35"/>
+      <c r="K72" s="36"/>
     </row>
     <row r="73" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A73" s="6">
         <v>10120063</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B73" s="25">
         <v>101200</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="35" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="34" t="s">
+      <c r="E73" s="35" t="s">
         <v>203</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -4793,29 +4822,29 @@
       <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H73" s="34" t="s">
+      <c r="H73" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I73" s="78" t="s">
+      <c r="I73" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J73" s="6"/>
-      <c r="K73" s="35"/>
+      <c r="K73" s="36"/>
     </row>
     <row r="74" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A74" s="6">
         <v>10120064</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B74" s="25">
         <v>101200</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" s="35" t="s">
         <v>204</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E74" s="34" t="s">
+      <c r="E74" s="35" t="s">
         <v>205</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -4824,29 +4853,29 @@
       <c r="G74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="34" t="s">
+      <c r="H74" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I74" s="78" t="s">
+      <c r="I74" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="35"/>
+      <c r="K74" s="36"/>
     </row>
     <row r="75" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A75" s="6">
         <v>10120065</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B75" s="25">
         <v>101200</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C75" s="35" t="s">
         <v>204</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E75" s="34" t="s">
+      <c r="E75" s="35" t="s">
         <v>206</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -4855,29 +4884,29 @@
       <c r="G75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="34" t="s">
+      <c r="H75" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I75" s="78" t="s">
+      <c r="I75" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="35"/>
+      <c r="K75" s="36"/>
     </row>
     <row r="76" s="6" customFormat="1" ht="16.5" spans="1:11">
       <c r="A76" s="6">
         <v>10120066</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B76" s="25">
         <v>101200</v>
       </c>
-      <c r="C76" s="34" t="s">
+      <c r="C76" s="35" t="s">
         <v>204</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E76" s="34" t="s">
+      <c r="E76" s="35" t="s">
         <v>207</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -4886,29 +4915,29 @@
       <c r="G76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H76" s="34" t="s">
+      <c r="H76" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="I76" s="78" t="s">
+      <c r="I76" s="81" t="s">
         <v>201</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="35"/>
+      <c r="K76" s="36"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A77" s="3">
         <v>10140001</v>
       </c>
-      <c r="B77" s="62">
+      <c r="B77" s="63">
         <v>101400</v>
       </c>
-      <c r="C77" s="62" t="s">
+      <c r="C77" s="63" t="s">
         <v>208</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E77" s="62" t="s">
+      <c r="E77" s="63" t="s">
         <v>140</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -4917,28 +4946,28 @@
       <c r="G77" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H77" s="29" t="s">
+      <c r="H77" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="I77" s="82" t="s">
+      <c r="I77" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="K77" s="63"/>
+      <c r="K77" s="64"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:11">
       <c r="A78" s="3">
         <v>10140011</v>
       </c>
-      <c r="B78" s="62">
+      <c r="B78" s="63">
         <v>101400</v>
       </c>
-      <c r="C78" s="62" t="s">
+      <c r="C78" s="63" t="s">
         <v>208</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E78" s="62" t="s">
+      <c r="E78" s="63" t="s">
         <v>140</v>
       </c>
       <c r="F78" s="3" t="s">
@@ -4947,28 +4976,28 @@
       <c r="G78" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H78" s="29" t="s">
+      <c r="H78" s="30" t="s">
         <v>211</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K78" s="63"/>
+      <c r="K78" s="64"/>
     </row>
     <row r="79" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A79" s="7">
         <v>10140021</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="30">
         <v>101400</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E79" s="29" t="s">
+      <c r="E79" s="30" t="s">
         <v>143</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -4977,28 +5006,28 @@
       <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="29" t="s">
+      <c r="H79" s="30" t="s">
         <v>143</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K79" s="30"/>
+      <c r="K79" s="31"/>
     </row>
     <row r="80" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A80" s="7">
         <v>10140022</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="30">
         <v>101400</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="30" t="s">
         <v>216</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E80" s="29" t="s">
+      <c r="E80" s="30" t="s">
         <v>143</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -5007,28 +5036,28 @@
       <c r="G80" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H80" s="29" t="s">
+      <c r="H80" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="I80" s="82" t="s">
+      <c r="I80" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="K80" s="30"/>
+      <c r="K80" s="31"/>
     </row>
     <row r="81" s="7" customFormat="1" ht="16.5" spans="1:11">
       <c r="A81" s="7">
         <v>10140023</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="30">
         <v>101400</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="30" t="s">
         <v>217</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E81" s="29" t="s">
+      <c r="E81" s="30" t="s">
         <v>143</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -5037,28 +5066,28 @@
       <c r="G81" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H81" s="29" t="s">
+      <c r="H81" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="I81" s="82" t="s">
+      <c r="I81" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="K81" s="30"/>
+      <c r="K81" s="31"/>
     </row>
     <row r="82" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A82" s="1">
         <v>10240011</v>
       </c>
-      <c r="B82" s="18">
+      <c r="B82" s="19">
         <v>102400</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -5067,16 +5096,16 @@
       <c r="G82" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H82" s="24" t="s">
+      <c r="H82" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J82" s="25" t="s">
+      <c r="J82" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K82" s="26" t="s">
+      <c r="K82" s="27" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5084,16 +5113,16 @@
       <c r="A83" s="1">
         <v>10240012</v>
       </c>
-      <c r="B83" s="18">
+      <c r="B83" s="19">
         <v>102400</v>
       </c>
-      <c r="C83" s="24" t="s">
+      <c r="C83" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E83" s="24" t="s">
+      <c r="E83" s="25" t="s">
         <v>31</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -5102,29 +5131,29 @@
       <c r="G83" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="24" t="s">
+      <c r="H83" s="25" t="s">
         <v>26</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J83" s="4"/>
-      <c r="K83" s="27"/>
+      <c r="K83" s="28"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A84" s="1">
         <v>10240021</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="19">
         <v>102400</v>
       </c>
-      <c r="C84" s="28" t="s">
+      <c r="C84" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="29" t="s">
+      <c r="E84" s="30" t="s">
         <v>36</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -5133,27 +5162,27 @@
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="29"/>
-      <c r="I84" s="77" t="s">
+      <c r="H84" s="30"/>
+      <c r="I84" s="80" t="s">
         <v>39</v>
       </c>
       <c r="J84" s="7"/>
-      <c r="K84" s="30"/>
+      <c r="K84" s="31"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A85" s="1">
         <v>10240022</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="19">
         <v>102400</v>
       </c>
-      <c r="C85" s="28" t="s">
+      <c r="C85" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E85" s="29" t="s">
+      <c r="E85" s="30" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -5162,27 +5191,27 @@
       <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="29"/>
+      <c r="H85" s="30"/>
       <c r="I85" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J85" s="29"/>
-      <c r="K85" s="31"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="32"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A86" s="1">
         <v>10240023</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="19">
         <v>102400</v>
       </c>
-      <c r="C86" s="28" t="s">
+      <c r="C86" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="30" t="s">
         <v>46</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -5191,27 +5220,27 @@
       <c r="G86" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H86" s="29"/>
+      <c r="H86" s="30"/>
       <c r="I86" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J86" s="29"/>
-      <c r="K86" s="31"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="32"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A87" s="1">
         <v>10240024</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="19">
         <v>102400</v>
       </c>
-      <c r="C87" s="28" t="s">
+      <c r="C87" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="30" t="s">
         <v>51</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -5220,27 +5249,27 @@
       <c r="G87" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="29"/>
+      <c r="H87" s="30"/>
       <c r="I87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J87" s="29"/>
-      <c r="K87" s="31"/>
+      <c r="J87" s="30"/>
+      <c r="K87" s="32"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A88" s="1">
         <v>10240025</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="19">
         <v>102400</v>
       </c>
-      <c r="C88" s="28" t="s">
+      <c r="C88" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="30" t="s">
         <v>56</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -5249,27 +5278,27 @@
       <c r="G88" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H88" s="29"/>
+      <c r="H88" s="30"/>
       <c r="I88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J88" s="29"/>
-      <c r="K88" s="31"/>
+      <c r="J88" s="30"/>
+      <c r="K88" s="32"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A89" s="1">
         <v>10240026</v>
       </c>
-      <c r="B89" s="18">
+      <c r="B89" s="19">
         <v>102400</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="29" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="30" t="s">
         <v>61</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -5278,16 +5307,16 @@
       <c r="G89" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H89" s="29" t="s">
+      <c r="H89" s="30" t="s">
         <v>26</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="25" t="s">
+      <c r="J89" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K89" s="31" t="s">
+      <c r="K89" s="32" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5295,16 +5324,16 @@
       <c r="A90" s="1">
         <v>10240031</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="19">
         <v>102400</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="C90" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D90" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E90" s="34" t="s">
+      <c r="E90" s="35" t="s">
         <v>61</v>
       </c>
       <c r="F90" s="6" t="s">
@@ -5313,14 +5342,14 @@
       <c r="G90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H90" s="34"/>
+      <c r="H90" s="35"/>
       <c r="I90" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J90" s="25" t="s">
+      <c r="J90" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K90" s="35" t="s">
+      <c r="K90" s="36" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5328,16 +5357,16 @@
       <c r="A91" s="1">
         <v>10240032</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="19">
         <v>102400</v>
       </c>
-      <c r="C91" s="32" t="s">
+      <c r="C91" s="33" t="s">
         <v>62</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="34" t="s">
+      <c r="E91" s="35" t="s">
         <v>67</v>
       </c>
       <c r="F91" s="6" t="s">
@@ -5346,147 +5375,147 @@
       <c r="G91" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H91" s="34"/>
-      <c r="I91" s="78" t="s">
+      <c r="H91" s="35"/>
+      <c r="I91" s="81" t="s">
         <v>39</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="35"/>
+      <c r="K91" s="36"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A92" s="1">
         <v>10240041</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="19">
         <v>102400</v>
       </c>
-      <c r="C92" s="36" t="s">
+      <c r="C92" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="37" t="s">
+      <c r="D92" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="38" t="s">
+      <c r="E92" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F92" s="37" t="s">
+      <c r="F92" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="37" t="s">
+      <c r="G92" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H92" s="38"/>
-      <c r="I92" s="37" t="s">
+      <c r="H92" s="39"/>
+      <c r="I92" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="J92" s="37"/>
-      <c r="K92" s="39"/>
+      <c r="J92" s="38"/>
+      <c r="K92" s="40"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A93" s="1">
         <v>10240051</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="19">
         <v>102400</v>
       </c>
-      <c r="C93" s="40" t="s">
+      <c r="C93" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D93" s="41" t="s">
+      <c r="D93" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E93" s="42" t="s">
+      <c r="E93" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="F93" s="41" t="s">
+      <c r="F93" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="41" t="s">
+      <c r="G93" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H93" s="42"/>
-      <c r="I93" s="79" t="s">
+      <c r="H93" s="43"/>
+      <c r="I93" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="J93" s="41"/>
-      <c r="K93" s="43"/>
+      <c r="J93" s="42"/>
+      <c r="K93" s="44"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A94" s="1">
         <v>10240052</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="19">
         <v>102400</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C94" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D94" s="44" t="s">
+      <c r="D94" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="42" t="s">
+      <c r="E94" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="41" t="s">
+      <c r="F94" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="G94" s="41" t="s">
+      <c r="G94" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="42"/>
-      <c r="I94" s="41" t="s">
+      <c r="H94" s="43"/>
+      <c r="I94" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="J94" s="25" t="s">
+      <c r="J94" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K94" s="43" t="s">
+      <c r="K94" s="44" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A95" s="45">
+      <c r="A95" s="46">
         <v>10240061</v>
       </c>
-      <c r="B95" s="19">
+      <c r="B95" s="20">
         <v>102400</v>
       </c>
-      <c r="C95" s="46" t="s">
+      <c r="C95" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="D95" s="47" t="s">
+      <c r="D95" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F95" s="45" t="s">
+      <c r="F95" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G95" s="45" t="s">
+      <c r="G95" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="19"/>
-      <c r="I95" s="45" t="s">
+      <c r="H95" s="20"/>
+      <c r="I95" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="J95" s="45"/>
-      <c r="K95" s="48"/>
+      <c r="J95" s="46"/>
+      <c r="K95" s="49"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A96" s="2">
         <v>10240071</v>
       </c>
-      <c r="B96" s="49">
+      <c r="B96" s="50">
         <v>102400</v>
       </c>
-      <c r="C96" s="50" t="s">
+      <c r="C96" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E96" s="49" t="s">
+      <c r="E96" s="50" t="s">
         <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -5495,26 +5524,26 @@
       <c r="G96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H96" s="49"/>
-      <c r="I96" s="80" t="s">
+      <c r="H96" s="50"/>
+      <c r="I96" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="K96" s="51"/>
+      <c r="K96" s="52"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A97" s="2">
         <v>10240072</v>
       </c>
-      <c r="B97" s="49">
+      <c r="B97" s="50">
         <v>102400</v>
       </c>
-      <c r="C97" s="50" t="s">
+      <c r="C97" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="49" t="s">
+      <c r="E97" s="50" t="s">
         <v>41</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -5523,27 +5552,27 @@
       <c r="G97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="49"/>
+      <c r="H97" s="50"/>
       <c r="I97" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="49"/>
-      <c r="K97" s="52"/>
+      <c r="J97" s="50"/>
+      <c r="K97" s="53"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A98" s="2">
         <v>10240073</v>
       </c>
-      <c r="B98" s="49">
+      <c r="B98" s="50">
         <v>102400</v>
       </c>
-      <c r="C98" s="50" t="s">
+      <c r="C98" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E98" s="49" t="s">
+      <c r="E98" s="50" t="s">
         <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -5552,27 +5581,27 @@
       <c r="G98" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H98" s="49"/>
+      <c r="H98" s="50"/>
       <c r="I98" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J98" s="49"/>
-      <c r="K98" s="52"/>
+      <c r="J98" s="50"/>
+      <c r="K98" s="53"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A99" s="2">
         <v>10240074</v>
       </c>
-      <c r="B99" s="49">
+      <c r="B99" s="50">
         <v>102400</v>
       </c>
-      <c r="C99" s="50" t="s">
+      <c r="C99" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="49" t="s">
+      <c r="E99" s="50" t="s">
         <v>51</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -5581,27 +5610,27 @@
       <c r="G99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H99" s="49"/>
+      <c r="H99" s="50"/>
       <c r="I99" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J99" s="49"/>
-      <c r="K99" s="52"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="53"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A100" s="2">
         <v>10240075</v>
       </c>
-      <c r="B100" s="49">
+      <c r="B100" s="50">
         <v>102400</v>
       </c>
-      <c r="C100" s="50" t="s">
+      <c r="C100" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="49" t="s">
+      <c r="E100" s="50" t="s">
         <v>56</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -5610,27 +5639,27 @@
       <c r="G100" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="49"/>
+      <c r="H100" s="50"/>
       <c r="I100" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J100" s="49"/>
-      <c r="K100" s="52"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="53"/>
     </row>
     <row r="101" s="2" customFormat="1" ht="16.5" spans="1:11">
       <c r="A101" s="2">
         <v>10240076</v>
       </c>
-      <c r="B101" s="49">
+      <c r="B101" s="50">
         <v>102400</v>
       </c>
-      <c r="C101" s="50" t="s">
+      <c r="C101" s="51" t="s">
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E101" s="49" t="s">
+      <c r="E101" s="50" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -5639,16 +5668,16 @@
       <c r="G101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="49" t="s">
+      <c r="H101" s="50" t="s">
         <v>26</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J101" s="25" t="s">
+      <c r="J101" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K101" s="52" t="s">
+      <c r="K101" s="53" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5656,14 +5685,14 @@
       <c r="A102" s="15">
         <v>10240091</v>
       </c>
-      <c r="B102" s="53">
+      <c r="B102" s="54">
         <v>102400</v>
       </c>
-      <c r="C102" s="53"/>
+      <c r="C102" s="54"/>
       <c r="D102" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E102" s="53" t="s">
+      <c r="E102" s="54" t="s">
         <v>84</v>
       </c>
       <c r="F102" s="15" t="s">
@@ -5672,14 +5701,14 @@
       <c r="G102" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H102" s="53" t="s">
+      <c r="H102" s="54" t="s">
         <v>26</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J102" s="53"/>
-      <c r="K102" s="54"/>
+      <c r="J102" s="54"/>
+      <c r="K102" s="55"/>
     </row>
     <row r="103" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A103" s="8">
@@ -5703,7 +5732,7 @@
       <c r="I103" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K103" s="66"/>
+      <c r="K103" s="67"/>
     </row>
     <row r="104" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A104" s="8">
@@ -5727,7 +5756,7 @@
       <c r="I104" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K104" s="66"/>
+      <c r="K104" s="67"/>
     </row>
     <row r="105" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A105" s="8">
@@ -5751,7 +5780,7 @@
       <c r="I105" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K105" s="66"/>
+      <c r="K105" s="67"/>
     </row>
     <row r="106" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A106" s="8">
@@ -5775,7 +5804,7 @@
       <c r="I106" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K106" s="66"/>
+      <c r="K106" s="67"/>
     </row>
     <row r="107" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A107" s="8">
@@ -5799,7 +5828,7 @@
       <c r="I107" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K107" s="66"/>
+      <c r="K107" s="67"/>
     </row>
     <row r="108" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A108" s="8">
@@ -5823,7 +5852,7 @@
       <c r="I108" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K108" s="66"/>
+      <c r="K108" s="67"/>
     </row>
     <row r="109" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A109" s="8">
@@ -5847,7 +5876,7 @@
       <c r="I109" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K109" s="66"/>
+      <c r="K109" s="67"/>
     </row>
     <row r="110" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A110" s="8">
@@ -5868,10 +5897,10 @@
       <c r="G110" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I110" s="84" t="s">
+      <c r="I110" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="K110" s="66"/>
+      <c r="K110" s="67"/>
     </row>
     <row r="111" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A111" s="8">
@@ -5898,7 +5927,7 @@
       <c r="I111" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K111" s="66"/>
+      <c r="K111" s="67"/>
     </row>
     <row r="112" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A112" s="8">
@@ -5925,7 +5954,7 @@
       <c r="I112" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K112" s="66"/>
+      <c r="K112" s="67"/>
     </row>
     <row r="113" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A113" s="8">
@@ -5952,7 +5981,7 @@
       <c r="I113" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K113" s="66"/>
+      <c r="K113" s="67"/>
     </row>
     <row r="114" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A114" s="8">
@@ -5979,7 +6008,7 @@
       <c r="I114" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K114" s="66"/>
+      <c r="K114" s="67"/>
     </row>
     <row r="115" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A115" s="8">
@@ -6006,7 +6035,7 @@
       <c r="I115" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K115" s="66"/>
+      <c r="K115" s="67"/>
     </row>
     <row r="116" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A116" s="8">
@@ -6033,7 +6062,7 @@
       <c r="I116" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K116" s="66"/>
+      <c r="K116" s="67"/>
     </row>
     <row r="117" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A117" s="8">
@@ -6060,7 +6089,7 @@
       <c r="I117" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K117" s="66"/>
+      <c r="K117" s="67"/>
     </row>
     <row r="118" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A118" s="8">
@@ -6087,7 +6116,7 @@
       <c r="I118" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K118" s="66"/>
+      <c r="K118" s="67"/>
     </row>
     <row r="119" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A119" s="8">
@@ -6117,7 +6146,7 @@
       <c r="I119" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="K119" s="66"/>
+      <c r="K119" s="67"/>
     </row>
     <row r="120" s="8" customFormat="1" ht="16.5" spans="1:11">
       <c r="A120" s="8">
@@ -6147,7 +6176,7 @@
       <c r="I120" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K120" s="66"/>
+      <c r="K120" s="67"/>
     </row>
     <row r="121" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A121" s="9">
@@ -6177,7 +6206,7 @@
       <c r="I121" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="K121" s="67"/>
+      <c r="K121" s="68"/>
     </row>
     <row r="122" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A122" s="9">
@@ -6207,7 +6236,7 @@
       <c r="I122" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K122" s="67"/>
+      <c r="K122" s="68"/>
     </row>
     <row r="123" s="9" customFormat="1" ht="17" customHeight="1" spans="1:11">
       <c r="A123" s="9">
@@ -6237,7 +6266,7 @@
       <c r="I123" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K123" s="67"/>
+      <c r="K123" s="68"/>
     </row>
     <row r="124" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A124" s="9">
@@ -6265,7 +6294,7 @@
       <c r="I124" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K124" s="67"/>
+      <c r="K124" s="68"/>
     </row>
     <row r="125" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A125" s="9">
@@ -6292,7 +6321,7 @@
       <c r="I125" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="K125" s="67"/>
+      <c r="K125" s="68"/>
     </row>
     <row r="126" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A126" s="9">
@@ -6320,7 +6349,7 @@
       <c r="I126" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="K126" s="67"/>
+      <c r="K126" s="68"/>
     </row>
     <row r="127" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A127" s="9">
@@ -6348,7 +6377,7 @@
       <c r="I127" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K127" s="67"/>
+      <c r="K127" s="68"/>
     </row>
     <row r="128" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A128" s="9">
@@ -6372,7 +6401,7 @@
       <c r="I128" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K128" s="67"/>
+      <c r="K128" s="68"/>
     </row>
     <row r="129" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A129" s="9">
@@ -6396,7 +6425,7 @@
       <c r="I129" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="K129" s="67"/>
+      <c r="K129" s="68"/>
     </row>
     <row r="130" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A130" s="9">
@@ -6417,7 +6446,7 @@
       <c r="I130" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K130" s="67"/>
+      <c r="K130" s="68"/>
     </row>
     <row r="131" s="9" customFormat="1" ht="16.5" spans="1:11">
       <c r="A131" s="9">
@@ -6438,7 +6467,7 @@
       <c r="I131" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K131" s="67"/>
+      <c r="K131" s="68"/>
     </row>
     <row r="132" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A132" s="10">
@@ -6468,7 +6497,7 @@
       <c r="I132" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K132" s="68"/>
+      <c r="K132" s="69"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A133" s="10">
@@ -6498,7 +6527,7 @@
       <c r="I133" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K133" s="68"/>
+      <c r="K133" s="69"/>
     </row>
     <row r="134" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A134" s="10">
@@ -6528,7 +6557,7 @@
       <c r="I134" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K134" s="68"/>
+      <c r="K134" s="69"/>
     </row>
     <row r="135" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A135" s="10">
@@ -6555,7 +6584,7 @@
       <c r="I135" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K135" s="68"/>
+      <c r="K135" s="69"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A136" s="10">
@@ -6582,7 +6611,7 @@
       <c r="I136" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K136" s="68"/>
+      <c r="K136" s="69"/>
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A137" s="10">
@@ -6609,7 +6638,7 @@
       <c r="I137" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K137" s="68"/>
+      <c r="K137" s="69"/>
     </row>
     <row r="138" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A138" s="10">
@@ -6636,7 +6665,7 @@
       <c r="I138" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K138" s="68"/>
+      <c r="K138" s="69"/>
     </row>
     <row r="139" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A139" s="10">
@@ -6663,7 +6692,7 @@
       <c r="I139" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K139" s="68"/>
+      <c r="K139" s="69"/>
     </row>
     <row r="140" s="10" customFormat="1" ht="16.5" spans="1:11">
       <c r="A140" s="10">
@@ -6693,7 +6722,7 @@
       <c r="I140" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="K140" s="68"/>
+      <c r="K140" s="69"/>
     </row>
     <row r="141" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A141" s="11">
@@ -6723,7 +6752,7 @@
       <c r="I141" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K141" s="69"/>
+      <c r="K141" s="70"/>
     </row>
     <row r="142" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A142" s="11">
@@ -6753,7 +6782,7 @@
       <c r="I142" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="K142" s="69"/>
+      <c r="K142" s="70"/>
     </row>
     <row r="143" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A143" s="11">
@@ -6783,7 +6812,7 @@
       <c r="I143" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K143" s="69"/>
+      <c r="K143" s="70"/>
     </row>
     <row r="144" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A144" s="11">
@@ -6813,7 +6842,7 @@
       <c r="I144" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="K144" s="69"/>
+      <c r="K144" s="70"/>
     </row>
     <row r="145" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A145" s="11">
@@ -6843,7 +6872,7 @@
       <c r="I145" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K145" s="69"/>
+      <c r="K145" s="70"/>
     </row>
     <row r="146" s="11" customFormat="1" ht="16.5" spans="1:11">
       <c r="A146" s="11">
@@ -6873,7 +6902,7 @@
       <c r="I146" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="K146" s="69"/>
+      <c r="K146" s="70"/>
     </row>
     <row r="147" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A147" s="12">
@@ -6903,7 +6932,7 @@
       <c r="I147" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="K147" s="70"/>
+      <c r="K147" s="71"/>
     </row>
     <row r="148" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A148" s="12">
@@ -6933,7 +6962,7 @@
       <c r="I148" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K148" s="70"/>
+      <c r="K148" s="71"/>
     </row>
     <row r="149" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A149" s="12">
@@ -6963,7 +6992,7 @@
       <c r="I149" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K149" s="70"/>
+      <c r="K149" s="71"/>
     </row>
     <row r="150" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A150" s="12">
@@ -6993,7 +7022,7 @@
       <c r="I150" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="K150" s="70"/>
+      <c r="K150" s="71"/>
     </row>
     <row r="151" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A151" s="12">
@@ -7023,7 +7052,7 @@
       <c r="I151" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="K151" s="70"/>
+      <c r="K151" s="71"/>
     </row>
     <row r="152" s="12" customFormat="1" ht="16.5" spans="1:11">
       <c r="A152" s="12">
@@ -7051,7 +7080,7 @@
       <c r="I152" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="K152" s="70"/>
+      <c r="K152" s="71"/>
     </row>
     <row r="153" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A153" s="13">
@@ -7081,7 +7110,7 @@
       <c r="I153" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="K153" s="71"/>
+      <c r="K153" s="72"/>
     </row>
     <row r="154" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A154" s="13">
@@ -7111,7 +7140,7 @@
       <c r="I154" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="K154" s="71"/>
+      <c r="K154" s="72"/>
     </row>
     <row r="155" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A155" s="13">
@@ -7141,7 +7170,7 @@
       <c r="I155" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="K155" s="71"/>
+      <c r="K155" s="72"/>
     </row>
     <row r="156" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A156" s="13">
@@ -7171,7 +7200,7 @@
       <c r="I156" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="K156" s="71"/>
+      <c r="K156" s="72"/>
     </row>
     <row r="157" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A157" s="13">
@@ -7181,7 +7210,7 @@
         <v>102300</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="D157" s="13" t="s">
         <v>262</v>
@@ -7201,23 +7230,23 @@
       <c r="I157" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="K157" s="71"/>
+      <c r="K157" s="72"/>
     </row>
     <row r="158" s="13" customFormat="1" ht="16.5" spans="1:11">
       <c r="A158" s="13">
-        <v>10230031</v>
+        <v>10230022</v>
       </c>
       <c r="B158" s="13">
         <v>102300</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F158" s="13" t="s">
         <v>133</v>
@@ -7229,1007 +7258,1105 @@
         <v>160</v>
       </c>
       <c r="I158" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="K158" s="71"/>
-    </row>
-    <row r="159" s="14" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A159" s="72">
+        <v>292</v>
+      </c>
+      <c r="K158" s="72"/>
+    </row>
+    <row r="159" s="13" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A159" s="13">
+        <v>10230031</v>
+      </c>
+      <c r="B159" s="13">
+        <v>102300</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F159" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G159" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="H159" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I159" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="K159" s="72"/>
+    </row>
+    <row r="160" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A160" s="73">
         <v>10340001</v>
       </c>
-      <c r="B159" s="72">
+      <c r="B160" s="73">
         <v>103400</v>
       </c>
-      <c r="C159" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="D159" s="72" t="s">
+      <c r="C160" s="73" t="s">
+        <v>293</v>
+      </c>
+      <c r="D160" s="73" t="s">
+        <v>294</v>
+      </c>
+      <c r="E160" s="73" t="s">
+        <v>295</v>
+      </c>
+      <c r="F160" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G160" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="H160" s="73" t="s">
+        <v>297</v>
+      </c>
+      <c r="I160" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="K160" s="74"/>
+    </row>
+    <row r="161" s="14" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A161" s="73">
+        <v>10340011</v>
+      </c>
+      <c r="B161" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C161" s="73" t="s">
+        <v>298</v>
+      </c>
+      <c r="D161" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="E161" s="73" t="s">
+        <v>295</v>
+      </c>
+      <c r="F161" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G161" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="H161" s="73"/>
+      <c r="I161" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K161" s="74"/>
+    </row>
+    <row r="162" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A162" s="73">
+        <v>10340021</v>
+      </c>
+      <c r="B162" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C162" s="73" t="s">
+        <v>293</v>
+      </c>
+      <c r="D162" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="E162" s="73" t="s">
+        <v>295</v>
+      </c>
+      <c r="F162" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G162" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="H162" s="73" t="s">
+        <v>297</v>
+      </c>
+      <c r="I162" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K162" s="75"/>
+    </row>
+    <row r="163" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A163" s="73">
+        <v>10340002</v>
+      </c>
+      <c r="B163" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C163" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="D163" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="E163" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="F163" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G163" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="H163" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="I163" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="K163" s="75"/>
+    </row>
+    <row r="164" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A164" s="73">
+        <v>10340012</v>
+      </c>
+      <c r="B164" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C164" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="D164" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="E164" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="F164" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G164" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="H164" s="73"/>
+      <c r="I164" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K164" s="75"/>
+    </row>
+    <row r="165" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A165" s="73">
+        <v>10340022</v>
+      </c>
+      <c r="B165" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C165" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="D165" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="E165" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="F165" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G165" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="H165" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="I165" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K165" s="75"/>
+    </row>
+    <row r="166" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A166" s="73">
+        <v>10340003</v>
+      </c>
+      <c r="B166" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C166" s="73" t="s">
+        <v>308</v>
+      </c>
+      <c r="D166" s="73" t="s">
+        <v>309</v>
+      </c>
+      <c r="E166" s="73" t="s">
+        <v>310</v>
+      </c>
+      <c r="F166" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G166" s="73" t="s">
+        <v>311</v>
+      </c>
+      <c r="H166" s="73" t="s">
+        <v>312</v>
+      </c>
+      <c r="I166" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="K166" s="75"/>
+    </row>
+    <row r="167" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A167" s="73">
+        <v>10340013</v>
+      </c>
+      <c r="B167" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C167" s="73" t="s">
+        <v>313</v>
+      </c>
+      <c r="D167" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="E167" s="73" t="s">
+        <v>310</v>
+      </c>
+      <c r="F167" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G167" s="73" t="s">
+        <v>311</v>
+      </c>
+      <c r="H167" s="73"/>
+      <c r="I167" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K167" s="75"/>
+    </row>
+    <row r="168" s="15" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A168" s="73">
+        <v>10340023</v>
+      </c>
+      <c r="B168" s="73">
+        <v>103400</v>
+      </c>
+      <c r="C168" s="73" t="s">
+        <v>308</v>
+      </c>
+      <c r="D168" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="E168" s="73" t="s">
+        <v>310</v>
+      </c>
+      <c r="F168" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G168" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="H168" s="73" t="s">
+        <v>312</v>
+      </c>
+      <c r="I168" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="K168" s="75"/>
+